--- a/output/data-ai-jobs.xlsx
+++ b/output/data-ai-jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N162"/>
+  <dimension ref="A1:N164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -522,12 +522,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Buyer Analyst</t>
+          <t>Scientific Quality Analyst</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Harrodsburg, Kentucky, 40330, USA</t>
+          <t>Dayton, Ohio, 45390, USA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,12 +537,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006282893/Buyer-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006308834/Scientific-Quality-Analyst</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -565,54 +565,54 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>d0576d5b86c709b987a3</t>
+          <t>f8084ffe768e890b6ed2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Job Title: Buyer Analyst / Procurement Tariff Specialist Job Description The Buyer Analyst / Procurement Tariff Specialist supports procurement and supplier teams by collecting, reviewing, validating, and documenting tariff-related information to drive customer recovery initiatives. This role serves as a key liaison between buyers, suppliers, and internal stakeholders, ensuring that tariff documentation is accurate, complete, and prepared for internal review and approval. The position offers a strong opportunity to gain experience in the automotive sector and contribute to the organization’s goal of becoming a leader in automotive electrical components. Responsibilities Collaborate closely with buyers and suppliers to understand internal and external tariff processes, including ongoing regulatory and business changes. Support the collection and validation of tariff-related documentation required for internal approvals and customer recovery initiatives. Independently review and evaluate supplier responses and supporting evidence to ensure they meet requirements for reporting to the internal Tariff Review Board. Ensure all tariff-related documentation is complete, accurate, properly organized, and ready for internal review and approval workflows. Perform data analysis and detailed document reviews to identify missing information, inconsistencies, and opportunities for process and documentation improvement. Maintain accurate records and detailed notes related to tariff submissions, approvals, and supporting documentation. Provide clear, accurate reporting and updates to team members, buyers, suppliers, and cross-functional stakeholders in a technology-enabled work environment. Communicate effectively in both verbal and written formats to align stakeholders and clarify requirements. Prioritize workload and manage multiple tasks while meeting deadlines and maintaining a high level of accuracy and attention to detail. Work with procurement, purchasing, and supply chain teams to support broader purchasing strategies and cost recovery activities. Leverage Microsoft Excel, including formulas and pivot tables, to analyze data, track information, and prepare reports. Contribute to continuous improvement of tariff documentation processes and approval workflows. Essential Skills Associates degree in a relevant field. Strong proficiency in Microsoft Excel, including knowledge of formulas, tables, and pivot tables. Experience in procurement, purchasing, supply chain, planning, logistics, or related business functions. Ability to perform data analysis and review documentation with a high level of accuracy and attention to detail. Strong verbal and written communication skills, including the ability to provide accurate and clear reporting. Self-motivated and able to work effectively with minimal direction or supervision. Ability to collaborate with buyers, suppliers, and cross-functional stakeholders in a technology-enabled environment. Understanding of basic pur</t>
+          <t>We are actively hiring for Quality Analysts to support a regenerative medicine laboratory here in the north Dayton, OH area. This role will primarily involve reviewing documentation to support the lab, coordinating and tracking Corrective and Preventative Actions (CAPAs), and other desk related duties. This role will not be in the lab, and will be more of a desk based role. Ideal candidates will have a Bachelors Degree in a scientific field and at minimum 6 months-1+ year of experience working in a highly regulated environment (food manufacturing, pharmaceutical, cosmetic, etc.). Job Description The Quality Analyst I performs quality control inspection and disposition of materials and products according to established specifications and regulatory requirements. This role conducts inspections using appropriate measuring instruments and methods, manages non-conforming materials and products within the established Quality System, and ensures adherence to applicable FDA, OSHA, and ISO regulations and standards. The position involves working under limited supervision, supporting lot release activities, and contributing to continuous improvement of quality processes in a rapidly growing, state-of-the-art facility. Responsibilities Perform reviews of batch production records and manufacturing records as part of lot release activities. Coordinate and track Corrective and Preventive Action (CAPA), Non-Conforming Report (NCR), and Deviation records, ensuring all tasks are completed on time. Coordinate and track the site environmental monitoring (EM) testing program. Assist teams in coordinating problem solving and root cause analysis for quality events. Ensure the development, review, and release of quarterly environmental monitoring trending reports and promptly escalate significant trends to management. Provide input based on knowledge and experience with batch release requirements. Provide Quality Management System (QMS) operations support to all current Good Manufacturing Practice (CGMP) departments. Perform Quality Control activities at processing or distribution sites, including incoming material inspections, in-process inspections, and finished product inspections. Inspect a range of products including medical devices, sterile processed human tissue-based products, unprocessed human tissue, component supplies, and labeling materials. Maintain accurate and complete records of Quality Control activities in accordance with Good Documentation Practices (GDP). Provide support related to gowning qualification and training. Ensure timely issuance, review, and approval of microbiology and environmental monitoring testing results. Interface with colleagues to ensure effective corrective and preventive actions are implemented for recurring product or process discrepancies. Assist in the review and approval of equipment qualifications. Assist in the review of calibration and preventive maintenance activities. Assist in hosting onsite regulatory audits and insp</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GIS Analyst</t>
+          <t>Senior Business Analyst | Digital Transformation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, Missouri, 63101, USA</t>
+          <t>Budapest,BU-Soroksari ut44, Budapest, Hungary</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>["OTHER"]</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-005238782/GIS-Analyst</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00070166152/senior-business-analyst-digital-transformation</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -635,39 +635,39 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2bb0d66e462a56093e20</t>
+          <t>5ea03dd36753c51922c0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Job Title: GIS Analyst Job Description The GIS Analyst will support Operation Services, an internal department that aids construction projects. The role involves completing engineering designs and cost estimates using GIS for various main and service works, collecting construction activity 'as-built' data with mobile CPS devices in the field, creating permanent asset records, and editing map features and correlating attribute data in GIS. The analyst will also perform final quality checks on GIS versioned data before posting, represent Engineering at project meetings, and conduct field visits to job sites to determine requirements for service and main work. Responsibilities Complete engineering designs and cost estimates using GIS for all types of main and service work. Collect construction activity 'as-built' using mobile CPS devices in the field for creating permanent asset records. Edit map features and correlating attribute data in the GIS. Perform final quality checks on GIS versioned data before it is posted to the GIS. Represent Engineering at internal and external project meetings as required. Visit job sites to determine requirements for service and main work. Perform preliminary reviews of development plans and interface with customers. Implement and train Engineering staff on new work processes for the GIS mapping system. Distribute and update maps for other departments as requested. Approve requests for the acquisition and release of easements and vacation of rights-of-way. Perform pipeline safety compliance-related GIS analysis as directed. Execute all other duties as assigned. Essential Skills Proficiency in ArcGIS and CAD. Knowledge of geography and construction drawings. Experience with as-built drawings, cost forecasting, and drafting. Additional Skills &amp; Qualifications Ability to complete engineering designs and cost estimates using GIS. Experience in collecting construction activity 'as-built' data using mobile CPS devices. Skill in editing map features and correlating attribute data in GIS. Work Environment The role is based in a professional engineering office, initially requiring attendance five days per week, reducing to three days per week after training. Work may be performed in both office and field settings, with exposure to the elements. Typical hours are 7:00 a.m. to 3:45 p.m., Monday through Friday, with potential for overtime and travel. Pay and Benefits The pay range for this position is $25.00 - $27.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependent</t>
+          <t>Senior Business Analyst | Digital Transformation Work location: Budapest, Hungary Work model: Hybrid Are you an experienced Business Analyst ready to take ownership beyond requirements gathering and help shape large-scale digital transformation initiatives? Join Cognizant's Intuitive Operations &amp; Automation business , where you will partner with clients across multiple industries and play a key role in assessing, designing and delivering process improvement and digital business transformation programs. What you'll do Partner with client business teams and process owners to shape digital transformation initiatives and develop appropriate solutions Own delivery beyond requirements gathering, discovery and analysis Structure, document and prioritize work to maintain a clear and actionable backlog Set priorities and make evidence-based trade-offs Manage delivery expectations across stakeholders and cross-functional teams Bridge the gap between business and technology Work closely with delivery teams throughout the SDLC Establish and embed reusable best practices Identify improvement opportunities and drive progress within agreed objectives and guardrails What we're looking for 8+ years of experience in business analysis and strategy development Strong solution-design capabilities Experience owning delivery across the SDLC and process improvement initiatives Strong understanding of technical frameworks and the ability to communicate effectively with developers Hands-on business analysis and process improvement experience Proven ability to build trusted client relationships and manage expectations Understanding of how AI and automation tools can improve day-to-day work Experience coordinating projects across multiple geographical regions Experience working in an Agile delivery environment Strong risk-management judgement Excellent Hungarian and English communication skills Nice to have Relevant project management certification Hands-on experience developing automation solutions or AI agents Aviation industry experience Ready to combine business analysis, technology and transformation? Apply and help turn complex business requirements into tangible digital outcomes. CogHU103 CogEU101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microbiology Lab Analyst</t>
+          <t>LIMS Master Data Analyst</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>De Pere, Wisconsin, 54115, USA</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006294891/Microbiology-Lab-Analyst</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/lims-master-data-analyst/411881</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -705,39 +705,39 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>f7a88bc11195d17c44cf</t>
+          <t>3a1e1eac41129fd05aee</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Microbiology Lab Analyst Job Description The Microbiology Lab Analyst serves as a Laboratory Technician responsible for performing analytical and microbiological testing on food products, ingredients, and environmental samples to support quality and safety programs. You will apply approved microbiological techniques and methodologies to ensure accurate, reliable results and help maintain compliance with regulatory and customer requirements. Working primarily on second shift, you will prepare and analyze samples, maintain a clean and organized laboratory, monitor and care for equipment, and assist with inventory and quality-related duties. Responsibilities Perform analytical and microbiological testing of food products, ingredients, and environmental samples in accordance with approved methods and protocols. Apply approved microbiological techniques and methodologies to evaluate indicator organisms, pathogens, and relevant chemistries. Prepare and analyze samples for indicator organisms, pathogens, and chemical parameters, ensuring accuracy and proper documentation. Notify laboratory management promptly of any deviations, out-of-specification results, or unusual findings in test results. Maintain appropriate inventory levels of reagents, media, consumables, and supplies required for testing activities. Provide routine preventive maintenance, basic troubleshooting, and thorough cleaning of laboratory equipment to ensure reliable operation. Support quality-related duties, including performing temperature checks, monitoring controls, and verifying proper storage conditions. Adhere to company policies, procedures, and customer requirements while following relevant regulatory and industry guidelines. Maintain a clean, organized, and safe laboratory environment using proper aseptic techniques and good laboratory practices. Stay current with scientific literature, emerging technologies, and industry trends related to food microbiology and analytical testing. Accurately record, interpret, and report test results in accordance with laboratory documentation standards. Collaborate with colleagues and other departments to support continuous improvement in laboratory processes and quality systems. Essential Skills Bachelor's degree in biology, chemistry, or a closely related science field. At least 2 years of experience in a commercial food-testing or analytical laboratory. Hands-on experience with microbiological testing of food products, ingredients, or environmental samples. Proficiency in aseptic sampling techniques and routine laboratory procedures. Knowledge of laboratory equipment operation, care, and basic troubleshooting. Familiarity with Good Laboratory Practices (GLP). Working knowledge of OSHA safety requirements in a laboratory environment. Experience with FDA, BAM, APHA, ISO, or USP methods relevant to microbiology or analytical testing. Ability to follow detailed protocols and standard operating procedures accurately. Strong attention to detail</t>
+          <t>LIMS Master Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) LIMS Master Data Analyst Reference Number: 411881 Published Date: 09/29/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the pharmaceutical and life sciences industry, is seeking a USA-Process &amp; Master Data Governance Manager I (Professional) to join their team. As a USA-Process &amp; Master Data Governance Manager I (Professional), you will be part of the Quality Operations department supporting data integrity and master data management initiatives. The ideal candidate will demonstrate strong analytical skills, effective communication, and a collaborative mindset, which will align successfully within the organization. Job Title: USA-Process &amp; Master Data Governance Manager I (Professional) Location: Swiftwater, PA Pay Range: $70.19 What's the Job? Support the maintenance and improvement of the Laboratory Information Management System (LIMS) to ensure data accuracy and compliance. Assist in updating master data for products, sample plans, and item codes to support data remediation and SPC projects. Ensure the LIMS system complies with all relevant regulatory standards, including cGMPs and 21CFR Part 11. Contribute to the creation and updating of training materials related to system changes and data management processes. Collaborate with cross-functional teams to support system validation, data migration, and SOP revisions. What's Needed? 1-3 years of hands-on experience with LabWare LIMS administration and basic system management. Strong knowledge of laboratory processes, cGMPs, and regulatory requirements in a pharmaceutical environment. Experience with master data management, system vali</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QA Analyst (1st Or 2nd Shift)</t>
+          <t>Logistics Analyst</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, Minnesota, 55343, USA</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006304138/QA-Analyst-1st-Or-2nd-Shift</t>
+          <t>https://www.manpower.com/en/job/business-operations/logistics-analyst-/5880519</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -775,34 +775,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>f36b2b677c56ba716997</t>
+          <t>55a327dd3e52a4c3c560</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Job Title: QA Analyst (1st or 2nd Shift) Job Description The QA Analyst plays a key role in ensuring product quality and regulatory compliance by auditing the facility and production lines, evaluating raw materials, bulk, and finished products, and driving continuous improvement efforts. This position is highly visible on the manufacturing floor and supports a world-class manufacturing control program through careful documentation review, training, and proactive quality oversight. Key Responsibilities Review batch records and manufacturing documentation to ensure GMP/GDP compliance. Support manufacturing operations through floor presence, audits, inspections, and quality oversight. Investigate deviations, non-conformances, and OOS events; perform root cause analysis and support CAPA activities. Train and mentor production personnel on quality systems, SOPs, and regulatory requirements. Approve production activities and product releases while ensuring specifications are met. Maintain and update SOPs, work instructions, controlled forms, and quality documentation. Identify recurring quality issues, implement corrective actions, and drive continuous improvement initiatives. Partner with production and warehouse teams to promote a strong quality culture and maintain compliance. Support lean manufacturing initiatives, including 5S and waste reduction efforts. Required Qualifications Bachelor's degree in Biology, Chemistry, or a related scientific discipline. 1+ year of experience in a GMP-regulated manufacturing environment (pharmaceutical, medical device, food, cosmetic, etc.). Experience reviewing batch records, manufacturing documentation, or production records. Working knowledge of GMP, GDP, FDA regulations, and quality systems. Experience with investigations, deviations, non-conformances, OOS events, and CAPA processes. Strong attention to detail and ability to identify documentation and product quality issues. Strong communication skills and ability to work cross-functionally in a manufacturing environment. Ability to work independently, prioritize multiple tasks, and maintain a sense of urgency. Preferred Qualifications Experience in pharmaceutical, OTC, medical device, cosmetic, or food manufacturing. Familiarity with cGMP, 21 CFR, and FDA-regulated environments. Experience supporting internal or external audits. Knowledge of lean manufacturing principles, including 5S. Experience working directly on a manufacturing floor in a QA capacity. Work Environment This is an on-site role in a diverse manufacturing facility with exposure to a wide range of products, including beauty, bath and body, lip balms, skincare, sunscreens, and cleaning detergents. The position offers flexibility to work either 1st shift (6:00 AM – 2:30 PM) or 2nd shift (2:00 PM – 10:00 PM), Monday through Friday, with a shift differential available for 2nd shift. Training typically occurs on 1st shift over a four-week period. The QA Analyst spends approximately 80–90% of the wo</t>
+          <t>Logistics Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Logistics Analyst Reference Number: 5880519 Published Date: 09/29/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE As a Logistics Analyst, you will support the Logistics and Transportation departments by enhancing data visibility, automating reporting processes, and developing analytical tools that facilitate faster and more informed business decisions. The ideal candidate will demonstrate strong analytical skills, a proactive approach, and excellent communication abilities, aligning well with the organization’s commitment to operational excellence and continuous improvement. Job Title: Logistics Analyst Location: Valencia, CA Pay Range: $28 - $30/hr. Shift: 40 hours a week What's the Job? Support Logistics and Transportation teams by improving data visibility and developing analytical tools. Automate recurring logistics reports to streamline data collection and reduce manual effort. Analyze transportation and logistics data to identify trends, risks, and cost-saving opportunities. Create and maintain Power BI dashboards and reports supporting operational metrics. Collaborate with cross-functional teams to translate operational needs into technical solutions and automation workflows. What's Needed? Bachelor’s degree in supply chain, Business Analytics, Data Analytics, or related field. 2–5 years of experience developing reports and dashboards using Power BI. Strong proficiency in Microsoft Excel, including data analysis, PivotTables, and advanced formulas. Experience working with ERP systems such as JD Edwards (JDE), SAP, or similar platforms. Excellent analytical, problem-solving, and communication skills with the ability to work with la</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>MeeBoss</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QA Analyst (1st Or 2nd Shift) job in Eden Prairie, Minnesota, USA | Actalent Careers</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -812,12 +812,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["contract"]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -827,12 +832,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006315478/QA-Analyst-1st-Or-2nd-Shift</t>
+          <t>https://meeboss.com/job/f88646c467fe4ffd33x50g~~</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -840,34 +845,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4051359ff1395ed1e99f</t>
+          <t>72200d5c2293618ecc96</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>QA Analyst (1st Or 2nd Shift) job in Eden Prairie, Minnesota, USA | Laboratory &amp; Sciences jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices 726a6eb49b01499898c7d01cfc5da1b8</t>
+          <t>ML Engineer – 4-5 Years Experience Title: Machine Learning Engineer Experience: 4-5 Years Location: Remote Employment: Full-Time Job Description We are looking for a Machine Learning Engineer with 3–4 years of experience to develop, deploy, and maintain machine learning solutions. The ideal candidate should have strong Python, ML, data processing, and cloud experience. Key Responsibilities Build, train, evaluate, and optimize ML models. Develop ML pipelines using Python and relevant frameworks. Work with structured and unstructured datasets. Perform feature engineering and model validation. Deploy models using cloud and container technologies. Monitor model performance and improve production models. Collaborate with data scientists, engineers, and business teams. Required Skills 3–4 years of ML/AI engineering experience. Strong Python programming. Experience with Scikit-learn, TensorFlow or PyTorch . Machine learning algorithms and statistics. SQL and data processing. Experience with AWS/Azure/GCP . REST APIs, Docker, and Git. ML deployment/MLOps experience. Strong problem-solving and communication skills. Preferred NLP/LLMs or Generative AI experience. MLflow, Kubeflow, Airflow or similar tools. Kubernetes experience. CI/CD and production ML pipelines.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pyramid Consulting</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Temporary Finance Analyst, Store Planning</t>
+          <t>225 results for data engineer jobs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -892,12 +897,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://www.pyramidcg.com/job-details/temporary-finance-analyst-store-planning-in-operations-jobs-1669426</t>
+          <t>https://www.roberthalf.com/us/en/jobs/all/data-engineer</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -905,34 +910,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0d4acc12e5d1bf3a0a35</t>
+          <t>c758d78b7b7b5d41e11a</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>{"css":"*#dm *.dmBody nav.u_1049841281{\ncolor:black !important}\n.u_1948361810{\n}\n.u_1828143305{\n}\n.u_1134588705{\n}\n*#dm *.dmBody div.u_1948361810{\nbackground-color:rgba(0,0,0,0) !important}\n*#dm *.dmBody div.u_1915430311 .similarJobsTitle{\nfont-weight:normal !important;\nfont-family:Dosis !important}\n*#dm *.dmBody div.u_1337134807 .linkApplyBtnText{\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1662312594 .linkApplyBtnText{\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-printJob .printJob{\ncolor:rgba(0,0,0,1) !important;\nfont-family:franklingothicurw !important}\n*#dm *.dmBody *.u_1955642683 div.shmJobAlert-Button{\ntext-align:LEFT !important}\n*#dm *.dmBody div.u_1045457657{\nbackground-color:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1662312594 .shLinkApplyBtn{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-title{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-saveJob div{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-printJob span{\nfont-family:Karla-VariableFont_wght !important;\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-emailJob a{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1955642683 input.shmJobAlert-Input{\ncolor:rgba(31,56,73,1) !important;\nbackground-color:rgba(0,0,0,0) !important;\nborder-style:solid !important;\nborder-width:1px !important;\nborder-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button span.text{\nfont-weight:bold !important;\ncolor:rgba(255,255,255,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button:hover span.text{\ncolor:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button.hover span.text{\ncolor:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1915430311 .similarJobsTitle h3{\nfont-family:Karla-VariableFont_wght !important;\ncolor:rgba(31,56,73,1) !important;\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1915430311 .sjJobName{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1915430311 .sjplaceTxt{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1915430311 .sjWorkTypeText{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1337134807 .shLinkApplyBtn{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody section.u_1897767439{\nbackground-image:url(https://irp.cdn-website.com/adb40814/dms3rep/multi/opt/Watercolor-Background-4-01-2880w.png) !important;\nbackground-color:rgb(238,238,238) !important;\nbackground-repeat:no-repeat !important;\nbackground-size:cover !important}\n*#dm *.dmBody div.u_1523290715 .wrapper{\ncolor:rgba(31,56,73,1) !i</t>
+          <t>225 Results for Data Engineer Jobs Search jobs now Find the right job type for you Create a job alert Explore how we help job seekers Contract talent Full-Time talent Learn how we work with you Executive search Finance and Accounting Technology Marketing and Creative Legal Administrative and Customer Support Technology Risk, Audit and Compliance Finance and Accounting Digital, Marketing and Customer Experience Legal Operations Human Resources 2026 Salary Guide Demand for Skilled Talent Report Job Market Outlook Press Room Tech insights Labor market overview AI in recruiting Navigating the AI era Staffing for small businesses Cost of a bad hire Browse jobs Find your next hire Our locations Add your latest resume to match with open positions. 225 results for data engineer jobs Data Engineer Boston, Massachusetts remote Temporary / Contract 55.4135 - 64.163 USD / Hourly We are looking for a skilled Data Engineer to join a 100% remote contract to hire position. This role focuses on developing and maintaining data warehouse integration processes, working closely with technical teams and business stakeholders to deliver reliable, high-quality data solutions. The ideal candidate brings deep experience in data transformation, warehouse architecture, and production support, along with a proactive approach to investigating and resolving complex data issues. Responsibilities: • Build, enhance, and maintain data loading and transformation workflows that feed enterprise data warehouse environments and related systems. • Create scalable warehouse integration solutions while producing clear technical documentation and following established engineering standards. • Contribute to data modeling efforts and collaborate with cross-functional teams on reporting structures and warehouse design decisions. • Partner with business stakeholders to understand operational needs and translate them into effective technical approaches and implementation plans. • Review solution quality through testing, validation, and design assessments to ensure dependable performance and efficient processing. • Monitor production data warehouse operations, investigate pipeline failures or data discrepancies, and resolve issues with urgency to reduce business disruption. • Work closely with development, quality assurance, and support teams to help deliver solutions on schedule across the full development lifecycle. • Raise risks, communicate technical concerns, and provide input on specifications to improve solution accuracy and delivery outcomes. 2026-09-25T00:00:00Z Data Engineer Remote, Ohio remote Temporary / Contract 0 - 0 USD / Yearly We are looking for a Data Engineer to support data-focused initiatives with a strong emphasis on controls, process clarity, and technical documentation. This is a Long-term Contract position expected to begin as a 3-4 month engagement at 40 hours per week, with remote work flexibility. The ideal candidate will help strengthen data workflows, improve reliab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>224 results for Data Engineer jobs</t>
+          <t>Senior Data Engineer - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -957,12 +962,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://www.roberthalf.com/us/en/jobs/all/data-engineer</t>
+          <t>https://www.judge.com/jobs/details/1153883</t>
         </is>
       </c>
       <c r="J8" t="b">
@@ -970,54 +975,49 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>915914fbf95151b2b6ec</t>
+          <t>0c5130fecdf6f6ac36c4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>224 Results for Data Engineer Jobs Search jobs now Find the right job type for you Create a job alert Explore how we help job seekers Contract talent Full-Time talent Learn how we work with you Executive search Finance and Accounting Technology Marketing and Creative Legal Administrative and Customer Support Technology Risk, Audit and Compliance Finance and Accounting Digital, Marketing and Customer Experience Legal Operations Human Resources 2026 Salary Guide Demand for Skilled Talent Report Job Market Outlook Press Room Tech insights Labor market overview AI in recruiting Navigating the AI era Staffing for small businesses Cost of a bad hire Browse jobs Find your next hire Our locations Add your latest resume to match with open positions. 224 results for Data Engineer jobs Data Engineer Boston, Massachusetts remote Temporary / Contract 55.4135 - 64.163 USD / Hourly We are looking for a skilled Data Engineer to join a 100% remote contract to hire position. This role focuses on developing and maintaining data warehouse integration processes, working closely with technical teams and business stakeholders to deliver reliable, high-quality data solutions. The ideal candidate brings deep experience in data transformation, warehouse architecture, and production support, along with a proactive approach to investigating and resolving complex data issues. Responsibilities: • Build, enhance, and maintain data loading and transformation workflows that feed enterprise data warehouse environments and related systems. • Create scalable warehouse integration solutions while producing clear technical documentation and following established engineering standards. • Contribute to data modeling efforts and collaborate with cross-functional teams on reporting structures and warehouse design decisions. • Partner with business stakeholders to understand operational needs and translate them into effective technical approaches and implementation plans. • Review solution quality through testing, validation, and design assessments to ensure dependable performance and efficient processing. • Monitor production data warehouse operations, investigate pipeline failures or data discrepancies, and resolve issues with urgency to reduce business disruption. • Work closely with development, quality assurance, and support teams to help deliver solutions on schedule across the full development lifecycle. • Raise risks, communicate technical concerns, and provide input on specifications to improve solution accuracy and delivery outcomes. 2026-09-25T00:00:00Z Data Engineer Madison, Wisconsin remote Permanent / Full Time 100000 - 140000 USD / Yearly We're partnering with a team that is expanding its cloud data capabilities and looking for a Data Engineer to help build the foundation that powers analytics, reporting, and data-driven decision making. This role offers the opportunity to work with large, complex datasets while helping improve how data is collected, organized, and delivere</t>
+          <t>Senior Data Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SQL Server Database Analyst Data Migration Reporting</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Database-Analyst-Remote-Rose-International-Job-508274.html</t>
+          <t>https://careers.wipro.com/job/Analyst/195409-en_US</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1040,39 +1040,39 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>108ddbbecdd818d1fd31</t>
+          <t>2864063fe92279d4c7e0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Education: â¢ Associate's DegreeExperience and Skills Required-â¢ Three or more years of professional experience with SQL and relational database systems.â¢ Strong proficiency in Microsoft SQL Server and T-SQL, including complex joins, stored procedures, views, and data manipulation scripts.â¢ Experience with large datasets, data extraction, transformation, validation, and reconciliation.â¢ Understanding of relational database design, indexing, and query optimization.â¢ Ability to interpret technical documentation, translate business requirements into SQL solutions, and communicate findings clearly.â¢ Ability to work independently, manage competing priorities, and collaborate with technical and nontechnical stakeholders.Experience and Skills Preferred-â¢ Experience with enterprise case management systems or large transactional applications.â¢ Data migration or legacy system modernization experience.â¢ Experience with SQL Server Integration Services (SSIS), Power BI, data warehousing, or reporting solutions.â¢ Experience troubleshooting application integrations and data interfaces and working with software vendors.â¢ Familiarity with judicial, criminal justice, or government information systems and handling sensitive data.â¢ Knowledge of data governance, data quality, and database security best practices.Ideal Candidateâ¢ A hands-on SQL professional who can independently investigate complex data issues, write and troubleshoot queries, communicate findings clearly, and collaborate across teams to support data accuracy, system reliability, and modernization initiatives.Position OverviewThe CLIENT is seeking an experienced SQL Database Analyst to provide technical support for statewide judicial applications, database systems, data integrations, and reporting initiatives. The analyst will work with application, data warehouse, and technical teams to analyze, extract, validate, and troubleshoot data across multiple systems. This position will also support system modernization, including data migration, integration testing, and reporting associated with the statewide case management system.Key ResponsibilitiesSQL Development and Data Analysisâ¢ Develop, maintain, and optimize complex SQL queries, stored procedures, views, and scripts.â¢ Analyze relational database structures and relationships among tables and data elements.â¢ Extract, transform, and validate data; troubleshoot discrepancies and database-related application issues.â¢ Assist with database documentation, data mapping, and technical specifications.Data Migration and System Integrationâ¢ Support data conversion and migration between legacy and modernized case management systems.â¢ Develop SQL scripts to identify, correct, and validate data discrepancies before and after migration.â¢ Reconcile converted data for accuracy and completeness; investigate data exchanged through external interfaces.â¢ Coordinate with application analysts, vendors, and technical teams to resolv</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 9/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: ͏ Shift:</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Senior Product Data Scientist - Customer Growth &amp; Retention (Contract)</t>
+          <t>GIS Analyst</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, 92129, USA</t>
+          <t>St. Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
+          <t>["OTHER"]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1102,11 +1102,11 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Data-Scientist-CA-San-Diego-Rose-International-Job-508285.html</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-005238782/GIS-Analyst</t>
         </is>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25b2b9cb37a81bcbece6</t>
+          <t>2bb0d66e462a56093e20</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Required Education:Bachelor's degree in Engineering, Data Science, Statistics, Mathematics, Computer Science, Economics, or a related quantitative fieldPreferred Education:Master'sRequired Skills:â¢ 4+ years of experience in product analytics, marketing analytics, or applied data science â ideally with exposure to customer experience measurement, growth analytics, or expert/agent-assisted service modelsâ¢ Advanced proficiency in SQL and "big data" technologies (eg, Databricks, Spark, Redshift, BigQuery); comfort with a BI tool (Tableau, Qlik, Dash) â¢ Solid grounding in experimentation design (A/B/n) and causal inference methods (propensity score matching, diff-in-diff, synthetic control) â including comfort applying these when clean experiments aren't feasible â¢ Strong business acumen and strategic thinking â able to translate a fuzzy business question into a testable hypothesis and measurement plan â¢ Strong data storytelling skills â able to rapidly build clear visualizations and communicate insights to non-technical stakeholders â¢ Excellent communication skills, with the ability to work independently against a defined scope typical of a contract engagementJob Summary:â¢ We are seeking a highly motivated Contractor Data Scientist to join our Customer Success Data Science team, focused on Smart Expert Growth and Retentionâ¢ In this role, you'll be the analytical backbone for understanding how our consumer and expert experiences work together to drive the best possible outcomes for customers â from identifying opportunity, to measuring impact, to uncovering new ways to create valueâ¢ You'll partner closely with expert operations, product, and marketing to turn data into decisions, and to prove out where combining human expertise with great customer experience delivers the best resultsâ¢ If you're passionate about using hard data to uncover creative, high-impact solutions at the intersection of customer experience and expert-driven growth, we'd love to hear from you!**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
+          <t>Job Title: GIS Analyst Job Description The GIS Analyst will support Operation Services, an internal department that aids construction projects. The role involves completing engineering designs and cost estimates using GIS for various main and service works, collecting construction activity 'as-built' data with mobile CPS devices in the field, creating permanent asset records, and editing map features and correlating attribute data in GIS. The analyst will also perform final quality checks on GIS versioned data before posting, represent Engineering at project meetings, and conduct field visits to job sites to determine requirements for service and main work. Responsibilities Complete engineering designs and cost estimates using GIS for all types of main and service work. Collect construction activity 'as-built' using mobile CPS devices in the field for creating permanent asset records. Edit map features and correlating attribute data in the GIS. Perform final quality checks on GIS versioned data before it is posted to the GIS. Represent Engineering at internal and external project meetings as required. Visit job sites to determine requirements for service and main work. Perform preliminary reviews of development plans and interface with customers. Implement and train Engineering staff on new work processes for the GIS mapping system. Distribute and update maps for other departments as requested. Approve requests for the acquisition and release of easements and vacation of rights-of-way. Perform pipeline safety compliance-related GIS analysis as directed. Execute all other duties as assigned. Essential Skills Proficiency in ArcGIS and CAD. Knowledge of geography and construction drawings. Experience with as-built drawings, cost forecasting, and drafting. Additional Skills &amp; Qualifications Ability to complete engineering designs and cost estimates using GIS. Experience in collecting construction activity 'as-built' data using mobile CPS devices. Skill in editing map features and correlating attribute data in GIS. Work Environment The role is based in a professional engineering office, initially requiring attendance five days per week, reducing to three days per week after training. Work may be performed in both office and field settings, with exposure to the elements. Typical hours are 7:00 a.m. to 3:45 p.m., Monday through Friday, with potential for overtime and travel. Pay and Benefits The pay range for this position is $25.00 - $27.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Inventory Analyst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Des Moines, Iowa, 50301, USA</t>
+          <t>Ponca City, Oklahoma, 74601, USA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1172,52 +1172,52 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006259257/Business-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006302292/Inventory-Analyst</t>
         </is>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-28T09:05:51+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>8610e737a7bdc9111012</t>
+          <t>ec610b5ec2ceee97639e</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Description o Strong stakeholder management and ability to work with challenging personalities. o Effective collaboration with cross functional teams and other BAs. o Strong analytical mindset with the ability to investigate issues independently. o Clear communication and consistent status reporting. o Experience working with third party vendors (FAST preferred). o Insurance background and policy administration experience preferred but not required. o Familiarity with DTCC (bonus). Skills Business analysis, Scrum, Agile, Requirement gathering, User stories Top Skills Details Business analysis,Scrum Additional Skills &amp; Qualifications Insurance experience and Policy Admin systems experience is a huge plus. Experience Level Expert Level Job Type &amp; Location This is a Contract position based out of Des Moines, IA. Pay and Benefits The pay range for this position is $55.00 - $55.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a hybrid position in Des Moines,IA. Application Deadline This position is anticipated to close on Sep 11, 2026. About TEKsystems We're partners in transformation. We help clients activate ideas and solutions to take advantage of a new world of opportunity. We are a team of 80,000 strong, working with over 6,000 clients, including 80% of the Fortune 500, across North America, Europe and Asia. As an industry leader in Full-Stack Technology Services, Talent Services, and real-world application, we work with progressive leaders to drive change. That's the power of true partnership. TEKsystems is an Allegis Group company. The company is an equal opportunity employer and will consider all applications without regards to race, sex, age, color, religion, national origin, veteran status, disability, sexual orientation, gender identity, genetic information or any characteristic protected by law. About TEKsystems and TEKsystems Global Services We’re a leading provider of business and technology services. We accelerate business transformation for our customers. Our expertise in strategy, design, execution and operations unlocks business value t</t>
+          <t>Job Title: Inventory Analyst Job Description We are seeking an experienced Inventory Analyst to support inventory control, materials management, and production operations within a manufacturing environment. This individual will play a critical role in maintaining inventory accuracy, supporting production schedules, investigating inventory discrepancies, and ensuring materials are available to meet customer and operational demands. The Inventory Analyst will partner closely with Production, Engineering, Materials Management, Supply Chain, and Warehouse teams to optimize material flow, improve inventory processes, and support overall operational efficiency. The ideal candidate will have experience with inventory management systems, cycle counting, ERP systems, and manufacturing operations. Responsibilities Perform daily cycle counts and inventory audits to maintain inventory accuracy. Investigate, analyze, and resolve inventory discrepancies. Monitor inventory levels and material availability to support production schedules. Maintain and update inventory records within ERP/MRP systems. Coordinate with production, warehouse, engineering, and supplier teams regarding material shortages and inventory concerns. Analyze inventory trends and recommend process improvements. Support receiving discrepancy investigations and non-conforming material processes. Assist with quarterly physical inventories and inventory reconciliations. Manage inventory transactions and ensure accurate item master data. Support continuous improvement initiatives related to inventory control and materials management. Essential Skills Bachelor's degree with 1+ year of related experience, Associate degree with 6+ years of experience, or equivalent combination of education and experience. Experience in inventory control, supply chain, materials management, or manufacturing operations. ERP/MRP system experience. Strong Microsoft Office skills, particularly Excel. Excellent organizational, analytical, and problem-solving skills. Strong attention to detail and data accuracy. Ability to manage multiple priorities in a fast-paced manufacturing environment. Strong communication and cross-functional collaboration skills. Additional Skills &amp; Qualifications SAP experience. Forklift certification or material handling experience. Shipping and receiving experience. Experience using RF scanners and barcode systems. APICS/CPIM certification. Knowledge of inventory optimization and continuous improvement methodologies. Experience supporting manufacturing and production environments. Work Environment This is a full-time, onsite role within a manufacturing environment. The position involves a fast-paced production setting supporting multiple departments, with frequent interaction with suppliers, production personnel, warehouse teams, and engineering groups. The work involves a combination of office-based analytical tasks and hands-on inventory audits within the production facility. Occasional overtim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr.</t>
+          <t>Microbiology Lab Analyst</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Des Moines, Iowa, 50301, USA</t>
+          <t>De Pere, Wisconsin, 54115, USA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1242,11 +1242,11 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006299146/Data-Engineer-Sr</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006294891/Microbiology-Lab-Analyst</t>
         </is>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1255,39 +1255,39 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>a40a64aac61d42f711cb</t>
+          <t>f7a88bc11195d17c44cf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>***MUST BE LOCAL TO DES MOINES, IA OR WILLING TO GO ONSITE IN DES MOINES, IOWA*** Description Data Engineer to join a product-focused engineering team responsible for delivering high-quality data solutions that drive business insights. This role will serve as a key contributor on a cross-functional Agile team and will help design, build, and maintain scalable data pipelines and data products that support enterprise analytics and decision-making. The ideal candidate is a proactive, hands-on engineer who can quickly adapt to a fast-paced environment, collaborate effectively with stakeholders, and contribute immediately to team objectives. Skills Python, Sql, Aws, snowflake, erwin, data modeling Top Skills Details Python,Sql,Aws Additional Skills &amp; Qualifications Team Environment • Join a collaborative team of approximately 4-6 engineers. • Work within a cross-functional Agile product team. • Regular interaction with multiple business and technology teams. • Strong emphasis on teamwork, communication, and problem-solving. Required Qualifications • Strong proficiency in Python development. • Experience working with AWS cloud services. • Strong SQL skills and experience with relational and analytical databases. • Experience using GitHub and modern source control practices. • Experience working within Agile development environments. • Strong communication and collaboration skills. • Ability to quickly learn new technologies and contribute with minimal ramp-up time. Preferred Qualifications • Experience extracting and integrating data through APIs. • Experience working with Snowflake. • Knowledge of data modeling concepts and tools such as Erwin. • Experience designing and implementing enterprise data solutions. • Familiarity with Informatica is helpful but not required. Experience Level Expert Level Job Type &amp; Location This is a Contract position based out of Des Moines, IA. Pay and Benefits The pay range for this position is $60.00 - $73.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully remote position. Application Deadline This position is antici</t>
+          <t>Microbiology Lab Analyst Job Description The Microbiology Lab Analyst serves as a Laboratory Technician responsible for performing analytical and microbiological testing on food products, ingredients, and environmental samples to support quality and safety programs. You will apply approved microbiological techniques and methodologies to ensure accurate, reliable results and help maintain compliance with regulatory and customer requirements. Working primarily on second shift, you will prepare and analyze samples, maintain a clean and organized laboratory, monitor and care for equipment, and assist with inventory and quality-related duties. Responsibilities Perform analytical and microbiological testing of food products, ingredients, and environmental samples in accordance with approved methods and protocols. Apply approved microbiological techniques and methodologies to evaluate indicator organisms, pathogens, and relevant chemistries. Prepare and analyze samples for indicator organisms, pathogens, and chemical parameters, ensuring accuracy and proper documentation. Notify laboratory management promptly of any deviations, out-of-specification results, or unusual findings in test results. Maintain appropriate inventory levels of reagents, media, consumables, and supplies required for testing activities. Provide routine preventive maintenance, basic troubleshooting, and thorough cleaning of laboratory equipment to ensure reliable operation. Support quality-related duties, including performing temperature checks, monitoring controls, and verifying proper storage conditions. Adhere to company policies, procedures, and customer requirements while following relevant regulatory and industry guidelines. Maintain a clean, organized, and safe laboratory environment using proper aseptic techniques and good laboratory practices. Stay current with scientific literature, emerging technologies, and industry trends related to food microbiology and analytical testing. Accurately record, interpret, and report test results in accordance with laboratory documentation standards. Collaborate with colleagues and other departments to support continuous improvement in laboratory processes and quality systems. Essential Skills Bachelor's degree in biology, chemistry, or a closely related science field. At least 2 years of experience in a commercial food-testing or analytical laboratory. Hands-on experience with microbiological testing of food products, ingredients, or environmental samples. Proficiency in aseptic sampling techniques and routine laboratory procedures. Knowledge of laboratory equipment operation, care, and basic troubleshooting. Familiarity with Good Laboratory Practices (GLP). Working knowledge of OSHA safety requirements in a laboratory environment. Experience with FDA, BAM, APHA, ISO, or USP methods relevant to microbiology or analytical testing. Ability to follow detailed protocols and standard operating procedures accurately. Strong attention to detail</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEKsystems</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Service Desk Analyst</t>
+          <t>QA Analyst (1st Or 2nd Shift)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ames, Iowa, 50010, USA</t>
+          <t>Eden Prairie, Minnesota, 55343, USA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1312,11 +1312,11 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006298075/Service-Desk-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006304138/QA-Analyst-1st-Or-2nd-Shift</t>
         </is>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1325,29 +1325,29 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>b36addfa96a59084ec8a</t>
+          <t>f36b2b677c56ba716997</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Description • Respond to and resolve customer requests and inquiries by tracking them in ticket management system • Provide information and instructions to users on various applications and equipment • Provide direct support via email, phone, remote, and in-person appointments • Identify technical needs of customers and find resolutions to address business needs • Install, maintain, and troubleshoot computer equipment and software • Performs routine backup and restores system and data files • Ensure devices are setup in a standard, secure, and consistent manner • Schedule customer installations and appointments • Ensure policies and standards are met and procedures are followed by staff • Maintain/manage ITS and CorePlus customer inventories • Triage incidents and requests, ensuring that students and FTEs are completing them in a timely manner • Attend team, departmental, and campus meetings • Provide guidance to student employees, including scheduling, training, and performance feedback • Document procedures, checklists, and other information required by the team • Provide backup support for purchasing CorePlus and Onsite requested IT equipment Skills Help desk, Technical support, Desktop, Customer service, Troubleshooting, Office 365, imaging Top Skills Details Help desk,Technical support,Desktop,Customer service,Troubleshooting Additional Skills &amp; Qualifications Supporting an enterprise level ticketing system. (Service Now) Job Type &amp; Location This is a Contract position based out of Ames, IA. Pay and Benefits The pay range for this position is $19.00 - $20.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully onsite position in Ames,IA. Application Deadline This position is anticipated to close on Sep 27, 2026. About TEKsystems We're partners in transformation. We help clients activate ideas and solutions to take advantage of a new world of opportunity. We are a team of 80,000 strong, working with over 6,000 clients, including 80% of the Fortune 500, across North America, Europe and Asia. As an industry leader in Full-Stack Technology Service</t>
+          <t>Job Title: QA Analyst (1st or 2nd Shift) Job Description The QA Analyst plays a key role in ensuring product quality and regulatory compliance by auditing the facility and production lines, evaluating raw materials, bulk, and finished products, and driving continuous improvement efforts. This position is highly visible on the manufacturing floor and supports a world-class manufacturing control program through careful documentation review, training, and proactive quality oversight. Key Responsibilities Review batch records and manufacturing documentation to ensure GMP/GDP compliance. Support manufacturing operations through floor presence, audits, inspections, and quality oversight. Investigate deviations, non-conformances, and OOS events; perform root cause analysis and support CAPA activities. Train and mentor production personnel on quality systems, SOPs, and regulatory requirements. Approve production activities and product releases while ensuring specifications are met. Maintain and update SOPs, work instructions, controlled forms, and quality documentation. Identify recurring quality issues, implement corrective actions, and drive continuous improvement initiatives. Partner with production and warehouse teams to promote a strong quality culture and maintain compliance. Support lean manufacturing initiatives, including 5S and waste reduction efforts. Required Qualifications Bachelor's degree in Biology, Chemistry, or a related scientific discipline. 1+ year of experience in a GMP-regulated manufacturing environment (pharmaceutical, medical device, food, cosmetic, etc.). Experience reviewing batch records, manufacturing documentation, or production records. Working knowledge of GMP, GDP, FDA regulations, and quality systems. Experience with investigations, deviations, non-conformances, OOS events, and CAPA processes. Strong attention to detail and ability to identify documentation and product quality issues. Strong communication skills and ability to work cross-functionally in a manufacturing environment. Ability to work independently, prioritize multiple tasks, and maintain a sense of urgency. Preferred Qualifications Experience in pharmaceutical, OTC, medical device, cosmetic, or food manufacturing. Familiarity with cGMP, 21 CFR, and FDA-regulated environments. Experience supporting internal or external audits. Knowledge of lean manufacturing principles, including 5S. Experience working directly on a manufacturing floor in a QA capacity. Work Environment This is an on-site role in a diverse manufacturing facility with exposure to a wide range of products, including beauty, bath and body, lip balms, skincare, sunscreens, and cleaning detergents. The position offers flexibility to work either 1st shift (6:00 AM – 2:30 PM) or 2nd shift (2:00 PM – 10:00 PM), Monday through Friday, with a shift differential available for 2nd shift. Training typically occurs on 1st shift over a four-week period. The QA Analyst spends approximately 80–90% of the wo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Data Analyst - Quincy, MA | Judge Group</t>
+          <t>QA Analyst (1st Or 2nd Shift) job in Eden Prairie, Minnesota, USA | Actalent Careers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1377,11 +1377,11 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1154548</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006315478/QA-Analyst-1st-Or-2nd-Shift</t>
         </is>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1390,29 +1390,29 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>a1a20ebd60e4b3f275ed</t>
+          <t>4051359ff1395ed1e99f</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Data Analyst - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>QA Analyst (1st Or 2nd Shift) job in Eden Prairie, Minnesota, USA | Laboratory &amp; Sciences jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices 7539d1f414fd4d70b3ff67c5bbda6001</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Functional Business Analyst - Irving, TX | Judge Group</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1427,7 +1427,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2017-08-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1437,52 +1442,52 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152177</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/743999658352528-big-data-engineer?oga=true</t>
         </is>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>86259526f0dbe79dda99</t>
+          <t>9bf4a4e2dae5cc85a155</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Functional Business Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi, Hope your are doing great! My name is Shyam and I am a Professional Recruiter at Agile, Inc. I have an open opportunity that you may be a good fit for. I came across your resume and think that you might be a good fit for the position listed below. Title: Big Data Engineer Location: Pittsburgh, PA Mode: Permanent Job Description: We are looking for a Big Data Engineer that will work on the collecting, storing, processing, and analyzing of large sets of data. The primary focus will be on choosing optimal solutions to use for these purposes, then maintaining, implementing, and monitoring them. You will also be responsible for integrating them with the architecture used across the company. Skills and Qualifications • Proficient understanding of distributed computing principles • Management of Hadoop cluster (Cloudera preferred), with all included services • Ability to solve any ongoing issues with operating the cluster • Proficiency with Hadoop v2, MapReduce, HDFS, Sqoop • Experience with building stream-processing systems, using solutions such as Storm or Spark-Streaming • Good knowledge of Big Data querying tools, such as Pig, Hive, and Impala • Experience with Spark • Experience with integration of data from multiple data sources such as MsSQL Server, Oracle, • Good understanding of SQL queries, joins, stored procedures, relational schemas • Experience with NoSQL databases, such as HBase, Cassandra, MongoDB (preferred) • Knowledge of various ETL techniques and frameworks, such as Flume • Experience with various messaging systems, such as Kafka or RabbitMQ • Experience with Cloudera FS domain knowledge a big plus but not required Thanks &amp; Regards "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>Agile Enterprise Solutions</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inventory Analyst</t>
+          <t>Data Analyst R Programming</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ponca City, Oklahoma, 74601, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1492,12 +1497,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>["FULL_TIME"]</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1507,12 +1512,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006302292/Inventory-Analyst</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91738120-data-analyst-r-programming?oga=true</t>
         </is>
       </c>
       <c r="J16" t="b">
@@ -1520,22 +1525,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-28T09:05:51+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ec610b5ec2ceee97639e</t>
+          <t>21e4d98805199fb268c1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Job Title: Inventory Analyst Job Description We are seeking an experienced Inventory Analyst to support inventory control, materials management, and production operations within a manufacturing environment. This individual will play a critical role in maintaining inventory accuracy, supporting production schedules, investigating inventory discrepancies, and ensuring materials are available to meet customer and operational demands. The Inventory Analyst will partner closely with Production, Engineering, Materials Management, Supply Chain, and Warehouse teams to optimize material flow, improve inventory processes, and support overall operational efficiency. The ideal candidate will have experience with inventory management systems, cycle counting, ERP systems, and manufacturing operations. Responsibilities Perform daily cycle counts and inventory audits to maintain inventory accuracy. Investigate, analyze, and resolve inventory discrepancies. Monitor inventory levels and material availability to support production schedules. Maintain and update inventory records within ERP/MRP systems. Coordinate with production, warehouse, engineering, and supplier teams regarding material shortages and inventory concerns. Analyze inventory trends and recommend process improvements. Support receiving discrepancy investigations and non-conforming material processes. Assist with quarterly physical inventories and inventory reconciliations. Manage inventory transactions and ensure accurate item master data. Support continuous improvement initiatives related to inventory control and materials management. Essential Skills Bachelor's degree with 1+ year of related experience, Associate degree with 6+ years of experience, or equivalent combination of education and experience. Experience in inventory control, supply chain, materials management, or manufacturing operations. ERP/MRP system experience. Strong Microsoft Office skills, particularly Excel. Excellent organizational, analytical, and problem-solving skills. Strong attention to detail and data accuracy. Ability to manage multiple priorities in a fast-paced manufacturing environment. Strong communication and cross-functional collaboration skills. Additional Skills &amp; Qualifications SAP experience. Forklift certification or material handling experience. Shipping and receiving experience. Experience using RF scanners and barcode systems. APICS/CPIM certification. Knowledge of inventory optimization and continuous improvement methodologies. Experience supporting manufacturing and production environments. Work Environment This is a full-time, onsite role within a manufacturing environment. The position involves a fast-paced production setting supporting multiple departments, with frequent interaction with suppliers, production personnel, warehouse teams, and engineering groups. The work involves a combination of office-based analytical tasks and hands-on inventory audits within the production facility. Occasional overtim</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 ECMS RQ# 127616 Duration of contract 2 months Years of Experience 6-7 yrs Detailed JD (cannot get relevant profiles with one liner JD, so provide clear JD with roles and responsibilities, it will help vendors in sourcing right candidates) Need 1 profile who has atleast 2 yrs of experience in R programming and who can code well in R.Overall 6 to 7 yrs with data analyst as required. Mandatory skills R Programming, Data analyst skill Work Location Irving(TX) Background check process to be followed: Before onboarding / After onboarding: BGV Agency: Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1552,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Architect ( Hadoop / Spark )</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1567,7 +1572,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2016-01-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1582,7 +1587,7 @@
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/743999658352528-big-data-engineer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88518504-data-architect-hadoop-spark-?oga=true</t>
         </is>
       </c>
       <c r="J17" t="b">
@@ -1595,17 +1600,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9bf4a4e2dae5cc85a155</t>
+          <t>067704edcb00e117f37a</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi, Hope your are doing great! My name is Shyam and I am a Professional Recruiter at Agile, Inc. I have an open opportunity that you may be a good fit for. I came across your resume and think that you might be a good fit for the position listed below. Title: Big Data Engineer Location: Pittsburgh, PA Mode: Permanent Job Description: We are looking for a Big Data Engineer that will work on the collecting, storing, processing, and analyzing of large sets of data. The primary focus will be on choosing optimal solutions to use for these purposes, then maintaining, implementing, and monitoring them. You will also be responsible for integrating them with the architecture used across the company. Skills and Qualifications • Proficient understanding of distributed computing principles • Management of Hadoop cluster (Cloudera preferred), with all included services • Ability to solve any ongoing issues with operating the cluster • Proficiency with Hadoop v2, MapReduce, HDFS, Sqoop • Experience with building stream-processing systems, using solutions such as Storm or Spark-Streaming • Good knowledge of Big Data querying tools, such as Pig, Hive, and Impala • Experience with Spark • Experience with integration of data from multiple data sources such as MsSQL Server, Oracle, • Good understanding of SQL queries, joins, stored procedures, relational schemas • Experience with NoSQL databases, such as HBase, Cassandra, MongoDB (preferred) • Knowledge of various ETL techniques and frameworks, such as Flume • Experience with various messaging systems, such as Kafka or RabbitMQ • Experience with Cloudera FS domain knowledge a big plus but not required Thanks &amp; Regards "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions, Inc "}, "jobDescription": {"title": "Job Description", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected 1. Spark / Hadoop / HBASE / Cassandra 2. D3 / Kibana / Power BI for visualization 3. Depth in industry best practices on How to process click stream, telemetry data coming web / devices "}, "qualifications": {"title": "Qualifications", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected "}, "additionalInformation": {"title": "Additional Information", "text": " "}}</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1622,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data Analyst R Programming</t>
+          <t>Data Architect With Azure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1632,12 +1637,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2016-03-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91738120-data-analyst-r-programming?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90995931-data-architect-with-azure?oga=true</t>
         </is>
       </c>
       <c r="J18" t="b">
@@ -1665,17 +1670,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>21e4d98805199fb268c1</t>
+          <t>5e42a504d189fe30c4fa</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 ECMS RQ# 127616 Duration of contract 2 months Years of Experience 6-7 yrs Detailed JD (cannot get relevant profiles with one liner JD, so provide clear JD with roles and responsibilities, it will help vendors in sourcing right candidates) Need 1 profile who has atleast 2 yrs of experience in R programming and who can code well in R.Overall 6 to 7 yrs with data analyst as required. Mandatory skills R Programming, Data analyst skill Work Location Irving(TX) Background check process to be followed: Before onboarding / After onboarding: BGV Agency: Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions (AES), a software development and consulting company, headquartered in Cheyenne, WY-and has 3 offices in US, and also has a strong offshore support and development center in Hyderabad, India. AES presently has over 200 consultants working across United states serving clients on various solutions namely, ERP (Oracle, SAP) Microsoft Technologies, Web technologies "}, "jobDescription": {"title": "Job Description", "text": " Strong architect with technical delivery skills. The platform is going to be on Azure Big Data Environment including HDInsights, Azure Data Lake, Cortana Analytics suite etc., so someone with strong integration skills, good understanding of Big Data technologies/concepts and familiarity with Cloud integrations would be useful. At a minimum a Data Architect with good exposure to Big Data technologies and concepts. "}, "qualifications": {"title": "Qualifications", "text": " Big Data Architect With Azure "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1692,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Data Architect ( Hadoop / Spark )</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1702,12 +1707,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2016-01-15</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1722,7 +1727,7 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88518504-data-architect-hadoop-spark-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90036367-data-modeler?oga=true</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -1735,17 +1740,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>067704edcb00e117f37a</t>
+          <t>2acf8accb8cab7cf4980</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions, Inc "}, "jobDescription": {"title": "Job Description", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected 1. Spark / Hadoop / HBASE / Cassandra 2. D3 / Kibana / Power BI for visualization 3. Depth in industry best practices on How to process click stream, telemetry data coming web / devices "}, "qualifications": {"title": "Qualifications", "text": "Need Data Architect who has implemented big data solution using Hadoop / Spark technologies. Person also should have experience of meeting with customer and define data strategy. Here are some core skills expected "}, "additionalInformation": {"title": "Additional Information", "text": " "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " 1 Data Modeler Technology Agnostic 12+ Yrs 2-3 months Peoria (IL) -Develops the Enterprise Logical Data Model (LDM) and holds LDM Reviews with Data SMEs. -Facilitates JAD sessions to determine data rules, Applies client Standards, checks models in and out of Model Repository, and documents data model translation decisions. -Logical Design - Demonstrated experience with large scale, multiple business solutions across divisions or enterprise. -Ability to communicate strategies and processes around data modeling and architecture to cross functional groups and senior levels. -Ability to influence multiple levels on highly technical issues and challenges, -Demonstrated experience to influence and coordinate third parties and suppliers. -Work with business/IT to define the LDM/PDM for BOM+Shipment+Sales etc. Intent is to reuse the same model for Actual projects eventually. -Create a manufacturing domain-specific logical data model, inclusive of structured and semi-/un-structured data. Should know how to consolidate data model information across SAP, the various internal industry models in use alongside unstructured &amp; schema-less data sourcing 2 Data Catalog / Lineage Architect IBM Infosphere Information Governance Catalog (IGC) integration with Azure Data Lake 10+ Yrs 2-3 months Peoria (IL) -Gather, define, and develop data catalog and data lineage for the determined scope. -Should have an understanding of how to integrate the IBM Infosphere Information Governance Catalog (IGC) within an Azure Data Lake. Contact : 630 315 9559 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": ""}}</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1762,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Data Architect With Azure</t>
+          <t>Data Modeler (Physical Modeling &amp; Oracle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1777,7 +1782,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2016-03-29</t>
+          <t>2016-02-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1792,7 +1797,7 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90995931-data-architect-with-azure?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/89389114-data-modeler-physical-modeling-oracle-?oga=true</t>
         </is>
       </c>
       <c r="J20" t="b">
@@ -1805,17 +1810,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5e42a504d189fe30c4fa</t>
+          <t>42d3008393a735c10ebf</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Agile Enterprise Solutions (AES), a software development and consulting company, headquartered in Cheyenne, WY-and has 3 offices in US, and also has a strong offshore support and development center in Hyderabad, India. AES presently has over 200 consultants working across United states serving clients on various solutions namely, ERP (Oracle, SAP) Microsoft Technologies, Web technologies "}, "jobDescription": {"title": "Job Description", "text": " Strong architect with technical delivery skills. The platform is going to be on Azure Big Data Environment including HDInsights, Azure Data Lake, Cortana Analytics suite etc., so someone with strong integration skills, good understanding of Big Data technologies/concepts and familiarity with Cloud integrations would be useful. At a minimum a Data Architect with good exposure to Big Data technologies and concepts. "}, "qualifications": {"title": "Qualifications", "text": " Big Data Architect With Azure "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " We are looking for a senior Data Modeler. Ideal candidate will have heavy hands on experience using Erwin to creating and maintain updates to data models, hands on Oracle experience, physical modeling, implementation experience and the ability to take ownership and help make enhancement suggestions to models. Required skills: • 7+ years of data modeling experience with a strong focus on Physical modeling • Must have heavy Erwin experience • Must have worked extensively with Oracle Databases. • Must have a strong Oracle DBA background – should have strong knowledge of replication, clustering. • Should have good PL/SQL skills. • Data model implementation experience • Advanced data modeler with experience in Design, creation, and maintenance data models representing production databases. • Financial experience is preferred. • Experience working with Netezza is preferred (but not mandatory) "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1832,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1842,12 +1847,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-01-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1862,7 +1867,7 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90036367-data-modeler?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88757017-data-warehouse-architect?oga=true</t>
         </is>
       </c>
       <c r="J21" t="b">
@@ -1875,17 +1880,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2acf8accb8cab7cf4980</t>
+          <t>dd7b5f57e42a3e48d371</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " 1 Data Modeler Technology Agnostic 12+ Yrs 2-3 months Peoria (IL) -Develops the Enterprise Logical Data Model (LDM) and holds LDM Reviews with Data SMEs. -Facilitates JAD sessions to determine data rules, Applies client Standards, checks models in and out of Model Repository, and documents data model translation decisions. -Logical Design - Demonstrated experience with large scale, multiple business solutions across divisions or enterprise. -Ability to communicate strategies and processes around data modeling and architecture to cross functional groups and senior levels. -Ability to influence multiple levels on highly technical issues and challenges, -Demonstrated experience to influence and coordinate third parties and suppliers. -Work with business/IT to define the LDM/PDM for BOM+Shipment+Sales etc. Intent is to reuse the same model for Actual projects eventually. -Create a manufacturing domain-specific logical data model, inclusive of structured and semi-/un-structured data. Should know how to consolidate data model information across SAP, the various internal industry models in use alongside unstructured &amp; schema-less data sourcing 2 Data Catalog / Lineage Architect IBM Infosphere Information Governance Catalog (IGC) integration with Azure Data Lake 10+ Yrs 2-3 months Peoria (IL) -Gather, define, and develop data catalog and data lineage for the determined scope. -Should have an understanding of how to integrate the IBM Infosphere Information Governance Catalog (IGC) within an Azure Data Lake. Contact : 630 315 9559 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": ""}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "• Excellent work experience on architecting, designing Enterprise Data Warehouse infrastructure with DB appliances (particularly Netezza) • Able to conduct strategy and architecture sessions and deliver artifacts such as EDW strategy (Current state, Interim State and Target state) and EDW Architecture (Conceptual, Logical and Physical) at detail level. • Good exposure to Hortonworks Data Platform (Data mgmt- Hadoop, Data Access- HBAse, Hive/Pig, Spark, Storm., Integration – Kafka, Flume..) • Good working experience on BI Technologies like Business objects and/or MicroStrategy and Visualization platforms like Tableau/Spotfire. • Good Knowledge on Enterprise modeling in both Relational and Dimensional area. • Good knowledge on DI technologies like Informatica Powercenter (preferred) • Good knowledge on implementing Audit, Balance (Data Recon) and Control (ABC framework) in the Data Warehousing platforms. • Provide technical and architectural subject matter expertise to the various development teams including communicating architectural decisions and mentoring other technical staff around the various development technologies and decisions. • May review work of other team members and mentor junior architects "}, "qualifications": {"title": "Qualifications", "text": "Data Warehouse Architect "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1902,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Data Modeler (Physical Modeling &amp; Oracle)</t>
+          <t>Database Administrator (NoSQL / Oracle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1912,12 +1917,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2016-02-12</t>
+          <t>2016-04-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1932,7 +1937,7 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/89389114-data-modeler-physical-modeling-oracle-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91427603-database-administrator-nosql-oracle-?oga=true</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -1945,17 +1950,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>42d3008393a735c10ebf</t>
+          <t>eb910a182e0aacee19cf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " We are looking for a senior Data Modeler. Ideal candidate will have heavy hands on experience using Erwin to creating and maintain updates to data models, hands on Oracle experience, physical modeling, implementation experience and the ability to take ownership and help make enhancement suggestions to models. Required skills: • 7+ years of data modeling experience with a strong focus on Physical modeling • Must have heavy Erwin experience • Must have worked extensively with Oracle Databases. • Must have a strong Oracle DBA background – should have strong knowledge of replication, clustering. • Should have good PL/SQL skills. • Data model implementation experience • Advanced data modeler with experience in Design, creation, and maintenance data models representing production databases. • Financial experience is preferred. • Experience working with Netezza is preferred (but not mandatory) "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 Detailed job description - Skill Set: Database Administrator (NoSQL / Oracle) Work Location Atlanta, GA Job description Database Administrator (NoSQL / Oracle) The candidate for NoSQL Database Administrator will be expected to have a broad knowledge of server and applications running in a distributed Linux environment. • Extensive troubleshooting experience is required. The engineer will be part of the Tier 4 support team for the product. • Knowledge of the following is a must: Apache Web Server, Linux OS, J2EE Platforms such as Weblogic, JBOSS, Tomcat or WebSphere. • Familiarity with Oracle and building Open Source applications (such as Apache) will be required. Hands on experience with the following: • Cassandra • Oracle RAC Experience with Enterprise Architectures Experience with virtualization and self service provisioning • Cloud appliances • VCloud/VMware • OpenStack • Experience with analytics and tuning analytics for performance • Familiarity with R programming/statisticser Experience with Enterprise Cloud back-up and Recovery Experience with distributed cache systems • Hazelcast Familiarity with transactions and data integrity Replication • Cross data center replication • Geo-Replication • Oracle GoldenGate and DataGuard Cloud Security integration • Computer security • Network security • Informational security Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1972,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>IVR Business Analyst</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1982,12 +1987,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2016-01-25</t>
+          <t>2016-04-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/88757017-data-warehouse-architect?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91706803-ivr-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J23" t="b">
@@ -2015,17 +2020,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>dd7b5f57e42a3e48d371</t>
+          <t>29d3945c6149cb7d27ce</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "• Excellent work experience on architecting, designing Enterprise Data Warehouse infrastructure with DB appliances (particularly Netezza) • Able to conduct strategy and architecture sessions and deliver artifacts such as EDW strategy (Current state, Interim State and Target state) and EDW Architecture (Conceptual, Logical and Physical) at detail level. • Good exposure to Hortonworks Data Platform (Data mgmt- Hadoop, Data Access- HBAse, Hive/Pig, Spark, Storm., Integration – Kafka, Flume..) • Good working experience on BI Technologies like Business objects and/or MicroStrategy and Visualization platforms like Tableau/Spotfire. • Good Knowledge on Enterprise modeling in both Relational and Dimensional area. • Good knowledge on DI technologies like Informatica Powercenter (preferred) • Good knowledge on implementing Audit, Balance (Data Recon) and Control (ABC framework) in the Data Warehousing platforms. • Provide technical and architectural subject matter expertise to the various development teams including communicating architectural decisions and mentoring other technical staff around the various development technologies and decisions. • May review work of other team members and mentor junior architects "}, "qualifications": {"title": "Qualifications", "text": "Data Warehouse Architect "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks and Regards John Lennon 630-315-9511 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "Business Analyst Profile in IVR. Good understanding of IVR features and Domain, Strong Knowledge of Industry best practices . Excellent Analytical skills and Communication , Experience: 12+ Years contact : 972-427-1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2042,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Database Administrator (NoSQL / Oracle)</t>
+          <t>Kronos Analyst</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2057,7 +2062,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2072,7 +2077,7 @@
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91427603-database-administrator-nosql-oracle-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104402-kronos-analyst?oga=true</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -2085,17 +2090,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>eb910a182e0aacee19cf</t>
+          <t>48ab717cae2854563a90</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Number of Openings 1 Detailed job description - Skill Set: Database Administrator (NoSQL / Oracle) Work Location Atlanta, GA Job description Database Administrator (NoSQL / Oracle) The candidate for NoSQL Database Administrator will be expected to have a broad knowledge of server and applications running in a distributed Linux environment. • Extensive troubleshooting experience is required. The engineer will be part of the Tier 4 support team for the product. • Knowledge of the following is a must: Apache Web Server, Linux OS, J2EE Platforms such as Weblogic, JBOSS, Tomcat or WebSphere. • Familiarity with Oracle and building Open Source applications (such as Apache) will be required. Hands on experience with the following: • Cassandra • Oracle RAC Experience with Enterprise Architectures Experience with virtualization and self service provisioning • Cloud appliances • VCloud/VMware • OpenStack • Experience with analytics and tuning analytics for performance • Familiarity with R programming/statisticser Experience with Enterprise Cloud back-up and Recovery Experience with distributed cache systems • Hazelcast Familiarity with transactions and data integrity Replication • Cross data center replication • Geo-Replication • Oracle GoldenGate and DataGuard Cloud Security integration • Computer security • Network security • Informational security Contact : 972 427 1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position plays a major role in the design, programming, testing, implementation, and support for integrations for our Workforce Management System which administers Time &amp; Attendance, Paid Time Off, and Labor Management. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2112,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IVR Business Analyst</t>
+          <t>Oracle eBS Techno Functional Analyst</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2122,12 +2127,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2016-12-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2142,7 +2147,7 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/91706803-ivr-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/103403807-oracle-ebs-techno-functional-analyst?oga=true</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -2155,17 +2160,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29d3945c6149cb7d27ce</t>
+          <t>c46f1d2e683e01fd3d10</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": "Business Analyst Profile in IVR. Good understanding of IVR features and Domain, Strong Knowledge of Industry best practices . Excellent Analytical skills and Communication , Experience: 12+ Years contact : 972-427-1833 "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " Semiconductor "}, "jobDescription": {"title": "Job Description", "text": " The Analyst In Oracle EBS With Functional And Technical Experience In The Following Modules · Financials · Procurement · Order Management, Advanced pricing Client is driving energy efficient innovations, empowering customers to reduce global energy use. The company is a leading supplier of semiconductor-based solutions, offering a comprehensive portfolio of energy efficient power and signal management, logic, standard and custom devices. The company’s products help engineers solve their unique design challenges in automotive, communications, computing, consumer, industrial, medical and military/aerospace applications. Client operates a responsive, reliable, world-class supply chain and quality program, and a network of manufacturing facilities, sales offices and design centers in key markets throughout North America, Europe and the Asia Pacific regions. Primary Location US-AZ-Phoenix Job IT Job Type Full-time Travel No Education Bachelor’s degree in Computer Science, Management Information Systems/Business information Systems, Engineering or equivalent experience. Master’s degree preferred. Technical Requirements · Must have 7+ years experience in working with Oracle E-Business Suite Applications R12 - should be able to understand the requirements, understand the data model/architecture of the system quickly and prepare technical documents, perform unit testing, and handle developmental tasks · Strong Experience in strong in Oracle PL/SQL, Forms/Reports, and Workflows . · Developer and Functional Analyst in the Oracle Financials, procurement, Order management and advanced pricing · Develop Technical and functional designs and provide functional documents based on business requirements. · Solution delivery activities including the analysis, design, development · Excellent communication skills be able to manage multiple priorities · Must possess strong skills in either Oracle R11 or R12 functional design and customization utilizing Oracle best practice methodology. · Demonstrated experience in the support of Oracle R11 or R12 applications including PL/SQL, SQL, Oracle workflow, Reports and Forms. · Ability to work in a fast-paced environment coordinating with internal customers to help support and enhance business systems. · Demonstrated ability to work in a team environment including the ability to work collaboratively with business users. · Ability to work independently on development projects. Soft Skill Competencies · Well regarded leader in design and development standards and methodology. · Capability to develop core software modules on enterprise level · Ability to hold the post of Application Manager · Strong facilitation and ability to represent team and organization. · Proven track record in working directly with clients to define/influence and negotiate the solutions that enable their business objec</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2182,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kronos Analyst</t>
+          <t>Report developer/analyst/consultant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2197,7 +2202,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2016-03-02</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2212,7 +2217,7 @@
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104402-kronos-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/93290901-report-developer-analyst-consultant?oga=true</t>
         </is>
       </c>
       <c r="J26" t="b">
@@ -2225,17 +2230,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>48ab717cae2854563a90</t>
+          <t>05b173f523c68702bbf4</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position plays a major role in the design, programming, testing, implementation, and support for integrations for our Workforce Management System which administers Time &amp; Attendance, Paid Time Off, and Labor Management. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " . "}, "jobDescription": {"title": "Job Description", "text": " Position : Report developer/analyst/consultant Location : Farmington, CT Duration: Fulltime, Responsibilities •Analyze customer requests for reports and translate business questions into report requirements on a daily basis •Design, develop, and deliver ad-hoc reports using variety of tools such as SQL, TOAD, or SSRS and perform ad-hoc data analysis to support ongoing projects •Work individually with customers to capture and manage their reporting requirements, and validate data. •Support all existing standard reports and reporting platforms, and update the knowledge base around it.•Support and troubleshoot technical issues related to data integrity, completeness or availability .•Convert frequently requested ad-hoc reports into a standard report with parameters and drill downs as needed •Support all internal processes and help analyze, automate, or standardize key activities and reports .•Conduct detailed data analysis and testing on ongoing projects and deliverables within the HR Analytics team. Requirements •At least 3-5 years of experience with variety of reporting tools and working in a production reporting environment. Prior experience with HR data is a plus •3-5 years of experience developing reports with expertise in SQL, TOAD, and SSRS to design, develop, and deliver reports for end users in variety of formats .•Very strong SQL skills with the ability to query and analyze large and complex datasets •Expertise in translating end user requirements into reports and provide consulting on data and interpretation of results •Strong experience working with variety of data sources such as SQL, Oracle, and detailed understanding of data entities and their relationships. •Strong analytical skills with the ability to analyze, test, and conduct analysis on demand and communicate with various groups •Strong written and verbal communication skills to work with business users individually and meet their requirements. •Prior experience working individually with proven abilities to get things done in a fast paced production environment .•Adapt quickly to internal processes and tools and be able to shift priorities as needed. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " H1B copy and Passport Number mandatory For Submission. "}}</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2252,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Oracle eBS Techno Functional Analyst</t>
+          <t>System Analyst (BI/DWH)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2262,12 +2267,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2016-12-05</t>
+          <t>2016-03-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2282,7 +2287,7 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/103403807-oracle-ebs-techno-functional-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90758817-system-analyst-bi-dwh-?oga=true</t>
         </is>
       </c>
       <c r="J27" t="b">
@@ -2295,17 +2300,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>c46f1d2e683e01fd3d10</t>
+          <t>e765218d0ec589c265ea</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " Semiconductor "}, "jobDescription": {"title": "Job Description", "text": " The Analyst In Oracle EBS With Functional And Technical Experience In The Following Modules · Financials · Procurement · Order Management, Advanced pricing Client is driving energy efficient innovations, empowering customers to reduce global energy use. The company is a leading supplier of semiconductor-based solutions, offering a comprehensive portfolio of energy efficient power and signal management, logic, standard and custom devices. The company’s products help engineers solve their unique design challenges in automotive, communications, computing, consumer, industrial, medical and military/aerospace applications. Client operates a responsive, reliable, world-class supply chain and quality program, and a network of manufacturing facilities, sales offices and design centers in key markets throughout North America, Europe and the Asia Pacific regions. Primary Location US-AZ-Phoenix Job IT Job Type Full-time Travel No Education Bachelor’s degree in Computer Science, Management Information Systems/Business information Systems, Engineering or equivalent experience. Master’s degree preferred. Technical Requirements · Must have 7+ years experience in working with Oracle E-Business Suite Applications R12 - should be able to understand the requirements, understand the data model/architecture of the system quickly and prepare technical documents, perform unit testing, and handle developmental tasks · Strong Experience in strong in Oracle PL/SQL, Forms/Reports, and Workflows . · Developer and Functional Analyst in the Oracle Financials, procurement, Order management and advanced pricing · Develop Technical and functional designs and provide functional documents based on business requirements. · Solution delivery activities including the analysis, design, development · Excellent communication skills be able to manage multiple priorities · Must possess strong skills in either Oracle R11 or R12 functional design and customization utilizing Oracle best practice methodology. · Demonstrated experience in the support of Oracle R11 or R12 applications including PL/SQL, SQL, Oracle workflow, Reports and Forms. · Ability to work in a fast-paced environment coordinating with internal customers to help support and enhance business systems. · Demonstrated ability to work in a team environment including the ability to work collaboratively with business users. · Ability to work independently on development projects. Soft Skill Competencies · Well regarded leader in design and development standards and methodology. · Capability to develop core software modules on enterprise level · Ability to hold the post of Application Manager · Strong facilitation and ability to represent team and organization. · Proven track record in working directly with clients to define/influence and negotiate the solutions that enable their business objec</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " "}, "jobDescription": {"title": "Job Description", "text": " Please note that the System/Data Analyst position is not really a Data Analyst position. What the client needs is System Analysts with BI/DWH background. This is not a Data Analyst role and not Functional role like BA. Please screen the candidates accordingly and share suitable profile for below requirement "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2322,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Report developer/analyst/consultant</t>
+          <t>Workforce Management Analyst</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2337,7 +2342,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2352,7 +2357,7 @@
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/93290901-report-developer-analyst-consultant?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104456-workforce-management-analyst?oga=true</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2365,34 +2370,34 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>05b173f523c68702bbf4</t>
+          <t>0d140e426844c92e6ab8</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " . "}, "jobDescription": {"title": "Job Description", "text": " Position : Report developer/analyst/consultant Location : Farmington, CT Duration: Fulltime, Responsibilities •Analyze customer requests for reports and translate business questions into report requirements on a daily basis •Design, develop, and deliver ad-hoc reports using variety of tools such as SQL, TOAD, or SSRS and perform ad-hoc data analysis to support ongoing projects •Work individually with customers to capture and manage their reporting requirements, and validate data. •Support all existing standard reports and reporting platforms, and update the knowledge base around it.•Support and troubleshoot technical issues related to data integrity, completeness or availability .•Convert frequently requested ad-hoc reports into a standard report with parameters and drill downs as needed •Support all internal processes and help analyze, automate, or standardize key activities and reports .•Conduct detailed data analysis and testing on ongoing projects and deliverables within the HR Analytics team. Requirements •At least 3-5 years of experience with variety of reporting tools and working in a production reporting environment. Prior experience with HR data is a plus •3-5 years of experience developing reports with expertise in SQL, TOAD, and SSRS to design, develop, and deliver reports for end users in variety of formats .•Very strong SQL skills with the ability to query and analyze large and complex datasets •Expertise in translating end user requirements into reports and provide consulting on data and interpretation of results •Strong experience working with variety of data sources such as SQL, Oracle, and detailed understanding of data entities and their relationships. •Strong analytical skills with the ability to analyze, test, and conduct analysis on demand and communicate with various groups •Strong written and verbal communication skills to work with business users individually and meet their requirements. •Prior experience working individually with proven abilities to get things done in a fast paced production environment .•Adapt quickly to internal processes and tools and be able to shift priorities as needed. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " H1B copy and Passport Number mandatory For Submission. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position is responsible for configuration on Kronos Workforce Management system (Kronos WFC) including establishing standards and requirements, evaluating and directing enhancements, and implementing configuration solutions for payroll work rules and calculated accrual configuration to ensure the system is meeting local, state, federal law and Hyatt Policy. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>CompuGain</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>System Analyst (BI/DWH)</t>
+          <t>Sr. Data Analyst (Brokerage/Finance) - SQL/Python</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Rockville Pike</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2402,12 +2407,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2016-03-21</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2422,7 +2427,7 @@
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90758817-system-analyst-bi-dwh-?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/Compugain1/743999723884801-sr-data-analyst-brokerage-finance-sql-python?oga=true</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -2435,34 +2440,34 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>e765218d0ec589c265ea</t>
+          <t>52176647527c6698e6d4</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " "}, "jobDescription": {"title": "Job Description", "text": " Please note that the System/Data Analyst position is not really a Data Analyst position. What the client needs is System Analysts with BI/DWH background. This is not a Data Analyst role and not Functional role like BA. Please screen the candidates accordingly and share suitable profile for below requirement "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " When we run surveillance patterns on market data, you will gather requirements, define the right data sources, manage requirements, manage delivery lifecycle and work with users on UAT. It falls into a very sr. BA/DA role but there’s a lot more involvement in the delivery portion. "}, "qualifications": {"title": "Qualifications", "text": " Financial industry experience (the preferred types of financial industries are companies like brokerages, exchanges, capital markets, securities, fixed income, equities firms or similar.) SQL expert – can EXPLAIN thought process clearly for how he/she approaches SQL problems. Business savvy communicator "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Agile Enterprise Solutions</t>
+          <t>CompuGain</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Workforce Management Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Rockville Pike</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2472,12 +2477,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2016-03-02</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2492,7 +2497,7 @@
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AgileEnterpriseSolutions/90104456-workforce-management-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/Compugain1/743999722586402-sr-data-engineer?oga=true</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -2505,34 +2510,34 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0d140e426844c92e6ab8</t>
+          <t>406d96610632ccfd5711</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " This position is responsible for configuration on Kronos Workforce Management system (Kronos WFC) including establishing standards and requirements, evaluating and directing enhancements, and implementing configuration solutions for payroll work rules and calculated accrual configuration to ensure the system is meeting local, state, federal law and Hyatt Policy. The Workforce Management Interface Analyst will partner with various Human Resources, Accounting, and Payroll/Tax groups to ensure that all interfaces are processed correctly and contain accurate information. Works under general supervision and usually reports to a project leader or manager. The following highlights the key job duties: "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " Job Functions: Analyze system requirements and design responsive algorithms and solutions Use big data and cloud technologies to produce production quality code Engage in performance tuning and scalability engineering Work with team, peers and management to identify objectives and set priorities Perform related SDLC engineering activities like sprint planning and estimation Work effectively in small agile teams Provide creative solutions to problems Identify opportunities for improvement and execute "}, "qualifications": {"title": "Qualifications", "text": " Essential skills: Experience with cloud based Big Data technologies Proficiency in Hive / Spark SQL Experience with Spark Experience with one or more programming languages like Scala, Python, and/or Java Ability to push the frontier of technology and independently pursue better alternatives "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CompuGain</t>
+          <t>Kforce</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst (Brokerage/Finance) - SQL/Python</t>
+          <t>IT App Security Analyst</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rockville Pike</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2542,12 +2547,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2020-11-05</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Compugain1/743999723884801-sr-data-analyst-brokerage-finance-sql-python?oga=true</t>
+          <t>https://myhiring.kforce.com/careersection/ex/jobdetail.ftl?job=260569&amp;tz=GMT%2B00%3A00&amp;tzname=UTC</t>
         </is>
       </c>
       <c r="J31" t="b">
@@ -2570,39 +2570,39 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-09T13:25:47+00:00</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>52176647527c6698e6d4</t>
+          <t>1deefb33608c95298288</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " When we run surveillance patterns on market data, you will gather requirements, define the right data sources, manage requirements, manage delivery lifecycle and work with users on UAT. It falls into a very sr. BA/DA role but there’s a lot more involvement in the delivery portion. "}, "qualifications": {"title": "Qualifications", "text": " Financial industry experience (the preferred types of financial industries are companies like brokerages, exchanges, capital markets, securities, fixed income, equities firms or similar.) SQL expert – can EXPLAIN thought process clearly for how he/she approaches SQL problems. Business savvy communicator "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Kforce Career Section Go to the main content section. | My Account Options | We're glad you're here. This service is set to disconnect automatically after {0} minutes of inactivity. Your session will end in {1} minutes. Click OK to reset the timer to {0} minutes. You have been signed out. This service is set to sign out after {0} minutes of inactivity. Job Search My Jobpage Basic Search | Advanced Search | My Submissions | My Job Cart | My Saved Searches | Beginning of the main content section. Return to the home page Printable Format Return to previous position on page - ( ) Qualifications : Refer a friend for this job Refer a friend Refer a candidate Submit a candidate's profile</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CompuGain</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rockville Pike</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Compugain1/743999722586402-sr-data-engineer?oga=true</t>
+          <t>https://www.manpower.com/en/job/computer/data-analyst/5871423</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -2640,39 +2640,39 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-27T08:32:47+00:00</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>406d96610632ccfd5711</t>
+          <t>41063c80a2ddf863b25d</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " It all started in 2000. It began with a vision to be a highly dependable Technology centric Human Capital Solutions partner to businesses looking to accelerate outcomes. ... With a passion for helping companies gain freedom from complex business problems, we added a spectrum of tech solutions to our offering. "}, "jobDescription": {"title": "Job Description", "text": " Job Functions: Analyze system requirements and design responsive algorithms and solutions Use big data and cloud technologies to produce production quality code Engage in performance tuning and scalability engineering Work with team, peers and management to identify objectives and set priorities Perform related SDLC engineering activities like sprint planning and estimation Work effectively in small agile teams Provide creative solutions to problems Identify opportunities for improvement and execute "}, "qualifications": {"title": "Qualifications", "text": " Essential skills: Experience with cloud based Big Data technologies Proficiency in Hive / Spark SQL Experience with Spark Experience with one or more programming languages like Scala, Python, and/or Java Ability to push the frontier of technology and independently pursue better alternatives "}, "additionalInformation": {"title": "Additional Information", "text": " All your information will be kept confidential according to EEO guidelines. "}}</t>
+          <t>Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Data Analyst Reference Number: 5871423 Published Date: 09/27/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, an organization committed to sustainability and responsible business practices, is seeking a ESG Data Analyst I to join their team. As a ESG Data Analyst I, you will be part of the Environmental, Social, and Governance department supporting ESG reporting and data management initiatives. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: ESG Data Analyst I Location: Remote Pay Range: $40.87 What's the Job? Support ESG data collection and disclosure preparation for internal and external reporting Assist with GHG emissions and environmental reporting, including Scope 1, Scope 2, and Scope 3 data Clean, organize, and analyze ESG data, performing preliminary calculations and variance checks Monitor ESG reporting frameworks and help organize information for reporting alignment Support the use and management of ESG reporting platforms and tools What's Needed? Bachelor’s degree in environmental science, sustainability, data science, information systems, business, finance, or related field 1–2 years of experience supporting ESG, sustainability, or climate reporting activities Experience collecting, organizing, reviewing, and analyzing data from multiple sources Familiarity with ESG, sustainability, or climate-related reporting concepts and frameworks Proficiency with Microsoft Excel or similar data management tools What's in it for me? Opportunity to build hands-on experience in ESG data management and sustainability r</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kforce</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT App Security Analyst</t>
+          <t>Data Engineer - PSQA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>City or Postal Code City or Postal Code</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2682,7 +2682,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Temporary</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2697,7 +2702,7 @@
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://myhiring.kforce.com/careersection/ex/jobdetail.ftl?job=260569&amp;tz=GMT%2B00%3A00&amp;tzname=UTC</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/data-engineer-psqa/409677</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2705,22 +2710,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-09T13:25:47+00:00</t>
+          <t>2026-09-25T08:11:27+00:00</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1deefb33608c95298288</t>
+          <t>534c232ef5998f017d61</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Kforce Career Section Go to the main content section. | My Account Options | We're glad you're here. This service is set to disconnect automatically after {0} minutes of inactivity. Your session will end in {1} minutes. Click OK to reset the timer to {0} minutes. You have been signed out. This service is set to sign out after {0} minutes of inactivity. Job Search My Jobpage Basic Search | Advanced Search | My Submissions | My Job Cart | My Saved Searches | Beginning of the main content section. Return to the home page Printable Format Return to previous position on page - ( ) Qualifications : Refer a friend for this job Refer a friend Refer a candidate Submit a candidate's profile</t>
+          <t>Data Engineer - PSQA | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Data Engineer - PSQA Reference Number: 409677 Published Date: 09/25/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the technology industry, is seeking a Data Engineer - PSQA to join their team. As a Data Engineer - PSQA, you will be part of the Quality Assurance department supporting the Product and Software Quality teams. The ideal candidate will demonstrate strong analytical skills, proactive problem-solving abilities, and excellent communication skills, which will align successfully in the organization. Job Title: Data Engineer - PSQA Location: Foster City, CA Pay Range: $38/hour + Benefits What's the Job? Design, build, and maintain dashboards and scorecards for PSQA release and quality metrics Query, aggregate, and transform release/version data using SQL and Python Develop ETL pipelines to process and simplify quality and release data from multiple components Model release- and version-based data to enable tracking and trend analysis over time Perform exploratory data analysis to surface insights and support data-driven quality decisions What's Needed? Strong SQL skills for querying, aggregation, and data modeling Proficiency in Python (Pandas/PySpark) for ETL and data transformation Experience building dashboards with BI tools such as QuickSight, Tableau, or Power BI Ability to model release/version-based data for longitudinal tracking Basic data science skills including statistics, exploratory data analysis, and notebook-based analysis What's in it for me? Opportunity to work on impactful projects that influence product quality and release processes Collaborative envi</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2737,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Financial Systems Analyst</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Phoenix, AZ, US</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2752,7 +2757,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2767,7 +2772,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/data-analyst/5871423</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/financial-systems-analyst/412786</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -2775,22 +2780,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-27T08:32:47+00:00</t>
+          <t>2026-09-28T19:01:50+00:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>41063c80a2ddf863b25d</t>
+          <t>825bacc2d448d0405906</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Data Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Data Analyst Reference Number: 5871423 Published Date: 09/27/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, an organization committed to sustainability and responsible business practices, is seeking a ESG Data Analyst I to join their team. As a ESG Data Analyst I, you will be part of the Environmental, Social, and Governance department supporting ESG reporting and data management initiatives. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: ESG Data Analyst I Location: Remote Pay Range: $40.87 What's the Job? Support ESG data collection and disclosure preparation for internal and external reporting Assist with GHG emissions and environmental reporting, including Scope 1, Scope 2, and Scope 3 data Clean, organize, and analyze ESG data, performing preliminary calculations and variance checks Monitor ESG reporting frameworks and help organize information for reporting alignment Support the use and management of ESG reporting platforms and tools What's Needed? Bachelor’s degree in environmental science, sustainability, data science, information systems, business, finance, or related field 1–2 years of experience supporting ESG, sustainability, or climate reporting activities Experience collecting, organizing, reviewing, and analyzing data from multiple sources Familiarity with ESG, sustainability, or climate-related reporting concepts and frameworks Proficiency with Microsoft Excel or similar data management tools What's in it for me? Opportunity to build hands-on experience in ESG data management and sustainability r</t>
+          <t>Our client, aerospace technology and manufacturing company, is seeking a Financial Systems Analyst to join their team. As a Financial Systems Analyst, you will be part of the Finance Systems organization supporting Finance, IT, and cross-functional teams. The ideal candidate will have strong communication skills, problem-solving abilities, and the ability to manage multiple priorities in a fast-paced environment, which will align successfully in the organization. Job Title: Financial Systems Analyst Location: Phoenix, AZ Pay Range: $42.81/hr What’s the Job? Administer and support Oracle HFM, Essbase, and Enterprise Performance Management (EPM) platforms. Support monthly and quarterly financial close processes, including consolidations, translations, eliminations, and journal processing. Manage metadata, business rules, calc scripts, reporting components, and period open/close configurations. Troubleshoot system issues, data anomalies, consolidation problems, and reporting irregularities. Coordinate UAT activities, maintain system documentation, and support SOX compliance and audit readiness. What’s Needed? Experience administering Oracle HFM, Essbase, or comparable EPM platforms. Strong understanding of financial close processes, consolidations, and accounting concepts. Hands-on experience with metadata management, business rules, calc scripts, and data integration flows. Experience troubleshooting complex system or data issues. Experience supporting SOX compliance and internal audit requirements. What’s in it for me? Opportunity to support critical Enterprise Performance Management (EPM) platforms. Exposure to financial consolidation, reporting, and governance processes. Collaboration with Finance, IT, and cross-functional stakeholders. Involvement in system enhancements, change management, and UAT initiatives. Experience supporting a large-scale aerospace financial systems environment. If this is a role that interests you and you’d like to learn more, click apply now and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis and Talent Solutions Experis® is a global leader in technology services and part of the ManpowerGroup® (NYSE: MAN) family of brands. We connect skilled technology professionals with meaningful opportunities where they can grow their careers, expand their expertise and make a real impact. Guided by the belief that it takes Human Ingenuity to unlock the true potential of technology, Experis helps people gain experience with leading organizations, build sought-after skills and take the next step toward a brighter future. Backed by ManpowerGroup's 75+ years of workforce expertise and global reach across more than 70 countries and territories, Experis brings the scale, insight and opportunity to help people and businesses thrive. ManpowerGroup is consistently recognized for its commitment to inclusion, ethics and res</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2807,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Data Engineer - PSQA</t>
+          <t>Hybrid Financial Analyst</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2812,7 +2817,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2822,7 +2827,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2837,7 +2842,7 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/data-engineer-psqa/409677</t>
+          <t>https://www.manpower.com/en/job/computer/hybrid-financial-analyst-/5856631</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -2845,22 +2850,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-25T08:11:27+00:00</t>
+          <t>2026-09-28T09:05:51+00:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>534c232ef5998f017d61</t>
+          <t>f177712205fd7fd46f19</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Data Engineer - PSQA | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Data Engineer - PSQA Reference Number: 409677 Published Date: 09/25/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the technology industry, is seeking a Data Engineer - PSQA to join their team. As a Data Engineer - PSQA, you will be part of the Quality Assurance department supporting the Product and Software Quality teams. The ideal candidate will demonstrate strong analytical skills, proactive problem-solving abilities, and excellent communication skills, which will align successfully in the organization. Job Title: Data Engineer - PSQA Location: Foster City, CA Pay Range: $38/hour + Benefits What's the Job? Design, build, and maintain dashboards and scorecards for PSQA release and quality metrics Query, aggregate, and transform release/version data using SQL and Python Develop ETL pipelines to process and simplify quality and release data from multiple components Model release- and version-based data to enable tracking and trend analysis over time Perform exploratory data analysis to surface insights and support data-driven quality decisions What's Needed? Strong SQL skills for querying, aggregation, and data modeling Proficiency in Python (Pandas/PySpark) for ETL and data transformation Experience building dashboards with BI tools such as QuickSight, Tableau, or Power BI Ability to model release/version-based data for longitudinal tracking Basic data science skills including statistics, exploratory data analysis, and notebook-based analysis What's in it for me? Opportunity to work on impactful projects that influence product quality and release processes Collaborative environment supp</t>
+          <t>Hybrid Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Hybrid Financial Analyst Reference Number: 5856631 Published Date: 09/28/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the financial services industry, is seeking a Hybrid Financial Analyst to join their team. As a Hybrid Financial Analyst, you will be part of the Finance Department supporting the Corporate Restructuring team. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: Hybrid Financial Analyst Location: El Segundo, CA (Hybrid - Remote and Onsite) Pay Range: $27.00/hr to $29.00/hr Shift: 10am to 6:30pm PT What's the Job? Monitor court websites for newly filed documents related to cases Review claims filed by creditors and respond to inquiries via phone and email Assist with special projects and perform administrative quality control reviews Manage case dockets and update public access websites with filed documents Coordinate and review ballots, proofs of claim, and change of address information What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus What's in it for me? Opportunity to grow into a Case Consultant role with potential salary increases Potential for promotion to management positions within the team Supportive work environment with professional development opportunities Flexible</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2877,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financial Systems Analyst</t>
+          <t>Operations &amp; Accounting Analyst</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2887,12 +2892,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2907,7 +2912,7 @@
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/financial-systems-analyst/412786</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/operationsaccountinganalyst/409173</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -2915,22 +2920,22 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-28T19:01:50+00:00</t>
+          <t>2026-09-26T08:04:24+00:00</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>825bacc2d448d0405906</t>
+          <t>d15e3872f8035f46d8c7</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Our client, aerospace technology and manufacturing company, is seeking a Financial Systems Analyst to join their team. As a Financial Systems Analyst, you will be part of the Finance Systems organization supporting Finance, IT, and cross-functional teams. The ideal candidate will have strong communication skills, problem-solving abilities, and the ability to manage multiple priorities in a fast-paced environment, which will align successfully in the organization. Job Title: Financial Systems Analyst Location: Phoenix, AZ Pay Range: $42.81/hr What’s the Job? Administer and support Oracle HFM, Essbase, and Enterprise Performance Management (EPM) platforms. Support monthly and quarterly financial close processes, including consolidations, translations, eliminations, and journal processing. Manage metadata, business rules, calc scripts, reporting components, and period open/close configurations. Troubleshoot system issues, data anomalies, consolidation problems, and reporting irregularities. Coordinate UAT activities, maintain system documentation, and support SOX compliance and audit readiness. What’s Needed? Experience administering Oracle HFM, Essbase, or comparable EPM platforms. Strong understanding of financial close processes, consolidations, and accounting concepts. Hands-on experience with metadata management, business rules, calc scripts, and data integration flows. Experience troubleshooting complex system or data issues. Experience supporting SOX compliance and internal audit requirements. What’s in it for me? Opportunity to support critical Enterprise Performance Management (EPM) platforms. Exposure to financial consolidation, reporting, and governance processes. Collaboration with Finance, IT, and cross-functional stakeholders. Involvement in system enhancements, change management, and UAT initiatives. Experience supporting a large-scale aerospace financial systems environment. If this is a role that interests you and you’d like to learn more, click apply now and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis and Talent Solutions Experis® is a global leader in technology services and part of the ManpowerGroup® (NYSE: MAN) family of brands. We connect skilled technology professionals with meaningful opportunities where they can grow their careers, expand their expertise and make a real impact. Guided by the belief that it takes Human Ingenuity to unlock the true potential of technology, Experis helps people gain experience with leading organizations, build sought-after skills and take the next step toward a brighter future. Backed by ManpowerGroup's 75+ years of workforce expertise and global reach across more than 70 countries and territories, Experis brings the scale, insight and opportunity to help people and businesses thrive. ManpowerGroup is consistently recognized for its commitment to inclusion, ethics and res</t>
+          <t>Operations &amp; Accounting Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Operations &amp; Accounting Analyst Reference Number: 409173 Published Date: 09/26/2026 Job Type: Permanent Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in the manufacturing and industrial sectors, is seeking an Operations &amp; Accounting Analyst to join their team. As an Operations &amp; Accounting Analyst, you will be part of the Finance department supporting operational and financial processes. The ideal candidate will have attention to detail, strong analytical skills, and excellent communication abilities, which will align successfully in the organization. Job Title: Operations &amp; Accounting Analyst Location: Cincinnati, Ohio What's the Job? Ensure all receivables and payables are processed and reconciled accurately and timely to support audit readiness and operational integrity. Manage cash flow performance through proactive credit control and vendor management to support business stability and growth. Streamline month-end close processes by identifying inefficiencies and improving workflow for faster reporting. Transform operational data into insightful analyses to aid management decision-making. Collaborate with cross-functional teams to maintain data integrity and ensure compliance with internal policies and standards. What's Needed? Bachelor’s degree in accounting, finance, or a related field (or equivalent experience). 2–4 years of experience in accounting, financial analysis, or operations finance. Proficiency with Microsoft Excel and familiarity with ERP or accounting systems. Strong analytical, problem-solving, and communication skills. Ability to manage multiple priorities in a fast-paced environment with attenti</t>
         </is>
       </c>
     </row>
@@ -2942,17 +2947,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst</t>
+          <t>Purchasing Analyst</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>City or Postal Code City or Postal Code</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2962,7 +2967,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2977,7 +2982,7 @@
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/hybrid-financial-analyst-/5856631</t>
+          <t>https://www.manpower.com/en/job/management/purchasing-analyst/5890232</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -2985,22 +2990,22 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-28T09:05:51+00:00</t>
+          <t>2026-09-27T08:32:47+00:00</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>f177712205fd7fd46f19</t>
+          <t>deae9ca8108b93dce864</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Hybrid Financial Analyst Reference Number: 5856631 Published Date: 09/28/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the financial services industry, is seeking a Hybrid Financial Analyst to join their team. As a Hybrid Financial Analyst, you will be part of the Finance Department supporting the Corporate Restructuring team. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: Hybrid Financial Analyst Location: El Segundo, CA (Hybrid - Remote and Onsite) Pay Range: $27.00/hr to $29.00/hr Shift: 10am to 6:30pm PT What's the Job? Monitor court websites for newly filed documents related to cases Review claims filed by creditors and respond to inquiries via phone and email Assist with special projects and perform administrative quality control reviews Manage case dockets and update public access websites with filed documents Coordinate and review ballots, proofs of claim, and change of address information What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus What's in it for me? Opportunity to grow into a Case Consultant role with potential salary increases Potential for promotion to management positions within the team Supportive work environment with professional development opportunities Flexible</t>
+          <t>Purchasing Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Purchasing Analyst Reference Number: 5890232 Published Date: 09/27/2026 Job Type: Temporary Industry: Management Hours: Full Time APPLY NOW SAVE SHARE Now Hiring: Purchasing Analyst Location: Dallas, TX Schedule: Monday-Friday | Approximately 7:00 AM - 4:00 PM Salary: $60,000 - $90,000 per year We are seeking an experienced Purchasing Analyst with experience in a manufacturing environment. The ideal candidate will have a strong background in sourcing, purchasing, and supply chain management. Key Responsibilities: Source and purchase metals, raw materials, and production supplies Analyze inventory levels and production requirements to determine purchasing needs Utilize ERP systems to manage purchasing activities and inventory data Develop and maintain vendor relationships Track purchase orders and ensure on-time delivery of materials Resolve shortages, delays, and other supply chain issues Support production operations by ensuring material availability Qualifications: Purchasing experience in a manufacturing environment required Experience sourcing metals, raw materials, and production supplies Strong ERP system experience required Ability to analyze inventory and production data to support purchasing decisions Proven vendor management and negotiation skills Strong organizational and problem-solving abilities If this is a role that interests you and you’d like to learn more, click Apply Now, and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis and Talent Solutions Manpower® is a global leader in contingent staffing and permanent resourcing, providing c</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3017,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Marketing Intelligence Analyst</t>
+          <t>Remote Data Analyst CA only</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3022,7 +3027,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3032,7 +3037,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3047,7 +3052,7 @@
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/marketing-intelligence-analyst/5883169</t>
+          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-ca-only-/5889335</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3055,22 +3060,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-25T08:11:27+00:00</t>
+          <t>2026-09-26T08:04:24+00:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>f7f171cfdb72efcca1a0</t>
+          <t>1c85522cebc8534c6229</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Marketing Intelligence Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Marketing Intelligence Analyst Reference Number: 5883169 Published Date: 09/25/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the manufacturing industry, is seeking a dedicated and innovative Marketing Intelligence Analyst to join their dynamic team. As a vital member of the marketing department supporting strategic initiatives, the ideal candidate will demonstrate analytical thinking, collaboration, and a proactive mindset to thrive in a fast-paced environment. Job Title: Marketing Intelligence Analyst Location: Atlanta, GA Pay Range: $97,000- $100,000 What's the Job? Design, develop, and maintain marketing dashboards using Power BI to deliver real-time insights on campaigns, audiences, content, and communication channels. Analyze historical and current marketing data to identify trends, opportunities, and key drivers affecting campaign performance and audience engagement. Create predictive models to forecast campaign outcomes, optimize channel mix, timing, and budget allocation, supporting data-driven marketing strategies. Collaborate with marketing, IT, and data engineering teams to integrate diverse data sources, ensuring a comprehensive view of marketing performance and customer behavior. Translate complex datasets and analytics into clear, actionable recommendations for marketing leadership to inform messaging, spend, and campaign design. What's Needed? Bachelor’s degree in Business, Marketing, Data Analytics, Information Systems, or related field. At least 2 years of experience supporting marketing teams with business intelligence, analytics, or data analysis. Proficiency in Powe</t>
+          <t>Remote Data Analyst CA only | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst CA only Reference Number: 5889335 Published Date: 09/26/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the restructuring and legal support industry, is seeking a dedicated and detail-oriented Remote Data Analyst CA only to join their team. As a Remote Data Analyst CA only, you will be part of the Corporate Restructuring department supporting critical legal and administrative functions. The ideal candidate will demonstrate strong organizational skills, excellent communication abilities, and a proactive mindset, which will align successfully in the organization. Job Title: Remote Data Analyst CA only Location: El Segundo, CA Pay Range: $27.00 to $29.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status, claim deadlines, and disbursements Assist with preparing and reviewing legal documents, ballots, and proofs of claim Coordinate mailings, compile service lists, and prepare affidavits of service Perform administrative quality control reviews to ensure accuracy and compliance What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus but not required What's in it for me? Weekly pay, with opportunities for overtime True contract-to-hire opportun</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3087,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operations &amp; Accounting Analyst</t>
+          <t>SAP Materials Analyst</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>City or Postal Code City or Postal Code</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3097,12 +3102,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3117,7 +3122,7 @@
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/operationsaccountinganalyst/409173</t>
+          <t>https://www.manpower.com/en/job/administration-and-support/sap-materials-analyst/5892555</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3125,22 +3130,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-26T08:04:24+00:00</t>
+          <t>2026-09-27T08:32:47+00:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>d15e3872f8035f46d8c7</t>
+          <t>d1ec400b0ea0df48e3ba</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Operations &amp; Accounting Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Operations &amp; Accounting Analyst Reference Number: 409173 Published Date: 09/26/2026 Job Type: Permanent Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in the manufacturing and industrial sectors, is seeking an Operations &amp; Accounting Analyst to join their team. As an Operations &amp; Accounting Analyst, you will be part of the Finance department supporting operational and financial processes. The ideal candidate will have attention to detail, strong analytical skills, and excellent communication abilities, which will align successfully in the organization. Job Title: Operations &amp; Accounting Analyst Location: Cincinnati, Ohio What's the Job? Ensure all receivables and payables are processed and reconciled accurately and timely to support audit readiness and operational integrity. Manage cash flow performance through proactive credit control and vendor management to support business stability and growth. Streamline month-end close processes by identifying inefficiencies and improving workflow for faster reporting. Transform operational data into insightful analyses to aid management decision-making. Collaborate with cross-functional teams to maintain data integrity and ensure compliance with internal policies and standards. What's Needed? Bachelor’s degree in accounting, finance, or a related field (or equivalent experience). 2–4 years of experience in accounting, financial analysis, or operations finance. Proficiency with Microsoft Excel and familiarity with ERP or accounting systems. Strong analytical, problem-solving, and communication skills. Ability to manage multiple priorities in a fast-paced environment with attenti</t>
+          <t>SAP Materials Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) SAP Materials Analyst Reference Number: 5892555 Published Date: 09/27/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the manufacturing industry, is seeking a SAP Materials Analyst to join their team. As a SAP Materials Analyst, you will be part of the Materials Department supporting supply chain and production teams. The ideal candidate will demonstrate strong attention to detail, excellent communication skills, and a proactive approach to problem-solving, which will align successfully in the organization. Job Title: SAP Materials Analyst Location: Mission, TX Pay Range: $16.50 Shift: 1st Schedule: Monday – Friday from 8:00 am to 5:00 pm What's the Job? Maintain and update SAP system data by adding and updating part numbers and uploading bill of Materials (BoMs) Implement Deviations and Change of Engineering (CN) in SAP to ensure accurate data management Coordinate the Change of Engineering (CN) and Deviation (DEV) processes from a material perspective Analyze Excess &amp; Obsolete (E&amp;O) inventory reports and work with planning, purchasing, engineering, and production teams to minimize waste Support continuous improvement initiatives for master data processes and ensure data accuracy and consistency What's Needed? High School Diploma or GED At least 2 years of experience with SAP Proficiency in master data management and analytical skills Strong attention to detail and excellent communication skills Ability to work independently and manage multiple activities in a fast-paced environment What's in it for me? Opportunity to work with a dynamic and innovative team Engage in meaningfu</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3157,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Purchasing Analyst</t>
+          <t>Vehicle Systems Engineering - Operations Analyst</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>City or Postal Code City or Postal Code</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3172,7 +3177,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3187,7 +3192,7 @@
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/management/purchasing-analyst/5890232</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/vehicle-systems-engineering-operations-analyst/410595</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -3195,22 +3200,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-27T08:32:47+00:00</t>
+          <t>2026-09-28T02:03:09+00:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>deae9ca8108b93dce864</t>
+          <t>8f7e55a3a4d97bdb995a</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Purchasing Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Purchasing Analyst Reference Number: 5890232 Published Date: 09/27/2026 Job Type: Temporary Industry: Management Hours: Full Time APPLY NOW SAVE SHARE Now Hiring: Purchasing Analyst Location: Dallas, TX Schedule: Monday-Friday | Approximately 7:00 AM - 4:00 PM Salary: $60,000 - $90,000 per year We are seeking an experienced Purchasing Analyst with experience in a manufacturing environment. The ideal candidate will have a strong background in sourcing, purchasing, and supply chain management. Key Responsibilities: Source and purchase metals, raw materials, and production supplies Analyze inventory levels and production requirements to determine purchasing needs Utilize ERP systems to manage purchasing activities and inventory data Develop and maintain vendor relationships Track purchase orders and ensure on-time delivery of materials Resolve shortages, delays, and other supply chain issues Support production operations by ensuring material availability Qualifications: Purchasing experience in a manufacturing environment required Experience sourcing metals, raw materials, and production supplies Strong ERP system experience required Ability to analyze inventory and production data to support purchasing decisions Proven vendor management and negotiation skills Strong organizational and problem-solving abilities If this is a role that interests you and you’d like to learn more, click Apply Now, and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis and Talent Solutions Manpower® is a global leader in contingent staffing and permanent resourcing, providing companies wit</t>
+          <t>Vehicle Systems Engineering - Operations Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Postal Code City or Postal Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Vehicle Systems Engineering - Operations Analyst Reference Number: 410595 Published Date: 09/28/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in vehicle development and engineering, is seeking a dedicated Operations Analyst to join their team. As an Operations Analyst, you will be part of the Vehicle Systems Engineering department supporting the Powertrain, Thermal, &amp; Electrical Engineering teams. The ideal candidate will demonstrate strong analytical skills, proactive communication, and a collaborative mindset, which will align successfully in the organization. Job Title: Vehicle Systems Engineering - Operations Analyst Location: Foster City, CA Pay Range: $45-$50/hour + Benefits What's the Job? Support monthly, quarterly, and annual financial planning cycles, including preparing and managing financial reports for Vehicle Systems Engineering leadership. Create and update budget forecasts, track purchase orders, and ensure timely receipt of goods and invoices. Serve as the primary point of contact for all topics related to the Vehicle System Engineering Budget. Provide regular status reports on budget actuals versus forecasts, and adjust forecasts as needed for the remainder of the budget year. Collaborate with finance controllers to resolve potential budget gaps and support responses to open questions regarding budgets. What's Needed? Degree in Financial Management or related field with 8+ years of relevant hands-on experience. Strong project management skills and excellent communication abilities. Proficiency in financial systems such as SAP, Excel</t>
         </is>
       </c>
     </row>
@@ -3222,17 +3227,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Remote Data Analyst CA only</t>
+          <t>Warranty Data Administration Analyst</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Detroit, MI, US</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3257,7 +3262,7 @@
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-ca-only-/5889335</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/warranty-data-administration-analyst/405692</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -3270,49 +3275,49 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1c85522cebc8534c6229</t>
+          <t>6f9485c053cd0b52b9bd</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Remote Data Analyst CA only | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst CA only Reference Number: 5889335 Published Date: 09/26/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the restructuring and legal support industry, is seeking a dedicated and detail-oriented Remote Data Analyst CA only to join their team. As a Remote Data Analyst CA only, you will be part of the Corporate Restructuring department supporting critical legal and administrative functions. The ideal candidate will demonstrate strong organizational skills, excellent communication abilities, and a proactive mindset, which will align successfully in the organization. Job Title: Remote Data Analyst CA only Location: El Segundo, CA Pay Range: $27.00 to $29.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status, claim deadlines, and disbursements Assist with preparing and reviewing legal documents, ballots, and proofs of claim Coordinate mailings, compile service lists, and prepare affidavits of service Perform administrative quality control reviews to ensure accuracy and compliance What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus but not required What's in it for me? Weekly pay, with opportunities for overtime True contract-to-hire opportun</t>
+          <t>Our client, a leading commercial vehicle manufacturing company , is seeking a Warranty Data Administration Analyst to join their team. As a Warranty Data Administration Analyst, you will be part of the Warranty Operations Department supporting the Warranty Analysis, Service Engineering, and Supplier Quality Teams . The ideal candidate will have strong analytical skills , attention to detail , and effective communication skills which will align successfully in the organization. Job Title: Warranty Data Administration Analyst Location: Detroit, MI Pay Range: $25.00 - $29.00/hour What's the Job? Analyze warranty claims data and develop reports, metrics, and dashboards to evaluate business performance and warranty trends. Investigate technical warranty issues by reviewing service documentation, diagnostic information, and component design details. Support failure analysis activities through examination and testing of failed engine and exhaust aftertreatment system components. Collaborate with dealerships, repair facilities, suppliers, and internal teams to resolve warranty claim issues and coordinate inspections. Prepare technical documentation, findings, and recommendations to support warranty evaluations and appeals. What's Needed? Bachelor's degree in Engineering, Data Analytics, Business, or a related technical field. Experience analyzing warranty, service, automotive, manufacturing, or technical data. Strong analytical and problem-solving skills with the ability to interpret large data sets. Proficiency with reporting tools, Microsoft Excel, and data visualization platforms such as Power BI or Tableau. Excellent communication skills with the ability to work cross-functionally with internal and external stakeholders. What's in it for me? Opportunity to support a global leader in commercial vehicle manufacturing. Exposure to advanced vehicle systems, engineering teams, and warranty operations. Collaborative and innovative work environment. Professional development and career growth opportunities. Competitive compensation and comprehensive benefits package. If this is a role that interests you and you'd like to learn more, click apply now and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis, Talent Solutions, and Jefferson Wells ManpowerGroup® (NYSE: MAN), the leading global workforce solutions company, helps organizations transform in a fast-changing world of work by sourcing, assessing, developing, and managing the talent that enables them to win. We develop innovative solutions for hundreds of thousands of organizations every year, providing them with skilled talent while finding meaningful, sustainable employment for millions of people across a wide range of industries and skills. Our expert family of brands – Manpower, Experis, Talent Solutions, and Jefferson Wells – creates substantial value for candidates and clients across</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>MeeBoss</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SAP Materials Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>["full-time", "part-time"]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3322,12 +3327,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/sap-materials-analyst/5892555</t>
+          <t>https://meeboss.com/job/00b818153660456733x62g~~</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -3335,54 +3340,49 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-27T08:32:47+00:00</t>
+          <t>2026-09-23T23:20:48+00:00</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>d1ec400b0ea0df48e3ba</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>SAP Materials Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) SAP Materials Analyst Reference Number: 5892555 Published Date: 09/27/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the manufacturing industry, is seeking a SAP Materials Analyst to join their team. As a SAP Materials Analyst, you will be part of the Materials Department supporting supply chain and production teams. The ideal candidate will demonstrate strong attention to detail, excellent communication skills, and a proactive approach to problem-solving, which will align successfully in the organization. Job Title: SAP Materials Analyst Location: Mission, TX Pay Range: $16.50 Shift: 1st Schedule: Monday – Friday from 8:00 am to 5:00 pm What's the Job? Maintain and update SAP system data by adding and updating part numbers and uploading bill of Materials (BoMs) Implement Deviations and Change of Engineering (CN) in SAP to ensure accurate data management Coordinate the Change of Engineering (CN) and Deviation (DEV) processes from a material perspective Analyze Excess &amp; Obsolete (E&amp;O) inventory reports and work with planning, purchasing, engineering, and production teams to minimize waste Support continuous improvement initiatives for master data processes and ensure data accuracy and consistency What's Needed? High School Diploma or GED At least 2 years of experience with SAP Proficiency in master data management and analytical skills Strong attention to detail and excellent communication skills Ability to work independently and manage multiple activities in a fast-paced environment What's in it for me? Opportunity to work with a dynamic and innovative team Engage in meaningful projects t</t>
+          <t>6de6c5cf2529df452bf0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>MeeBoss</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vehicle Systems Engineering - Operations Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>["full-time", "part-time", "internship"]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/vehicle-systems-engineering-operations-analyst/410595</t>
+          <t>https://meeboss.com/job/81a50fedcfe84ecc33Nz3g~~</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -3405,54 +3405,54 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-28T02:03:09+00:00</t>
+          <t>2026-09-23T08:08:19+00:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>8f7e55a3a4d97bdb995a</t>
+          <t>71430bd98e5344483dbd</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Vehicle Systems Engineering - Operations Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Vehicle Systems Engineering - Operations Analyst Reference Number: 410595 Published Date: 09/28/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in vehicle development and engineering, is seeking a dedicated Operations Analyst to join their team. As an Operations Analyst, you will be part of the Vehicle Systems Engineering department supporting the Powertrain, Thermal, &amp; Electrical Engineering teams. The ideal candidate will demonstrate strong analytical skills, proactive communication, and a collaborative mindset, which will align successfully in the organization. Job Title: Vehicle Systems Engineering - Operations Analyst Location: Foster City, CA Pay Range: $45-$50/hour + Benefits What's the Job? Support monthly, quarterly, and annual financial planning cycles, including preparing and managing financial reports for Vehicle Systems Engineering leadership. Create and update budget forecasts, track purchase orders, and ensure timely receipt of goods and invoices. Serve as the primary point of contact for all topics related to the Vehicle System Engineering Budget. Provide regular status reports on budget actuals versus forecasts, and adjust forecasts as needed for the remainder of the budget year. Collaborate with finance controllers to resolve potential budget gaps and support responses to open questions regarding budgets. What's Needed? Degree in Financial Management or related field with 8+ years of relevant hands-on experience. Strong project management skills and excellent communication abilities. Proficiency in financial systems such as SAP, Excel (pivot tabl</t>
+          <t>We are looking for a Data Analyst to join our team remotely. In this position, you will help us make data-driven decisions by analyzing complex datasets and providing insights that drive business performance. What You'll Do Conduct data cleaning and preparation to ensure accuracy and reliability. Utilize SQL to extract and manipulate data for analysis. Create data visualizations to present findings clearly and effectively. Perform statistical analysis to identify trends and patterns. Apply machine learning techniques to enhance data insights. Collaborate with cross-functional teams to support data-driven initiatives. What We're Looking For Proficiency in data visualization tools and techniques. Strong SQL skills for data querying and manipulation. Experience with statistical analysis and data cleaning. Familiarity with Excel for data management and analysis. Knowledge of Python for data analysis and machine learning. Ability to communicate findings effectively to non-technical stakeholders. Benefits &amp; Compensation Competitive salary between $75,000 and $95,000 per year. Flexible work environment with remote options.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>Motion Recruitment</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Warranty Data Administration Analyst</t>
+          <t>Associate Data Engineer - CTH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US</t>
+          <t>Fort Worth, Texas, 76155, United States</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/warranty-data-administration-analyst/405692</t>
+          <t>https://motionrecruitment.com/tech-jobs/fort-worth/contract/associate-data-engineer-cth/884700</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -3475,39 +3475,39 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-26T08:04:24+00:00</t>
+          <t>2026-09-15T18:37:24+00:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>6f9485c053cd0b52b9bd</t>
+          <t>eeba2482b3e3680a7e15</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Our client, a leading commercial vehicle manufacturing company , is seeking a Warranty Data Administration Analyst to join their team. As a Warranty Data Administration Analyst, you will be part of the Warranty Operations Department supporting the Warranty Analysis, Service Engineering, and Supplier Quality Teams . The ideal candidate will have strong analytical skills , attention to detail , and effective communication skills which will align successfully in the organization. Job Title: Warranty Data Administration Analyst Location: Detroit, MI Pay Range: $25.00 - $29.00/hour What's the Job? Analyze warranty claims data and develop reports, metrics, and dashboards to evaluate business performance and warranty trends. Investigate technical warranty issues by reviewing service documentation, diagnostic information, and component design details. Support failure analysis activities through examination and testing of failed engine and exhaust aftertreatment system components. Collaborate with dealerships, repair facilities, suppliers, and internal teams to resolve warranty claim issues and coordinate inspections. Prepare technical documentation, findings, and recommendations to support warranty evaluations and appeals. What's Needed? Bachelor's degree in Engineering, Data Analytics, Business, or a related technical field. Experience analyzing warranty, service, automotive, manufacturing, or technical data. Strong analytical and problem-solving skills with the ability to interpret large data sets. Proficiency with reporting tools, Microsoft Excel, and data visualization platforms such as Power BI or Tableau. Excellent communication skills with the ability to work cross-functionally with internal and external stakeholders. What's in it for me? Opportunity to support a global leader in commercial vehicle manufacturing. Exposure to advanced vehicle systems, engineering teams, and warranty operations. Collaborative and innovative work environment. Professional development and career growth opportunities. Competitive compensation and comprehensive benefits package. If this is a role that interests you and you'd like to learn more, click apply now and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis, Talent Solutions, and Jefferson Wells ManpowerGroup® (NYSE: MAN), the leading global workforce solutions company, helps organizations transform in a fast-changing world of work by sourcing, assessing, developing, and managing the talent that enables them to win. We develop innovative solutions for hundreds of thousands of organizations every year, providing them with skilled talent while finding meaningful, sustainable employment for millions of people across a wide range of industries and skills. Our expert family of brands – Manpower, Experis, Talent Solutions, and Jefferson Wells – creates substantial value for candidates and clients across</t>
+          <t>Description: Associate Data Engineer Location: Fort Worth Texas 76155 United State (Hybrid) What you'll do As noted above, this list is intended to reflect the current job but there may be additional essential functions (and certainly non-essential job functions) that are not referenced. Management will modify the job or require other tasks be performed whenever it is deemed appropriate to do so, observing, of course, any legal obligations including any collective bargaining obligations. • Work closely with source data application teams and product owners to design, implement and support analytics solutions that provide insights to make better decisions • Implement data migration and data engineering solutions using Azure products and services: (Azure Data Lake Storage, Azure Data Factory, Azure Functions, Event Hub, Azure Stream Analytics, Azure Databricks, etc.) and traditional data warehouse tools • Perform multiple aspects involved in the development lifecycle - design, cloud engineering (Infrastructure, network, security, and administration), ingestion, preparation, data modeling, testing, CICD pipelines, performance tuning, deployments, consumption, BI, alerting, prod support • Develop technical solutions and collaborate within a team environment as well as work independently • Be a part of a DevOps team that completely owns and supports their product • Follow coding standards, best practices and privacy and security guidelines • Be part of multi-functional technical and domain skills team All you'll need for success Minimum Qualifications - Education &amp; Prior Job Experience • Bachelor's degree in Computer Science, Computer Engineering, Technology, Information Systems (CIS/MIS), Engineering or related technical discipline, or equivalent experience/training • 1+ years experience building data solutions, using agile and DevOps practices. • 1+ years data analytics experience using SQL • 1+ years experience with Cloud technologies (especially Microsoft Azure) Preferred Qualifications - Education &amp; Prior Job Experience • 2+ years software solution development using agile, dev ops practices. • 2+ years data analytics experience using SQL • 2+ years using SQL, Python and Spark • 1+ years experience with Cloud Technologies (especially Microsoft Azure) Skills, Licenses, and Certifications • Expertise with a Cloud based technology stack for data management, ingestion, curation and consumption layers. • Azure Databricks 1-3 years of experience is needed for this role Top Skills: SQL, building data solutions, develops practices, Microsoft Azure(Generic), Python, Sequel Nice to Have Skills: Spark and Databricks Describe a great candidate that you are looking for and what skills and experience they will have: Knowledge of software design principles, understanding of big data, knowledge of SQL, good work ethics What is the team environment and structure like?:Very laid-back work environment, with a tech lead and 3 other senior and junior developers. Candid</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MeeBoss</t>
+          <t>Motion Recruitment</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Business Data Analyst</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Alpharetta, Georgia, 30009, United States</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>["full-time", "part-time"]</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/00b818153660456733x62g~~</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/business-data-analyst/887454</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -3545,49 +3545,54 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-23T23:20:48+00:00</t>
+          <t>2026-09-14T21:22:24+00:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>6de6c5cf2529df452bf0</t>
+          <t>fd8f32a1f36407c076dc</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Job Description Business Data Analyst Location: Remote (US) Duration: 6-Month Contract (Potential Extension) Compensation: Up to $40/hr A leading business intelligence and information services organization is seeking a Business Data Analyst to support a high-visibility analytics platform used to drive strategic decision-making across multiple departments. This role is ideal for someone who enjoys working with complex datasets, uncovering meaningful insights, improving data quality, and developing solutions that help business teams make better decisions. The successful candidate will partner closely with stakeholders to understand business needs, identify opportunities for improvement, and deliver reliable reporting and analytical tools. The position combines data analysis, business problem-solving, reporting, and technical solution development in a collaborative remote environment. While a strong analytical mindset is critical, the ability to leverage technology to automate processes and improve efficiency will be equally important. Required Skills &amp; Experience 3+ years of experience in a Data Analyst, Business Data Analyst, Reporting Analyst, or Business Intelligence Analyst role Advanced experience using Python for data analysis, automation, and data processing Strong experience working with large and complex datasets Experience using Pandas and related data analysis libraries Proven ability to identify and resolve data quality issues Experience building reports, dashboards, and business insights for stakeholders Experience integrating and analyzing data from multiple sources including APIs, spreadsheets, and databases Strong analytical, critical thinking, and problem-solving skills Ability to communicate findings and recommendations to both technical and non-technical audiences Desired Skills &amp; Experience Experience with business intelligence and reporting solutions Familiarity with Streamlit, Dash, Gradio, or similar data applications SQL and database experience Experience with data validation and quality control processes Knowledge of modern data governance practices Experience creating automated reporting workflows Exposure to cloud-based analytics environments Background supporting sales, operations, financial, or strategic reporting functions What You Will Be Doing Daily Responsibilities Analyze, validate, and standardize data from multiple business sources Support and enhance a production analytics platform used across the organization Develop automated processes that improve reporting efficiency and data accuracy Build dashboards, reports, and analytical solutions for business stakeholders Investigate data discrepancies and implement quality control measures Integrate data from external and internal systems to improve visibility and decision-making Partner directly with business teams to gather requirements and deliver solutions Identify opportunities to streamline processes and improve operational reporting Create documentation for rep</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MeeBoss</t>
+          <t>Motion Recruitment</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Cybersecurity Data Engineer - Python/SQL/PowerBi/Security Analytics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Alpharetta, Georgia, 30009, United States</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>["full-time", "part-time", "internship"]</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3602,7 +3607,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/81a50fedcfe84ecc33Nz3g~~</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-security-analytics/888444</t>
         </is>
       </c>
       <c r="J46" t="b">
@@ -3610,22 +3615,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-23T08:08:19+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>71430bd98e5344483dbd</t>
+          <t>ad181cacc5375145c150</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>We are looking for a Data Analyst to join our team remotely. In this position, you will help us make data-driven decisions by analyzing complex datasets and providing insights that drive business performance. What You'll Do Conduct data cleaning and preparation to ensure accuracy and reliability. Utilize SQL to extract and manipulate data for analysis. Create data visualizations to present findings clearly and effectively. Perform statistical analysis to identify trends and patterns. Apply machine learning techniques to enhance data insights. Collaborate with cross-functional teams to support data-driven initiatives. What We're Looking For Proficiency in data visualization tools and techniques. Strong SQL skills for data querying and manipulation. Experience with statistical analysis and data cleaning. Familiarity with Excel for data management and analysis. Knowledge of Python for data analysis and machine learning. Ability to communicate findings effectively to non-technical stakeholders. Benefits &amp; Compensation Competitive salary between $75,000 and $95,000 per year. Flexible work environment with remote options.</t>
+          <t>Job Description A leading organization within a highly regulated cloud environment is seeking a Cybersecurity Data Engineer to support security analytics, continuous monitoring, and automation initiatives across enterprise and cloud platforms. This role is ideal for someone who enjoys working at the intersection of cybersecurity, data engineering, and analytics. You'll leverage security telemetry, vulnerability data, and operational metrics to create meaningful insights, automate reporting processes, and improve overall security visibility. While the environment operates under regulatory requirements, the primary focus is on security data analysis, dashboard development, monitoring, and automation. You will collaborate with security, engineering, and infrastructure teams to build scalable reporting solutions, develop security metrics, and enhance the organization's ability to identify trends, risks, and opportunities for improvement. Location: Alpharetta, GA (Hybrid, 1 day onsite per week) Contract: 6 Months with potential extension and conversion opportunity Compensation: $40-$60/hour Required Skills &amp; Experience 3+ years of experience in cybersecurity, security analytics, security operations, or a related field Strong Python development and automation experience Advanced SQL skills with experience querying and analyzing large datasets Experience building dashboards and reports using Power BI or similar BI platforms Experience working with security logs, alerts, telemetry, vulnerability data, and incident response information Experience with Microsoft Defender or similar security monitoring solutions Familiarity with Microsoft Azure and cloud security concepts Understanding of security operations, threat monitoring, vulnerability management, and incident response Experience with ETL processes, reporting workflows, and data analytics Strong analytical, troubleshooting, and communication skills Desired Skills &amp; Experience Experience working in a Blue Team or Security Operations Center (SOC) environment Experience developing security analytics and reporting solutions Familiarity with FedRAMP, NIST, or similar regulatory frameworks Experience automating security monitoring or reporting processes using Python or PowerShell Relevant cybersecurity certifications What You Will Be Doing Daily Responsibilities: 100% Hands On Analyze security data from logs, vulnerability scans, monitoring platforms, and incident response activities Design, develop, and maintain Power BI dashboards and reporting solutions Build automation tools and reporting processes using Python Write and optimize SQL queries to support investigations, metrics, and reporting needs Monitor security events and telemetry to identify trends, anomalies, and potential threats Support security operations through incident analysis and continuous monitoring activities Develop and track security KPIs and operational metrics Partner with security, engineering, and infrastructure teams to improve se</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3642,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - CTH</t>
+          <t>Cybersecurity Data Engineer, Python/SQL/PowerBi - Georgia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, Texas, 76155, United States</t>
+          <t>Alpharetta, Georgia, 30009, United States</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3657,7 +3662,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3672,7 +3677,7 @@
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/fort-worth/contract/associate-data-engineer-cth/884700</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-georgia/887207</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3680,22 +3685,22 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-15T18:37:24+00:00</t>
+          <t>2026-09-10T18:09:10+00:00</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>eeba2482b3e3680a7e15</t>
+          <t>ee4d1750d211c7261738</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Description: Associate Data Engineer Location: Fort Worth Texas 76155 United State (Hybrid) What you'll do As noted above, this list is intended to reflect the current job but there may be additional essential functions (and certainly non-essential job functions) that are not referenced. Management will modify the job or require other tasks be performed whenever it is deemed appropriate to do so, observing, of course, any legal obligations including any collective bargaining obligations. • Work closely with source data application teams and product owners to design, implement and support analytics solutions that provide insights to make better decisions • Implement data migration and data engineering solutions using Azure products and services: (Azure Data Lake Storage, Azure Data Factory, Azure Functions, Event Hub, Azure Stream Analytics, Azure Databricks, etc.) and traditional data warehouse tools • Perform multiple aspects involved in the development lifecycle - design, cloud engineering (Infrastructure, network, security, and administration), ingestion, preparation, data modeling, testing, CICD pipelines, performance tuning, deployments, consumption, BI, alerting, prod support • Develop technical solutions and collaborate within a team environment as well as work independently • Be a part of a DevOps team that completely owns and supports their product • Follow coding standards, best practices and privacy and security guidelines • Be part of multi-functional technical and domain skills team All you'll need for success Minimum Qualifications - Education &amp; Prior Job Experience • Bachelor's degree in Computer Science, Computer Engineering, Technology, Information Systems (CIS/MIS), Engineering or related technical discipline, or equivalent experience/training • 1+ years experience building data solutions, using agile and DevOps practices. • 1+ years data analytics experience using SQL • 1+ years experience with Cloud technologies (especially Microsoft Azure) Preferred Qualifications - Education &amp; Prior Job Experience • 2+ years software solution development using agile, dev ops practices. • 2+ years data analytics experience using SQL • 2+ years using SQL, Python and Spark • 1+ years experience with Cloud Technologies (especially Microsoft Azure) Skills, Licenses, and Certifications • Expertise with a Cloud based technology stack for data management, ingestion, curation and consumption layers. • Azure Databricks 1-3 years of experience is needed for this role Top Skills: SQL, building data solutions, develops practices, Microsoft Azure(Generic), Python, Sequel Nice to Have Skills: Spark and Databricks Describe a great candidate that you are looking for and what skills and experience they will have: Knowledge of software design principles, understanding of big data, knowledge of SQL, good work ethics What is the team environment and structure like?:Very laid-back work environment, with a tech lead and 3 other senior and junior developers. Candid</t>
+          <t>Job Description An industry-leading organization is hiring a Cybersecurity Data Engineer to help transform security and vulnerability data into actionable insights for security and engineering teams. This is a highly data-focused security position centered around collecting, processing, analyzing, and reporting on data generated from vulnerability scans and security tools. In this role, you will use Python and SQL to work with security data, build and maintain data pipelines, and transform raw scan data into clean, usable datasets. You will also develop reporting and dashboards using Power BI, Microsoft Fabric, or similar data visualization tools . The ideal candidate has a strong background in data engineering, cybersecurity, or a combination of both. Candidates with experience as a Data Engineer working with security data, Cybersecurity Engineer with strong Python and SQL skills, or Security Analyst who has moved into data and automation are encouraged to apply. Required Skills &amp; Experience Strong proficiency in Python Strong proficiency in SQL Experience working with data pipelines, ETL, databases, or data warehousing Experience working with Power BI, Microsoft Fabric, or similar business intelligence/data visualization platforms Experience working with security, vulnerability, compliance, or cybersecurity-related data Experience analyzing data from vulnerability scans, security tools, assessments, or similar sources Strong data analysis and problem-solving skills Experience working with large datasets Experience with JSON, XML, and Excel Bachelor's degree 3–5+ years of relevant professional experience Desired Skills &amp; Experience Experience working in a cybersecurity, information security, or security engineering environment Experience with vulnerability management or security scanning tools Experience automating security or data processes with Python Experience building security dashboards and reporting in Power BI Experience with Microsoft Azure or cloud security Experience with Microsoft Defender or similar security platforms Experience working with security logs, alerts, vulnerability data, or other security telemetry Familiarity with FedRAMP, NIST, or other security/compliance frameworks Experience with PowerShell Experience supporting security metrics, continuous monitoring, or security posture reporting What You Will Be Doing Daily Responsibilities Collect, process, and analyze data from vulnerability scans, security tools, assessments, and other security sources Build and maintain data pipelines and ETL processes for security-related data Use Python to automate data processing, analysis, reporting, and security workflows Use SQL to query databases, manipulate data, and develop reporting datasets Transform raw scan and security data into clean, usable datasets Build and maintain Power BI and Microsoft Fabric dashboards and reports Develop KPIs and metrics to help security teams measure and track their security posture Analyze large secu</t>
         </is>
       </c>
     </row>
@@ -3707,27 +3712,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Business Data Analyst</t>
+          <t>Data Architect | Richardson | AWS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, 30009, United States</t>
+          <t>Richardson, Texas, 75080, United States</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3742,7 +3747,7 @@
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/business-data-analyst/887454</t>
+          <t>https://motionrecruitment.com/tech-jobs/richardson/direct-hire/data-architect-richardson-aws/884037</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -3750,22 +3755,22 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-14T21:22:24+00:00</t>
+          <t>2026-08-20T15:21:06+00:00</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>fd8f32a1f36407c076dc</t>
+          <t>a3f3fd8a2c38f7e08d8d</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Job Description Business Data Analyst Location: Remote (US) Duration: 6-Month Contract (Potential Extension) Compensation: Up to $40/hr A leading business intelligence and information services organization is seeking a Business Data Analyst to support a high-visibility analytics platform used to drive strategic decision-making across multiple departments. This role is ideal for someone who enjoys working with complex datasets, uncovering meaningful insights, improving data quality, and developing solutions that help business teams make better decisions. The successful candidate will partner closely with stakeholders to understand business needs, identify opportunities for improvement, and deliver reliable reporting and analytical tools. The position combines data analysis, business problem-solving, reporting, and technical solution development in a collaborative remote environment. While a strong analytical mindset is critical, the ability to leverage technology to automate processes and improve efficiency will be equally important. Required Skills &amp; Experience 3+ years of experience in a Data Analyst, Business Data Analyst, Reporting Analyst, or Business Intelligence Analyst role Advanced experience using Python for data analysis, automation, and data processing Strong experience working with large and complex datasets Experience using Pandas and related data analysis libraries Proven ability to identify and resolve data quality issues Experience building reports, dashboards, and business insights for stakeholders Experience integrating and analyzing data from multiple sources including APIs, spreadsheets, and databases Strong analytical, critical thinking, and problem-solving skills Ability to communicate findings and recommendations to both technical and non-technical audiences Desired Skills &amp; Experience Experience with business intelligence and reporting solutions Familiarity with Streamlit, Dash, Gradio, or similar data applications SQL and database experience Experience with data validation and quality control processes Knowledge of modern data governance practices Experience creating automated reporting workflows Exposure to cloud-based analytics environments Background supporting sales, operations, financial, or strategic reporting functions What You Will Be Doing Daily Responsibilities Analyze, validate, and standardize data from multiple business sources Support and enhance a production analytics platform used across the organization Develop automated processes that improve reporting efficiency and data accuracy Build dashboards, reports, and analytical solutions for business stakeholders Investigate data discrepancies and implement quality control measures Integrate data from external and internal systems to improve visibility and decision-making Partner directly with business teams to gather requirements and deliver solutions Identify opportunities to streamline processes and improve operational reporting Create documentation for rep</t>
+          <t>We are seeking a Senior Data Architect to help drive the next generation of enterprise data capabilities within a rapidly growing, newly centralized data organization. This role will play a key part in designing and implementing modern data architectures, data products, and strategic roadmaps that support enterprise-wide analytics, reporting, and AI initiatives. In this highly visible position, you will partner directly with business leaders, engineering teams, and data stakeholders to define data strategy, architect scalable solutions, and establish best practices across a modern AWS and Snowflake ecosystem. This is an opportunity to influence the future-state data platform from the ground up within a highly collaborative and strategic environment. Required Skills &amp; Experience Strong experience designing enterprise Data Architectures, Data Warehouses, and scalable cloud-based data platforms Deep expertise with AWS and Snowflake, including warehouse sizing, clustering, partitioning, and performance optimization Experience developing data roadmaps, architecture standards, and long-term data strategies Strong understanding of data ingestion patterns, data integration frameworks, and modern data engineering practices Desired Skills &amp; Experience Experience with AI-enabled data architectures and emerging AI technologies Knowledge of RAG (Retrieval-Augmented Generation), Vector Databases, MCP, and Large Language Models (LLMs) Experience building data products and supporting advanced analytics initiatives Financial services, banking, or regulated industry experience What You Will Be Doing Design and implement enterprise data architectures leveraging AWS and Snowflake Define data platform strategy, roadmaps, and best practices in partnership with business and technology leaders Architect scalable data ingestion, storage, governance, and analytics solutions Evaluate and incorporate emerging AI technologies and data products into the organization's long-term vision Applicants must be currently authorized to work in the US on a full-time basis now and in the future</t>
         </is>
       </c>
     </row>
@@ -3777,17 +3782,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer - Python/SQL/PowerBi/Security Analytics</t>
+          <t>Data Engineer / Charlotte / Hybrid</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, 30009, United States</t>
+          <t>Charlotte, NC, 28202, United States</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3797,7 +3802,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3812,7 +3817,7 @@
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-security-analytics/888444</t>
+          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/data-engineer-charlotte-hybrid/861817</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -3820,22 +3825,22 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-08-04T16:52:57+00:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>ad181cacc5375145c150</t>
+          <t>c4ff54db51fe9b4cb6c0</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Job Description A leading organization within a highly regulated cloud environment is seeking a Cybersecurity Data Engineer to support security analytics, continuous monitoring, and automation initiatives across enterprise and cloud platforms. This role is ideal for someone who enjoys working at the intersection of cybersecurity, data engineering, and analytics. You'll leverage security telemetry, vulnerability data, and operational metrics to create meaningful insights, automate reporting processes, and improve overall security visibility. While the environment operates under regulatory requirements, the primary focus is on security data analysis, dashboard development, monitoring, and automation. You will collaborate with security, engineering, and infrastructure teams to build scalable reporting solutions, develop security metrics, and enhance the organization's ability to identify trends, risks, and opportunities for improvement. Location: Alpharetta, GA (Hybrid, 1 day onsite per week) Contract: 6 Months with potential extension and conversion opportunity Compensation: $40-$60/hour Required Skills &amp; Experience 3+ years of experience in cybersecurity, security analytics, security operations, or a related field Strong Python development and automation experience Advanced SQL skills with experience querying and analyzing large datasets Experience building dashboards and reports using Power BI or similar BI platforms Experience working with security logs, alerts, telemetry, vulnerability data, and incident response information Experience with Microsoft Defender or similar security monitoring solutions Familiarity with Microsoft Azure and cloud security concepts Understanding of security operations, threat monitoring, vulnerability management, and incident response Experience with ETL processes, reporting workflows, and data analytics Strong analytical, troubleshooting, and communication skills Desired Skills &amp; Experience Experience working in a Blue Team or Security Operations Center (SOC) environment Experience developing security analytics and reporting solutions Familiarity with FedRAMP, NIST, or similar regulatory frameworks Experience automating security monitoring or reporting processes using Python or PowerShell Relevant cybersecurity certifications What You Will Be Doing Daily Responsibilities: 100% Hands On Analyze security data from logs, vulnerability scans, monitoring platforms, and incident response activities Design, develop, and maintain Power BI dashboards and reporting solutions Build automation tools and reporting processes using Python Write and optimize SQL queries to support investigations, metrics, and reporting needs Monitor security events and telemetry to identify trends, anomalies, and potential threats Support security operations through incident analysis and continuous monitoring activities Develop and track security KPIs and operational metrics Partner with security, engineering, and infrastructure teams to improve se</t>
+          <t>Outstanding long-term contract opportunity! A well-known Financial Services Company is looking for a Data Engineer in Charlotte, NC (Hybrid). Work with the brightest minds at one of the largest financial institutions in the world. This is long-term contract opportunity that includes a competitive benefit package! Our client has been around for over 150 years and is continuously innovating in today's digital age. If you want to work for a company that is not only a household name, but also truly cares about satisfying customers' financial needs and helping people succeed financially, apply today. Contract Duration: 12 Months Required Skills &amp; Experience 7+ years of Data engineering experience 7+ years of MS SQL server experience 7+ years of Teradata experience 7+ years of SDLC (System Development Life Cycle) experience 5+ years of experience in Teradata database technology and products such as TASM, Unity, Data mover and Query Grid 5+ years of ETL (Extract, Transform, Load) development experience using Ab Initio 5+ years of Autosys experience 5+ years of scripting and automation experience 4+ years of experience with Enterprise Risk Data What You Will Be Doing Provide technology design, develop and support Risk and Regulatory platform capabilities, functions and processes. Understand business requirements with respects to data and reporting needs. Analyze source data and perform data gap analysis, source to target mappings, and data integration design. Design and implement highly distributed, scalable processes - Data Enrichments using Ab Initio, SQL, Strong data enrichment &amp; delivery techniques using various technology stack: Jenkins, Artifactory, Git, Autosys, DTS, NDM, and PCF. Evaluate solutions, review system architecture, design and tools to achieve project objectives including usability, performance, reliability, and monitoring, control, and security requirements. Assist all technology partners/developers to use the agreed technology/tools and interfaces to ensure smooth integration, security &amp; reliability across DEV, SIT, UAT and Production. Performance tuning and designing of high-performance applications involving huge data processing.</t>
         </is>
       </c>
     </row>
@@ -3847,27 +3852,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer, Python/SQL/PowerBi - Georgia</t>
+          <t>Data Engineer/GCP/Bigquery/Dearborn, MI Local</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, 30009, United States</t>
+          <t>Dearborn, Michigan, 48126, United States</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3882,7 +3887,7 @@
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-georgia/887207</t>
+          <t>https://motionrecruitment.com/tech-jobs/dearborn/direct-hire/data-engineer-gcp-bigquery-dearborn-mi-local/882054</t>
         </is>
       </c>
       <c r="J50" t="b">
@@ -3890,22 +3895,22 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-10T18:09:10+00:00</t>
+          <t>2026-07-30T00:04:01+00:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>ee4d1750d211c7261738</t>
+          <t>54d0fb23c39271735fd6</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Job Description An industry-leading organization is hiring a Cybersecurity Data Engineer to help transform security and vulnerability data into actionable insights for security and engineering teams. This is a highly data-focused security position centered around collecting, processing, analyzing, and reporting on data generated from vulnerability scans and security tools. In this role, you will use Python and SQL to work with security data, build and maintain data pipelines, and transform raw scan data into clean, usable datasets. You will also develop reporting and dashboards using Power BI, Microsoft Fabric, or similar data visualization tools . The ideal candidate has a strong background in data engineering, cybersecurity, or a combination of both. Candidates with experience as a Data Engineer working with security data, Cybersecurity Engineer with strong Python and SQL skills, or Security Analyst who has moved into data and automation are encouraged to apply. Required Skills &amp; Experience Strong proficiency in Python Strong proficiency in SQL Experience working with data pipelines, ETL, databases, or data warehousing Experience working with Power BI, Microsoft Fabric, or similar business intelligence/data visualization platforms Experience working with security, vulnerability, compliance, or cybersecurity-related data Experience analyzing data from vulnerability scans, security tools, assessments, or similar sources Strong data analysis and problem-solving skills Experience working with large datasets Experience with JSON, XML, and Excel Bachelor's degree 3–5+ years of relevant professional experience Desired Skills &amp; Experience Experience working in a cybersecurity, information security, or security engineering environment Experience with vulnerability management or security scanning tools Experience automating security or data processes with Python Experience building security dashboards and reporting in Power BI Experience with Microsoft Azure or cloud security Experience with Microsoft Defender or similar security platforms Experience working with security logs, alerts, vulnerability data, or other security telemetry Familiarity with FedRAMP, NIST, or other security/compliance frameworks Experience with PowerShell Experience supporting security metrics, continuous monitoring, or security posture reporting What You Will Be Doing Daily Responsibilities Collect, process, and analyze data from vulnerability scans, security tools, assessments, and other security sources Build and maintain data pipelines and ETL processes for security-related data Use Python to automate data processing, analysis, reporting, and security workflows Use SQL to query databases, manipulate data, and develop reporting datasets Transform raw scan and security data into clean, usable datasets Build and maintain Power BI and Microsoft Fabric dashboards and reports Develop KPIs and metrics to help security teams measure and track their security posture Analyze large secu</t>
+          <t>Our client is seeking an Analytics Migration Engineer to join their team on a full-time basis. In this role, you will lead the migration and modernization of analytical code, data pipelines, and statistical models from legacy on-premise environments to Bitquery in modern cloud platforms (GCP), ensuring analytical continuity as outputs, data, and AI/ML models are validated across environments. *This role is hybrid 3 days a week in Dearborn, MI* You will work across data engineering, analytics, and data science teams to maintain business-critical reporting and modeling while enabling a scalable, cloud-based analytics ecosystem. This role blends migration execution, validation, and optimization, giving you the chance to help shape a modern, future-ready analytics environment. Required Skills &amp; Experience Bachelor's Degree in a quantitative or technical field (Computer Science, Data Science, Statistics, Mathematics, Engineering, or related) Experience with analytical programming languages such as SAS 9.4, SAS Viya, Python, and SQL Experience with cloud data platforms (GCP, AWS, or Azure) or supporting on-prem to cloud migrations Experience with Bigquery Experience validating data outputs, dashboards, and statistical or machine learning models Strong understanding of data structures, ETL processes, and analytical workflows Experience troubleshooting data discrepancies and performing root cause analysis Ability to work across cross-functional teams, including data engineering, analytics, and business stakeholders Strong attention to detail and commitment to data accuracy and quality Desired Skills &amp; Experience Experience migrating SAS-based analytical environments to cloud platforms Experience validating and deploying machine learning models in cloud environments (e.g., Vertex AI) Familiarity with automated testing frameworks and data pipeline orchestration tools (e.g., Airflow, Cloud Composer) Experience optimizing analytical code and queries for performance and scalability in the cloud Experience supporting large-scale analytics or CRM data ecosystems Strong documentation and process design skills to support repeatable migration frameworks Ability to translate technical findings into clear insights for non-technical stakeholders Experience in large enterprise or highly regulated data environments What You Will Be Doing Migrate legacy analytical code (SAS, SQL, Python) and data pipelines from on-prem environments to GCP, refactoring workflows for modern cloud architecture and best practices Validate and reconcile outputs between legacy and cloud environments to ensure consistency and accuracy across data, reporting, and models Perform regression testing and quality assurance across datasets, dashboards, and statistical/ML models to confirm functional parity post-migration Support migration and re-platforming of AI/ML and statistical models, troubleshooting discrepancies in data, code logic, and performance Partner with data engineering, analytics, and</t>
         </is>
       </c>
     </row>
@@ -3917,27 +3922,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Data Architect | Richardson | AWS</t>
+          <t>Data Quality Tester / ETL / SQL / Chicago</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richardson, Texas, 75080, United States</t>
+          <t>Chicago, Illinois, 60603, United States</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3952,7 +3957,7 @@
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/richardson/direct-hire/data-architect-richardson-aws/884037</t>
+          <t>https://motionrecruitment.com/tech-jobs/chicago/contract/data-quality-tester-etl-sql-chicago/888265</t>
         </is>
       </c>
       <c r="J51" t="b">
@@ -3960,22 +3965,22 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-20T15:21:06+00:00</t>
+          <t>2026-09-23T18:46:37+00:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>a3f3fd8a2c38f7e08d8d</t>
+          <t>947d7f87986456a2fec1</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>We are seeking a Senior Data Architect to help drive the next generation of enterprise data capabilities within a rapidly growing, newly centralized data organization. This role will play a key part in designing and implementing modern data architectures, data products, and strategic roadmaps that support enterprise-wide analytics, reporting, and AI initiatives. In this highly visible position, you will partner directly with business leaders, engineering teams, and data stakeholders to define data strategy, architect scalable solutions, and establish best practices across a modern AWS and Snowflake ecosystem. This is an opportunity to influence the future-state data platform from the ground up within a highly collaborative and strategic environment. Required Skills &amp; Experience Strong experience designing enterprise Data Architectures, Data Warehouses, and scalable cloud-based data platforms Deep expertise with AWS and Snowflake, including warehouse sizing, clustering, partitioning, and performance optimization Experience developing data roadmaps, architecture standards, and long-term data strategies Strong understanding of data ingestion patterns, data integration frameworks, and modern data engineering practices Desired Skills &amp; Experience Experience with AI-enabled data architectures and emerging AI technologies Knowledge of RAG (Retrieval-Augmented Generation), Vector Databases, MCP, and Large Language Models (LLMs) Experience building data products and supporting advanced analytics initiatives Financial services, banking, or regulated industry experience What You Will Be Doing Design and implement enterprise data architectures leveraging AWS and Snowflake Define data platform strategy, roadmaps, and best practices in partnership with business and technology leaders Architect scalable data ingestion, storage, governance, and analytics solutions Evaluate and incorporate emerging AI technologies and data products into the organization's long-term vision Applicants must be currently authorized to work in the US on a full-time basis now and in the future</t>
+          <t>A leading organization is seeking a Data Quality Assurance Engineer to join its growing Data &amp; Analytics team in a hybrid work environment. This full-time opportunity offers the chance to work with modern data warehousing technologies, cloud data platforms, ETL processes, Master Data Management solutions, and business intelligence tools that support critical enterprise initiatives. This role is ideal for someone who enjoys solving complex data challenges and ensuring information accuracy across large-scale systems. The successful candidate will play a key role in establishing and expanding enterprise data quality standards while partnering closely with analytics, architecture, engineering, and business teams. This is an opportunity to make a measurable impact, gain visibility across multiple departments, and influence the future direction of data quality practices. Required Skills &amp; Experience • Strong hands-on experience with ETL testing and data validation • Advanced SQL skills for data analysis, reconciliation, and verification • Experience working with dimensional data models and data warehouses • Ability to execute data migration and data integrity testing initiatives • Experience creating test plans, test cases, and regression testing strategies • Strong root cause analysis and troubleshooting skills • Experience working within Agile delivery environments • Excellent communication and stakeholder management skills Desired Skills &amp; Experience • Experience with Amazon Redshift or other cloud-based data warehouses • Exposure to Master Data Management (MDM) platforms • Experience validating BI dashboards and enterprise reporting solutions • Knowledge of Tableau, Power BI, Hex, or similar analytics platforms • Experience with Python, PowerShell, JavaScript, C#, or similar scripting languages • Experience with SSIS packages or related ETL technologies • Background in data quality frameworks and automation initiatives What You Will Be Doing • Validate data movement between source and target systems • Execute ETL, regression, migration, and performance testing activities • Perform data reconciliation and integrity checks across enterprise platforms • Develop and maintain testing documentation and test strategies • Partner with engineering teams to identify and resolve data issues • Support analytics teams through report and dashboard validation • Help establish best practices for data quality and testing governance Tech Breakdown • 40% SQL &amp; Data Validation • 25% ETL Testing &amp; Data Integration • 20% Data Warehousing &amp; Cloud Platforms • 15% Analytics &amp; Reporting Tools Daily Responsibilities • 70% Hands On Testing &amp; Validation • 10% Test Planning &amp; Documentation • 20% Team Collaboration &amp; Stakeholder Engagement The Offer • Bonus eligible You will receive the following benefits: • Medical, Dental, and Vision Insurance • Vacation Time • 401(k) Program • Paid Holidays • Professional Development Opportunities • Stock Options (where applicable) Applicants</t>
         </is>
       </c>
     </row>
@@ -3987,17 +3992,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Data Engineer / Charlotte / Hybrid</t>
+          <t>Data Scientist / Fully Remote / Work Life Balance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28202, United States</t>
+          <t>Detroit, Michigan, 48226, United States</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4007,7 +4012,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4022,7 +4027,7 @@
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/data-engineer-charlotte-hybrid/861817</t>
+          <t>https://motionrecruitment.com/tech-jobs/detroit/contract/data-scientist-fully-remote-work-life-balance/887341</t>
         </is>
       </c>
       <c r="J52" t="b">
@@ -4030,22 +4035,22 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-04T16:52:57+00:00</t>
+          <t>2026-09-11T18:11:05+00:00</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>c4ff54db51fe9b4cb6c0</t>
+          <t>af0f816b04e17bba2a23</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Outstanding long-term contract opportunity! A well-known Financial Services Company is looking for a Data Engineer in Charlotte, NC (Hybrid). Work with the brightest minds at one of the largest financial institutions in the world. This is long-term contract opportunity that includes a competitive benefit package! Our client has been around for over 150 years and is continuously innovating in today's digital age. If you want to work for a company that is not only a household name, but also truly cares about satisfying customers' financial needs and helping people succeed financially, apply today. Contract Duration: 12 Months Required Skills &amp; Experience 7+ years of Data engineering experience 7+ years of MS SQL server experience 7+ years of Teradata experience 7+ years of SDLC (System Development Life Cycle) experience 5+ years of experience in Teradata database technology and products such as TASM, Unity, Data mover and Query Grid 5+ years of ETL (Extract, Transform, Load) development experience using Ab Initio 5+ years of Autosys experience 5+ years of scripting and automation experience 4+ years of experience with Enterprise Risk Data What You Will Be Doing Provide technology design, develop and support Risk and Regulatory platform capabilities, functions and processes. Understand business requirements with respects to data and reporting needs. Analyze source data and perform data gap analysis, source to target mappings, and data integration design. Design and implement highly distributed, scalable processes - Data Enrichments using Ab Initio, SQL, Strong data enrichment &amp; delivery techniques using various technology stack: Jenkins, Artifactory, Git, Autosys, DTS, NDM, and PCF. Evaluate solutions, review system architecture, design and tools to achieve project objectives including usability, performance, reliability, and monitoring, control, and security requirements. Assist all technology partners/developers to use the agreed technology/tools and interfaces to ensure smooth integration, security &amp; reliability across DEV, SIT, UAT and Production. Performance tuning and designing of high-performance applications involving huge data processing.</t>
+          <t>A rapidly growing analytics and technology consulting organization is seeking a Data Scientist to join its team. This full-time opportunity offers the chance to work with modern analytics technologies including Python, SQL, Databricks, Tableau, Power BI, and machine learning platforms while helping enterprise clients solve complex business challenges through data. Candidates can expect a highly collaborative environment where analytics, engineering, and business strategy intersect. What makes this opportunity especially exciting is the variety of projects and industries you'll support. Rather than being limited to a single product or business unit, you'll tackle forecasting, customer analytics, optimization, experimentation, and predictive modeling initiatives for organizations making critical decisions around customers, products, and market strategy. This role is ideal for someone who enjoys both deep technical problem solving and partnering with stakeholders to drive measurable business outcomes. Required Skills &amp; Experience 2+ years of professional Data Science or Advanced Analytics experience Strong Python development skills Advanced SQL experience Experience building predictive models and machine learning solutions Experience with forecasting, regression, classification, or segmentation Databricks experience Tableau and/or Power BI experience Git or GitLab experience Strong communication and stakeholder management skills Bachelor's degree in a quantitative discipline or equivalent experience Desired Skills &amp; Experience Optimization modeling experience A/B testing and experimentation design MLflow or MLOps exposure SAS or R experience Data governance and data quality expertise Experience within consulting environments What You Will Be Doing Tech Breakdown 40% Python &amp; Machine Learning 30% SQL &amp; Data Engineering Collaboration 20% Visualization &amp; Reporting 10% MLOps &amp; Model Deployment Daily Responsibilities 80% Hands On 5% Management Duties 15% Team Collaboration The Offer Competitive hourly rate You will receive the following benefits: Medical, Dental, and Vision Insurance Career Development Opportunities Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
         </is>
       </c>
     </row>
@@ -4057,17 +4062,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Data Engineer/GCP/Bigquery/Dearborn, MI Local</t>
+          <t>Lead Data Platform Engineer – Robotics Systems - Boston</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dearborn, Michigan, 48126, United States</t>
+          <t>Boston, MA, 02116, United States</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4077,7 +4082,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4092,7 +4097,7 @@
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dearborn/direct-hire/data-engineer-gcp-bigquery-dearborn-mi-local/882054</t>
+          <t>https://motionrecruitment.com/tech-jobs/boston/direct-hire/lead-data-platform-engineer-robotics-systems-boston/883681</t>
         </is>
       </c>
       <c r="J53" t="b">
@@ -4105,17 +4110,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>54d0fb23c39271735fd6</t>
+          <t>7f60e69fe18cfd4636a3</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Our client is seeking an Analytics Migration Engineer to join their team on a full-time basis. In this role, you will lead the migration and modernization of analytical code, data pipelines, and statistical models from legacy on-premise environments to Bitquery in modern cloud platforms (GCP), ensuring analytical continuity as outputs, data, and AI/ML models are validated across environments. *This role is hybrid 3 days a week in Dearborn, MI* You will work across data engineering, analytics, and data science teams to maintain business-critical reporting and modeling while enabling a scalable, cloud-based analytics ecosystem. This role blends migration execution, validation, and optimization, giving you the chance to help shape a modern, future-ready analytics environment. Required Skills &amp; Experience Bachelor's Degree in a quantitative or technical field (Computer Science, Data Science, Statistics, Mathematics, Engineering, or related) Experience with analytical programming languages such as SAS 9.4, SAS Viya, Python, and SQL Experience with cloud data platforms (GCP, AWS, or Azure) or supporting on-prem to cloud migrations Experience with Bigquery Experience validating data outputs, dashboards, and statistical or machine learning models Strong understanding of data structures, ETL processes, and analytical workflows Experience troubleshooting data discrepancies and performing root cause analysis Ability to work across cross-functional teams, including data engineering, analytics, and business stakeholders Strong attention to detail and commitment to data accuracy and quality Desired Skills &amp; Experience Experience migrating SAS-based analytical environments to cloud platforms Experience validating and deploying machine learning models in cloud environments (e.g., Vertex AI) Familiarity with automated testing frameworks and data pipeline orchestration tools (e.g., Airflow, Cloud Composer) Experience optimizing analytical code and queries for performance and scalability in the cloud Experience supporting large-scale analytics or CRM data ecosystems Strong documentation and process design skills to support repeatable migration frameworks Ability to translate technical findings into clear insights for non-technical stakeholders Experience in large enterprise or highly regulated data environments What You Will Be Doing Migrate legacy analytical code (SAS, SQL, Python) and data pipelines from on-prem environments to GCP, refactoring workflows for modern cloud architecture and best practices Validate and reconcile outputs between legacy and cloud environments to ensure consistency and accuracy across data, reporting, and models Perform regression testing and quality assurance across datasets, dashboards, and statistical/ML models to confirm functional parity post-migration Support migration and re-platforming of AI/ML and statistical models, troubleshooting discrepancies in data, code logic, and performance Partner with data engineering, analytics, and</t>
+          <t>Job Description A cutting-edge automation company is hiring a Lead Data Platform Engineer to help power the next generation of intelligent warehouse and distribution center technologies. The organization develops advanced robotic solutions that automate storage, retrieval, sorting, and fulfillment operations for some of the largest supply chain and retail networks in the world. Through a combination of robotics, artificial intelligence, computer vision, and large-scale software systems, the company is transforming how products move through modern logistics environments. As a Lead Data Platform Engineer, you will focus on building the foundational data infrastructure that supports enterprise-scale robotic operations. Unlike a traditional data engineering role centered on reporting and analytics, this position is responsible for developing the platforms that enable operational intelligence, system optimization, fleet orchestration, and AI-driven decision-making across thousands of interconnected robotic assets. You will work closely with software engineers, controls engineers, robotics specialists, machine learning teams, and product leaders to architect highly available data systems capable of handling enormous volumes of operational data. The ideal candidate is passionate about distributed systems, platform engineering, and building reliable data services that serve both real-time and analytical workloads. This role offers the opportunity to shape technical strategy while remaining deeply involved in hands-on engineering. Required Skills &amp; Experience Strong experience building large-scale distributed data platforms Advanced proficiency with Python, Java, or Scala Deep knowledge of data architecture and systems design Experience with Kafka, Spark, Flink, or similar distributed processing technologies Experience with cloud-native architectures in AWS, Azure, or GCP Knowledge of infrastructure automation and containerized environments Experience supporting high-volume streaming data systems Strong SQL and database performance optimization skills Experience with CI/CD and software engineering best practices Understanding of event-driven architectures Desired Skills &amp; Experience 6+ years of Data Engineering or Platform Engineering experience Experience supporting robotics, manufacturing, industrial automation, or IoT environments Familiarity with machine learning infrastructure and feature engineering platforms Experience with Kubernetes and cloud-native services Knowledge of operational analytics and industrial telemetry systems Experience leading technical projects and mentoring engineers Bachelor's degree in Computer Science, Engineering, Information Systems, or related field Experience working in fast-growing technology organizations What You Will Be Doing Daily Responsibilities 100% Hands On Design and build scalable data platforms supporting robotic fleet operations Develop streaming architectures that process millions of operational events dail</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4132,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Data Quality Tester / ETL / SQL / Chicago</t>
+          <t>Lead Senior Technology and Data Engineer - Raleigh, Nc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, 60603, United States</t>
+          <t>Raleigh, North Carolina, 27639, United States</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4147,7 +4152,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4162,7 +4167,7 @@
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chicago/contract/data-quality-tester-etl-sql-chicago/888265</t>
+          <t>https://motionrecruitment.com/tech-jobs/raleigh/contract/lead-senior-technology-and-data-engineer-raleigh-nc/885751</t>
         </is>
       </c>
       <c r="J54" t="b">
@@ -4170,22 +4175,22 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-23T18:46:37+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>947d7f87986456a2fec1</t>
+          <t>a468a6ee8abaf78d93d2</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>A leading organization is seeking a Data Quality Assurance Engineer to join its growing Data &amp; Analytics team in a hybrid work environment. This full-time opportunity offers the chance to work with modern data warehousing technologies, cloud data platforms, ETL processes, Master Data Management solutions, and business intelligence tools that support critical enterprise initiatives. This role is ideal for someone who enjoys solving complex data challenges and ensuring information accuracy across large-scale systems. The successful candidate will play a key role in establishing and expanding enterprise data quality standards while partnering closely with analytics, architecture, engineering, and business teams. This is an opportunity to make a measurable impact, gain visibility across multiple departments, and influence the future direction of data quality practices. Required Skills &amp; Experience • Strong hands-on experience with ETL testing and data validation • Advanced SQL skills for data analysis, reconciliation, and verification • Experience working with dimensional data models and data warehouses • Ability to execute data migration and data integrity testing initiatives • Experience creating test plans, test cases, and regression testing strategies • Strong root cause analysis and troubleshooting skills • Experience working within Agile delivery environments • Excellent communication and stakeholder management skills Desired Skills &amp; Experience • Experience with Amazon Redshift or other cloud-based data warehouses • Exposure to Master Data Management (MDM) platforms • Experience validating BI dashboards and enterprise reporting solutions • Knowledge of Tableau, Power BI, Hex, or similar analytics platforms • Experience with Python, PowerShell, JavaScript, C#, or similar scripting languages • Experience with SSIS packages or related ETL technologies • Background in data quality frameworks and automation initiatives What You Will Be Doing • Validate data movement between source and target systems • Execute ETL, regression, migration, and performance testing activities • Perform data reconciliation and integrity checks across enterprise platforms • Develop and maintain testing documentation and test strategies • Partner with engineering teams to identify and resolve data issues • Support analytics teams through report and dashboard validation • Help establish best practices for data quality and testing governance Tech Breakdown • 40% SQL &amp; Data Validation • 25% ETL Testing &amp; Data Integration • 20% Data Warehousing &amp; Cloud Platforms • 15% Analytics &amp; Reporting Tools Daily Responsibilities • 70% Hands On Testing &amp; Validation • 10% Test Planning &amp; Documentation • 20% Team Collaboration &amp; Stakeholder Engagement The Offer • Bonus eligible You will receive the following benefits: • Medical, Dental, and Vision Insurance • Vacation Time • 401(k) Program • Paid Holidays • Professional Development Opportunities • Stock Options (where applicable) Applicants</t>
+          <t>Job Description An enterprise technology company is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Raleigh, North Carolina . This role is centered on strengthening Infrastructure as Code security across cloud environments and supporting secure software delivery practices at scale. The team is focused on building preventative controls, improving policy management, and increasing visibility into security issues before code and infrastructure reach production. The ideal candidate will enjoy working across security, DevOps, and engineering functions to develop practical solutions that improve risk management while supporting the speed and efficiency of modern development teams. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and training activities. Manage policy</t>
         </is>
       </c>
     </row>
@@ -4197,17 +4202,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Data Scientist / Fully Remote / Work Life Balance</t>
+          <t>Lead Technology and Data Engineer - Chandler, Az</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, Michigan, 48226, United States</t>
+          <t>Chandler, Arizona, 85244, United States</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4217,7 +4222,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4232,7 +4237,7 @@
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/detroit/contract/data-scientist-fully-remote-work-life-balance/887341</t>
+          <t>https://motionrecruitment.com/tech-jobs/chandler/contract/lead-technology-and-data-engineer-chandler-az/885745</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -4240,22 +4245,22 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-11T18:11:05+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>af0f816b04e17bba2a23</t>
+          <t>ff09e0a1045d952ba482</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A rapidly growing analytics and technology consulting organization is seeking a Data Scientist to join its team. This full-time opportunity offers the chance to work with modern analytics technologies including Python, SQL, Databricks, Tableau, Power BI, and machine learning platforms while helping enterprise clients solve complex business challenges through data. Candidates can expect a highly collaborative environment where analytics, engineering, and business strategy intersect. What makes this opportunity especially exciting is the variety of projects and industries you'll support. Rather than being limited to a single product or business unit, you'll tackle forecasting, customer analytics, optimization, experimentation, and predictive modeling initiatives for organizations making critical decisions around customers, products, and market strategy. This role is ideal for someone who enjoys both deep technical problem solving and partnering with stakeholders to drive measurable business outcomes. Required Skills &amp; Experience 2+ years of professional Data Science or Advanced Analytics experience Strong Python development skills Advanced SQL experience Experience building predictive models and machine learning solutions Experience with forecasting, regression, classification, or segmentation Databricks experience Tableau and/or Power BI experience Git or GitLab experience Strong communication and stakeholder management skills Bachelor's degree in a quantitative discipline or equivalent experience Desired Skills &amp; Experience Optimization modeling experience A/B testing and experimentation design MLflow or MLOps exposure SAS or R experience Data governance and data quality expertise Experience within consulting environments What You Will Be Doing Tech Breakdown 40% Python &amp; Machine Learning 30% SQL &amp; Data Engineering Collaboration 20% Visualization &amp; Reporting 10% MLOps &amp; Model Deployment Daily Responsibilities 80% Hands On 5% Management Duties 15% Team Collaboration The Offer Competitive hourly rate You will receive the following benefits: Medical, Dental, and Vision Insurance Career Development Opportunities Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
+          <t>Job Description A forward-thinking enterprise organization is looking to add a Technology and Data Engineer 5 to its hybrid team in Chandler, Arizona . This opportunity is ideal for an engineer who enjoys working at the intersection of cloud security, automation, and infrastructure governance. The team is focused on improving how security is integrated into cloud deployments by leveraging Infrastructure as Code controls, automated policy validation, and secure development practices. In this role, you will contribute to initiatives designed to strengthen cloud environments, improve security coverage across deployment pipelines, and provide engineers with practical tools and processes that support secure infrastructure delivery. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and tra</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4272,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lead Data Platform Engineer – Robotics Systems - Boston</t>
+          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, 02116, United States</t>
+          <t>City of Industry, California, 91732, United States</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4287,7 +4292,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4302,7 +4307,7 @@
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/boston/direct-hire/lead-data-platform-engineer-robotics-systems-boston/883681</t>
+          <t>https://motionrecruitment.com/tech-jobs/city-of-industry/direct-hire/mid-senior-data-engineer-sql-python-dbt-and-snowflake/885666</t>
         </is>
       </c>
       <c r="J56" t="b">
@@ -4310,22 +4315,22 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-30T00:04:01+00:00</t>
+          <t>2026-08-20T21:14:14+00:00</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>7f60e69fe18cfd4636a3</t>
+          <t>4b469a327ab71e782f37</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Job Description A cutting-edge automation company is hiring a Lead Data Platform Engineer to help power the next generation of intelligent warehouse and distribution center technologies. The organization develops advanced robotic solutions that automate storage, retrieval, sorting, and fulfillment operations for some of the largest supply chain and retail networks in the world. Through a combination of robotics, artificial intelligence, computer vision, and large-scale software systems, the company is transforming how products move through modern logistics environments. As a Lead Data Platform Engineer, you will focus on building the foundational data infrastructure that supports enterprise-scale robotic operations. Unlike a traditional data engineering role centered on reporting and analytics, this position is responsible for developing the platforms that enable operational intelligence, system optimization, fleet orchestration, and AI-driven decision-making across thousands of interconnected robotic assets. You will work closely with software engineers, controls engineers, robotics specialists, machine learning teams, and product leaders to architect highly available data systems capable of handling enormous volumes of operational data. The ideal candidate is passionate about distributed systems, platform engineering, and building reliable data services that serve both real-time and analytical workloads. This role offers the opportunity to shape technical strategy while remaining deeply involved in hands-on engineering. Required Skills &amp; Experience Strong experience building large-scale distributed data platforms Advanced proficiency with Python, Java, or Scala Deep knowledge of data architecture and systems design Experience with Kafka, Spark, Flink, or similar distributed processing technologies Experience with cloud-native architectures in AWS, Azure, or GCP Knowledge of infrastructure automation and containerized environments Experience supporting high-volume streaming data systems Strong SQL and database performance optimization skills Experience with CI/CD and software engineering best practices Understanding of event-driven architectures Desired Skills &amp; Experience 6+ years of Data Engineering or Platform Engineering experience Experience supporting robotics, manufacturing, industrial automation, or IoT environments Familiarity with machine learning infrastructure and feature engineering platforms Experience with Kubernetes and cloud-native services Knowledge of operational analytics and industrial telemetry systems Experience leading technical projects and mentoring engineers Bachelor's degree in Computer Science, Engineering, Information Systems, or related field Experience working in fast-growing technology organizations What You Will Be Doing Daily Responsibilities 100% Hands On Design and build scalable data platforms supporting robotic fleet operations Develop streaming architectures that process millions of operational events dail</t>
+          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake City of Industry, CA | Full-Time Our client is a growing organization seeking a Data Engineer to join its expanding technology team. This is a hands-on role focused on building and maintaining production data solutions, supporting critical data operations, and improving the reliability and scalability of the overall data environment. The ideal candidate is a strong hands-on engineer who enjoys working with production systems, troubleshooting unfamiliar problems, and taking ownership of data pipelines and operational processes. What You’ll Be Doing Design, build, and maintain production-grade data pipelines and transformations Develop and maintain reliable data models supporting reporting, analytics, and business applications Work extensively with SQL, Python, dbt, and cloud-based data technologies Own day-to-day production data operations, including orchestration, scheduled refreshes, monitoring, and alerting Troubleshoot pipeline failures, data quality issues, and other production incidents Support database administration activities, including user access, roles, permissions, performance, and maintenance Manage data deployments and contribute to CI/CD and infrastructure automation Investigate unfamiliar or poorly documented data sources and determine how systems, schemas, and integrations function Build data solutions supporting reporting, billing, customer, and operational use cases Integrate and work with data from internal, third-party, and legacy systems Partner with engineering, product, operations, and business teams to translate requirements into technical solutions Participate in code reviews and contribute to engineering standards and best practices Improve documentation, knowledge sharing, and overall platform reliability Required Qualifications Strong SQL skills, including complex joins, window functions, aggregations, NULL handling, and understanding of data grain Hands-on Python development experience, including maintaining code running in production Professional experience building or supporting production data pipelines Experience with a modern data transformation framework; dbt strongly preferred Strong understanding of dimensional data modeling, including: Fact and dimension tables Data grain Conformed dimensions Slowly changing dimensions Experience supporting production environments, including deployments, monitoring, environment management, troubleshooting, and incident response Strong experience with Git, pull requests, code reviews, and CI/CD Ability to independently investigate and debug unfamiliar technical problems Strong communication skills and ability to work across technical and business teams Comfortable contributing within an established architecture and engineering environment Preferred Qualifications Experience with Snowflake Experience with Microsoft Azure Familiarity with Azure Data Factory (ADF), ADLS Gen2, and/or Key Vault Terraform or other Infrastructu</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4342,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lead Senior Technology and Data Engineer - Raleigh, Nc</t>
+          <t>SAP Snowflake Analytics Engineer / Hybrid / Scottsdale, AZ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, North Carolina, 27639, United States</t>
+          <t>Scottsdale, AZ, 85251, United States</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4357,7 +4362,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4372,7 +4377,7 @@
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/raleigh/contract/lead-senior-technology-and-data-engineer-raleigh-nc/885751</t>
+          <t>https://motionrecruitment.com/tech-jobs/scottsdale/contract/sap-snowflake-analytics-engineer-hybrid-scottsdale-az/886105</t>
         </is>
       </c>
       <c r="J57" t="b">
@@ -4380,22 +4385,22 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-09-16T23:20:04+00:00</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>a468a6ee8abaf78d93d2</t>
+          <t>ad6fe94f94bd642a688c</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Job Description An enterprise technology company is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Raleigh, North Carolina . This role is centered on strengthening Infrastructure as Code security across cloud environments and supporting secure software delivery practices at scale. The team is focused on building preventative controls, improving policy management, and increasing visibility into security issues before code and infrastructure reach production. The ideal candidate will enjoy working across security, DevOps, and engineering functions to develop practical solutions that improve risk management while supporting the speed and efficiency of modern development teams. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and training activities. Manage policy</t>
+          <t>Our client, a clean energy developer and operator across the US, is actively hiring an Analytics Engineer to join their team in Scottsdale, AZ! This will be a hybrid role and will require 3 days a week onsite. In this role, you will be responsible for building and owning the semantic layer and data mart strategy that connects the raw operational and financial data to the business teams who depend on it. A significant portion of your work will focus on modeling data replicated from SAP, our financial and other operational platforms into Snowflake building clean, tested, and well-documented dbt models that serve Hex dashboards and Snowflake semantic models queryable by LLMs. Contract Duration: 12 Months Required Skills &amp; Experience Bachelor's degree in Computer Science, Engineering, Mathematics, or related field 3+ years in an Analytics Engineering, Data Engineering, or BI Engineering role Working knowledge of Snowflake SQL and Python proficiency What You Will Be Doing Design and maintain the staging and intermediate dbt model layers for financial, operational, and asset-management data replicated from SAP (ERP) into Snowflake Build and maintain Snowflake semantic models (definitions that allow LLMs and BI tools to query business metrics without ad-hoc SQL Create documentation, data dictionaries, and training materials that enable analysts to use data marts and Hex workbooks independently</t>
         </is>
       </c>
     </row>
@@ -4407,27 +4412,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lead Technology and Data Engineer - Chandler, Az</t>
+          <t>Senior Analytics Engineer – Robotics Intelligence - Somerville</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chandler, Arizona, 85244, United States</t>
+          <t>Somerville, MA, 02144, United States</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4442,7 +4447,7 @@
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chandler/contract/lead-technology-and-data-engineer-chandler-az/885745</t>
+          <t>https://motionrecruitment.com/tech-jobs/somerville/direct-hire/senior-analytics-engineer-robotics-intelligence-somerville/883684</t>
         </is>
       </c>
       <c r="J58" t="b">
@@ -4450,22 +4455,22 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-07-30T00:04:01+00:00</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>ff09e0a1045d952ba482</t>
+          <t>dac7b1e5eaec687e0b24</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Job Description A forward-thinking enterprise organization is looking to add a Technology and Data Engineer 5 to its hybrid team in Chandler, Arizona . This opportunity is ideal for an engineer who enjoys working at the intersection of cloud security, automation, and infrastructure governance. The team is focused on improving how security is integrated into cloud deployments by leveraging Infrastructure as Code controls, automated policy validation, and secure development practices. In this role, you will contribute to initiatives designed to strengthen cloud environments, improve security coverage across deployment pipelines, and provide engineers with practical tools and processes that support secure infrastructure delivery. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and tra</t>
+          <t>Job Description An innovative robotics company is hiring a Senior Analytics Engineer to help transform operational and robotic system data into actionable insights that drive product performance, customer success, and fleet optimization. The organization develops advanced robotic picking and automation solutions used in high-volume fulfillment and logistics environments, where efficiency, accuracy, and system intelligence are critical to success. As a Senior Analytics Engineer, you will sit at the intersection of data engineering, analytics, and business strategy. Unlike traditional data engineering positions focused on infrastructure or platform development, this role is responsible for building trusted datasets, defining operational metrics, and delivering insight frameworks that help teams understand how robotic systems perform in real-world environments. You will work closely with product managers, robotics engineers, implementation teams, customer success teams, and executive leadership to create a unified view of operational performance across customer deployments. The ideal candidate enjoys turning complex data into meaningful business outcomes and is passionate about helping organizations make smarter decisions through analytics. This role offers the unique opportunity to influence how robotics performance is measured, understood, and improved while building scalable data solutions that directly impact customers and product development efforts. Required Skills &amp; Experience Strong SQL expertise Professional experience with Python Experience building analytics data models and reporting datasets Knowledge of dimensional modeling and data warehousing concepts Experience with modern BI and visualization tools Experience transforming raw operational data into business metrics Strong understanding of ETL and data transformation workflows Experience working with cloud data platforms Familiarity with data governance and data quality practices Excellent communication and stakeholder management skills Desired Skills &amp; Experience 5+ years of Analytics Engineering, Data Analytics, or Data Engineering experience Experience supporting operational or industrial technology environments Familiarity with robotics, automation, logistics, or supply chain operations Experience creating executive dashboards and KPI frameworks Knowledge of dbt and modern analytics engineering practices Experience working directly with business stakeholders Bachelor's degree in Computer Science, Analytics, Engineering, Mathematics, or related field Experience in a startup or fast-growth technology company What You Will Be Doing Daily Responsibilities 100% Hands On Build analytics-ready datasets supporting robotics performance measurement Develop KPI frameworks that measure productivity, utilization, accuracy, and operational efficiency Create dashboards and reporting solutions used by leadership, customers, and engineering teams Partner with robotics engineers to understand syste</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4482,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>City of Industry, California, 91732, United States</t>
+          <t>Chicago, VA, 60606, United States</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4497,7 +4502,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4512,7 +4517,7 @@
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/city-of-industry/direct-hire/mid-senior-data-engineer-sql-python-dbt-and-snowflake/885666</t>
+          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer/885522</t>
         </is>
       </c>
       <c r="J59" t="b">
@@ -4520,22 +4525,22 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-20T21:14:14+00:00</t>
+          <t>2026-08-19T18:08:19+00:00</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>4b469a327ab71e782f37</t>
+          <t>968938ae19236c36071b</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake City of Industry, CA | Full-Time Our client is a growing organization seeking a Data Engineer to join its expanding technology team. This is a hands-on role focused on building and maintaining production data solutions, supporting critical data operations, and improving the reliability and scalability of the overall data environment. The ideal candidate is a strong hands-on engineer who enjoys working with production systems, troubleshooting unfamiliar problems, and taking ownership of data pipelines and operational processes. What You’ll Be Doing Design, build, and maintain production-grade data pipelines and transformations Develop and maintain reliable data models supporting reporting, analytics, and business applications Work extensively with SQL, Python, dbt, and cloud-based data technologies Own day-to-day production data operations, including orchestration, scheduled refreshes, monitoring, and alerting Troubleshoot pipeline failures, data quality issues, and other production incidents Support database administration activities, including user access, roles, permissions, performance, and maintenance Manage data deployments and contribute to CI/CD and infrastructure automation Investigate unfamiliar or poorly documented data sources and determine how systems, schemas, and integrations function Build data solutions supporting reporting, billing, customer, and operational use cases Integrate and work with data from internal, third-party, and legacy systems Partner with engineering, product, operations, and business teams to translate requirements into technical solutions Participate in code reviews and contribute to engineering standards and best practices Improve documentation, knowledge sharing, and overall platform reliability Required Qualifications Strong SQL skills, including complex joins, window functions, aggregations, NULL handling, and understanding of data grain Hands-on Python development experience, including maintaining code running in production Professional experience building or supporting production data pipelines Experience with a modern data transformation framework; dbt strongly preferred Strong understanding of dimensional data modeling, including: Fact and dimension tables Data grain Conformed dimensions Slowly changing dimensions Experience supporting production environments, including deployments, monitoring, environment management, troubleshooting, and incident response Strong experience with Git, pull requests, code reviews, and CI/CD Ability to independently investigate and debug unfamiliar technical problems Strong communication skills and ability to work across technical and business teams Comfortable contributing within an established architecture and engineering environment Preferred Qualifications Experience with Snowflake Experience with Microsoft Azure Familiarity with Azure Data Factory (ADF), ADLS Gen2, and/or Key Vault Terraform or other Infrastructu</t>
+          <t>Join a growing, data-driven organization that is investing heavily in its modern cloud data platform and analytics capabilities. We are seeking a Senior Databricks Data Engineer to design, build, and optimize enterprise-scale data solutions using Databricks, Azure, PySpark, Delta Lake, SQL, and modern cloud technologies. This is a full-time opportunity for an engineer who is passionate about building scalable data products and shaping the future of data architecture. You'll have the opportunity to drive architecture decisions, influence engineering standards, and help build a best-in-class Lakehouse platform from the ground up. We're looking for someone who thrives in complex environments, enjoys solving large-scale data challenges, and wants to work alongside talented engineers who value innovation and continuous learning. If you're seeking a role that offers technical ownership, career growth, exposure to cutting-edge technologies, and strong work-life balance, this is an opportunity worth exploring. Required Skills &amp; Experience 7+ years of experience in Data Engineering, Data Warehousing, or Data Platform development 3+ years of hands-on Databricks experience in a production environment Strong expertise with PySpark and Apache Spark Advanced SQL development and query optimization skills Experience building ETL/ELT pipelines at enterprise scale Experience working within Azure, AWS, or GCP cloud environments Excellent communication skills and ability to partner with technical and business stakeholders Desired Skills &amp; Experience Azure Data Factory, Azure Synapse, or Microsoft Fabric experience Experience with Kafka or event-driven architectures Databricks Workflows, Airflow, or similar orchestration tools Infrastructure as Code using Terraform or ARM templates Experience supporting AI, Machine Learning, or advanced analytics initiatives Prior experience mentoring engineers or leading technical initiatives What You Will Be Doing Tech Breakdown 50% Databricks / PySpark / Spark 25% Azure Data Platform Services 25% SQL &amp; Data Modeling Daily Responsibilities 70% Hands On 30% Team Collaboration The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -4547,17 +4552,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAP Snowflake Analytics Engineer / Hybrid / Scottsdale, AZ</t>
+          <t>Senior Data Engineer / Databricks / AI / Chicagoland Area</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, 85251, United States</t>
+          <t>Oak Brook, Illinois, 60523, United States</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4567,7 +4572,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4582,7 +4587,7 @@
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/scottsdale/contract/sap-snowflake-analytics-engineer-hybrid-scottsdale-az/886105</t>
+          <t>https://motionrecruitment.com/tech-jobs/oak-brook/contract/senior-data-engineer-databricks-ai-chicagoland-area/885362</t>
         </is>
       </c>
       <c r="J60" t="b">
@@ -4590,22 +4595,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-16T23:20:04+00:00</t>
+          <t>2026-08-18T18:12:31+00:00</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>ad6fe94f94bd642a688c</t>
+          <t>0fd058a73f75ae299c7d</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Our client, a clean energy developer and operator across the US, is actively hiring an Analytics Engineer to join their team in Scottsdale, AZ! This will be a hybrid role and will require 3 days a week onsite. In this role, you will be responsible for building and owning the semantic layer and data mart strategy that connects the raw operational and financial data to the business teams who depend on it. A significant portion of your work will focus on modeling data replicated from SAP, our financial and other operational platforms into Snowflake building clean, tested, and well-documented dbt models that serve Hex dashboards and Snowflake semantic models queryable by LLMs. Contract Duration: 12 Months Required Skills &amp; Experience Bachelor's degree in Computer Science, Engineering, Mathematics, or related field 3+ years in an Analytics Engineering, Data Engineering, or BI Engineering role Working knowledge of Snowflake SQL and Python proficiency What You Will Be Doing Design and maintain the staging and intermediate dbt model layers for financial, operational, and asset-management data replicated from SAP (ERP) into Snowflake Build and maintain Snowflake semantic models (definitions that allow LLMs and BI tools to query business metrics without ad-hoc SQL Create documentation, data dictionaries, and training materials that enable analysts to use data marts and Hex workbooks independently</t>
+          <t>A rapidly growing enterprise organization in the automotive technology and distribution space is seeking a Data Engineer to join its team in Oak Brook, Illinois. This full-time role offers the opportunity to build scalable cloud-based data solutions that support analytics, operational reporting, machine learning, and AI initiatives. The ideal candidate will have experience with Python, SQL, modern data platforms, and enterprise-scale ETL development. What makes this opportunity stand out is the chance to help modernize a complex data ecosystem that spans cloud platforms, APIs, operational applications, and legacy databases. The organization is making substantial investments in data-driven decision making and artificial intelligence, creating an environment where engineers can influence architecture, work with cutting-edge technologies, and make a measurable business impact. This is an ideal role for professionals who enjoy solving large-scale data challenges while collaborating with cross-functional stakeholders. Required Skills &amp; Experience 4+ years of Data Engineering experience Strong SQL development expertise Python or Scala programming experience Experience building ETL/ELT pipelines Hands-on experience with Snowflake, Databricks, Redshift, or BigQuery Knowledge of data warehousing concepts and dimensional modeling Experience with orchestration platforms such as Airflow, Prefect, or Dagster Understanding of CI/CD practices and version control Experience integrating data from APIs and enterprise applications Desired Skills &amp; Experience AWS cloud experience Experience with Kafka or Kinesis Streaming data architecture AI/ML data pipeline exposure Supply chain, ERP, or CRM integration experience Data observability and monitoring tools Enterprise-scale data modernization projects Master's degree in Computer Science, Engineering, or related field What You Will Be Doing Tech Breakdown 40% Python Development 30% SQL &amp; Data Engineering 20% Cloud Data Platforms (Snowflake/Databricks/AWS) 10% Data Orchestration &amp; Automation Daily Responsibilities 75% Hands On Engineering 15% Team Collaboration 10% Strategic Architecture &amp; Design The Offer Competitive Salary You will receive the following benefits: Medical, Dental, and Vision Insurance Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
         </is>
       </c>
     </row>
@@ -4617,12 +4622,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer – Robotics Intelligence - Somerville</t>
+          <t>Senior Data Engineer / Databricks / End-to-End Ownerhp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Somerville, MA, 02144, United States</t>
+          <t>Chicago, Illinois, 60603, United States</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4632,12 +4637,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>DIRECT HIRE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4652,7 +4657,7 @@
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/somerville/direct-hire/senior-analytics-engineer-robotics-intelligence-somerville/883684</t>
+          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer-databricks-end-to-end-ownerhp/876474</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -4660,22 +4665,22 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-30T00:04:01+00:00</t>
+          <t>2026-09-01T18:18:15+00:00</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>dac7b1e5eaec687e0b24</t>
+          <t>804829dfb347ca52e5ac</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Job Description An innovative robotics company is hiring a Senior Analytics Engineer to help transform operational and robotic system data into actionable insights that drive product performance, customer success, and fleet optimization. The organization develops advanced robotic picking and automation solutions used in high-volume fulfillment and logistics environments, where efficiency, accuracy, and system intelligence are critical to success. As a Senior Analytics Engineer, you will sit at the intersection of data engineering, analytics, and business strategy. Unlike traditional data engineering positions focused on infrastructure or platform development, this role is responsible for building trusted datasets, defining operational metrics, and delivering insight frameworks that help teams understand how robotic systems perform in real-world environments. You will work closely with product managers, robotics engineers, implementation teams, customer success teams, and executive leadership to create a unified view of operational performance across customer deployments. The ideal candidate enjoys turning complex data into meaningful business outcomes and is passionate about helping organizations make smarter decisions through analytics. This role offers the unique opportunity to influence how robotics performance is measured, understood, and improved while building scalable data solutions that directly impact customers and product development efforts. Required Skills &amp; Experience Strong SQL expertise Professional experience with Python Experience building analytics data models and reporting datasets Knowledge of dimensional modeling and data warehousing concepts Experience with modern BI and visualization tools Experience transforming raw operational data into business metrics Strong understanding of ETL and data transformation workflows Experience working with cloud data platforms Familiarity with data governance and data quality practices Excellent communication and stakeholder management skills Desired Skills &amp; Experience 5+ years of Analytics Engineering, Data Analytics, or Data Engineering experience Experience supporting operational or industrial technology environments Familiarity with robotics, automation, logistics, or supply chain operations Experience creating executive dashboards and KPI frameworks Knowledge of dbt and modern analytics engineering practices Experience working directly with business stakeholders Bachelor's degree in Computer Science, Analytics, Engineering, Mathematics, or related field Experience in a startup or fast-growth technology company What You Will Be Doing Daily Responsibilities 100% Hands On Build analytics-ready datasets supporting robotics performance measurement Develop KPI frameworks that measure productivity, utilization, accuracy, and operational efficiency Create dashboards and reporting solutions used by leadership, customers, and engineering teams Partner with robotics engineers to understand syste</t>
+          <t>A well-established, global professional services organization is expanding its Data &amp; AI engineering team and hiring a Data Engineer to support a large-scale cloud data platform initiative. This role is based in Chicago and focuses on building modern data pipelines using Azure Databricks, Python, SQL, and Spark in a production environment. This is a hands-on engineering opportunity for someone who enjoys owning data pipelines end-to-end and wants exposure to enterprise-scale data challenges. You’ll work alongside experienced engineers and business partners to turn raw data into trusted, analytics-ready datasets that power reporting, insights, and AI use cases. This team is early in its Databricks journey, which means your work will matter immediately. You’ll help shape how pipelines are built, how data is governed, and how the platform evolves over time. It’s ideal for a strong mid-level engineer who wants to deepen their Databricks expertise while working on a highly visible, long-term transformation initiative. Required Skills &amp; Experience 6+ years of hands-on data engineering experience Strong experience building pipelines using Databricks Proficiency in Python and SQL for production data processing Working knowledge of Apache Spark and Delta Lake Experience with cloud data storage (ADLS, object storage) Experience with data modeling and schema design Familiarity with Git, CI/CD concepts, and basic testing/monitoring Desired Skills &amp; Experience Azure Databricks in an enterprise environment Experience with Unity Catalog and Databricks Jobs/Workflows Exposure to streaming or CDC pipelines Experience supporting BI or AI use cases Familiarity with Infrastructure as Code What You Will Be Doing Tech Breakdown 70% Azure Databricks / Spark / Delta Lake 20% Python &amp; SQL development 10% CI/CD, testing, and optimization Daily Responsibilities 80% Hands-On Engineering 10% Collaboration with BI, AI, and product teams 10% Documentation, reviews, and platform improvements The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -4687,17 +4692,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer | DBT Specialist</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, VA, 60606, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4707,7 +4712,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4722,7 +4727,7 @@
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer/885522</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-specialist/886415</t>
         </is>
       </c>
       <c r="J62" t="b">
@@ -4730,22 +4735,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-19T18:08:19+00:00</t>
+          <t>2026-08-30T23:11:06+00:00</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>968938ae19236c36071b</t>
+          <t>0104668f9fd195e113f5</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Join a growing, data-driven organization that is investing heavily in its modern cloud data platform and analytics capabilities. We are seeking a Senior Databricks Data Engineer to design, build, and optimize enterprise-scale data solutions using Databricks, Azure, PySpark, Delta Lake, SQL, and modern cloud technologies. This is a full-time opportunity for an engineer who is passionate about building scalable data products and shaping the future of data architecture. You'll have the opportunity to drive architecture decisions, influence engineering standards, and help build a best-in-class Lakehouse platform from the ground up. We're looking for someone who thrives in complex environments, enjoys solving large-scale data challenges, and wants to work alongside talented engineers who value innovation and continuous learning. If you're seeking a role that offers technical ownership, career growth, exposure to cutting-edge technologies, and strong work-life balance, this is an opportunity worth exploring. Required Skills &amp; Experience 7+ years of experience in Data Engineering, Data Warehousing, or Data Platform development 3+ years of hands-on Databricks experience in a production environment Strong expertise with PySpark and Apache Spark Advanced SQL development and query optimization skills Experience building ETL/ELT pipelines at enterprise scale Experience working within Azure, AWS, or GCP cloud environments Excellent communication skills and ability to partner with technical and business stakeholders Desired Skills &amp; Experience Azure Data Factory, Azure Synapse, or Microsoft Fabric experience Experience with Kafka or event-driven architectures Databricks Workflows, Airflow, or similar orchestration tools Infrastructure as Code using Terraform or ARM templates Experience supporting AI, Machine Learning, or advanced analytics initiatives Prior experience mentoring engineers or leading technical initiatives What You Will Be Doing Tech Breakdown 50% Databricks / PySpark / Spark 25% Azure Data Platform Services 25% SQL &amp; Data Modeling Daily Responsibilities 70% Hands On 30% Team Collaboration The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description We are searching for a seasoned Data Engineer with a specialty in the workings of DBT. In this position you will be joining a small team (3-4 people) and helping across a variety of data projects (storage, ingestion, data cleaning, transformation) specifically focused on the building, rebuilding and owning of internal DBT project (models, tests, macros, docs, exposures). This person will be setting the standard for data testing &amp; modelling. Experience in a cloud-based environment (Snowflake Ideally) is also required. This is an opportunity to join a smaller team and own projects from start to finish without huge oversight or micromanagement. This is a fully remote position within the US with a team across three separate time zones. Required Skills &amp; Experience 7+ Years of Data Engineering 3+ years with DBT Cloud platforms Snowflake Databricks Python Desired Skills &amp; Experience BI/Data visualization PowerBI, Fabric, tableau What You Will Be Doing Daily Responsibilities 80% 20% Team Collaboration The Offer You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -4757,27 +4762,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Databricks / AI / Chicagoland Area</t>
+          <t>Senior Data Engineer | Snowflake | DBT | FiveTran | Addison, TX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oak Brook, Illinois, 60523, United States</t>
+          <t>Addison, Texas, 75001, United States</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>DIRECT HIRE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4792,7 +4797,7 @@
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/oak-brook/contract/senior-data-engineer-databricks-ai-chicagoland-area/885362</t>
+          <t>https://motionrecruitment.com/tech-jobs/addison/direct-hire/senior-data-engineer-snowflake-dbt-fivetran-addison-tx/884977</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -4800,22 +4805,22 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-18T18:12:31+00:00</t>
+          <t>2026-08-30T23:11:06+00:00</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0fd058a73f75ae299c7d</t>
+          <t>4e0366afed1d5979acd2</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A rapidly growing enterprise organization in the automotive technology and distribution space is seeking a Data Engineer to join its team in Oak Brook, Illinois. This full-time role offers the opportunity to build scalable cloud-based data solutions that support analytics, operational reporting, machine learning, and AI initiatives. The ideal candidate will have experience with Python, SQL, modern data platforms, and enterprise-scale ETL development. What makes this opportunity stand out is the chance to help modernize a complex data ecosystem that spans cloud platforms, APIs, operational applications, and legacy databases. The organization is making substantial investments in data-driven decision making and artificial intelligence, creating an environment where engineers can influence architecture, work with cutting-edge technologies, and make a measurable business impact. This is an ideal role for professionals who enjoy solving large-scale data challenges while collaborating with cross-functional stakeholders. Required Skills &amp; Experience 4+ years of Data Engineering experience Strong SQL development expertise Python or Scala programming experience Experience building ETL/ELT pipelines Hands-on experience with Snowflake, Databricks, Redshift, or BigQuery Knowledge of data warehousing concepts and dimensional modeling Experience with orchestration platforms such as Airflow, Prefect, or Dagster Understanding of CI/CD practices and version control Experience integrating data from APIs and enterprise applications Desired Skills &amp; Experience AWS cloud experience Experience with Kafka or Kinesis Streaming data architecture AI/ML data pipeline exposure Supply chain, ERP, or CRM integration experience Data observability and monitoring tools Enterprise-scale data modernization projects Master's degree in Computer Science, Engineering, or related field What You Will Be Doing Tech Breakdown 40% Python Development 30% SQL &amp; Data Engineering 20% Cloud Data Platforms (Snowflake/Databricks/AWS) 10% Data Orchestration &amp; Automation Daily Responsibilities 75% Hands On Engineering 15% Team Collaboration 10% Strategic Architecture &amp; Design The Offer Competitive Salary You will receive the following benefits: Medical, Dental, and Vision Insurance Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
+          <t>We are hiring for a Senior Data Engineer to join a manufacturing &amp; services organization to help build &amp; own a new data warehouse. This person will be working with a consulting org &amp; internal leadership to establish a data warehouse, build ingestions from data sources, and surface clean data for internal reporting &amp; future AI use. This is a senior level position Ideal for someone who has independently designed, built &amp; maintained data pipelines and is comfortable working relatively independently. To be considered applicants must have experience with the core tech stack of Snowflake, DBT, and Fivetran This is a hybrid position (3x/week) in Addison, TX Applicants must be currently authorized to work in the US on a full-time basis now and in the future. Required Skills &amp; Experience 7+ years of experience in data engineering Snowflake DBT Fivetran Python SQL Desired Skills &amp; Experience Bachelor’s degree in computer science, data analytics, or similar What You Will Be Doing Daily Responsibilities 80% Hands On 20% Team Collaboration The Offer Eligible for Annual Salary Bonus You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) &amp; Match</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4832,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Databricks / End-to-End Ownerhp</t>
+          <t>Senior Data Engineer – Robotics - Wilmington, Ma</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, 60603, United States</t>
+          <t>Wilmington, MA, 01887, United States</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4842,12 +4847,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DIRECT HIRE</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4862,7 +4867,7 @@
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer-databricks-end-to-end-ownerhp/876474</t>
+          <t>https://motionrecruitment.com/tech-jobs/wilmington/direct-hire/senior-data-engineer-robotics-wilmington-ma/883680</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -4870,22 +4875,22 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-01T18:18:15+00:00</t>
+          <t>2026-07-30T00:04:01+00:00</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>804829dfb347ca52e5ac</t>
+          <t>aa9de16fbfec7e07b3ed</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>A well-established, global professional services organization is expanding its Data &amp; AI engineering team and hiring a Data Engineer to support a large-scale cloud data platform initiative. This role is based in Chicago and focuses on building modern data pipelines using Azure Databricks, Python, SQL, and Spark in a production environment. This is a hands-on engineering opportunity for someone who enjoys owning data pipelines end-to-end and wants exposure to enterprise-scale data challenges. You’ll work alongside experienced engineers and business partners to turn raw data into trusted, analytics-ready datasets that power reporting, insights, and AI use cases. This team is early in its Databricks journey, which means your work will matter immediately. You’ll help shape how pipelines are built, how data is governed, and how the platform evolves over time. It’s ideal for a strong mid-level engineer who wants to deepen their Databricks expertise while working on a highly visible, long-term transformation initiative. Required Skills &amp; Experience 6+ years of hands-on data engineering experience Strong experience building pipelines using Databricks Proficiency in Python and SQL for production data processing Working knowledge of Apache Spark and Delta Lake Experience with cloud data storage (ADLS, object storage) Experience with data modeling and schema design Familiarity with Git, CI/CD concepts, and basic testing/monitoring Desired Skills &amp; Experience Azure Databricks in an enterprise environment Experience with Unity Catalog and Databricks Jobs/Workflows Exposure to streaming or CDC pipelines Experience supporting BI or AI use cases Familiarity with Infrastructure as Code What You Will Be Doing Tech Breakdown 70% Azure Databricks / Spark / Delta Lake 20% Python &amp; SQL development 10% CI/CD, testing, and optimization Daily Responsibilities 80% Hands-On Engineering 10% Collaboration with BI, AI, and product teams 10% Documentation, reviews, and platform improvements The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description A rapidly growing robotics company is hiring a Senior Data Engineer to help build the data infrastructure that powers next-generation autonomous warehouse automation solutions. The organization develops autonomous mobile robotic systems used in large-scale fulfillment and logistics environments, enabling customers to optimize inventory movement, order fulfillment, and operational efficiency through advanced robotics and intelligent software. As a Senior Data Engineer, you will play a critical role in designing and scaling the data platforms that support robotic operations, fleet management, analytics, machine learning initiatives, and customer-facing reporting. You will work closely with robotics engineers, software developers, product managers, data scientists, and operations teams to transform massive volumes of telemetry, operational events, sensor data, and system logs into reliable and actionable datasets. In this role, you will build highly scalable data pipelines that collect information from thousands of connected robotic devices operating in real-world environments. You will be responsible for ensuring data quality, reliability, accessibility, and performance across the organization's analytics ecosystem. The ideal candidate enjoys solving complex engineering challenges involving high-volume streaming data, distributed systems, cloud platforms, and real-time operational insights. This position offers the opportunity to work at the intersection of robotics, data engineering, and industrial automation while helping drive the future of warehouse technology. Required Skills &amp; Experience Strong proficiency in Python and SQL Experience building and maintaining large-scale data pipelines Experience with cloud-based data platforms (AWS preferred) Knowledge of ETL and ELT frameworks Experience with data warehousing technologies Experience processing large volumes of event-driven or streaming data Knowledge of distributed data systems and scalable architectures Experience with Spark, Kafka, Airflow, or similar technologies Strong understanding of data modeling and database design Software engineering best practices including testing and version control Desired Skills &amp; Experience 5+ years of Data Engineering experience Experience working with IoT, robotics, sensor, or telemetry datasets Experience supporting machine learning or analytics teams Familiarity with real-time data processing architectures Knowledge of warehouse automation, logistics, or supply chain technologies Experience with Databricks or modern cloud analytics platforms Bachelor's degree in Computer Science, Data Engineering, Engineering, or related field Experience working in a fast-paced startup or high-growth environment What You Will Be Doing Daily Responsibilities 100% Hands On Design and develop scalable pipelines that ingest telemetry data from robotic fleets Build data solutions supporting analytics, reporting, and machine learning initiatives Create and main</t>
         </is>
       </c>
     </row>
@@ -4897,17 +4902,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | DBT Specialist</t>
+          <t>Senior Data Governance Engineer – Robotics Data Management - Waltham</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>Waltham, MA, 02452, United States</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4917,7 +4922,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4932,7 +4937,7 @@
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-specialist/886415</t>
+          <t>https://motionrecruitment.com/tech-jobs/waltham/direct-hire/senior-data-governance-engineer-robotics-data-management-waltham/883699</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -4940,22 +4945,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-30T23:11:06+00:00</t>
+          <t>2026-07-30T00:04:01+00:00</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>0104668f9fd195e113f5</t>
+          <t>acd6ea39dec7cb7c67de</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Job Description We are searching for a seasoned Data Engineer with a specialty in the workings of DBT. In this position you will be joining a small team (3-4 people) and helping across a variety of data projects (storage, ingestion, data cleaning, transformation) specifically focused on the building, rebuilding and owning of internal DBT project (models, tests, macros, docs, exposures). This person will be setting the standard for data testing &amp; modelling. Experience in a cloud-based environment (Snowflake Ideally) is also required. This is an opportunity to join a smaller team and own projects from start to finish without huge oversight or micromanagement. This is a fully remote position within the US with a team across three separate time zones. Required Skills &amp; Experience 7+ Years of Data Engineering 3+ years with DBT Cloud platforms Snowflake Databricks Python Desired Skills &amp; Experience BI/Data visualization PowerBI, Fabric, tableau What You Will Be Doing Daily Responsibilities 80% 20% Team Collaboration The Offer You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description A global robotics and automation company is seeking a Senior Data Governance Engineer to help establish the policies, standards, and technical frameworks that ensure data remains discoverable, trustworthy, secure, and usable across the organization. The company develops AI-driven automation solutions for warehouse and fulfillment operations, generating large volumes of operational, engineering, customer, and system data that support critical business and product decisions. As a Senior Data Governance Engineer, you will be responsible for creating the foundation that enables teams to effectively manage and utilize data throughout its lifecycle. Unlike traditional data engineering positions focused on pipelines, analytics, machine learning infrastructure, integrations, quality monitoring, or operational reporting, this role focuses on data ownership, metadata management, lineage, cataloging, governance processes, and enterprise data standards. You will partner with engineering, analytics, robotics, product, security, and leadership teams to improve data transparency and consistency across the business. The ideal candidate enjoys bringing structure to complex environments, creating scalable governance frameworks, and helping organizations maximize the value of their data assets. This role offers the opportunity to influence how data is managed across a rapidly growing robotics company while working alongside teams building cutting-edge automation technology. Required Skills &amp; Experience Strong proficiency in SQL and Python Experience implementing data governance programs or frameworks Knowledge of metadata management and data catalog solutions Experience documenting data lineage and data ownership models Understanding of data management best practices Experience with cloud-based data platforms and warehouses Knowledge of data privacy and security principles Familiarity with data stewardship and governance processes Strong analytical and organizational skills Excellent communication and stakeholder management abilities Desired Skills &amp; Experience 5+ years of Data Engineering, Data Governance, Data Management, or Analytics experience Experience supporting industrial technology, robotics, manufacturing, or logistics organizations Familiarity with modern data catalog and governance platforms Experience developing enterprise data standards and policies Knowledge of regulatory and compliance requirements related to data management Experience working across multiple technical and business teams Bachelor's degree in Computer Science, Information Systems, Engineering, or related field Experience in a fast-growing technology company What You Will Be Doing Daily Responsibilities 100% Hands On Build and maintain processes that improve data ownership and accountability across the organization Develop and document data lineage for critical business and operational datasets Implement governance standards that improve data consistency and usability</t>
         </is>
       </c>
     </row>
@@ -4967,27 +4972,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Snowflake | DBT | FiveTran | Addison, TX</t>
+          <t>Senior Data Operations Engineer – Autonomous Robotics - Waltham, Ma</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Addison, Texas, 75001, United States</t>
+          <t>waltham, MA, 02452, United States</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DIRECT HIRE</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5002,7 +5007,7 @@
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/addison/direct-hire/senior-data-engineer-snowflake-dbt-fivetran-addison-tx/884977</t>
+          <t>https://motionrecruitment.com/tech-jobs/waltham/direct-hire/senior-data-operations-engineer-autonomous-robotics-waltham-ma/883690</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -5010,22 +5015,22 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-30T23:11:06+00:00</t>
+          <t>2026-07-30T00:04:01+00:00</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>4e0366afed1d5979acd2</t>
+          <t>7f1f67aaf2ba15353b39</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>We are hiring for a Senior Data Engineer to join a manufacturing &amp; services organization to help build &amp; own a new data warehouse. This person will be working with a consulting org &amp; internal leadership to establish a data warehouse, build ingestions from data sources, and surface clean data for internal reporting &amp; future AI use. This is a senior level position Ideal for someone who has independently designed, built &amp; maintained data pipelines and is comfortable working relatively independently. To be considered applicants must have experience with the core tech stack of Snowflake, DBT, and Fivetran This is a hybrid position (3x/week) in Addison, TX Applicants must be currently authorized to work in the US on a full-time basis now and in the future. Required Skills &amp; Experience 7+ years of experience in data engineering Snowflake DBT Fivetran Python SQL Desired Skills &amp; Experience Bachelor’s degree in computer science, data analytics, or similar What You Will Be Doing Daily Responsibilities 80% Hands On 20% Team Collaboration The Offer Eligible for Annual Salary Bonus You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) &amp; Match</t>
+          <t>Job Description A leading robotics company is hiring a Senior Data Operations Engineer to support the operational performance and continuous improvement of large-scale autonomous robotic deployments. The organization develops intelligent robotic systems that operate inside fast-paced warehouse and logistics environments, generating enormous volumes of performance, workflow, and operational data every day. As a Senior Data Operations Engineer, you will be responsible for turning operational data into actionable workflows that improve fleet performance, deployment success, customer outcomes, and business efficiency. Unlike traditional data engineering roles focused on pipelines, platforms, analytics, machine learning, integration, or data quality, this position sits closer to operations and focuses on using data to optimize the day-to-day performance of robotic systems deployed in the field. You will work closely with robotics operations teams, deployment engineers, customer success managers, software engineers, and business stakeholders to identify operational trends, performance bottlenecks, and opportunities for continuous improvement. The ideal candidate enjoys solving operational challenges with data and building scalable systems that help organizations make faster and smarter decisions. This role is perfect for someone who likes the combination of data engineering, operational excellence, process optimization, and real-world problem solving within a highly automated technology environment. Required Skills &amp; Experience Strong proficiency in SQL and Python Experience supporting operational reporting and business processes Experience building automated data workflows Understanding of ETL and data orchestration concepts Experience working with cloud-based data platforms Knowledge of workflow automation and process optimization Experience analyzing operational or production datasets Ability to identify trends, anomalies, and business improvement opportunities Strong communication and stakeholder management skills Experience translating business requirements into scalable data solutions Desired Skills &amp; Experience 5+ years of Data Engineering, Data Operations, Business Intelligence, or Analytics experience Experience supporting robotics, logistics, warehousing, manufacturing, or industrial operations Familiarity with operational KPIs and performance management frameworks Experience with workflow automation platforms Knowledge of supply chain or fulfillment operations Experience building self-service reporting solutions Bachelor's degree in Computer Science, Engineering, Information Systems, Analytics, or related field Experience in a high-growth technology company What You Will Be Doing Daily Responsibilities 100% Hands On Build data solutions that support robotic deployment and operational teams Develop automated reporting workflows that improve visibility into fleet performance Analyze operational data to identify inefficiencies and improvement o</t>
         </is>
       </c>
     </row>
@@ -5037,12 +5042,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Robotics - Wilmington, Ma</t>
+          <t>Senior Data Quality Engineer – Robotics Operations - Boston</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wilmington, MA, 01887, United States</t>
+          <t>Boston, MA, 02116, United States</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5072,7 +5077,7 @@
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/wilmington/direct-hire/senior-data-engineer-robotics-wilmington-ma/883680</t>
+          <t>https://motionrecruitment.com/tech-jobs/boston/direct-hire/senior-data-quality-engineer-robotics-operations-boston/883686</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -5085,17 +5090,17 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>aa9de16fbfec7e07b3ed</t>
+          <t>b9c80033967b5b5eb0d1</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Job Description A rapidly growing robotics company is hiring a Senior Data Engineer to help build the data infrastructure that powers next-generation autonomous warehouse automation solutions. The organization develops autonomous mobile robotic systems used in large-scale fulfillment and logistics environments, enabling customers to optimize inventory movement, order fulfillment, and operational efficiency through advanced robotics and intelligent software. As a Senior Data Engineer, you will play a critical role in designing and scaling the data platforms that support robotic operations, fleet management, analytics, machine learning initiatives, and customer-facing reporting. You will work closely with robotics engineers, software developers, product managers, data scientists, and operations teams to transform massive volumes of telemetry, operational events, sensor data, and system logs into reliable and actionable datasets. In this role, you will build highly scalable data pipelines that collect information from thousands of connected robotic devices operating in real-world environments. You will be responsible for ensuring data quality, reliability, accessibility, and performance across the organization's analytics ecosystem. The ideal candidate enjoys solving complex engineering challenges involving high-volume streaming data, distributed systems, cloud platforms, and real-time operational insights. This position offers the opportunity to work at the intersection of robotics, data engineering, and industrial automation while helping drive the future of warehouse technology. Required Skills &amp; Experience Strong proficiency in Python and SQL Experience building and maintaining large-scale data pipelines Experience with cloud-based data platforms (AWS preferred) Knowledge of ETL and ELT frameworks Experience with data warehousing technologies Experience processing large volumes of event-driven or streaming data Knowledge of distributed data systems and scalable architectures Experience with Spark, Kafka, Airflow, or similar technologies Strong understanding of data modeling and database design Software engineering best practices including testing and version control Desired Skills &amp; Experience 5+ years of Data Engineering experience Experience working with IoT, robotics, sensor, or telemetry datasets Experience supporting machine learning or analytics teams Familiarity with real-time data processing architectures Knowledge of warehouse automation, logistics, or supply chain technologies Experience with Databricks or modern cloud analytics platforms Bachelor's degree in Computer Science, Data Engineering, Engineering, or related field Experience working in a fast-paced startup or high-growth environment What You Will Be Doing Daily Responsibilities 100% Hands On Design and develop scalable pipelines that ingest telemetry data from robotic fleets Build data solutions supporting analytics, reporting, and machine learning initiatives Create and main</t>
+          <t>Job Description An innovative robotics and automation company is hiring a Senior Data Quality Engineer to ensure the reliability, accuracy, and integrity of data generated across large-scale robotic fulfillment operations. The organization develops intelligent automation solutions that help customers improve warehouse productivity, order accuracy, and operational efficiency through advanced robotics and software platforms. As robotic deployments continue to grow, high-quality data has become critical to product development, operational decision-making, customer success, and system performance. As a Senior Data Quality Engineer, you will focus on ensuring that data produced by robotic systems is trustworthy, complete, and actionable. Unlike traditional data engineering roles that primarily concentrate on building pipelines or analytics platforms, this position centers on developing frameworks, processes, and tooling that continuously validate data quality throughout the organization's technology ecosystem. You will collaborate closely with software engineers, robotics teams, product managers, customer operations groups, and data professionals to identify data issues before they impact customers or business operations. This role requires a strong understanding of data flows, quality assurance methodologies, automation, and operational systems. The ideal candidate enjoys investigating anomalies, creating scalable validation systems, and driving continuous improvements across enterprise data environments. Required Skills &amp; Experience Strong proficiency in SQL and Python Experience developing data quality frameworks and validation processes Experience working with large-scale operational datasets Knowledge of ETL and data integration processes Experience with cloud-based data platforms Understanding of database design and data modeling principles Experience creating automated testing and monitoring solutions Strong analytical and troubleshooting skills Experience with data governance and data integrity best practices Excellent communication and cross-functional collaboration skills Desired Skills &amp; Experience 5+ years of Data Engineering, Data Quality, Analytics Engineering, or related experience Experience supporting robotics, manufacturing, logistics, or industrial systems Familiarity with telemetry, event, or operational data sources Experience with data observability tools Knowledge of warehouse automation technologies Experience with cloud-native analytics environments Bachelor's degree in Computer Science, Information Systems, Engineering, Mathematics, or related field Experience operating in a fast-paced technology environment What You Will Be Doing Daily Responsibilities 100% Hands On Design and implement automated data quality monitoring and validation systems Investigate anomalies and inconsistencies within robotic operational datasets Develop testing frameworks that validate data throughout ingestion and transformation processes Partner wit</t>
         </is>
       </c>
     </row>
@@ -5107,12 +5112,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Senior Data Governance Engineer – Robotics Data Management - Waltham</t>
+          <t>Senior Machine Learning Data Engineer - Cambridge</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Waltham, MA, 02452, United States</t>
+          <t>Cambridge, MA, 02140, United States</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5142,7 +5147,7 @@
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/waltham/direct-hire/senior-data-governance-engineer-robotics-data-management-waltham/883699</t>
+          <t>https://motionrecruitment.com/tech-jobs/cambridge/direct-hire/senior-machine-learning-data-engineer-cambridge/883687</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -5155,17 +5160,17 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>acd6ea39dec7cb7c67de</t>
+          <t>1fdd32f9c59214fdd83a</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Job Description A global robotics and automation company is seeking a Senior Data Governance Engineer to help establish the policies, standards, and technical frameworks that ensure data remains discoverable, trustworthy, secure, and usable across the organization. The company develops AI-driven automation solutions for warehouse and fulfillment operations, generating large volumes of operational, engineering, customer, and system data that support critical business and product decisions. As a Senior Data Governance Engineer, you will be responsible for creating the foundation that enables teams to effectively manage and utilize data throughout its lifecycle. Unlike traditional data engineering positions focused on pipelines, analytics, machine learning infrastructure, integrations, quality monitoring, or operational reporting, this role focuses on data ownership, metadata management, lineage, cataloging, governance processes, and enterprise data standards. You will partner with engineering, analytics, robotics, product, security, and leadership teams to improve data transparency and consistency across the business. The ideal candidate enjoys bringing structure to complex environments, creating scalable governance frameworks, and helping organizations maximize the value of their data assets. This role offers the opportunity to influence how data is managed across a rapidly growing robotics company while working alongside teams building cutting-edge automation technology. Required Skills &amp; Experience Strong proficiency in SQL and Python Experience implementing data governance programs or frameworks Knowledge of metadata management and data catalog solutions Experience documenting data lineage and data ownership models Understanding of data management best practices Experience with cloud-based data platforms and warehouses Knowledge of data privacy and security principles Familiarity with data stewardship and governance processes Strong analytical and organizational skills Excellent communication and stakeholder management abilities Desired Skills &amp; Experience 5+ years of Data Engineering, Data Governance, Data Management, or Analytics experience Experience supporting industrial technology, robotics, manufacturing, or logistics organizations Familiarity with modern data catalog and governance platforms Experience developing enterprise data standards and policies Knowledge of regulatory and compliance requirements related to data management Experience working across multiple technical and business teams Bachelor's degree in Computer Science, Information Systems, Engineering, or related field Experience in a fast-growing technology company What You Will Be Doing Daily Responsibilities 100% Hands On Build and maintain processes that improve data ownership and accountability across the organization Develop and document data lineage for critical business and operational datasets Implement governance standards that improve data consistency and usability</t>
+          <t>Job Description A fast-growing robotics company is seeking a Senior Machine Learning Data Engineer to help develop the data foundation that powers intelligent robotic systems operating in high-throughput logistics environments. The organization builds AI-driven automation solutions that leverage computer vision, machine learning, and robotic manipulation to solve complex real-world challenges involving package handling, object identification, and operational optimization. As a Senior Machine Learning Data Engineer, you will focus on the collection, preparation, management, and delivery of data used to train, evaluate, and improve machine learning models. Unlike traditional data engineering positions that concentrate on analytics, reporting, or platform infrastructure, this role is centered on enabling AI and computer vision teams to build more accurate and effective robotic systems. You will work closely with machine learning engineers, roboticists, software developers, and product teams to create scalable data pipelines capable of handling large volumes of image, video, sensor, and operational data. The ideal candidate enjoys solving challenges surrounding data labeling, feature generation, model training datasets, data versioning, and machine learning infrastructure. This role offers the opportunity to directly influence how AI systems learn and improve within a cutting-edge robotics environment. Required Skills &amp; Experience Strong proficiency with Python and SQL Experience building data pipelines for machine learning workloads Experience working with large-scale image, video, or sensor datasets Knowledge of data processing frameworks such as Spark or Ray Experience with cloud platforms such as AWS Understanding of data modeling and storage solutions for ML applications Experience building ETL workflows and automation solutions Familiarity with machine learning lifecycle concepts Experience with version control and software engineering best practices Strong problem-solving and analytical skills Desired Skills &amp; Experience 5+ years of Data Engineering or Machine Learning Infrastructure experience Experience supporting computer vision or AI-focused teams Robotics, automation, or industrial technology experience Familiarity with model training workflows and feature engineering Experience with annotation platforms and data labeling operations Knowledge of MLOps tools and practices Experience working with unstructured datasets Bachelor's degree in Computer Science, Data Engineering, Engineering, Mathematics, or a related field What You Will Be Doing Daily Responsibilities 100% Hands On Build and maintain machine learning data pipelines supporting robotics and AI initiatives Develop processes that prepare image, video, and sensor datasets for model training Partner with machine learning teams to improve the quality and accessibility of training data Design scalable storage and retrieval solutions for large unstructured datasets Create data validation</t>
         </is>
       </c>
     </row>
@@ -5177,27 +5182,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Senior Data Operations Engineer – Autonomous Robotics - Waltham, Ma</t>
+          <t>Senior Python Data Engineer / Architecture / ETL Pipelines / Hybrid in Smyrna</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>waltham, MA, 02452, United States</t>
+          <t>Marietta, Georgia, 30067, United States</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>DIRECT HIRE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5212,7 +5217,7 @@
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/waltham/direct-hire/senior-data-operations-engineer-autonomous-robotics-waltham-ma/883690</t>
+          <t>https://motionrecruitment.com/tech-jobs/marietta/direct-hire/senior-python-data-engineer-architecture-etl-pipelines-hybrid-in-smyrna/878315</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -5220,22 +5225,22 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-30T00:04:01+00:00</t>
+          <t>2026-08-04T13:37:21+00:00</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>7f1f67aaf2ba15353b39</t>
+          <t>e4f94c56e691df2a6089</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Job Description A leading robotics company is hiring a Senior Data Operations Engineer to support the operational performance and continuous improvement of large-scale autonomous robotic deployments. The organization develops intelligent robotic systems that operate inside fast-paced warehouse and logistics environments, generating enormous volumes of performance, workflow, and operational data every day. As a Senior Data Operations Engineer, you will be responsible for turning operational data into actionable workflows that improve fleet performance, deployment success, customer outcomes, and business efficiency. Unlike traditional data engineering roles focused on pipelines, platforms, analytics, machine learning, integration, or data quality, this position sits closer to operations and focuses on using data to optimize the day-to-day performance of robotic systems deployed in the field. You will work closely with robotics operations teams, deployment engineers, customer success managers, software engineers, and business stakeholders to identify operational trends, performance bottlenecks, and opportunities for continuous improvement. The ideal candidate enjoys solving operational challenges with data and building scalable systems that help organizations make faster and smarter decisions. This role is perfect for someone who likes the combination of data engineering, operational excellence, process optimization, and real-world problem solving within a highly automated technology environment. Required Skills &amp; Experience Strong proficiency in SQL and Python Experience supporting operational reporting and business processes Experience building automated data workflows Understanding of ETL and data orchestration concepts Experience working with cloud-based data platforms Knowledge of workflow automation and process optimization Experience analyzing operational or production datasets Ability to identify trends, anomalies, and business improvement opportunities Strong communication and stakeholder management skills Experience translating business requirements into scalable data solutions Desired Skills &amp; Experience 5+ years of Data Engineering, Data Operations, Business Intelligence, or Analytics experience Experience supporting robotics, logistics, warehousing, manufacturing, or industrial operations Familiarity with operational KPIs and performance management frameworks Experience with workflow automation platforms Knowledge of supply chain or fulfillment operations Experience building self-service reporting solutions Bachelor's degree in Computer Science, Engineering, Information Systems, Analytics, or related field Experience in a high-growth technology company What You Will Be Doing Daily Responsibilities 100% Hands On Build data solutions that support robotic deployment and operational teams Develop automated reporting workflows that improve visibility into fleet performance Analyze operational data to identify inefficiencies and improvement o</t>
+          <t>A client is looking to bring on a Staff Python Data Engineer to join their team. This team is based in Marietta, GA and in the 2 days week. For the first 3 months, you’ll be heavily on-site partnering with the CTO as this is his key product and they are still hands on. You’ll be joining a growing team working on a variety of different applications internally and externally for shipping out collectible products. You’ll be architecting new features, leading the development, joining a team of software developers and some in the infrastructure. You’ll be the sole owner of this analytics product that is used by real estate agents to view modeled data of transactions. You’d be working mostly in an individual capacity with support from others on the data teams. You’d be joining a high-level team to make a massive impact on the products and team that is scaling rapidly! This client is looking for someone who is extremely independent and seeks other confident individuals to make a significant impact on their services, new initiatives, and culture. They’re looking for someone with strong critical thinking and decision making skills who can hit the ground running. Required Skills &amp; Experience 8+ years of experience with Python 5+ years of experience with Postgres 5+ years of experience with Kafka, Kubernetes 5+ years of experience with data warehousing 4-year degree Desired Skills &amp; Experience Experience with real estate products What You Will Be Doing Tech Breakdown 10% Leadership 90% Development Daily Responsibilities 90% Hands-on development 10% Leadership The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance 401k matching Bonus Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -5247,27 +5252,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer – Robotics Operations - Boston</t>
+          <t>Senior Technology and Data Engineer - AWS/Python/Wiz - Charlotte, Nc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, 02116, United States</t>
+          <t>Charlotte, North Carolina, 28270, United States</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5282,7 +5287,7 @@
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/boston/direct-hire/senior-data-quality-engineer-robotics-operations-boston/883686</t>
+          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/senior-technology-and-data-engineer-aws-python-wiz-charlotte-nc/885741</t>
         </is>
       </c>
       <c r="J70" t="b">
@@ -5290,22 +5295,22 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-30T00:04:01+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>b9c80033967b5b5eb0d1</t>
+          <t>fd3fc8487a48b83c5587</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Job Description An innovative robotics and automation company is hiring a Senior Data Quality Engineer to ensure the reliability, accuracy, and integrity of data generated across large-scale robotic fulfillment operations. The organization develops intelligent automation solutions that help customers improve warehouse productivity, order accuracy, and operational efficiency through advanced robotics and software platforms. As robotic deployments continue to grow, high-quality data has become critical to product development, operational decision-making, customer success, and system performance. As a Senior Data Quality Engineer, you will focus on ensuring that data produced by robotic systems is trustworthy, complete, and actionable. Unlike traditional data engineering roles that primarily concentrate on building pipelines or analytics platforms, this position centers on developing frameworks, processes, and tooling that continuously validate data quality throughout the organization's technology ecosystem. You will collaborate closely with software engineers, robotics teams, product managers, customer operations groups, and data professionals to identify data issues before they impact customers or business operations. This role requires a strong understanding of data flows, quality assurance methodologies, automation, and operational systems. The ideal candidate enjoys investigating anomalies, creating scalable validation systems, and driving continuous improvements across enterprise data environments. Required Skills &amp; Experience Strong proficiency in SQL and Python Experience developing data quality frameworks and validation processes Experience working with large-scale operational datasets Knowledge of ETL and data integration processes Experience with cloud-based data platforms Understanding of database design and data modeling principles Experience creating automated testing and monitoring solutions Strong analytical and troubleshooting skills Experience with data governance and data integrity best practices Excellent communication and cross-functional collaboration skills Desired Skills &amp; Experience 5+ years of Data Engineering, Data Quality, Analytics Engineering, or related experience Experience supporting robotics, manufacturing, logistics, or industrial systems Familiarity with telemetry, event, or operational data sources Experience with data observability tools Knowledge of warehouse automation technologies Experience with cloud-native analytics environments Bachelor's degree in Computer Science, Information Systems, Engineering, Mathematics, or related field Experience operating in a fast-paced technology environment What You Will Be Doing Daily Responsibilities 100% Hands On Design and implement automated data quality monitoring and validation systems Investigate anomalies and inconsistencies within robotic operational datasets Develop testing frameworks that validate data throughout ingestion and transformation processes Partner wit</t>
+          <t>Job Description A large enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Charlotte, North Carolina . This role supports enterprise cloud security initiatives focused on Infrastructure as Code (IaC), CI/CD security integration, policy enforcement, and developer enablement. The selected professional will work closely with engineering, security, and platform teams to strengthen deployment security across cloud-native environments. This position offers the opportunity to influence security controls at scale while helping teams build, test, and deploy infrastructure in a secure and efficient manner. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Monitor pipeline health and troubleshoot failed scans. Validate severity, de-duplicate findings, suppress false positives, and route issues to appropriate teams. Tune IaC policies and manage staged policy enforcement. Integrate Wiz CLI into CI/CD pipelines and implement gating thresholds. Publish artifacts for traceability and optimize scan performance. Deploy and maintain Wiz DevOps extensions and Wiz Scanner integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins environments. Enable local scanning, pull request scanning, and IDE workflows. Partner with platform teams to embed security controls into standard deployment processes. Provide support sessions, remediation guidance, and developer enablement resources. Manage upgrades, policy refreshes, and tool reliability initiatives. Coordinate with vendor support teams and product resources. Maintain exception management processes and governance controls. Integrate workflows with ServiceNow for tracking and reporting. Create dashboards covering coverage, MTTR, block rates, exception aging, and audit evidence. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medica</t>
         </is>
       </c>
     </row>
@@ -5317,27 +5322,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Data Engineer - Cambridge</t>
+          <t>Senior Technology and Data Engineer - Irving, Tx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cambridge, MA, 02140, United States</t>
+          <t>Irving, Texas, 75059, United States</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5352,7 +5357,7 @@
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/cambridge/direct-hire/senior-machine-learning-data-engineer-cambridge/883687</t>
+          <t>https://motionrecruitment.com/tech-jobs/irving/contract/senior-technology-and-data-engineer-irving-tx/885743</t>
         </is>
       </c>
       <c r="J71" t="b">
@@ -5360,22 +5365,22 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-30T00:04:01+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1fdd32f9c59214fdd83a</t>
+          <t>e1a6ec1ce6f095d8053c</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Job Description A fast-growing robotics company is seeking a Senior Machine Learning Data Engineer to help develop the data foundation that powers intelligent robotic systems operating in high-throughput logistics environments. The organization builds AI-driven automation solutions that leverage computer vision, machine learning, and robotic manipulation to solve complex real-world challenges involving package handling, object identification, and operational optimization. As a Senior Machine Learning Data Engineer, you will focus on the collection, preparation, management, and delivery of data used to train, evaluate, and improve machine learning models. Unlike traditional data engineering positions that concentrate on analytics, reporting, or platform infrastructure, this role is centered on enabling AI and computer vision teams to build more accurate and effective robotic systems. You will work closely with machine learning engineers, roboticists, software developers, and product teams to create scalable data pipelines capable of handling large volumes of image, video, sensor, and operational data. The ideal candidate enjoys solving challenges surrounding data labeling, feature generation, model training datasets, data versioning, and machine learning infrastructure. This role offers the opportunity to directly influence how AI systems learn and improve within a cutting-edge robotics environment. Required Skills &amp; Experience Strong proficiency with Python and SQL Experience building data pipelines for machine learning workloads Experience working with large-scale image, video, or sensor datasets Knowledge of data processing frameworks such as Spark or Ray Experience with cloud platforms such as AWS Understanding of data modeling and storage solutions for ML applications Experience building ETL workflows and automation solutions Familiarity with machine learning lifecycle concepts Experience with version control and software engineering best practices Strong problem-solving and analytical skills Desired Skills &amp; Experience 5+ years of Data Engineering or Machine Learning Infrastructure experience Experience supporting computer vision or AI-focused teams Robotics, automation, or industrial technology experience Familiarity with model training workflows and feature engineering Experience with annotation platforms and data labeling operations Knowledge of MLOps tools and practices Experience working with unstructured datasets Bachelor's degree in Computer Science, Data Engineering, Engineering, Mathematics, or a related field What You Will Be Doing Daily Responsibilities 100% Hands On Build and maintain machine learning data pipelines supporting robotics and AI initiatives Develop processes that prepare image, video, and sensor datasets for model training Partner with machine learning teams to improve the quality and accessibility of training data Design scalable storage and retrieval solutions for large unstructured datasets Create data validation</t>
+          <t>Job Description A growing enterprise technology team is seeking a Technology and Data Engineer 5 for a hybrid position in Irving, TX . This role is focused on securing Infrastructure as Code deployments and helping engineering teams identify cloud security risks before they reach production. The ideal candidate will bring experience building policy-driven security controls, supporting CI/CD environments, and improving security visibility across modern cloud platforms. You will work with development, platform, and security teams to enhance automated scanning, strengthen governance processes, and support scalable cloud security practices across the organization. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, consulting experience, training, military experience, or education. 8+ years of AppSec, Cloud Security, or DevSecOps experience. Hands-on Terraform and Kubernetes security experience. Experience using Wiz or similar IaC security tools. Policy as Code experience using OPA/Rego or equivalent technologies. Strong understanding of CI/CD tools and Git-based workflows. Excellent communication and troubleshooting skills. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect management experience. VS Code or developer IDE enablement experience. AWS, Azure, or GCP certifications. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA. Build automated regression tests for security policies. Monitor pipeline health and investigate scan failures. Validate findings, remove duplicates, and reduce false positives. Manage policy updates and staged enforcement processes. Integrate Wiz CLI into CI/CD workflows. Deploy and maintain Wiz scanning solutions and extensions. Support GitHub, GitLab, Azure DevOps, and Jenkins integrations. Enable local, pull request, and IDE-based scanning workflows. Partner with engineering teams to improve adoption of security controls. Provide remediation guidance and developer support. Maintain platform upgrades, testing, and tool reliability. Coordinate with vendor support and product teams. Track exceptions and governance requirements. Integrate findings workflows with ServiceNow. Prepare dashboards, metrics, audit evidence, and reporting. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5392,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Senior Python Data Engineer / Architecture / ETL Pipelines / Hybrid in Smyrna</t>
+          <t>Senior Technology and Data Engineer - San Antonio, Tx</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Marietta, Georgia, 30067, United States</t>
+          <t>San Antonio, MA, 28248, United States</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5402,12 +5407,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DIRECT HIRE</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5422,7 +5427,7 @@
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/marietta/direct-hire/senior-python-data-engineer-architecture-etl-pipelines-hybrid-in-smyrna/878315</t>
+          <t>https://motionrecruitment.com/tech-jobs/san-antonio/contract/senior-technology-and-data-engineer-san-antonio-tx/885752</t>
         </is>
       </c>
       <c r="J72" t="b">
@@ -5430,22 +5435,22 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-04T13:37:21+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>e4f94c56e691df2a6089</t>
+          <t>f2be99140aa593342f82</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>A client is looking to bring on a Staff Python Data Engineer to join their team. This team is based in Marietta, GA and in the 2 days week. For the first 3 months, you’ll be heavily on-site partnering with the CTO as this is his key product and they are still hands on. You’ll be joining a growing team working on a variety of different applications internally and externally for shipping out collectible products. You’ll be architecting new features, leading the development, joining a team of software developers and some in the infrastructure. You’ll be the sole owner of this analytics product that is used by real estate agents to view modeled data of transactions. You’d be working mostly in an individual capacity with support from others on the data teams. You’d be joining a high-level team to make a massive impact on the products and team that is scaling rapidly! This client is looking for someone who is extremely independent and seeks other confident individuals to make a significant impact on their services, new initiatives, and culture. They’re looking for someone with strong critical thinking and decision making skills who can hit the ground running. Required Skills &amp; Experience 8+ years of experience with Python 5+ years of experience with Postgres 5+ years of experience with Kafka, Kubernetes 5+ years of experience with data warehousing 4-year degree Desired Skills &amp; Experience Experience with real estate products What You Will Be Doing Tech Breakdown 10% Leadership 90% Development Daily Responsibilities 90% Hands-on development 10% Leadership The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance 401k matching Bonus Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description A dynamic enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in San Antonio, Texas . This position is geared toward professionals who are passionate about cloud security and Infrastructure as Code governance. The team is focused on building security directly into cloud deployment processes, helping engineering organizations identify misconfigurations early, strengthen policy compliance, and improve overall security posture. You'll have the opportunity to work alongside cloud, platform, and security teams to enhance automated controls, streamline security operations, and promote secure development practices across complex enterprise environments. This role is ideal for someone who enjoys solving technical challenges, driving automation, and helping organizations scale cloud security capabilities. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deploym</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5462,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Senior Technology and Data Engineer - AWS/Python/Wiz - Charlotte, Nc</t>
+          <t>Sr. Data Architect / Hybrid in Atlanta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, North Carolina, 28270, United States</t>
+          <t>Dunwoody, Georgia, 30328, United States</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5472,12 +5477,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>DIRECT HIRE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5492,7 +5497,7 @@
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/senior-technology-and-data-engineer-aws-python-wiz-charlotte-nc/885741</t>
+          <t>https://motionrecruitment.com/tech-jobs/dunwoody/direct-hire/srdot-data-architect-hybrid-in-atlanta/887122</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -5500,22 +5505,22 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-09-09T22:58:57+00:00</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>fd3fc8487a48b83c5587</t>
+          <t>f94b5ce84b315b66e62f</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Job Description A large enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Charlotte, North Carolina . This role supports enterprise cloud security initiatives focused on Infrastructure as Code (IaC), CI/CD security integration, policy enforcement, and developer enablement. The selected professional will work closely with engineering, security, and platform teams to strengthen deployment security across cloud-native environments. This position offers the opportunity to influence security controls at scale while helping teams build, test, and deploy infrastructure in a secure and efficient manner. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Monitor pipeline health and troubleshoot failed scans. Validate severity, de-duplicate findings, suppress false positives, and route issues to appropriate teams. Tune IaC policies and manage staged policy enforcement. Integrate Wiz CLI into CI/CD pipelines and implement gating thresholds. Publish artifacts for traceability and optimize scan performance. Deploy and maintain Wiz DevOps extensions and Wiz Scanner integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins environments. Enable local scanning, pull request scanning, and IDE workflows. Partner with platform teams to embed security controls into standard deployment processes. Provide support sessions, remediation guidance, and developer enablement resources. Manage upgrades, policy refreshes, and tool reliability initiatives. Coordinate with vendor support teams and product resources. Maintain exception management processes and governance controls. Integrate workflows with ServiceNow for tracking and reporting. Create dashboards covering coverage, MTTR, block rates, exception aging, and audit evidence. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medica</t>
+          <t>A client is looking to bring on a Senior Data Architect to join their team. This team is based in Atlanta, GA just outside of the perimeter. You’ll be working on this client’s core ERP application in the farming industry. This position is core the data application. You’ll be the first hire of this nature for this team working with 2 DBA’s. This is an extremely tenured position that is key to the team and product. You’ll be providing data-driven solutions for a nearshore team along with the local team. You’ll be spending most of the time will be partnering with different departments on delivering solutions for their microservice migration.. You’ll be working with SqlServer, Azure Blob Storage, Data Lakes, Data Warehouses, and CosmosDB. You’d be joining a high-level team to make a massive impact on the products and team that is scaling rapidly. This is a smaller team with a lot of flexibility that’s looking to scale significantly, and they need a go getter! This client is looking for someone who is extremely independent and seeks other confident individuals to make a significant impact on their services, new initiatives, and culture. They’re looking for a tenured individual and someone looking for others who want to come to the team and stay and make a great impact. This role is specifically designed to lead the teams integration and development of agentic AI. Required Skills &amp; Experience 15+ years of experience as a with SQL Server, Azure Blob Storage 8+ year of experience with partnering with Databricks, Data Lakes, Data Warehouses, Cosmos, 5+ years of experience with PowerBI modeling Desired Skills &amp; Experience Experience in Agentic AI, ML, and IOT product development What You Will Be Doing Tech Breakdown 90% New Development 10% Maintenance Daily Responsibilities 90% Hands-on development 10% Leadership The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance 401k matching Bonus Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5532,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Senior Technology and Data Engineer - Irving, Tx</t>
+          <t>Technolgy and Data Engineer 5 - Des Moines, Ia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, Texas, 75059, United States</t>
+          <t>Des Moines, Iowa, 50308, United States</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5562,7 +5567,7 @@
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/irving/contract/senior-technology-and-data-engineer-irving-tx/885743</t>
+          <t>https://motionrecruitment.com/tech-jobs/des-moines/contract/technolgy-and-data-engineer-5-des-moines-ia/885746</t>
         </is>
       </c>
       <c r="J74" t="b">
@@ -5570,22 +5575,22 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-09-18T13:23:55+00:00</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>e1a6ec1ce6f095d8053c</t>
+          <t>6bf0c522dd76b4f094da</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Job Description A growing enterprise technology team is seeking a Technology and Data Engineer 5 for a hybrid position in Irving, TX . This role is focused on securing Infrastructure as Code deployments and helping engineering teams identify cloud security risks before they reach production. The ideal candidate will bring experience building policy-driven security controls, supporting CI/CD environments, and improving security visibility across modern cloud platforms. You will work with development, platform, and security teams to enhance automated scanning, strengthen governance processes, and support scalable cloud security practices across the organization. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, consulting experience, training, military experience, or education. 8+ years of AppSec, Cloud Security, or DevSecOps experience. Hands-on Terraform and Kubernetes security experience. Experience using Wiz or similar IaC security tools. Policy as Code experience using OPA/Rego or equivalent technologies. Strong understanding of CI/CD tools and Git-based workflows. Excellent communication and troubleshooting skills. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect management experience. VS Code or developer IDE enablement experience. AWS, Azure, or GCP certifications. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA. Build automated regression tests for security policies. Monitor pipeline health and investigate scan failures. Validate findings, remove duplicates, and reduce false positives. Manage policy updates and staged enforcement processes. Integrate Wiz CLI into CI/CD workflows. Deploy and maintain Wiz scanning solutions and extensions. Support GitHub, GitLab, Azure DevOps, and Jenkins integrations. Enable local, pull request, and IDE-based scanning workflows. Partner with engineering teams to improve adoption of security controls. Provide remediation guidance and developer support. Maintain platform upgrades, testing, and tool reliability. Coordinate with vendor support and product teams. Track exceptions and governance requirements. Integrate findings workflows with ServiceNow. Prepare dashboards, metrics, audit evidence, and reporting. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description A growing enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Des Moines, Iowa . This position will focus on improving cloud infrastructure security by embedding automated controls into development and deployment workflows. The team is looking for someone who can help enhance Infrastructure as Code security practices, support policy governance initiatives, and strengthen security oversight throughout the software delivery process. You will collaborate with engineers, security professionals, and platform teams to create scalable solutions that help identify risk early, improve compliance alignment, and enable secure cloud deployments across enterprise environments. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions,</t>
         </is>
       </c>
     </row>
@@ -5597,12 +5602,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Senior Technology and Data Engineer - San Antonio, Tx</t>
+          <t>Technology and Data Engineer - Washington, Dc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Antonio, MA, 28248, United States</t>
+          <t>Washington, District Of Columbia, 20420, United States</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5632,7 +5637,7 @@
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/san-antonio/contract/senior-technology-and-data-engineer-san-antonio-tx/885752</t>
+          <t>https://motionrecruitment.com/tech-jobs/washington/contract/technology-and-data-engineer-washington-dc/885753</t>
         </is>
       </c>
       <c r="J75" t="b">
@@ -5640,22 +5645,22 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-09-18T13:23:55+00:00</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>f2be99140aa593342f82</t>
+          <t>ba8b64ba649bef28e6a0</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Job Description A dynamic enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in San Antonio, Texas . This position is geared toward professionals who are passionate about cloud security and Infrastructure as Code governance. The team is focused on building security directly into cloud deployment processes, helping engineering organizations identify misconfigurations early, strengthen policy compliance, and improve overall security posture. You'll have the opportunity to work alongside cloud, platform, and security teams to enhance automated controls, streamline security operations, and promote secure development practices across complex enterprise environments. This role is ideal for someone who enjoys solving technical challenges, driving automation, and helping organizations scale cloud security capabilities. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deploym</t>
+          <t>Job Description A large enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Washington, DC . This position supports key cloud security initiatives designed to improve how infrastructure is built, secured, and deployed across the organization. The team is focused on implementing preventative controls within Infrastructure as Code workflows, strengthening governance processes, and helping engineering teams address security concerns earlier in the development lifecycle. The selected candidate will work across security, cloud, and engineering functions to support scalable security practices that improve visibility, streamline risk management, and enhance the reliability of cloud deployment processes. This is an excellent opportunity for someone who enjoys combining technical security expertise with automation and collaboration. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize</t>
         </is>
       </c>
     </row>
@@ -5667,12 +5672,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sr. Data Architect / Hybrid in Atlanta</t>
+          <t>Technology and Data Engineer 5 - Minneapolic, Mn</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dunwoody, Georgia, 30328, United States</t>
+          <t>Minneapolis, Minnesota, 55408, United States</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5682,12 +5687,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DIRECT HIRE</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5702,7 +5707,7 @@
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dunwoody/direct-hire/srdot-data-architect-hybrid-in-atlanta/887122</t>
+          <t>https://motionrecruitment.com/tech-jobs/minneapolis/contract/technology-and-data-engineer-5-minneapolic-mn/885744</t>
         </is>
       </c>
       <c r="J76" t="b">
@@ -5710,22 +5715,22 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-09-09T22:58:57+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>f94b5ce84b315b66e62f</t>
+          <t>e9d3b3cd2bc35cb85d4a</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>A client is looking to bring on a Senior Data Architect to join their team. This team is based in Atlanta, GA just outside of the perimeter. You’ll be working on this client’s core ERP application in the farming industry. This position is core the data application. You’ll be the first hire of this nature for this team working with 2 DBA’s. This is an extremely tenured position that is key to the team and product. You’ll be providing data-driven solutions for a nearshore team along with the local team. You’ll be spending most of the time will be partnering with different departments on delivering solutions for their microservice migration.. You’ll be working with SqlServer, Azure Blob Storage, Data Lakes, Data Warehouses, and CosmosDB. You’d be joining a high-level team to make a massive impact on the products and team that is scaling rapidly. This is a smaller team with a lot of flexibility that’s looking to scale significantly, and they need a go getter! This client is looking for someone who is extremely independent and seeks other confident individuals to make a significant impact on their services, new initiatives, and culture. They’re looking for a tenured individual and someone looking for others who want to come to the team and stay and make a great impact. This role is specifically designed to lead the teams integration and development of agentic AI. Required Skills &amp; Experience 15+ years of experience as a with SQL Server, Azure Blob Storage 8+ year of experience with partnering with Databricks, Data Lakes, Data Warehouses, Cosmos, 5+ years of experience with PowerBI modeling Desired Skills &amp; Experience Experience in Agentic AI, ML, and IOT product development What You Will Be Doing Tech Breakdown 90% New Development 10% Maintenance Daily Responsibilities 90% Hands-on development 10% Leadership The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance 401k matching Bonus Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description A respected enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Minneapolis, Minnesota . In this role, you will help advance security practices across cloud infrastructure and software delivery environments by integrating security controls directly into the deployment process. The team is focused on improving Infrastructure as Code security, strengthening governance standards, and providing engineering teams with actionable feedback that supports secure deployments. This position offers the opportunity to work on complex cloud security initiatives while partnering with development, platform, and DevOps teams to improve risk visibility, automate security validation, and enhance overall operational effectiveness. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct off</t>
         </is>
       </c>
     </row>
@@ -5737,17 +5742,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Technolgy and Data Engineer 5 - Des Moines, Ia</t>
+          <t>Threat Detection &amp; Security Analytics Engineer - Georgia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Des Moines, Iowa, 50308, United States</t>
+          <t>Alpharetta, Georgia, 30009, United States</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5757,7 +5762,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5772,7 +5777,7 @@
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/des-moines/contract/technolgy-and-data-engineer-5-des-moines-ia/885746</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/threat-detection-and-security-analytics-engineer-georgia/888545</t>
         </is>
       </c>
       <c r="J77" t="b">
@@ -5780,39 +5785,39 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-09-18T13:23:55+00:00</t>
+          <t>2026-09-28T19:01:50+00:00</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>6bf0c522dd76b4f094da</t>
+          <t>a5c7a5407f8dbed28b03</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Job Description A growing enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Des Moines, Iowa . This position will focus on improving cloud infrastructure security by embedding automated controls into development and deployment workflows. The team is looking for someone who can help enhance Infrastructure as Code security practices, support policy governance initiatives, and strengthen security oversight throughout the software delivery process. You will collaborate with engineers, security professionals, and platform teams to create scalable solutions that help identify risk early, improve compliance alignment, and enable secure cloud deployments across enterprise environments. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions,</t>
+          <t>Job Description A leading enterprise technology organization is seeking a Threat Detection &amp; Security Analytics Engineer to join its cybersecurity team. This role is designed for a security-first professional who can strengthen threat detection, monitoring, incident analysis, and vulnerability management efforts while leveraging data and automation to improve security visibility and operational effectiveness. The ideal candidate will bring hands-on experience in security operations, threat monitoring, and incident response, along with the analytical skills needed to transform security telemetry into actionable insights. This position works closely with security, engineering, and infrastructure teams to identify risks, improve detection capabilities, and enhance overall security posture across enterprise and cloud environments. While Python, SQL, and reporting tools are important components of the role, the primary focus is cybersecurity operations, threat detection, and security analytics. Required Skills &amp; Experience 5+ years of experience in cybersecurity, security operations, threat detection, or a related security discipline Strong experience with threat monitoring, incident response, and vulnerability management Experience investigating security events, alerts, logs, and telemetry Hands-on experience with Microsoft Defender or similar security platforms Experience working within Microsoft Azure environments Strong Python scripting and automation skills Strong SQL skills with experience querying and analyzing security data Understanding of security operations, threat detection methodologies, and incident response processes Ability to communicate technical findings and security risks to various stakeholders Strong analytical, troubleshooting, and problem-solving abilities Desired Skills &amp; Experience Experience in a SOC, Security Operations, or Blue Team environment Experience developing security analytics and detection use cases Familiarity with regulated environments and continuous monitoring programs Experience automating security workflows with Python or PowerShell Experience building dashboards and operational reporting solutions using Power BI or similar tools Knowledge of threat hunting techniques and security investigation methodologies Security certifications are a plus What You Will Be Doing Daily Responsibilities Monitor, investigate, and respond to security alerts and suspicious activity across enterprise and cloud environments Analyze security telemetry to identify trends, anomalies, threats, and operational risks Support incident response, containment, and remediation efforts Evaluate vulnerability data and partner with technical teams to prioritize remediation activities Develop and enhance security detections, monitoring capabilities, and operational processes Build automation solutions using Python to improve security operations efficiency Utilize SQL to support investigations, reporting, and security analytics initiatives Crea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Motion Recruitment</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Technology and Data Engineer - Washington, Dc</t>
+          <t>NEW JOB OPENING CONSTRUCTION PERMITTING ANALYST UTILITY PERMITS ANALYST IN Thousand Oaks, CA, USA!</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, District Of Columbia, 20420, United States</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5822,12 +5827,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/washington/contract/technology-and-data-engineer-washington-dc/885753</t>
+          <t>https://www.roseint.com/Jobs/Project-Analyst-JD-CA-Thousand-Oaks-Rose-International-Job-508276.html</t>
         </is>
       </c>
       <c r="J78" t="b">
@@ -5850,39 +5850,39 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-18T13:23:55+00:00</t>
+          <t>2026-09-28T19:01:50+00:00</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>ba8b64ba649bef28e6a0</t>
+          <t>5428387a3b2df608e121</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Job Description A large enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Washington, DC . This position supports key cloud security initiatives designed to improve how infrastructure is built, secured, and deployed across the organization. The team is focused on implementing preventative controls within Infrastructure as Code workflows, strengthening governance processes, and helping engineering teams address security concerns earlier in the development lifecycle. The selected candidate will work across security, cloud, and engineering functions to support scalable security practices that improve visibility, streamline risk management, and enhance the reliability of cloud deployment processes. This is an excellent opportunity for someone who enjoys combining technical security expertise with automation and collaboration. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize</t>
+          <t>Construction Permitting Analyst Utility Permits Analyst - Thousand Oaks, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING CONSTRUCTION PERMITTING ANALYST UTILITY PERMITS ANALYST IN Thousand Oaks, CA, USA! Date Posted: 09/28/2026 Hiring Organization: Rose International Position Number: 508276 Industry: Utility Job Title: Construction Permitting Analyst Utility Permits Analyst Job Location: Thousand Oaks, CA, USA, 91361 Work Model: Hybrid Work Model Details: Hybrid: Onsite Tu &amp; W Shift: M-F 7-4 Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 35.62 Max Hourly Rate($): 35.62 Must Have Skills/Attributes: MS Excel, MS Word, SharePoint Experience Desired: Reviewing and interpreting construction drawings, plans, maps, and/or designs. (1 yrs); Experience monitoring and updating permit statuses, approvals, and expiration dates. (1 yrs); Experience supporting public right-of-way (ROW) permitting activities. (1 yrs); Microsoft Word, Excel, Access, and SharePoint proficiency (1 yrs); Familiarity with construction permitting processes (1 yrs); Ability to support permit negotiations and approval requirements (1 yrs) Required Minimum Education: High School Diploma or equivalent **C2C is not available** Job Description Required Education â¢ High School Diploma Required Experience â¢ 1+ year of experience reviewing and interpreting construction drawings, plans, maps, and/or designs. â¢ Experience working with construction timelines, construction personnel, and clients. â¢ Experience monitoring and updating permit statuses, approvals, and expiration dates. Preferred Experience â¢ Experience coordinating with local government agencies, municipalities, or other external stakeholders. â¢ Experience supporting public right-of-way (ROW) permitting activities. Required Skills â¢ Strong organizational and time management skills â¢ Excellent verbal and written communication skills â¢ Microsoft Word, Excel, Access, and SharePoint proficiency â¢ Ability to build and maintain positive stakeholder relationships â¢ Ability to coordinate multiple permitting activities and track required updates. Preferred Skills â¢ Familiarity with construction permitting processes â¢ Ability to communicate effectively with Cities, Counties, Caltrans, and other regulatory agencies â¢ Ability to support permit negotiations and approval requirements Key Responsibilities â¢ Coordinate with Cities, Counties, Caltrans, and local agencies to obtain construction permits for work within the public right-of-way (ROW). â¢ Secure permits supporting the installation, maintenance, and operation of utility facilities. â¢ Coordinate with internal departments, government agencies, municipalities, and external stakeholders throughout the permitting process. â¢ Ensure permitting activities meet applicable approval and compliance requirements. â¢ Track permit statuses, approvals, and expirat</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Motion Recruitment</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Technology and Data Engineer 5 - Minneapolic, Mn</t>
+          <t>NEW JOB OPENING CONTACT CENTER OPERATIONS ANALYST - REAL-TIME ANALYTICS IN San Diego, CA, USA!</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, Minnesota, 55408, United States</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5892,12 +5892,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5907,12 +5902,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/minneapolis/contract/technology-and-data-engineer-5-minneapolic-mn/885744</t>
+          <t>https://www.roseint.com/Jobs/Operations-Analyst-Intermediate-CA-San-Diego-Rose-International-Job-508188.html</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -5920,54 +5915,49 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>e9d3b3cd2bc35cb85d4a</t>
+          <t>fd811d63c6d490cc279b</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Job Description A respected enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Minneapolis, Minnesota . In this role, you will help advance security practices across cloud infrastructure and software delivery environments by integrating security controls directly into the deployment process. The team is focused on improving Infrastructure as Code security, strengthening governance standards, and providing engineering teams with actionable feedback that supports secure deployments. This position offers the opportunity to work on complex cloud security initiatives while partnering with development, platform, and DevOps teams to improve risk visibility, automate security validation, and enhance overall operational effectiveness. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct off</t>
+          <t>Contact Center Operations Analyst - Real-Time Analytics - San Diego, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING CONTACT CENTER OPERATIONS ANALYST - REAL-TIME ANALYTICS IN San Diego, CA, USA! Date Posted: 09/25/2026 Hiring Organization: Rose International Position Number: 508188 Industry: Software/Financial Services/IT Company Job Title: Contact Center Operations Analyst - Real-Time Analytics Job Location: San Diego, CA, USA, 92129 Work Model: Hybrid Work Model Details: 3 days onsite per week Shift: Standard Business Hours Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 20 Min Hourly Rate($): 40.00 Max Hourly Rate($): 46.00 Must Have Skills/Attributes: Contact Center, Grafana, MS Word Experience Desired: Experience with Contact Center operations (3-5 yrs); Working knowledge of contact center queue management systems (Amazon Connect, Grafana) (5+ yrs) **C2C is not available** Job Description Required Skills: â¢ 3-5 years of experience with Contact Center operations Working knowledge of contact center queue management systems (Amazon Connect, Grafana, or similar contact center tooling) Industry knowledge and experience managing contact center Key Performance Indicators (Average Handle Time, Abandon Rate, Average Speed of Answer, Service Level Agreements etc.) Strong interpersonal skills and ability to work well in dynamic &amp; matrix team environments Experience with analytics to understand, manipulate and report data in an impactful way Ability to work independently and navigate ambiguity Responsibilities Leverage existing tools to inform the business on the current state of issues impacting Customer Success, and the status (both current and trended) of key performance indicators for contact queues to a variety of stakeholders Develop insights and ad-hoc analyses to understand root causes, develop forecasted outcomes, and meet business needs intraday Lead cross-functional initiatives to optimize performance for the near term, short term, and medium term time horizons Effectively communicate and interact with Sr. Leadership to create awareness on any relevant root causes and build confidence in intraday efforts to reach effective business solutions Prioritize competing tasks, foster stakeholder buy-in, manage multiple projects, and communicate progress effectively Job Summary: Come join the Client Customer Success Real-Time Operation Team. As a Support Operations Analyst IV you will operate in a fast-paced Customer Success organization, analyze contact center service level performance, generate insights and recommendations, drive results, and communicate effectively with leaders and partners at multiple levels. **Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business ne</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Motion Recruitment</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Threat Detection &amp; Security Analytics Engineer - Georgia</t>
+          <t>NEW JOB OPENING LEARNING &amp; DEVELOPMENT BUSINESS ANALYST - TRAINING EVALUATION &amp; LMS IN IRWINDALE, CA, USA!</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, 30009, United States</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5977,12 +5967,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/threat-detection-and-security-analytics-engineer-georgia/888545</t>
+          <t>https://www.roseint.com/Jobs/Business-Analyst-CA-Irwindale-Rose-International-Job-508176.html</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -5990,22 +5980,22 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-09-28T19:01:50+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>a5c7a5407f8dbed28b03</t>
+          <t>30c842484d4bb880771c</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Job Description A leading enterprise technology organization is seeking a Threat Detection &amp; Security Analytics Engineer to join its cybersecurity team. This role is designed for a security-first professional who can strengthen threat detection, monitoring, incident analysis, and vulnerability management efforts while leveraging data and automation to improve security visibility and operational effectiveness. The ideal candidate will bring hands-on experience in security operations, threat monitoring, and incident response, along with the analytical skills needed to transform security telemetry into actionable insights. This position works closely with security, engineering, and infrastructure teams to identify risks, improve detection capabilities, and enhance overall security posture across enterprise and cloud environments. While Python, SQL, and reporting tools are important components of the role, the primary focus is cybersecurity operations, threat detection, and security analytics. Required Skills &amp; Experience 5+ years of experience in cybersecurity, security operations, threat detection, or a related security discipline Strong experience with threat monitoring, incident response, and vulnerability management Experience investigating security events, alerts, logs, and telemetry Hands-on experience with Microsoft Defender or similar security platforms Experience working within Microsoft Azure environments Strong Python scripting and automation skills Strong SQL skills with experience querying and analyzing security data Understanding of security operations, threat detection methodologies, and incident response processes Ability to communicate technical findings and security risks to various stakeholders Strong analytical, troubleshooting, and problem-solving abilities Desired Skills &amp; Experience Experience in a SOC, Security Operations, or Blue Team environment Experience developing security analytics and detection use cases Familiarity with regulated environments and continuous monitoring programs Experience automating security workflows with Python or PowerShell Experience building dashboards and operational reporting solutions using Power BI or similar tools Knowledge of threat hunting techniques and security investigation methodologies Security certifications are a plus What You Will Be Doing Daily Responsibilities Monitor, investigate, and respond to security alerts and suspicious activity across enterprise and cloud environments Analyze security telemetry to identify trends, anomalies, threats, and operational risks Support incident response, containment, and remediation efforts Evaluate vulnerability data and partner with technical teams to prioritize remediation activities Develop and enhance security detections, monitoring capabilities, and operational processes Build automation solutions using Python to improve security operations efficiency Utilize SQL to support investigations, reporting, and security analytics initiatives Crea</t>
+          <t>Learning &amp; Development Business Analyst - Training Evaluation &amp; LMS - Irwindale, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING LEARNING &amp; DEVELOPMENT BUSINESS ANALYST - TRAINING EVALUATION &amp; LMS IN IRWINDALE, CA, USA! Date Posted: 09/25/2026 Hiring Organization: Rose International Position Number: 508176 Industry: Utility Job Title: Learning &amp; Development Business Analyst - Training Evaluation &amp; LMS Job Location: Irwindale, CA, USA, 91706 Work Model: Hybrid Work Model Details: Onsite meeting as needed Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 7 Min Hourly Rate($): 38.60 Max Hourly Rate($): 38.60 Must Have Skills/Attributes: Learning and Development, Learning Management System (LMS), Training Experience Desired: Combined experience in learning and development or training (5-7 yrs); Experience developing and implementing evaluation methodologies (5 yrs); Knowledge of SuccessFactors Learning (LMS) (5 yrs) Required Minimum Education: Bachelorâs Degree Preferred Education: Masterâs Degree **C2C is not available** Job Description Required Education: â¢ Bachelorâs Degree in Industrial &amp; Organizational Psychology, Human Resources, or other related discipline Preferred License/Certification: â¢ Masterâs Degree in Industrial &amp; Organizational Psychology, Human Resources, or other related discipline Required Experience, Knowledge &amp; Skills: â¢ 5-7 years of combined experience in learning and development or training â¢ Experience in training and development â¢ Experience developing and implementing evaluation methodologies (e.g., questionnaires, focus groups, observations, interviews) â¢ Experience developing questionnaires with survey tools (e.g., Alchemer, SurveyMonkey, Qualtrics) â¢ Experience using the Kirkpatrick model to evaluate the effectiveness of training â¢ Experience analyzing large amounts of complex data â¢ Experience creating reports and dashboards â¢ Experience developing and delivering technical presentations to both technical and non-technical audiences â¢ Ability to prioritize multiple duties/projects, take lead and follow through on all assignments â¢ Ability to work well under pressure, adjust to changing priorities, organize a heavy workload, take ownership, and follow through on all assignments â¢ Ability to take initiative and accountability for the accuracy of information and for achieving results â¢ Ability to work well in a team environment and perform with minimal supervision â¢ Strong interpersonal and oral communications skills with proven record of building relationships and communicating complex information in a concise and straightforward manner Preferred Experience, Knowledge &amp; Skills: â¢ Experience in developing company-wide measurement strategies â¢ Experience creating dashboards using Power BI â¢ Knowledge of SuccessFactors Learning (LMS) Job Summary: In this role, you will partner with Organizational Unit l</t>
         </is>
       </c>
     </row>
@@ -6017,22 +6007,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING CONSTRUCTION PERMITTING ANALYST UTILITY PERMITS ANALYST IN Thousand Oaks, CA, USA!</t>
+          <t>SQL Server Database Analyst Data Migration Reporting</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6047,7 +6042,7 @@
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Project-Analyst-JD-CA-Thousand-Oaks-Rose-International-Job-508276.html</t>
+          <t>https://www.roseint.com/Jobs/Database-Analyst-Remote-Rose-International-Job-508274.html</t>
         </is>
       </c>
       <c r="J81" t="b">
@@ -6055,22 +6050,22 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-09-28T19:01:50+00:00</t>
+          <t>2026-09-29T00:48:58+00:00</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>5428387a3b2df608e121</t>
+          <t>108ddbbecdd818d1fd31</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Construction Permitting Analyst Utility Permits Analyst - Thousand Oaks, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING CONSTRUCTION PERMITTING ANALYST UTILITY PERMITS ANALYST IN Thousand Oaks, CA, USA! Date Posted: 09/28/2026 Hiring Organization: Rose International Position Number: 508276 Industry: Utility Job Title: Construction Permitting Analyst Utility Permits Analyst Job Location: Thousand Oaks, CA, USA, 91361 Work Model: Hybrid Work Model Details: Hybrid: Onsite Tu &amp; W Shift: M-F 7-4 Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 35.62 Max Hourly Rate($): 35.62 Must Have Skills/Attributes: MS Excel, MS Word, SharePoint Experience Desired: Reviewing and interpreting construction drawings, plans, maps, and/or designs. (1 yrs); Experience monitoring and updating permit statuses, approvals, and expiration dates. (1 yrs); Experience supporting public right-of-way (ROW) permitting activities. (1 yrs); Microsoft Word, Excel, Access, and SharePoint proficiency (1 yrs); Familiarity with construction permitting processes (1 yrs); Ability to support permit negotiations and approval requirements (1 yrs) Required Minimum Education: High School Diploma or equivalent **C2C is not available** Job Description Required Education â¢ High School Diploma Required Experience â¢ 1+ year of experience reviewing and interpreting construction drawings, plans, maps, and/or designs. â¢ Experience working with construction timelines, construction personnel, and clients. â¢ Experience monitoring and updating permit statuses, approvals, and expiration dates. Preferred Experience â¢ Experience coordinating with local government agencies, municipalities, or other external stakeholders. â¢ Experience supporting public right-of-way (ROW) permitting activities. Required Skills â¢ Strong organizational and time management skills â¢ Excellent verbal and written communication skills â¢ Microsoft Word, Excel, Access, and SharePoint proficiency â¢ Ability to build and maintain positive stakeholder relationships â¢ Ability to coordinate multiple permitting activities and track required updates. Preferred Skills â¢ Familiarity with construction permitting processes â¢ Ability to communicate effectively with Cities, Counties, Caltrans, and other regulatory agencies â¢ Ability to support permit negotiations and approval requirements Key Responsibilities â¢ Coordinate with Cities, Counties, Caltrans, and local agencies to obtain construction permits for work within the public right-of-way (ROW). â¢ Secure permits supporting the installation, maintenance, and operation of utility facilities. â¢ Coordinate with internal departments, government agencies, municipalities, and external stakeholders throughout the permitting process. â¢ Ensure permitting activities meet applicable approval and compliance requirements. â¢ Track permit statuses, approvals, and expirat</t>
+          <t>Education: â¢ Associate's DegreeExperience and Skills Required-â¢ Three or more years of professional experience with SQL and relational database systems.â¢ Strong proficiency in Microsoft SQL Server and T-SQL, including complex joins, stored procedures, views, and data manipulation scripts.â¢ Experience with large datasets, data extraction, transformation, validation, and reconciliation.â¢ Understanding of relational database design, indexing, and query optimization.â¢ Ability to interpret technical documentation, translate business requirements into SQL solutions, and communicate findings clearly.â¢ Ability to work independently, manage competing priorities, and collaborate with technical and nontechnical stakeholders.Experience and Skills Preferred-â¢ Experience with enterprise case management systems or large transactional applications.â¢ Data migration or legacy system modernization experience.â¢ Experience with SQL Server Integration Services (SSIS), Power BI, data warehousing, or reporting solutions.â¢ Experience troubleshooting application integrations and data interfaces and working with software vendors.â¢ Familiarity with judicial, criminal justice, or government information systems and handling sensitive data.â¢ Knowledge of data governance, data quality, and database security best practices.Ideal Candidateâ¢ A hands-on SQL professional who can independently investigate complex data issues, write and troubleshoot queries, communicate findings clearly, and collaborate across teams to support data accuracy, system reliability, and modernization initiatives.Position OverviewThe CLIENT is seeking an experienced SQL Database Analyst to provide technical support for statewide judicial applications, database systems, data integrations, and reporting initiatives. The analyst will work with application, data warehouse, and technical teams to analyze, extract, validate, and troubleshoot data across multiple systems. This position will also support system modernization, including data migration, integration testing, and reporting associated with the statewide case management system.Key ResponsibilitiesSQL Development and Data Analysisâ¢ Develop, maintain, and optimize complex SQL queries, stored procedures, views, and scripts.â¢ Analyze relational database structures and relationships among tables and data elements.â¢ Extract, transform, and validate data; troubleshoot discrepancies and database-related application issues.â¢ Assist with database documentation, data mapping, and technical specifications.Data Migration and System Integrationâ¢ Support data conversion and migration between legacy and modernized case management systems.â¢ Develop SQL scripts to identify, correct, and validate data discrepancies before and after migration.â¢ Reconcile converted data for accuracy and completeness; investigate data exchanged through external interfaces.â¢ Coordinate with application analysts, vendors, and technical teams to resolv</t>
         </is>
       </c>
     </row>
@@ -6082,22 +6077,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING CONTACT CENTER OPERATIONS ANALYST - REAL-TIME ANALYTICS IN San Diego, CA, USA!</t>
+          <t>Senior Data Analyst - Python, SQL &amp; ETL | Utility Analytics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Oakland, CA, 94612, USA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Operations-Analyst-Intermediate-CA-San-Diego-Rose-International-Job-508188.html</t>
+          <t>https://www.roseint.com/Jobs/Data-Analyst-CA-Oakland-Rose-International-Job-508236.html</t>
         </is>
       </c>
       <c r="J82" t="b">
@@ -6120,22 +6120,22 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-09-26T08:04:24+00:00</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>fd811d63c6d490cc279b</t>
+          <t>e57086c456c26cce669a</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Contact Center Operations Analyst - Real-Time Analytics - San Diego, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING CONTACT CENTER OPERATIONS ANALYST - REAL-TIME ANALYTICS IN San Diego, CA, USA! Date Posted: 09/25/2026 Hiring Organization: Rose International Position Number: 508188 Industry: Software/Financial Services/IT Company Job Title: Contact Center Operations Analyst - Real-Time Analytics Job Location: San Diego, CA, USA, 92129 Work Model: Hybrid Work Model Details: 3 days onsite per week Shift: Standard Business Hours Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 20 Min Hourly Rate($): 40.00 Max Hourly Rate($): 46.00 Must Have Skills/Attributes: Contact Center, Grafana, MS Word Experience Desired: Experience with Contact Center operations (3-5 yrs); Working knowledge of contact center queue management systems (Amazon Connect, Grafana) (5+ yrs) **C2C is not available** Job Description Required Skills: â¢ 3-5 years of experience with Contact Center operations Working knowledge of contact center queue management systems (Amazon Connect, Grafana, or similar contact center tooling) Industry knowledge and experience managing contact center Key Performance Indicators (Average Handle Time, Abandon Rate, Average Speed of Answer, Service Level Agreements etc.) Strong interpersonal skills and ability to work well in dynamic &amp; matrix team environments Experience with analytics to understand, manipulate and report data in an impactful way Ability to work independently and navigate ambiguity Responsibilities Leverage existing tools to inform the business on the current state of issues impacting Customer Success, and the status (both current and trended) of key performance indicators for contact queues to a variety of stakeholders Develop insights and ad-hoc analyses to understand root causes, develop forecasted outcomes, and meet business needs intraday Lead cross-functional initiatives to optimize performance for the near term, short term, and medium term time horizons Effectively communicate and interact with Sr. Leadership to create awareness on any relevant root causes and build confidence in intraday efforts to reach effective business solutions Prioritize competing tasks, foster stakeholder buy-in, manage multiple projects, and communicate progress effectively Job Summary: Come join the Client Customer Success Real-Time Operation Team. As a Support Operations Analyst IV you will operate in a fast-paced Customer Success organization, analyze contact center service level performance, generate insights and recommendations, drive results, and communicate effectively with leaders and partners at multiple levels. **Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business ne</t>
+          <t>Required Education:â¢ BA/BS Degree in Computer Science, Engineering, or other related field or equivalent work experienceRequired Experience, Knowledge &amp; Skills:â¢ 4 years of related work experienceâ¢ Coding skills (Python, SQL, etc.)â¢ Experience developing ETL pipelinesâ¢ Demonstrated communication skillsPreferred Experience, Knowledge &amp; Skills:â¢ Advanced skill in Python (or similar programming languages) for data analysis and automationâ¢ Advanced skill in SQL and database query languages for extracting, transforming, and analyzing data from data environmentsâ¢ Advanced skill in designing and maintaining ETL processes for large datasetsâ¢ Experience with data visualization and dashboarding toolsâ¢ Experience in GIS preferredâ¢ Familiarity with utility operationsâ¢ Able to analyze and interpret data and effectively communicate findingsJob Summary:Analytics support for Client NPA and zonal electrification programs, an initiative focused on accelerating building electrification to avoid gas infrastructure investments and support long-term decarbonization goals.Job Responsibilities:â¢ ETL Pipeline Creation: Develop and maintain an extract-transform-load data pipeline across multiple different core data environments to screen and prioritize electrification opportunities across Client systemâ¢ New Data Sources: Provide recommendations to enhance data pipeline with new data sources and improved data processesâ¢ Process Automation: Create automated data routines and processes for reporting and data delivery, ensuring accurate data manipulation and data cleansingâ¢ Dashboards and Ad Hoc Analysis: Develop and communicate clear, concise, and actionable data analyses in the form of dashboards or ad hoc reports**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
         </is>
       </c>
     </row>
@@ -6147,22 +6147,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING LEARNING &amp; DEVELOPMENT BUSINESS ANALYST - TRAINING EVALUATION &amp; LMS IN IRWINDALE, CA, USA!</t>
+          <t>Senior Product Data Scientist - Customer Growth &amp; Retention (Contract)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>San Diego, CA, 92129, USA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6177,7 +6182,7 @@
       </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Business-Analyst-CA-Irwindale-Rose-International-Job-508176.html</t>
+          <t>https://www.roseint.com/Jobs/Data-Scientist-CA-San-Diego-Rose-International-Job-508285.html</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -6185,22 +6190,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-09-29T00:48:58+00:00</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>30c842484d4bb880771c</t>
+          <t>25b2b9cb37a81bcbece6</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Learning &amp; Development Business Analyst - Training Evaluation &amp; LMS - Irwindale, CA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING LEARNING &amp; DEVELOPMENT BUSINESS ANALYST - TRAINING EVALUATION &amp; LMS IN IRWINDALE, CA, USA! Date Posted: 09/25/2026 Hiring Organization: Rose International Position Number: 508176 Industry: Utility Job Title: Learning &amp; Development Business Analyst - Training Evaluation &amp; LMS Job Location: Irwindale, CA, USA, 91706 Work Model: Hybrid Work Model Details: Onsite meeting as needed Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 7 Min Hourly Rate($): 38.60 Max Hourly Rate($): 38.60 Must Have Skills/Attributes: Learning and Development, Learning Management System (LMS), Training Experience Desired: Combined experience in learning and development or training (5-7 yrs); Experience developing and implementing evaluation methodologies (5 yrs); Knowledge of SuccessFactors Learning (LMS) (5 yrs) Required Minimum Education: Bachelorâs Degree Preferred Education: Masterâs Degree **C2C is not available** Job Description Required Education: â¢ Bachelorâs Degree in Industrial &amp; Organizational Psychology, Human Resources, or other related discipline Preferred License/Certification: â¢ Masterâs Degree in Industrial &amp; Organizational Psychology, Human Resources, or other related discipline Required Experience, Knowledge &amp; Skills: â¢ 5-7 years of combined experience in learning and development or training â¢ Experience in training and development â¢ Experience developing and implementing evaluation methodologies (e.g., questionnaires, focus groups, observations, interviews) â¢ Experience developing questionnaires with survey tools (e.g., Alchemer, SurveyMonkey, Qualtrics) â¢ Experience using the Kirkpatrick model to evaluate the effectiveness of training â¢ Experience analyzing large amounts of complex data â¢ Experience creating reports and dashboards â¢ Experience developing and delivering technical presentations to both technical and non-technical audiences â¢ Ability to prioritize multiple duties/projects, take lead and follow through on all assignments â¢ Ability to work well under pressure, adjust to changing priorities, organize a heavy workload, take ownership, and follow through on all assignments â¢ Ability to take initiative and accountability for the accuracy of information and for achieving results â¢ Ability to work well in a team environment and perform with minimal supervision â¢ Strong interpersonal and oral communications skills with proven record of building relationships and communicating complex information in a concise and straightforward manner Preferred Experience, Knowledge &amp; Skills: â¢ Experience in developing company-wide measurement strategies â¢ Experience creating dashboards using Power BI â¢ Knowledge of SuccessFactors Learning (LMS) Job Summary: In this role, you will partner with Organizational Unit l</t>
+          <t>Required Education:Bachelor's degree in Engineering, Data Science, Statistics, Mathematics, Computer Science, Economics, or a related quantitative fieldPreferred Education:Master'sRequired Skills:â¢ 4+ years of experience in product analytics, marketing analytics, or applied data science â ideally with exposure to customer experience measurement, growth analytics, or expert/agent-assisted service modelsâ¢ Advanced proficiency in SQL and "big data" technologies (eg, Databricks, Spark, Redshift, BigQuery); comfort with a BI tool (Tableau, Qlik, Dash) â¢ Solid grounding in experimentation design (A/B/n) and causal inference methods (propensity score matching, diff-in-diff, synthetic control) â including comfort applying these when clean experiments aren't feasible â¢ Strong business acumen and strategic thinking â able to translate a fuzzy business question into a testable hypothesis and measurement plan â¢ Strong data storytelling skills â able to rapidly build clear visualizations and communicate insights to non-technical stakeholders â¢ Excellent communication skills, with the ability to work independently against a defined scope typical of a contract engagementJob Summary:â¢ We are seeking a highly motivated Contractor Data Scientist to join our Customer Success Data Science team, focused on Smart Expert Growth and Retentionâ¢ In this role, you'll be the analytical backbone for understanding how our consumer and expert experiences work together to drive the best possible outcomes for customers â from identifying opportunity, to measuring impact, to uncovering new ways to create valueâ¢ You'll partner closely with expert operations, product, and marketing to turn data into decisions, and to prove out where combining human expertise with great customer experience delivers the best resultsâ¢ If you're passionate about using hard data to uncover creative, high-impact solutions at the intersection of customer experience and expert-driven growth, we'd love to hear from you!**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6217,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Python, SQL &amp; ETL | Utility Analytics</t>
+          <t>Senior Technical Business Analyst for AI, Data Integration &amp; Azure DevOps</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oakland, CA, 94612, USA</t>
+          <t>White Plains, NY, 10601, USA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6232,7 +6237,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6247,7 +6252,7 @@
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Data-Analyst-CA-Oakland-Rose-International-Job-508236.html</t>
+          <t>https://www.roseint.com/Jobs/Business-Analyst-NY-White-Plains-Rose-International-Job-508265.html</t>
         </is>
       </c>
       <c r="J84" t="b">
@@ -6255,39 +6260,39 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-26T08:04:24+00:00</t>
+          <t>2026-09-28T19:01:50+00:00</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>e57086c456c26cce669a</t>
+          <t>978155b1145c206a4974</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Required Education:â¢ BA/BS Degree in Computer Science, Engineering, or other related field or equivalent work experienceRequired Experience, Knowledge &amp; Skills:â¢ 4 years of related work experienceâ¢ Coding skills (Python, SQL, etc.)â¢ Experience developing ETL pipelinesâ¢ Demonstrated communication skillsPreferred Experience, Knowledge &amp; Skills:â¢ Advanced skill in Python (or similar programming languages) for data analysis and automationâ¢ Advanced skill in SQL and database query languages for extracting, transforming, and analyzing data from data environmentsâ¢ Advanced skill in designing and maintaining ETL processes for large datasetsâ¢ Experience with data visualization and dashboarding toolsâ¢ Experience in GIS preferredâ¢ Familiarity with utility operationsâ¢ Able to analyze and interpret data and effectively communicate findingsJob Summary:Analytics support for Client NPA and zonal electrification programs, an initiative focused on accelerating building electrification to avoid gas infrastructure investments and support long-term decarbonization goals.Job Responsibilities:â¢ ETL Pipeline Creation: Develop and maintain an extract-transform-load data pipeline across multiple different core data environments to screen and prioritize electrification opportunities across Client systemâ¢ New Data Sources: Provide recommendations to enhance data pipeline with new data sources and improved data processesâ¢ Process Automation: Create automated data routines and processes for reporting and data delivery, ensuring accurate data manipulation and data cleansingâ¢ Dashboards and Ad Hoc Analysis: Develop and communicate clear, concise, and actionable data analyses in the form of dashboards or ad hoc reports**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
+          <t>Required Education:â¢ BS in Computer Science, Information Systems, or a related field from an accredited institution, or equivalent experience.Preferred Certifications:Any of the following BA certifications is a plus: â¢ IIBA Entry Certificate in Business Analysis (ECBA) â¢ IIBA Certification of Competency in Business Analysis (CCBA) â¢ IIBA Certified Business Analysis Professional (CBAP) â¢ IIBA Agile Analysis Certification (AAC) â¢ IQBBA Certified Foundation Level Business Analyst (CFLBA) â¢ IREB Certified Professional for Requirements Engineering (CPRE) â¢ PMI-Professional in Business Analysis (PBA) Certification. Certifications in Agile, DevOps, or programming languages, or data management are a plus.Skillsâ¢ Demonstrated experience as a business analyst in software implementations or deployments. â¢ Proficient in programming languages such as Java, C++/C, and Oracle Database. â¢ 5+ years of relevant experience, preferably in Business Analysis for IT projects, including cloud computing and data integration. â¢ Programming experience.â¢ Expertise in Excel, including macros. â¢ A deep understanding of technical concepts, principles, and terminology. â¢ Knowledge and expertise in AI usage in Business analysis. â¢ Extensive experience in data profiling, analysis, and querying. â¢ Experience working on data integration projects. â¢ Extensive experience in developing detailed functional and technical requirements. â¢ Knowledge of data science concepts, data products, and extensive experience in gathering data requirements. â¢ Experience working within the Agile framework and employing DevOps (Azure DevOps preferred). â¢ Excellent analytical, critical thinking, and problem-solving abilities. â¢ Familiar with automated testing tools. â¢ Ability to work effectively in a team environment with both employees and consultants. â¢ Strong communication skills across various levels of technical and business teams. â¢ Proven management and organizational skills. â¢ Strong adaptability and capacity to work in fast-paced environments. Job Functions &amp; ResponsibilitiesThe Contingent worker will be expected to deliver the following activities over the course of the engagement: a. Requirements Elicitation, Analysis, and Management â¢ Facilitate sessions with stakeholders to gather business, functional, and non-functional requirements. â¢ Document requirements as BRDs, user stories, use cases, and acceptance criteria. â¢ Maintain a requirements traceability matrix across all delivery phases. â¢ Validate requirements with stakeholders and vendors for clarity and alignment. â¢ Support ongoing refinement, prioritization, and requirements change control. b. Business Process Analysis and Design â¢ Identify process gaps, pain points, and improvement opportunities. â¢ Design future state (TO BE) processes aligned with policies and operational goals. â¢ Create process maps, swim lanes, and related models for stakeholder communication. â¢ C</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Senior Technical Business Analyst for AI, Data Integration &amp; Azure DevOps</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>White Plains, NY, 10601, USA</t>
+          <t>Des Moines, Iowa, 50301, USA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6297,12 +6302,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6317,7 +6322,7 @@
       </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Business-Analyst-NY-White-Plains-Rose-International-Job-508265.html</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006259257/Business-Analyst</t>
         </is>
       </c>
       <c r="J85" t="b">
@@ -6325,49 +6330,54 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-28T19:01:50+00:00</t>
+          <t>2026-09-29T00:48:58+00:00</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>978155b1145c206a4974</t>
+          <t>8610e737a7bdc9111012</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Required Education:â¢ BS in Computer Science, Information Systems, or a related field from an accredited institution, or equivalent experience.Preferred Certifications:Any of the following BA certifications is a plus: â¢ IIBA Entry Certificate in Business Analysis (ECBA) â¢ IIBA Certification of Competency in Business Analysis (CCBA) â¢ IIBA Certified Business Analysis Professional (CBAP) â¢ IIBA Agile Analysis Certification (AAC) â¢ IQBBA Certified Foundation Level Business Analyst (CFLBA) â¢ IREB Certified Professional for Requirements Engineering (CPRE) â¢ PMI-Professional in Business Analysis (PBA) Certification. Certifications in Agile, DevOps, or programming languages, or data management are a plus.Skillsâ¢ Demonstrated experience as a business analyst in software implementations or deployments. â¢ Proficient in programming languages such as Java, C++/C, and Oracle Database. â¢ 5+ years of relevant experience, preferably in Business Analysis for IT projects, including cloud computing and data integration. â¢ Programming experience.â¢ Expertise in Excel, including macros. â¢ A deep understanding of technical concepts, principles, and terminology. â¢ Knowledge and expertise in AI usage in Business analysis. â¢ Extensive experience in data profiling, analysis, and querying. â¢ Experience working on data integration projects. â¢ Extensive experience in developing detailed functional and technical requirements. â¢ Knowledge of data science concepts, data products, and extensive experience in gathering data requirements. â¢ Experience working within the Agile framework and employing DevOps (Azure DevOps preferred). â¢ Excellent analytical, critical thinking, and problem-solving abilities. â¢ Familiar with automated testing tools. â¢ Ability to work effectively in a team environment with both employees and consultants. â¢ Strong communication skills across various levels of technical and business teams. â¢ Proven management and organizational skills. â¢ Strong adaptability and capacity to work in fast-paced environments. Job Functions &amp; ResponsibilitiesThe Contingent worker will be expected to deliver the following activities over the course of the engagement: a. Requirements Elicitation, Analysis, and Management â¢ Facilitate sessions with stakeholders to gather business, functional, and non-functional requirements. â¢ Document requirements as BRDs, user stories, use cases, and acceptance criteria. â¢ Maintain a requirements traceability matrix across all delivery phases. â¢ Validate requirements with stakeholders and vendors for clarity and alignment. â¢ Support ongoing refinement, prioritization, and requirements change control. b. Business Process Analysis and Design â¢ Identify process gaps, pain points, and improvement opportunities. â¢ Design future state (TO BE) processes aligned with policies and operational goals. â¢ Create process maps, swim lanes, and related models for stakeholder communication. â¢ C</t>
+          <t>Description o Strong stakeholder management and ability to work with challenging personalities. o Effective collaboration with cross functional teams and other BAs. o Strong analytical mindset with the ability to investigate issues independently. o Clear communication and consistent status reporting. o Experience working with third party vendors (FAST preferred). o Insurance background and policy administration experience preferred but not required. o Familiarity with DTCC (bonus). Skills Business analysis, Scrum, Agile, Requirement gathering, User stories Top Skills Details Business analysis,Scrum Additional Skills &amp; Qualifications Insurance experience and Policy Admin systems experience is a huge plus. Experience Level Expert Level Job Type &amp; Location This is a Contract position based out of Des Moines, IA. Pay and Benefits The pay range for this position is $55.00 - $55.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a hybrid position in Des Moines,IA. Application Deadline This position is anticipated to close on Sep 11, 2026. About TEKsystems We're partners in transformation. We help clients activate ideas and solutions to take advantage of a new world of opportunity. We are a team of 80,000 strong, working with over 6,000 clients, including 80% of the Fortune 500, across North America, Europe and Asia. As an industry leader in Full-Stack Technology Services, Talent Services, and real-world application, we work with progressive leaders to drive change. That's the power of true partnership. TEKsystems is an Allegis Group company. The company is an equal opportunity employer and will consider all applications without regards to race, sex, age, color, religion, national origin, veteran status, disability, sexual orientation, gender identity, genetic information or any characteristic protected by law. About TEKsystems and TEKsystems Global Services We’re a leading provider of business and technology services. We accelerate business transformation for our customers. Our expertise in strategy, design, execution and operations unlocks business value t</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AI Engineer - Jersey City, NJ | Judge Group</t>
+          <t>Data Engineer - Sr.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Des Moines, Iowa, 50301, USA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6382,7 +6392,7 @@
       </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1153723</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006299146/Data-Engineer-Sr</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -6390,49 +6400,54 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-09-29T00:48:58+00:00</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>93caa55cea9f688962eb</t>
+          <t>a40a64aac61d42f711cb</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>AI Engineer - Jersey City, NJ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>***MUST BE LOCAL TO DES MOINES, IA OR WILLING TO GO ONSITE IN DES MOINES, IOWA*** Description Data Engineer to join a product-focused engineering team responsible for delivering high-quality data solutions that drive business insights. This role will serve as a key contributor on a cross-functional Agile team and will help design, build, and maintain scalable data pipelines and data products that support enterprise analytics and decision-making. The ideal candidate is a proactive, hands-on engineer who can quickly adapt to a fast-paced environment, collaborate effectively with stakeholders, and contribute immediately to team objectives. Skills Python, Sql, Aws, snowflake, erwin, data modeling Top Skills Details Python,Sql,Aws Additional Skills &amp; Qualifications Team Environment • Join a collaborative team of approximately 4-6 engineers. • Work within a cross-functional Agile product team. • Regular interaction with multiple business and technology teams. • Strong emphasis on teamwork, communication, and problem-solving. Required Qualifications • Strong proficiency in Python development. • Experience working with AWS cloud services. • Strong SQL skills and experience with relational and analytical databases. • Experience using GitHub and modern source control practices. • Experience working within Agile development environments. • Strong communication and collaboration skills. • Ability to quickly learn new technologies and contribute with minimal ramp-up time. Preferred Qualifications • Experience extracting and integrating data through APIs. • Experience working with Snowflake. • Knowledge of data modeling concepts and tools such as Erwin. • Experience designing and implementing enterprise data solutions. • Familiarity with Informatica is helpful but not required. Experience Level Expert Level Job Type &amp; Location This is a Contract position based out of Des Moines, IA. Pay and Benefits The pay range for this position is $60.00 - $73.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully remote position. Application Deadline This position is antici</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AI Prompt Engineer - Charlotte, NC | Judge Group</t>
+          <t>Service Desk Analyst</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Ames, Iowa, 50010, USA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6447,7 +6462,7 @@
       </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146776</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006298075/Service-Desk-Analyst</t>
         </is>
       </c>
       <c r="J87" t="b">
@@ -6455,22 +6470,22 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-25T01:55:13+00:00</t>
+          <t>2026-09-29T00:48:58+00:00</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>03227ef1e4accb60da7c</t>
+          <t>b36addfa96a59084ec8a</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>AI Prompt Engineer - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Description • Respond to and resolve customer requests and inquiries by tracking them in ticket management system • Provide information and instructions to users on various applications and equipment • Provide direct support via email, phone, remote, and in-person appointments • Identify technical needs of customers and find resolutions to address business needs • Install, maintain, and troubleshoot computer equipment and software • Performs routine backup and restores system and data files • Ensure devices are setup in a standard, secure, and consistent manner • Schedule customer installations and appointments • Ensure policies and standards are met and procedures are followed by staff • Maintain/manage ITS and CorePlus customer inventories • Triage incidents and requests, ensuring that students and FTEs are completing them in a timely manner • Attend team, departmental, and campus meetings • Provide guidance to student employees, including scheduling, training, and performance feedback • Document procedures, checklists, and other information required by the team • Provide backup support for purchasing CorePlus and Onsite requested IT equipment Skills Help desk, Technical support, Desktop, Customer service, Troubleshooting, Office 365, imaging Top Skills Details Help desk,Technical support,Desktop,Customer service,Troubleshooting Additional Skills &amp; Qualifications Supporting an enterprise level ticketing system. (Service Now) Job Type &amp; Location This is a Contract position based out of Ames, IA. Pay and Benefits The pay range for this position is $19.00 - $20.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully onsite position in Ames,IA. Application Deadline This position is anticipated to close on Sep 27, 2026. About TEKsystems We're partners in transformation. We help clients activate ideas and solutions to take advantage of a new world of opportunity. We are a team of 80,000 strong, working with over 6,000 clients, including 80% of the Fortune 500, across North America, Europe and Asia. As an industry leader in Full-Stack Technology Service</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6497,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Agentic AI Developer - Irving, TX | Judge Group</t>
+          <t>AI Engineer - Jersey City, NJ | Judge Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6512,7 +6527,7 @@
       </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1149623</t>
+          <t>https://www.judge.com/jobs/details/1153723</t>
         </is>
       </c>
       <c r="J88" t="b">
@@ -6520,22 +6535,22 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-24T18:51:45+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>c15fa838b2e4c9d28d55</t>
+          <t>93caa55cea9f688962eb</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Agentic AI Developer - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>AI Engineer - Jersey City, NJ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6562,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Analyst, Sales Operations - San Jose, CA | Judge Group</t>
+          <t>AI Prompt Engineer - Charlotte, NC | Judge Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6577,7 +6592,7 @@
       </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148139</t>
+          <t>https://www.judge.com/jobs/details/1146776</t>
         </is>
       </c>
       <c r="J89" t="b">
@@ -6585,22 +6600,22 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-08-20T00:04:09+00:00</t>
+          <t>2026-09-25T01:55:13+00:00</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>68dfd25047875496bc9e</t>
+          <t>03227ef1e4accb60da7c</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Analyst, Sales Operations - San Jose, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>AI Prompt Engineer - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6627,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Business Analyst - Denver, CO | Judge Group</t>
+          <t>Agentic AI Developer - Irving, TX | Judge Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6642,7 +6657,7 @@
       </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152312</t>
+          <t>https://www.judge.com/jobs/details/1149623</t>
         </is>
       </c>
       <c r="J90" t="b">
@@ -6650,22 +6665,22 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-15T18:37:24+00:00</t>
+          <t>2026-09-24T18:51:45+00:00</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>f941cb0c25b86249f148</t>
+          <t>c15fa838b2e4c9d28d55</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Business Analyst - Denver, CO | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Agentic AI Developer - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6692,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Business Analyst - Fort Washington, PA | Judge Group</t>
+          <t>Analyst, Sales Operations - San Jose, CA | Judge Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6707,7 +6722,7 @@
       </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148290</t>
+          <t>https://www.judge.com/jobs/details/1148139</t>
         </is>
       </c>
       <c r="J91" t="b">
@@ -6715,22 +6730,22 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-15T08:09:04+00:00</t>
+          <t>2026-08-20T00:04:09+00:00</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>8a6f124e5d536c8ef414</t>
+          <t>68dfd25047875496bc9e</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Analyst, Sales Operations - San Jose, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6757,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Clinical Data Analyst - Mendota, MN | Judge Group</t>
+          <t>Business Analyst - Denver, CO | Judge Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6772,7 +6787,7 @@
       </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152038</t>
+          <t>https://www.judge.com/jobs/details/1152312</t>
         </is>
       </c>
       <c r="J92" t="b">
@@ -6780,22 +6795,22 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-20T17:52:22+00:00</t>
+          <t>2026-09-15T18:37:24+00:00</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>bfe14f70ddd5ffa00fc7</t>
+          <t>f941cb0c25b86249f148</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Clinical Data Analyst - Mendota, MN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Business Analyst - Denver, CO | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6822,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group</t>
+          <t>Business Analyst - Fort Washington, PA | Judge Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6837,7 +6852,7 @@
       </c>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151557</t>
+          <t>https://www.judge.com/jobs/details/1148290</t>
         </is>
       </c>
       <c r="J93" t="b">
@@ -6845,22 +6860,22 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-22T23:20:34+00:00</t>
+          <t>2026-09-15T08:09:04+00:00</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>dbbd50ecf8c65363c2cf</t>
+          <t>8a6f124e5d536c8ef414</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6887,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Data Analyst - Bridgeport, PA | Judge Group</t>
+          <t>Clinical Data Analyst - Mendota, MN | Judge Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6902,7 +6917,7 @@
       </c>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1136576</t>
+          <t>https://www.judge.com/jobs/details/1152038</t>
         </is>
       </c>
       <c r="J94" t="b">
@@ -6910,22 +6925,22 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-20T17:52:22+00:00</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>c0ccf3207abc77a8082c</t>
+          <t>bfe14f70ddd5ffa00fc7</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Data Analyst - Bridgeport, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Clinical Data Analyst - Mendota, MN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6952,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Data Analyst - REMOTE | Judge Group</t>
+          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6947,7 +6962,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6967,7 +6982,7 @@
       </c>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152271</t>
+          <t>https://www.judge.com/jobs/details/1151557</t>
         </is>
       </c>
       <c r="J95" t="b">
@@ -6975,22 +6990,22 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-09-15T18:37:24+00:00</t>
+          <t>2026-09-22T23:20:34+00:00</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>b4f1d6b499090da09acc</t>
+          <t>dbbd50ecf8c65363c2cf</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Data Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7017,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Data Analyst - Raleigh, NC | Judge Group</t>
+          <t>Data Analyst - Bridgeport, PA | Judge Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7032,7 +7047,7 @@
       </c>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148342</t>
+          <t>https://www.judge.com/jobs/details/1136576</t>
         </is>
       </c>
       <c r="J96" t="b">
@@ -7040,22 +7055,22 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-08-20T21:14:14+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>f19e41e24774007ea610</t>
+          <t>c0ccf3207abc77a8082c</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Data Analyst - Raleigh, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst - Bridgeport, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7082,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group</t>
+          <t>Data Analyst - Quincy, MA | Judge Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7097,7 +7112,7 @@
       </c>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1153276</t>
+          <t>https://www.judge.com/jobs/details/1154548</t>
         </is>
       </c>
       <c r="J97" t="b">
@@ -7105,22 +7120,22 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-09-21T21:30:32+00:00</t>
+          <t>2026-09-29T00:48:58+00:00</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>4f3de9bf942013deebd3</t>
+          <t>a1a20ebd60e4b3f275ed</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7147,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group</t>
+          <t>Data Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7162,7 +7177,7 @@
       </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1154009</t>
+          <t>https://www.judge.com/jobs/details/1152271</t>
         </is>
       </c>
       <c r="J98" t="b">
@@ -7170,22 +7185,22 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-09-15T18:37:24+00:00</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>9e672045d3da1c9cd4fa</t>
+          <t>b4f1d6b499090da09acc</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7212,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Data Engineer III - Newport Beach, CA | Judge Group</t>
+          <t>Data Analyst - Raleigh, NC | Judge Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7227,7 +7242,7 @@
       </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1144820</t>
+          <t>https://www.judge.com/jobs/details/1148342</t>
         </is>
       </c>
       <c r="J99" t="b">
@@ -7235,22 +7250,22 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-09-21T08:22:47+00:00</t>
+          <t>2026-08-20T21:14:14+00:00</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>31d0b821f28109290adb</t>
+          <t>f19e41e24774007ea610</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Data Engineer III - Newport Beach, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst - Raleigh, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7277,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Charlotte, NC | Judge Group</t>
+          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7292,7 +7307,7 @@
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151679</t>
+          <t>https://www.judge.com/jobs/details/1153276</t>
         </is>
       </c>
       <c r="J100" t="b">
@@ -7300,22 +7315,22 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-09-21T21:30:32+00:00</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>eedfda40feaf829fbd7b</t>
+          <t>4f3de9bf942013deebd3</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7342,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Irving, TX | Judge Group</t>
+          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7337,7 +7352,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7357,7 +7372,7 @@
       </c>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152840</t>
+          <t>https://www.judge.com/jobs/details/1154009</t>
         </is>
       </c>
       <c r="J101" t="b">
@@ -7365,22 +7380,22 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-09-23T23:20:48+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>4dd97acc24963fd8d2f5</t>
+          <t>9e672045d3da1c9cd4fa</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7407,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Data Product Manager - Sacramento, CA | Judge Group</t>
+          <t>Data Engineer III - Newport Beach, CA | Judge Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7422,7 +7437,7 @@
       </c>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1135310</t>
+          <t>https://www.judge.com/jobs/details/1144820</t>
         </is>
       </c>
       <c r="J102" t="b">
@@ -7430,22 +7445,22 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-21T08:22:47+00:00</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>a89c4407724b716bd195</t>
+          <t>31d0b821f28109290adb</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Data Product Manager - Sacramento, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Engineer III - Newport Beach, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7472,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Data Scientist IV - Bridgewater, NJ | Judge Group</t>
+          <t>Data Management Analyst - Charlotte, NC | Judge Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7487,7 +7502,7 @@
       </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1073820</t>
+          <t>https://www.judge.com/jobs/details/1151679</t>
         </is>
       </c>
       <c r="J103" t="b">
@@ -7495,22 +7510,22 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-09-28T09:05:51+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>c71947cbb7c82f6e5c8f</t>
+          <t>eedfda40feaf829fbd7b</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Data Scientist IV - Bridgewater, NJ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Management Analyst - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7537,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Data Platforms, Integra - Dallas, TX | Judge Group</t>
+          <t>Data Management Analyst - Irving, TX | Judge Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7552,7 +7567,7 @@
       </c>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1150826</t>
+          <t>https://www.judge.com/jobs/details/1152840</t>
         </is>
       </c>
       <c r="J104" t="b">
@@ -7560,22 +7575,22 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-09-14T21:22:24+00:00</t>
+          <t>2026-09-23T23:20:48+00:00</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>d2654b8df420bb54954f</t>
+          <t>4dd97acc24963fd8d2f5</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Data Platforms, Integra - Dallas, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Management Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7602,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - Harrisburg, PA | Judge Group</t>
+          <t>Data Product Manager - Sacramento, CA | Judge Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7617,7 +7632,7 @@
       </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146284</t>
+          <t>https://www.judge.com/jobs/details/1135310</t>
         </is>
       </c>
       <c r="J105" t="b">
@@ -7625,22 +7640,22 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-08-10T15:43:04+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>3cc2077fc0d4218f6327</t>
+          <t>a89c4407724b716bd195</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - Harrisburg, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Product Manager - Sacramento, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7667,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Helpdesk Analyst - Malvern, PA | Judge Group</t>
+          <t>Data Scientist IV - Bridgewater, NJ | Judge Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7682,7 +7697,7 @@
       </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151341</t>
+          <t>https://www.judge.com/jobs/details/1073820</t>
         </is>
       </c>
       <c r="J106" t="b">
@@ -7690,22 +7705,22 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-09-23T14:05:04+00:00</t>
+          <t>2026-09-28T09:05:51+00:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>ce53ed4f7e18a63c41f4</t>
+          <t>c71947cbb7c82f6e5c8f</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Helpdesk Analyst - Malvern, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Scientist IV - Bridgewater, NJ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7732,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group</t>
+          <t>Enterprise Data Architect (Data Platforms, Integra - Dallas, TX | Judge Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7747,7 +7762,7 @@
       </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1140197</t>
+          <t>https://www.judge.com/jobs/details/1150826</t>
         </is>
       </c>
       <c r="J107" t="b">
@@ -7755,22 +7770,22 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-09-14T21:22:24+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>94849065fcdb6cf16558</t>
+          <t>d2654b8df420bb54954f</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Enterprise Data Architect (Data Platforms, Integra - Dallas, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7797,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Senior .Net AI Developer - Austin, TX | Judge Group</t>
+          <t>Functional Business Analyst - Irving, TX | Judge Group</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7812,7 +7827,7 @@
       </c>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151815</t>
+          <t>https://www.judge.com/jobs/details/1152177</t>
         </is>
       </c>
       <c r="J108" t="b">
@@ -7820,22 +7835,22 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-09-14T15:26:51+00:00</t>
+          <t>2026-09-29T00:48:58+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>149cf6b5d7418a85b10e</t>
+          <t>86259526f0dbe79dda99</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Senior .Net AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Functional Business Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7862,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Senior AI Developer - Southlake, TX | Judge Group</t>
+          <t>Helpdesk Analyst - Malvern, PA | Judge Group</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7877,7 +7892,7 @@
       </c>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1134711</t>
+          <t>https://www.judge.com/jobs/details/1151341</t>
         </is>
       </c>
       <c r="J109" t="b">
@@ -7885,22 +7900,22 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-09-25T08:11:27+00:00</t>
+          <t>2026-09-23T14:05:04+00:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>780df2da3a341d97cc3d</t>
+          <t>ce53ed4f7e18a63c41f4</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Senior AI Developer - Southlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Helpdesk Analyst - Malvern, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7927,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group</t>
+          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7942,7 +7957,7 @@
       </c>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1136598</t>
+          <t>https://www.judge.com/jobs/details/1140197</t>
         </is>
       </c>
       <c r="J110" t="b">
@@ -7950,22 +7965,22 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-09-17T18:40:12+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>7d81f6ff26fd959356ed</t>
+          <t>94849065fcdb6cf16558</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7992,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group</t>
+          <t>Senior .Net AI Developer - Austin, TX | Judge Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8007,7 +8022,7 @@
       </c>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148934</t>
+          <t>https://www.judge.com/jobs/details/1151815</t>
         </is>
       </c>
       <c r="J111" t="b">
@@ -8015,22 +8030,22 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-09-18T22:59:13+00:00</t>
+          <t>2026-09-14T15:26:51+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>07bfae59552b3c821572</t>
+          <t>149cf6b5d7418a85b10e</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior .Net AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8057,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Senior Java AI Developer - Austin, TX | Judge Group</t>
+          <t>Senior AI Developer - Southlake, TX | Judge Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8072,7 +8087,7 @@
       </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1145633</t>
+          <t>https://www.judge.com/jobs/details/1134711</t>
         </is>
       </c>
       <c r="J112" t="b">
@@ -8080,22 +8095,22 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-09-25T08:11:27+00:00</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>feac664cd0965bceede2</t>
+          <t>780df2da3a341d97cc3d</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Senior Java AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior AI Developer - Southlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8122,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group</t>
+          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8137,7 +8152,7 @@
       </c>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152660</t>
+          <t>https://www.judge.com/jobs/details/1136598</t>
         </is>
       </c>
       <c r="J113" t="b">
@@ -8145,22 +8160,22 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-09-16T23:20:04+00:00</t>
+          <t>2026-09-17T18:40:12+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2cc2da9382ae114b4977</t>
+          <t>7d81f6ff26fd959356ed</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8187,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sr. AI / ML Engineer - REMOTE | Judge Group</t>
+          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8182,7 +8197,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8202,7 +8217,7 @@
       </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146485</t>
+          <t>https://www.judge.com/jobs/details/1148934</t>
         </is>
       </c>
       <c r="J114" t="b">
@@ -8210,22 +8225,22 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-09-18T22:59:13+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>c8fc83cf9a9fbd548fd2</t>
+          <t>07bfae59552b3c821572</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Sr. AI / ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8252,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group</t>
+          <t>Senior Java AI Developer - Austin, TX | Judge Group</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8267,7 +8282,7 @@
       </c>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1147907</t>
+          <t>https://www.judge.com/jobs/details/1145633</t>
         </is>
       </c>
       <c r="J115" t="b">
@@ -8275,22 +8290,22 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>94c82ba3d6ab78504fcf</t>
+          <t>feac664cd0965bceede2</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior Java AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8317,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Support Analyst 1 - Tempe, AZ | Judge Group</t>
+          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8332,7 +8347,7 @@
       </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151176</t>
+          <t>https://www.judge.com/jobs/details/1152660</t>
         </is>
       </c>
       <c r="J116" t="b">
@@ -8340,22 +8355,22 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-09-28T19:01:50+00:00</t>
+          <t>2026-09-16T23:20:04+00:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>b3b2a4c5afdc040c1aa9</t>
+          <t>2cc2da9382ae114b4977</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Support Analyst 1 - Tempe, AZ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8382,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tapestry Configuration Analyst - REMOTE | Judge Group</t>
+          <t>Sr. AI / ML Engineer - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8397,7 +8412,7 @@
       </c>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1099718</t>
+          <t>https://www.judge.com/jobs/details/1146485</t>
         </is>
       </c>
       <c r="J117" t="b">
@@ -8405,22 +8420,22 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-09-21T21:30:32+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>867e313f74ad45486e73</t>
+          <t>c8fc83cf9a9fbd548fd2</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Tapestry Configuration Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Sr. AI / ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8447,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Technical Business Analyst - REMOTE | Judge Group</t>
+          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8442,7 +8457,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8462,7 +8477,7 @@
       </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1153570</t>
+          <t>https://www.judge.com/jobs/details/1147907</t>
         </is>
       </c>
       <c r="J118" t="b">
@@ -8470,22 +8485,22 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-09-22T23:20:34+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>c8e2837acf6512e9b2ab</t>
+          <t>94c82ba3d6ab78504fcf</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Technical Business Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8512,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Test Analyst III - Chattanooga, TN | Judge Group</t>
+          <t>Support Analyst 1 - Tempe, AZ | Judge Group</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8527,7 +8542,7 @@
       </c>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152671</t>
+          <t>https://www.judge.com/jobs/details/1151176</t>
         </is>
       </c>
       <c r="J119" t="b">
@@ -8540,29 +8555,29 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>7e0bfed42cef4d482dec</t>
+          <t>b3b2a4c5afdc040c1aa9</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Test Analyst III - Chattanooga, TN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Support Analyst 1 - Tempe, AZ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Administrative Assistant/Entry Level Business Analyst</t>
+          <t>Tapestry Configuration Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8572,17 +8587,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2015-10-20</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8592,12 +8602,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86114043-administrative-assistant-entry-level-business-analyst?oga=true</t>
+          <t>https://www.judge.com/jobs/details/1099718</t>
         </is>
       </c>
       <c r="J120" t="b">
@@ -8605,34 +8615,34 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-21T21:30:32+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>0824e44805cde39b3822</t>
+          <t>867e313f74ad45486e73</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Under the direction of supervisors, will be responsible for providing administrative support, as well as general clerical/secretarial support to the team. Ability to act as a team player, strong interpersonal skills, and willingness to multi-task and prioritize are critical requirements. Skills/Knowledge Required: MUST have - advanced skills: MS Outlook, Visio, Excel, Word, PowerPoint MUST have - experience with SOW contracts MUST have - IProcurement (Oracle) experience (2-4 years) Ability to work independently, while acting as a team player, as certain responsibilities will be shared. Willingness to work in a fast paced environment where individual initiative and accountability to the team are required. Strong interpersonal skills Ability to multi-task and prioritize. Excellent written and oral communication skills. "}, "qualifications": {"title": "Qualifications", "text": " Responsibilities will include, but are not limited to, the following: Providing administrative support to supervisors, including: Managing schedules, meetings, travel arrangements, and expense reports. Offering general secretarial/clerical support to supervisors. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. Implementing/organizing/maintaining files, records, and databases. Updating invoice tracking for supervisors. Telephone coverage, as assigned. Providing shared support to department Managers. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, kushal kumar Contact: +1 (201)932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>Tapestry Configuration Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Technical Business Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8642,17 +8652,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2016-01-13</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8662,12 +8667,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/88443359-application-support-analyst?oga=true</t>
+          <t>https://www.judge.com/jobs/details/1153570</t>
         </is>
       </c>
       <c r="J121" t="b">
@@ -8675,34 +8680,34 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-22T23:20:34+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>4299b8fc9cc8be3bfc33</t>
+          <t>c8e2837acf6512e9b2ab</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Key Responsibilities : • Flexible to work between 12pm to 9pm, Sunday to Friday (5 days a week) • Fully responsible for delivery of key feeds within the agreed SLA • Monitoring, Trouble shooting and Supporting the day to day activities • Use business and application knowledge to investigate issues raised and assist in the production of Incident reports, which form part of the shift handover • This role is to be the interface between users and IT project • Adherence to documented procedural standards • Escalate issues which cannot be resolved by the Analyst, in a timely manner • Have a strong Customer Focus in order to provide a professional support service to both internal and external cliental • To assist with the streamlining of the support area i.e. suggesting where procedures can be improved without the introduction of risk • Maintain Knowledge base and share experience with support team members • Should take ownership of any tasks/issue handled by the team (even when other teams involved) "}, "qualifications": {"title": "Qualifications", "text": " Qualifications / Technical knowledge &amp; Experience required : Qualifications: • Graduate in Computer Science discipline Technical Skills: • SQL knowledge (be able to read/write complex queries with joint between table, knowledge on optimizing SQL statements) • Unix (be comfortable working on a Unix environment) "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal kumar 201-932-1539 "}}</t>
+          <t>Technical Business Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Applications System Analyst</t>
+          <t>Test Analyst III - Chattanooga, TN | Judge Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8717,12 +8722,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2017-02-01</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107273359-applications-system-analyst?oga=true</t>
+          <t>https://www.judge.com/jobs/details/1152671</t>
         </is>
       </c>
       <c r="J122" t="b">
@@ -8745,22 +8745,22 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-28T19:01:50+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>e8f6fd68f0c8963a7a1b</t>
+          <t>7e0bfed42cef4d482dec</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " • Reviews, analyzes, and modifies programming systems including encoding, testing, debugging and installing to support an organization's application systems. • Consults with users to identify current operating procedures and to clarify program objectives. • May be expected to write documentation to describe program development, logic, coding, and corrections. • Writes manual for users to describe installation and operating procedures. • May require a bachelor's degree in a related area and 2-5 years of experience in the field or in a related area. • Familiar with relational databases and client-server concepts. • Relies on limited experience and judgment to plan and accomplish goals. • Performs a variety of tasks. Works under general supervision; typically reports to a project leader or manager. • A certain degree of creativity and latitude is required. "}, "qualifications": {"title": "Qualifications", "text": " NOTE: Need Google Analytics "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
+          <t>Test Analyst III - Chattanooga, TN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Business Analyst/Qlikeview Developer</t>
+          <t>Administrative Assistant/Entry Level Business Analyst</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86505098-business-analyst-qlikeview-developer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86114043-administrative-assistant-entry-level-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J123" t="b">
@@ -8820,17 +8820,17 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>9247a1e706741e8b0544</t>
+          <t>0824e44805cde39b3822</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " SPECIFIC SKILLS REQUIRED Superior knowledge of standard database tools, especially SQL Query writing, including relational and multidimensional database skills using SQL, Oracle, Sybase, MS Access. Must have at least 5-7 years’ experience in building and managing databases. 3-5 years’ experience with implementing and managing BI tools like Cognos, Business Objects, Microstrategy etc. Experience in developing and designing interactive dash boards and query, reporting, and analysis software, including data visualization programs like QlikTech, Tableau, Microsoft etc. QlikView Designer and Developer, User Interface Design, VBScript, Agile Development. 2-3 yrs experience designing &amp; developing query &amp; reports using in-memory data visualization programs Qlikview or Tableau is required. Experience in gathering requirement, server installation, migration, security management. Experience in developing QlikView and QVD files. Experience in setting up and management of QlikView server providing permission to users The Qlikview developer will be responsible for developing and documenting the Qlikview solution according to specified business requirements. The Qlik Developer will be responsible to build the data model and perform appropriate extract-transformation load (ETL) in support of the business requirements. "}, "qualifications": {"title": "Qualifications", "text": " EXPERIENCE REQUIRED Master’s degree in Computer Science, Information Technology or Information Sciences or Technical Discipline or equivalent 5-7 years of experience in business analytics; close work with sales analysis or providing tools to sales teams Database and SQL experience required. Excellent Analytical Skills are required. Experience in building dashboards and implementing businesses solutions. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Under the direction of supervisors, will be responsible for providing administrative support, as well as general clerical/secretarial support to the team. Ability to act as a team player, strong interpersonal skills, and willingness to multi-task and prioritize are critical requirements. Skills/Knowledge Required: MUST have - advanced skills: MS Outlook, Visio, Excel, Word, PowerPoint MUST have - experience with SOW contracts MUST have - IProcurement (Oracle) experience (2-4 years) Ability to work independently, while acting as a team player, as certain responsibilities will be shared. Willingness to work in a fast paced environment where individual initiative and accountability to the team are required. Strong interpersonal skills Ability to multi-task and prioritize. Excellent written and oral communication skills. "}, "qualifications": {"title": "Qualifications", "text": " Responsibilities will include, but are not limited to, the following: Providing administrative support to supervisors, including: Managing schedules, meetings, travel arrangements, and expense reports. Offering general secretarial/clerical support to supervisors. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. Implementing/organizing/maintaining files, records, and databases. Updating invoice tracking for supervisors. Telephone coverage, as assigned. Providing shared support to department Managers. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, kushal kumar Contact: +1 (201)932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Business analyst</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2015-10-23</t>
+          <t>2016-01-13</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86239602-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/88443359-application-support-analyst?oga=true</t>
         </is>
       </c>
       <c r="J124" t="b">
@@ -8890,17 +8890,17 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>62f9684d4a4312d88e6f</t>
+          <t>4299b8fc9cc8be3bfc33</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Key Responsibilities : • Flexible to work between 12pm to 9pm, Sunday to Friday (5 days a week) • Fully responsible for delivery of key feeds within the agreed SLA • Monitoring, Trouble shooting and Supporting the day to day activities • Use business and application knowledge to investigate issues raised and assist in the production of Incident reports, which form part of the shift handover • This role is to be the interface between users and IT project • Adherence to documented procedural standards • Escalate issues which cannot be resolved by the Analyst, in a timely manner • Have a strong Customer Focus in order to provide a professional support service to both internal and external cliental • To assist with the streamlining of the support area i.e. suggesting where procedures can be improved without the introduction of risk • Maintain Knowledge base and share experience with support team members • Should take ownership of any tasks/issue handled by the team (even when other teams involved) "}, "qualifications": {"title": "Qualifications", "text": " Qualifications / Technical knowledge &amp; Experience required : Qualifications: • Graduate in Computer Science discipline Technical Skills: • SQL knowledge (be able to read/write complex queries with joint between table, knowledge on optimizing SQL statements) • Unix (be comfortable working on a Unix environment) "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Business analyst</t>
+          <t>Applications System Analyst</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85863294-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107273359-applications-system-analyst?oga=true</t>
         </is>
       </c>
       <c r="J125" t="b">
@@ -8960,17 +8960,17 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>cc841923fe467641e8cf</t>
+          <t>e8f6fd68f0c8963a7a1b</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " • Reviews, analyzes, and modifies programming systems including encoding, testing, debugging and installing to support an organization's application systems. • Consults with users to identify current operating procedures and to clarify program objectives. • May be expected to write documentation to describe program development, logic, coding, and corrections. • Writes manual for users to describe installation and operating procedures. • May require a bachelor's degree in a related area and 2-5 years of experience in the field or in a related area. • Familiar with relational databases and client-server concepts. • Relies on limited experience and judgment to plan and accomplish goals. • Performs a variety of tasks. Works under general supervision; typically reports to a project leader or manager. • A certain degree of creativity and latitude is required. "}, "qualifications": {"title": "Qualifications", "text": " NOTE: Need Google Analytics "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Computer Vision Algorithm Engineer</t>
+          <t>Business Analyst/Qlikeview Developer</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100672079-computer-vision-algorithm-engineer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86505098-business-analyst-qlikeview-developer?oga=true</t>
         </is>
       </c>
       <c r="J126" t="b">
@@ -9030,17 +9030,17 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>17b90594009fe99d1583</t>
+          <t>9247a1e706741e8b0544</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Description and Requirements: Responsibilities/Descriptions: The candidate is expected to play an active role in computer vision technology development and implementation. Under the supervision of a senior scientist/researcher or project leader to conduct R&amp;D work in the areas of advanced computer vision/media processing technology. Qualifications / Requirements: Ph.D or Master degree in relevant discipline/field, such as EE or CS. * Strong programming skills in C / C++ for both Windows and Linux is a must * Ample hands-on experience with OpenCV is a strong plus * High proficiency and good experience with Android programming is a big plus. * Good programming skills in Java and Python is also a plus * 3+ years algorithm R&amp;D experiences in the areas of computer vision, information retrieval, machine learning, media processing, and related fields with proven track record. * Good communication skills, both verbal and written "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Saikat Ghosh Senior Technical Recruiter Desk: (201) 524 9600 Ext. 7452 Direct: (201) 613 5178 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " SPECIFIC SKILLS REQUIRED Superior knowledge of standard database tools, especially SQL Query writing, including relational and multidimensional database skills using SQL, Oracle, Sybase, MS Access. Must have at least 5-7 years’ experience in building and managing databases. 3-5 years’ experience with implementing and managing BI tools like Cognos, Business Objects, Microstrategy etc. Experience in developing and designing interactive dash boards and query, reporting, and analysis software, including data visualization programs like QlikTech, Tableau, Microsoft etc. QlikView Designer and Developer, User Interface Design, VBScript, Agile Development. 2-3 yrs experience designing &amp; developing query &amp; reports using in-memory data visualization programs Qlikview or Tableau is required. Experience in gathering requirement, server installation, migration, security management. Experience in developing QlikView and QVD files. Experience in setting up and management of QlikView server providing permission to users The Qlikview developer will be responsible for developing and documenting the Qlikview solution according to specified business requirements. The Qlik Developer will be responsible to build the data model and perform appropriate extract-transformation load (ETL) in support of the business requirements. "}, "qualifications": {"title": "Qualifications", "text": " EXPERIENCE REQUIRED Master’s degree in Computer Science, Information Technology or Information Sciences or Technical Discipline or equivalent 5-7 years of experience in business analytics; close work with sales analysis or providing tools to sales teams Database and SQL experience required. Excellent Analytical Skills are required. Experience in building dashboards and implementing businesses solutions. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Business analyst</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2017-02-07</t>
+          <t>2015-10-23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107710098-data-architect?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86239602-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J127" t="b">
@@ -9100,17 +9100,17 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>02e4361c9124b313e587</t>
+          <t>62f9684d4a4312d88e6f</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " RESPONSIBILITIES: • Translating customers business &amp; technical requirements into a data solution architecture in alignment with ADP's overall architectural directions and strategies. • A Technical leader who drives the customers’ transformation to modern Data Architecture &amp; store technologies such as NoSQL. • Develops a deep understanding of the current/future technical challenges of customers, and based on that understanding, formulates an aspirational application architecture and transformation roadmap. • Translates complex Data store centric requirements and use cases to technical artifacts such as application specifications, data models and architectural blueprints. • Identify and implement Performance improvements and track performance metrics. • Establish and drive standards (performance, security) across products. • Develop strategies for data acquisition; achieve recovery, and implementation of database. • Should work with Database Administrators and Data Analysts to ensure they can easily use and access data. • Maintain database integrity and plan for natural disaster and cyber-attacks. • Making use of code and data the architect should turn it into logical patterns that can be used for analysis purpose. • Deliver convincing and persuasive presentations to both technical and business teams. • As the custodian of Common Data Model will provide the requisite standards and governance around the canonical model. "}, "qualifications": {"title": "Qualifications", "text": " QUALIFICATIONS REQUIRED: • Excellent knowledge of Computation Theory, Data Structures, Algorithms, Design Patterns and Data Modelling techniques. • Excellent communication, articulation and presentation skills. • Experience building large scale distributed data processing systems/applications. • Strong foundational knowledge and experience with distributed systems and computing systems in general. • Deep understanding of various ETL/ELT tools is required. • Skilled at logical and physical data modeling, data policies, warehousing, strategy and query languages. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Business analyst</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2016-10-25</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100992416-data-migration-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85863294-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J128" t="b">
@@ -9170,17 +9170,17 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2b87177fd8a91d1b3c10</t>
+          <t>cc841923fe467641e8cf</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": ""}, "qualifications": {"title": "Qualifications", "text": " Required qualifications: • At least 5 years of IT related experience • 3-5 years working with databases with demonstrated expertise in SQL, PL/SQL, Oracle 11, ETL tools, Data conversion, Data De-duplication, Data Cleansing methodologies • Be able to build SQL data queries • Demonstrated experience in analyzing data sets and Effective at understanding a problem and developing one or many approaches to solving the problem. • Assist in designing, planning and managing the data migration process. • Work with subject matter experts and project team to identify, define, collate, document and communicate the data migration requirements. • Experience in Data Migration methodologies • Highly effective working in a team, as well as working independently. • Perform source system data analysis in order to manage source to target data mapping. • Perform migration and testing of static data and transaction data from one core system to another. • Perform data migration audit, reconciliation and exception reporting. • Assist with the identification of trends or patterns in complex data sets • Filter and “clean” data, and review reports, printouts, and performance indicators Create Test Plans and Test Cases for all scenario types and execute. (i.e. positive, negative testing, boundary) Verify requirement traceability from System Requirements through test cases and defects Ensure that testing activities will allow applications to meet business requirements and systems goals, fulfil end-user requirements, and identify and resolve systems issues Work with the developers to understand the technical requirement/design being built in a project Validate Test Preparation of environments and verify all teams are aligned with what needs to occur to build/prepare the test environments Coordinate, track and report regularly on execution of system testing Verify defects are effectively recorded, communicated and understood Analyze and ensure test results and changes/defect are reflected in the test case and test cases are updated appropriately based on resolution Identify and recommend process improvements as necessary Excellent written and oral communication skills Excellent listening and interpersonal skills (includes</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Data Security analyst</t>
+          <t>Computer Vision Algorithm Engineer</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2016-10-20</t>
+          <t>2016-10-19</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100745719-data-security-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100672079-computer-vision-algorithm-engineer?oga=true</t>
         </is>
       </c>
       <c r="J129" t="b">
@@ -9240,17 +9240,17 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>bce9bd6942bda16e1d08</t>
+          <t>17b90594009fe99d1583</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Scope/Responsibilities/Duties: • 0-2 years general experience, bachelor’ s degree or equivalent combo of education/experience; • Some experience in desired tech area; position functions with high level of supervision; • Assesses security and/or compliance of university systems; responsible for assessing, monitoring and analyzing data, identifying security, risk or compliance issues and/or events • Leveraging job aids for common issues or incidents • Demonstrated ability to work in a team, attention to detail, solid written communications and some technology experience • To perform system based risk assessments. • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "qualifications": {"title": "Qualifications", "text": " • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards, Kushal Kumar Talent Acquisition Specialist Tel: 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Description and Requirements: Responsibilities/Descriptions: The candidate is expected to play an active role in computer vision technology development and implementation. Under the supervision of a senior scientist/researcher or project leader to conduct R&amp;D work in the areas of advanced computer vision/media processing technology. Qualifications / Requirements: Ph.D or Master degree in relevant discipline/field, such as EE or CS. * Strong programming skills in C / C++ for both Windows and Linux is a must * Ample hands-on experience with OpenCV is a strong plus * High proficiency and good experience with Android programming is a big plus. * Good programming skills in Java and Python is also a plus * 3+ years algorithm R&amp;D experiences in the areas of computer vision, information retrieval, machine learning, media processing, and related fields with proven track record. * Good communication skills, both verbal and written "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Saikat Ghosh Senior Technical Recruiter Desk: (201) 524 9600 Ext. 7452 Direct: (201) 613 5178 "}}</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EDI Programmer Analyst &amp; Manager</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2016-06-29</t>
+          <t>2017-02-07</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93892950-edi-programmer-analyst-manager?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107710098-data-architect?oga=true</t>
         </is>
       </c>
       <c r="J130" t="b">
@@ -9310,17 +9310,17 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>36926768d7d1374bbba5</t>
+          <t>02e4361c9124b313e587</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: EDI Programmer Analyst &amp; Manager Duration: Permanent/Full Time Location: San Francisco, CA Interview: Phone &amp; F2F(But can do Skype) Locals are highly preferred "}, "qualifications": {"title": "Qualifications", "text": " Proficient in: · BizTalk · EDI application mapping techniques · HIPAA ASC X12 transaction sets for healthcare (834, 837, 277, 835, 997/9, 270/1, 276/7, Proprietary Auths) · HIPAA 5010 · HIPAA security policies and procedures. · .NET &amp; SQL · Systems implementation "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Chandra Kumar Tel: 201-549-2655 Desk: (201) 524 9600 Ext: 7794 chandra at ustechsolutionsinc dot com "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " RESPONSIBILITIES: • Translating customers business &amp; technical requirements into a data solution architecture in alignment with ADP's overall architectural directions and strategies. • A Technical leader who drives the customers’ transformation to modern Data Architecture &amp; store technologies such as NoSQL. • Develops a deep understanding of the current/future technical challenges of customers, and based on that understanding, formulates an aspirational application architecture and transformation roadmap. • Translates complex Data store centric requirements and use cases to technical artifacts such as application specifications, data models and architectural blueprints. • Identify and implement Performance improvements and track performance metrics. • Establish and drive standards (performance, security) across products. • Develop strategies for data acquisition; achieve recovery, and implementation of database. • Should work with Database Administrators and Data Analysts to ensure they can easily use and access data. • Maintain database integrity and plan for natural disaster and cyber-attacks. • Making use of code and data the architect should turn it into logical patterns that can be used for analysis purpose. • Deliver convincing and persuasive presentations to both technical and business teams. • As the custodian of Common Data Model will provide the requisite standards and governance around the canonical model. "}, "qualifications": {"title": "Qualifications", "text": " QUALIFICATIONS REQUIRED: • Excellent knowledge of Computation Theory, Data Structures, Algorithms, Design Patterns and Data Modelling techniques. • Excellent communication, articulation and presentation skills. • Experience building large scale distributed data processing systems/applications. • Strong foundational knowledge and experience with distributed systems and computing systems in general. • Deep understanding of various ETL/ELT tools is required. • Skilled at logical and physical data modeling, data policies, warehousing, strategy and query languages. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EFT Processing Analyst</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2015-12-09</t>
+          <t>2016-10-25</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87772674-eft-processing-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100992416-data-migration-analyst?oga=true</t>
         </is>
       </c>
       <c r="J131" t="b">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>ff66976e897c4a7cacad</t>
+          <t>2b87177fd8a91d1b3c10</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Title: EFT Processing Analyst Duration: Approx. 3 months Location: Austin, TX Responsibilities: Perform ACH operational functions within required deadlines and NACHA compliance. Process received ACH exception-items and disputes, including DNE s and WSUD s. Originate R10 s, NOC s and other manual return items. Gather verifications for deposit-exceptions for cardholder account management. Reply to garnishments, liens, and levies in a timely, accurate, and compliant manner. Take phone calls and respond to inquiries from customers, banks, government entities, and internal departments. Provide consistent, high-quality customer service that meets or exceeds established standards. Maintain spreadsheets related to credit-adjustment activity, and create regular summaries and reports on departmental activities using Access, Excel, and Word. Recommend improvements that result in more efficient procedures. Understand and adhere to strict compliance and regulatory requirements. Comfortably work within a defined attendance and punctuality policy that is designed to help our customers. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Sam Contact : 201-613-5164 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": ""}, "qualifications": {"title": "Qualifications", "text": " Required qualifications: • At least 5 years of IT related experience • 3-5 years working with databases with demonstrated expertise in SQL, PL/SQL, Oracle 11, ETL tools, Data conversion, Data De-duplication, Data Cleansing methodologies • Be able to build SQL data queries • Demonstrated experience in analyzing data sets and Effective at understanding a problem and developing one or many approaches to solving the problem. • Assist in designing, planning and managing the data migration process. • Work with subject matter experts and project team to identify, define, collate, document and communicate the data migration requirements. • Experience in Data Migration methodologies • Highly effective working in a team, as well as working independently. • Perform source system data analysis in order to manage source to target data mapping. • Perform migration and testing of static data and transaction data from one core system to another. • Perform data migration audit, reconciliation and exception reporting. • Assist with the identification of trends or patterns in complex data sets • Filter and “clean” data, and review reports, printouts, and performance indicators Create Test Plans and Test Cases for all scenario types and execute. (i.e. positive, negative testing, boundary) Verify requirement traceability from System Requirements through test cases and defects Ensure that testing activities will allow applications to meet business requirements and systems goals, fulfil end-user requirements, and identify and resolve systems issues Work with the developers to understand the technical requirement/design being built in a project Validate Test Preparation of environments and verify all teams are aligned with what needs to occur to build/prepare the test environments Coordinate, track and report regularly on execution of system testing Verify defects are effectively recorded, communicated and understood Analyze and ensure test results and changes/defect are reflected in the test case and test cases are updated appropriately based on resolution Identify and recommend process improvements as necessary Excellent written and oral communication skills Excellent listening and interpersonal skills (includes</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MDM Data Analyst I</t>
+          <t>Data Security analyst</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2016-12-06</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/103472117-mdm-data-analyst-i?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100745719-data-security-analyst?oga=true</t>
         </is>
       </c>
       <c r="J132" t="b">
@@ -9450,17 +9450,17 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>3a12d7e1695e93f24087</t>
+          <t>bce9bd6942bda16e1d08</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Title: MDM Data Analyst I Location: Lexington, MA, 02421 Duration: 12-+ Months Description: The MDM Data Analyst reports to the MDM/Data Governance Manager and is responsible for the end-to-end master data customer and product maintenance processes within U.S. Commercial Operations. This person is responsible for MDM data quality, processes and business rules. He/she will be responsible for working with the various business area leads to ensure cross-team processes are efficient and master data is consistent, accurate and compliant across applications. % of Time Job Function and Description 35% Data Steward Team Management • Responsible for daily MDM data steward activities • Perform ad hoc customer and product master data requests • Participate in MDM UAT testing 45% Operational Excellence • Responsible for defining MDM Standard Operating Procedures (SOPs) and Work Instructions (WIs) • Responsible for ensuring the accuracy and completeness of customer and product master data • Responsible for understanding the end-to-end processes for maintaining customer master and product data across business areas • Responsible for customer and product data harmonization across multiple sources 20% Cross-Functional Collaboration • Work closely with Commercial Ops Governance team and adhere to implemented principles and process standards • Work with IT to coordinate and define business user impacts of MDM application changes including resolving issues and planning for enhancements and upgrades • Assist in the definition of master data sourcing and services strategies including the evaluation of third party data providers and services under the direction of the MDM/Data Governance Manager Education and Experience Requirements • Bachelor's degree in the field of computer science, information technology, engineering or business administration, Management Information Systems, Finance, Sciences or related area or equivalent experience • Advanced Degree preferred • 1-3 years of work experience, Pharma related preferred • Informatica MDM/IDD experience preferred • One full cycle of an MDM implementation preferred • Has basic knowledge of Pharmaceutical Commercial business environment/operations Key Skills, Abilities, and Competencies • Establishes good working relat</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Scope/Responsibilities/Duties: • 0-2 years general experience, bachelor’ s degree or equivalent combo of education/experience; • Some experience in desired tech area; position functions with high level of supervision; • Assesses security and/or compliance of university systems; responsible for assessing, monitoring and analyzing data, identifying security, risk or compliance issues and/or events • Leveraging job aids for common issues or incidents • Demonstrated ability to work in a team, attention to detail, solid written communications and some technology experience • To perform system based risk assessments. • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "qualifications": {"title": "Qualifications", "text": " • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards, Kushal Kumar Talent Acquisition Specialist Tel: 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mobile Automation Test Analyst</t>
+          <t>EDI Programmer Analyst &amp; Manager</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2016-06-08</t>
+          <t>2016-06-29</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93157465-mobile-automation-test-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93892950-edi-programmer-analyst-manager?oga=true</t>
         </is>
       </c>
       <c r="J133" t="b">
@@ -9520,17 +9520,17 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>80c10598e102ec2e4da0</t>
+          <t>36926768d7d1374bbba5</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: Mobile Automation Test Analyst Duration: 6 – 12 + Months Location: Anoka, MN Interview: Phone &amp; F2F Mandate "}, "qualifications": {"title": "Qualifications", "text": " • 8+ years of experience in software automation testing, with 3-4+ years of experience in UFT/selenium automation experience • Expert in UFT 12.5 with Perfecto Mobil combination • Object Oriented programming – class structure, code re-use, abstract thinking/Page object model • Strong sense of self-motivation, organizing, strong analytical skills and attention to details • Hands-on experience in VB/Java scripting/ Junit/TestNG/programing experience • Experience in reporting metrics and status to management • Experience writing complex SQL queries • Experience in Mobile Testing(Perfecto/Appium) • Experience working with multiple software development methodologies and QA Tools • Manual QA concepts like laying out a scenario into design steps (linear thinking) • Experience in an Agile environment/Behavior driven Development testing(Cucumber/Specflow) "}, "additionalInformation": {"title": "Additional Information", "text": " Chandra Kumar 201-549-2655 Chandra at ustechsolutionsinc com "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: EDI Programmer Analyst &amp; Manager Duration: Permanent/Full Time Location: San Francisco, CA Interview: Phone &amp; F2F(But can do Skype) Locals are highly preferred "}, "qualifications": {"title": "Qualifications", "text": " Proficient in: · BizTalk · EDI application mapping techniques · HIPAA ASC X12 transaction sets for healthcare (834, 837, 277, 835, 997/9, 270/1, 276/7, Proprietary Auths) · HIPAA 5010 · HIPAA security policies and procedures. · .NET &amp; SQL · Systems implementation "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Chandra Kumar Tel: 201-549-2655 Desk: (201) 524 9600 Ext: 7794 chandra at ustechsolutionsinc dot com "}}</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shipboard Business Systems Analyst</t>
+          <t>EFT Processing Analyst</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2015-12-11</t>
+          <t>2015-12-09</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87837860-shipboard-business-systems-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87772674-eft-processing-analyst?oga=true</t>
         </is>
       </c>
       <c r="J134" t="b">
@@ -9590,17 +9590,17 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>c6ecd4c346de62f82786</t>
+          <t>ff66976e897c4a7cacad</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Essential Day to Day Responsibilities: • Analyzes business and user needs, documentation of requirements per RCCL standards, and translation into proper system requirement specifications. • Participate in solution option evaluations with IT teams and business partners. • Responsible for initial planning and estimation of low to moderate complexity projects and requests. • Interfaces with PMO on developing a comprehensive project plan and leading business partners in their areas such as training, testing, operational changes/plans, user acceptance testing and deployment to the field (global locations). • Remains engaged throughout the project at critical milestones, also working with business partners on their portions of the project. • Assists in providing product training to internal IT teams. Required skills/competencies: The ideal candidate will have experience working in a large hotel/resort environment along with knowledge of and experience supporting enterprise back office systems. The successful candidate will be expected to gain knowledge of current cruise, hotel/resort, entertainment and technology trends and be able to participate in discussion of their application in the cruise industry and at RCCL. "}, "qualifications": {"title": "Qualifications", "text": " CANDIDATE QUALIFICATIONS • Excellent interpersonal skills, including oral and written communication skills • Relevant experience as a Business Analyst, some directly with business teams • Hospitality Experience, including Front Office, Back Office, and Guest Entertainment Systems support required • Experience with Mobile Hospitality solutions (iOS/Android) • Excellent organizational skills • Ability to adapt and excel in a fast paced, dynamic work environment • Ability to manage changing priorities • Ability to make sound business decisions, putting the good of the team, the project and of RCCL first. • Ability to own and drive issues to resolution, sense of urgency with strong follow-up skills • Experience developing and executing testing strategies &amp; test scripts • Ability to work with and maintain confidential and proprietary information. Candidate may be required to agree to and sign project related Non-disclosure agreements. Preferred Skills: Experience of Fidelio Cruise Property</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Title: EFT Processing Analyst Duration: Approx. 3 months Location: Austin, TX Responsibilities: Perform ACH operational functions within required deadlines and NACHA compliance. Process received ACH exception-items and disputes, including DNE s and WSUD s. Originate R10 s, NOC s and other manual return items. Gather verifications for deposit-exceptions for cardholder account management. Reply to garnishments, liens, and levies in a timely, accurate, and compliant manner. Take phone calls and respond to inquiries from customers, banks, government entities, and internal departments. Provide consistent, high-quality customer service that meets or exceeds established standards. Maintain spreadsheets related to credit-adjustment activity, and create regular summaries and reports on departmental activities using Access, Excel, and Word. Recommend improvements that result in more efficient procedures. Understand and adhere to strict compliance and regulatory requirements. Comfortably work within a defined attendance and punctuality policy that is designed to help our customers. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Sam Contact : 201-613-5164 "}}</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst/BIE</t>
+          <t>MDM Data Analyst I</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2016-12-06</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85837517-sr-data-analyst-bie?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/103472117-mdm-data-analyst-i?oga=true</t>
         </is>
       </c>
       <c r="J135" t="b">
@@ -9660,17 +9660,17 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>598b89494bc90bc7bd81</t>
+          <t>3a12d7e1695e93f24087</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Key Responsibilities: · Track and report on the metrics and trends we rely upon to run our business. · Answer ad hoc questions that help inform our product design decisions. · Use data to identify opportunities and then use spoken and written words to influence stakeholders and tech teams to respond to them · Architect the right data ecosystem to efficiently supply the answers we need · Define product requirements, success metrics, and A/B testing schemes that accelerate our pace of innovation · Audit launched products and recommend iterative steps based on measurable results · Uphold the highest standards of data collection, reporting, and analysis across our team through all phases of software development "}, "qualifications": {"title": "Qualifications", "text": " The successful candidate will demonstrate: · A track record delivering impactful results in a consumer oriented industry · High attention to detail and precision in all forms of communication · Proven ability to influence everyone from executives to teammates · A composed, poised and professional demeanor. · A history of teamwork and willingness to roll up one’s sleeves to get the job done · Strong analytical and quantitative skills (including the ability to effectively use tools such as Excel and SQL on large data sets) and an ability to use hard data and metrics to back up assumptions and develop project business cases. Basic Qualifications · BS or MS or PHD in Applied Mathematics, Statistics, Economics, Computer Science or other quantitative disciplines · Experience working with large data sets · Excellent SQL query skills · Strong problem solving skills, and an ability to apply them in the context of a fast-paced business environment · Good written and oral communication skills to translate complex models and analysis results into layman terms · Capable and motivated to collaboratively work with a diverse and innovative team of engineers, analysts, operations personnel and business management to deliver results. · Familiarity with statistical methodologies Preferred Qualifications · Previous product or program management experience · Thrives in agile environments · Comfortable working in a Unix/Linux environment · Experience with web analytics · Experience in experimental design · Pre</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Title: MDM Data Analyst I Location: Lexington, MA, 02421 Duration: 12-+ Months Description: The MDM Data Analyst reports to the MDM/Data Governance Manager and is responsible for the end-to-end master data customer and product maintenance processes within U.S. Commercial Operations. This person is responsible for MDM data quality, processes and business rules. He/she will be responsible for working with the various business area leads to ensure cross-team processes are efficient and master data is consistent, accurate and compliant across applications. % of Time Job Function and Description 35% Data Steward Team Management • Responsible for daily MDM data steward activities • Perform ad hoc customer and product master data requests • Participate in MDM UAT testing 45% Operational Excellence • Responsible for defining MDM Standard Operating Procedures (SOPs) and Work Instructions (WIs) • Responsible for ensuring the accuracy and completeness of customer and product master data • Responsible for understanding the end-to-end processes for maintaining customer master and product data across business areas • Responsible for customer and product data harmonization across multiple sources 20% Cross-Functional Collaboration • Work closely with Commercial Ops Governance team and adhere to implemented principles and process standards • Work with IT to coordinate and define business user impacts of MDM application changes including resolving issues and planning for enhancements and upgrades • Assist in the definition of master data sourcing and services strategies including the evaluation of third party data providers and services under the direction of the MDM/Data Governance Manager Education and Experience Requirements • Bachelor's degree in the field of computer science, information technology, engineering or business administration, Management Information Systems, Finance, Sciences or related area or equivalent experience • Advanced Degree preferred • 1-3 years of work experience, Pharma related preferred • Informatica MDM/IDD experience preferred • One full cycle of an MDM implementation preferred • Has basic knowledge of Pharmaceutical Commercial business environment/operations Key Skills, Abilities, and Competencies • Establishes good working relat</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sr. IT Communication Analyst</t>
+          <t>Mobile Automation Test Analyst</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2016-06-08</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86563413-sr-it-communication-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93157465-mobile-automation-test-analyst?oga=true</t>
         </is>
       </c>
       <c r="J136" t="b">
@@ -9730,17 +9730,17 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>618dae4b9e249bc47945</t>
+          <t>80c10598e102ec2e4da0</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Prerequisites: · 10-15 year experience in corporate or internal communications required IT marketing experience preferred Experience providing communications planning and implementation for a matrixed, global IT organization · Experience sourcing images, developing artwork and developing logos · Pharmaceutical industry experience a plus Ability to deal effectively with all levels of an organization, from senior executives to entry-level team members · Ability to build effective personal networks to get things done with a minimum of resources · Excellent written and verbal communication skills are required · Ability to synthesize complex IT concepts and information for a non-IT audience Strong presentation and facilitation skills · Experience planning global, remote communication events such as town halls and managing related equipment · Experience with web design and content management · Experience with SharePoint Advanced proficiency with Word, PowerPoint, Outlook and Excel · Experience in Internet imaging sourcing and concept design · Strong knowledge of communications best practices "}, "qualifications": {"title": "Qualifications", "text": " Summary: This position serves as the internal strategic and tactical communications lead for the Global Information Technology organization. Responsibilities will include, but are not limited to, the following: · Establish, maintain and evolve the communication framework within global IT organization Develop overall strategic communication plan in alignment with global IT strategies, goals and objectives · Manage and produce quarterly, global IT town hall meetings for Chief Information Officer, including logistics, agenda, content, on-site staffing and post-event measurement Manage and produce quarterly, functional town hall meetings for IT Senior Leadership Team (ITSLT) members, including logistics, agenda, content, on-site staffing and post-event measurement via surveys · Draft and review executive presentations for internal Client audiences and external industry audiences · Schedule and communicate executive meet and greet sessions (e.g., Breakfast with the CIO) · Review, edit and communicate annual Global IT goals and objectives in consultation with the Chief Information Officer Ensure strategic alignment</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: Mobile Automation Test Analyst Duration: 6 – 12 + Months Location: Anoka, MN Interview: Phone &amp; F2F Mandate "}, "qualifications": {"title": "Qualifications", "text": " • 8+ years of experience in software automation testing, with 3-4+ years of experience in UFT/selenium automation experience • Expert in UFT 12.5 with Perfecto Mobil combination • Object Oriented programming – class structure, code re-use, abstract thinking/Page object model • Strong sense of self-motivation, organizing, strong analytical skills and attention to details • Hands-on experience in VB/Java scripting/ Junit/TestNG/programing experience • Experience in reporting metrics and status to management • Experience writing complex SQL queries • Experience in Mobile Testing(Perfecto/Appium) • Experience working with multiple software development methodologies and QA Tools • Manual QA concepts like laying out a scenario into design steps (linear thinking) • Experience in an Agile environment/Behavior driven Development testing(Cucumber/Specflow) "}, "additionalInformation": {"title": "Additional Information", "text": " Chandra Kumar 201-549-2655 Chandra at ustechsolutionsinc com "}}</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Support Analyst</t>
+          <t>Shipboard Business Systems Analyst</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2015-12-11</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/109625889-support-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87837860-shipboard-business-systems-analyst?oga=true</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9800,29 +9800,29 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2a655a025e9258d5b76f</t>
+          <t>c6ecd4c346de62f82786</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi , My name is Raghava from Keshav Consulting Solutions. I have job opening with one of our direct clients. Below is the job description for your reference. Title: Support Analyst Duration: 12 Months Location: 4101 Capital Blvd. Raleigh NC 27604 Job Description: Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. The support consists of documenting and coordinating activities with respect to the installation and configuration of Genetec Security Center and IP cameras, SV32 devices, door aggregators and all system components deployed for FACS project. •Support to the Enterprise Application team, in respect to the installation and configuration of Genetec Security Center and IP cameras SV32 devices, door aggregators and all system components deployed for FACS project.•Assisting the deployment team with troubleshooting installation/configuration issues for the Genetec Security Center and Samsung IP cameras.•Receiving, logging and fully documenting requests for support from help desk, other service delivery staff and/or users; investigate problems and other requests for support from the deployment/project team and determine appropriate actions to be taken.•Monitoring progress of requests for support through resolution and ensure users and other interested parties are kept informed.•Escalate 3rd party software and hardware issues to Application Owner; insuring proper attention is given to the issue depending on severity and impact to project schedule.• Communicating technical information to a variety of internal and external stakeholders both verbally and in writing. Technical writing services and support for the developing software documentation at the enterprise level. Provide services documenting technical configurations for a complex multi-site deployment of a Genetec System for Access Control and Video Management at NCDOT.•Assist in the creation of document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Maintain and update as needed the document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Must have the ability to capture incidents and issues identified by the project with the ability to document resolution(s) for the team leader providing weekly status reports to Management.•Proven experience with supporting</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Essential Day to Day Responsibilities: • Analyzes business and user needs, documentation of requirements per RCCL standards, and translation into proper system requirement specifications. • Participate in solution option evaluations with IT teams and business partners. • Responsible for initial planning and estimation of low to moderate complexity projects and requests. • Interfaces with PMO on developing a comprehensive project plan and leading business partners in their areas such as training, testing, operational changes/plans, user acceptance testing and deployment to the field (global locations). • Remains engaged throughout the project at critical milestones, also working with business partners on their portions of the project. • Assists in providing product training to internal IT teams. Required skills/competencies: The ideal candidate will have experience working in a large hotel/resort environment along with knowledge of and experience supporting enterprise back office systems. The successful candidate will be expected to gain knowledge of current cruise, hotel/resort, entertainment and technology trends and be able to participate in discussion of their application in the cruise industry and at RCCL. "}, "qualifications": {"title": "Qualifications", "text": " CANDIDATE QUALIFICATIONS • Excellent interpersonal skills, including oral and written communication skills • Relevant experience as a Business Analyst, some directly with business teams • Hospitality Experience, including Front Office, Back Office, and Guest Entertainment Systems support required • Experience with Mobile Hospitality solutions (iOS/Android) • Excellent organizational skills • Ability to adapt and excel in a fast paced, dynamic work environment • Ability to manage changing priorities • Ability to make sound business decisions, putting the good of the team, the project and of RCCL first. • Ability to own and drive issues to resolution, sense of urgency with strong follow-up skills • Experience developing and executing testing strategies &amp; test scripts • Ability to work with and maintain confidential and proprietary information. Candidate may be required to agree to and sign project related Non-disclosure agreements. Preferred Skills: Experience of Fidelio Cruise Property</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AI Architect - Agentic AI</t>
+          <t>Sr. Data Analyst/BIE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9837,7 +9837,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9847,12 +9852,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/AI-Architect-Agentic-AI/191866-en_US</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85837517-sr-data-analyst-bie?oga=true</t>
         </is>
       </c>
       <c r="J138" t="b">
@@ -9860,34 +9865,34 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-06T05:54:14+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>1e0078f336199470d02f</t>
+          <t>598b89494bc90bc7bd81</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>AI Architect - Agentic AI Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Architect - Agentic AI City: Seongnam-si State/Province: Gyeonggido Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at w</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Key Responsibilities: · Track and report on the metrics and trends we rely upon to run our business. · Answer ad hoc questions that help inform our product design decisions. · Use data to identify opportunities and then use spoken and written words to influence stakeholders and tech teams to respond to them · Architect the right data ecosystem to efficiently supply the answers we need · Define product requirements, success metrics, and A/B testing schemes that accelerate our pace of innovation · Audit launched products and recommend iterative steps based on measurable results · Uphold the highest standards of data collection, reporting, and analysis across our team through all phases of software development "}, "qualifications": {"title": "Qualifications", "text": " The successful candidate will demonstrate: · A track record delivering impactful results in a consumer oriented industry · High attention to detail and precision in all forms of communication · Proven ability to influence everyone from executives to teammates · A composed, poised and professional demeanor. · A history of teamwork and willingness to roll up one’s sleeves to get the job done · Strong analytical and quantitative skills (including the ability to effectively use tools such as Excel and SQL on large data sets) and an ability to use hard data and metrics to back up assumptions and develop project business cases. Basic Qualifications · BS or MS or PHD in Applied Mathematics, Statistics, Economics, Computer Science or other quantitative disciplines · Experience working with large data sets · Excellent SQL query skills · Strong problem solving skills, and an ability to apply them in the context of a fast-paced business environment · Good written and oral communication skills to translate complex models and analysis results into layman terms · Capable and motivated to collaboratively work with a diverse and innovative team of engineers, analysts, operations personnel and business management to deliver results. · Familiarity with statistical methodologies Preferred Qualifications · Previous product or program management experience · Thrives in agile environments · Comfortable working in a Unix/Linux environment · Experience with web analytics · Experience in experimental design · Pre</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. IT Communication Analyst</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9897,12 +9902,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9912,12 +9922,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/AI-Engineer/192784-en_US</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86563413-sr-it-communication-analyst?oga=true</t>
         </is>
       </c>
       <c r="J139" t="b">
@@ -9925,34 +9935,34 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-07T15:38:07+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>9c78a109514702595d71</t>
+          <t>618dae4b9e249bc47945</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Engineer City: Austin State/Province: Texas Posting Start Date: 8/7/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Prerequisites: · 10-15 year experience in corporate or internal communications required IT marketing experience preferred Experience providing communications planning and implementation for a matrixed, global IT organization · Experience sourcing images, developing artwork and developing logos · Pharmaceutical industry experience a plus Ability to deal effectively with all levels of an organization, from senior executives to entry-level team members · Ability to build effective personal networks to get things done with a minimum of resources · Excellent written and verbal communication skills are required · Ability to synthesize complex IT concepts and information for a non-IT audience Strong presentation and facilitation skills · Experience planning global, remote communication events such as town halls and managing related equipment · Experience with web design and content management · Experience with SharePoint Advanced proficiency with Word, PowerPoint, Outlook and Excel · Experience in Internet imaging sourcing and concept design · Strong knowledge of communications best practices "}, "qualifications": {"title": "Qualifications", "text": " Summary: This position serves as the internal strategic and tactical communications lead for the Global Information Technology organization. Responsibilities will include, but are not limited to, the following: · Establish, maintain and evolve the communication framework within global IT organization Develop overall strategic communication plan in alignment with global IT strategies, goals and objectives · Manage and produce quarterly, global IT town hall meetings for Chief Information Officer, including logistics, agenda, content, on-site staffing and post-event measurement Manage and produce quarterly, functional town hall meetings for IT Senior Leadership Team (ITSLT) members, including logistics, agenda, content, on-site staffing and post-event measurement via surveys · Draft and review executive presentations for internal Client audiences and external industry audiences · Schedule and communicate executive meet and greet sessions (e.g., Breakfast with the CIO) · Review, edit and communicate annual Global IT goals and objectives in consultation with the Chief Information Officer Ensure strategic alignment</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ANALYST L3</t>
+          <t>Support Analyst</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9967,7 +9977,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9977,12 +9992,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/ANALYST-L3/191665-en_US</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/109625889-support-analyst?oga=true</t>
         </is>
       </c>
       <c r="J140" t="b">
@@ -9990,22 +10005,22 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-08-26T09:29:59+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>b60ef76300a4cd102640</t>
+          <t>2a655a025e9258d5b76f</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>ANALYST L3 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L3 City: Chennai State/Province: Tamil Nadu Posting Start Date: 9/10/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Ext</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi , My name is Raghava from Keshav Consulting Solutions. I have job opening with one of our direct clients. Below is the job description for your reference. Title: Support Analyst Duration: 12 Months Location: 4101 Capital Blvd. Raleigh NC 27604 Job Description: Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. The support consists of documenting and coordinating activities with respect to the installation and configuration of Genetec Security Center and IP cameras, SV32 devices, door aggregators and all system components deployed for FACS project. •Support to the Enterprise Application team, in respect to the installation and configuration of Genetec Security Center and IP cameras SV32 devices, door aggregators and all system components deployed for FACS project.•Assisting the deployment team with troubleshooting installation/configuration issues for the Genetec Security Center and Samsung IP cameras.•Receiving, logging and fully documenting requests for support from help desk, other service delivery staff and/or users; investigate problems and other requests for support from the deployment/project team and determine appropriate actions to be taken.•Monitoring progress of requests for support through resolution and ensure users and other interested parties are kept informed.•Escalate 3rd party software and hardware issues to Application Owner; insuring proper attention is given to the issue depending on severity and impact to project schedule.• Communicating technical information to a variety of internal and external stakeholders both verbally and in writing. Technical writing services and support for the developing software documentation at the enterprise level. Provide services documenting technical configurations for a complex multi-site deployment of a Genetec System for Access Control and Video Management at NCDOT.•Assist in the creation of document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Maintain and update as needed the document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Must have the ability to capture incidents and issues identified by the project with the ability to document resolution(s) for the team leader providing weekly status reports to Management.•Proven experience with supporting</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10032,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>AI Architect - Agentic AI</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10047,7 +10062,7 @@
       </c>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Agentic-AI-Engineer/199620-en_US</t>
+          <t>https://careers.wipro.com/job/AI-Architect-Agentic-AI/191866-en_US</t>
         </is>
       </c>
       <c r="J141" t="b">
@@ -10055,22 +10070,22 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-09-23T08:08:19+00:00</t>
+          <t>2026-08-06T05:54:14+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>69a88595cd09fa24a854</t>
+          <t>1e0078f336199470d02f</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Agentic AI Engineer City: Pune State/Province: Maharashtra Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job</t>
+          <t>AI Architect - Agentic AI Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Architect - Agentic AI City: Seongnam-si State/Province: Gyeonggido Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at w</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10097,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10112,7 +10127,7 @@
       </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/19657-en_US</t>
+          <t>https://careers.wipro.com/job/AI-Engineer/192784-en_US</t>
         </is>
       </c>
       <c r="J142" t="b">
@@ -10120,22 +10135,22 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-07T15:38:07+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>712e3cf849669eebaeb3</t>
+          <t>9c78a109514702595d71</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram, Bengaluru State/Province: Haryana, Karnataka Posting Start Date: 1/8/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Des</t>
+          <t>AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: AI Engineer City: Austin State/Province: Texas Posting Start Date: 8/7/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10162,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>ANALYST L3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10177,7 +10192,7 @@
       </c>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/19047-en_US</t>
+          <t>https://careers.wipro.com/job/ANALYST-L3/191665-en_US</t>
         </is>
       </c>
       <c r="J143" t="b">
@@ -10185,22 +10200,22 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-08-26T09:29:59+00:00</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2309aeb0bc27a46040b3</t>
+          <t>b60ef76300a4cd102640</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 10/24/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Des</t>
+          <t>ANALYST L3 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L3 City: Chennai State/Province: Tamil Nadu Posting Start Date: 9/10/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Ext</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10227,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10242,7 +10257,7 @@
       </c>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/182957-en_US</t>
+          <t>https://careers.wipro.com/job/Agentic-AI-Engineer/199620-en_US</t>
         </is>
       </c>
       <c r="J144" t="b">
@@ -10250,22 +10265,22 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-09-15T13:59:48+00:00</t>
+          <t>2026-09-23T08:08:19+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>7cb438ddc969c89c7d8c</t>
+          <t>69a88595cd09fa24a854</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 9/2/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: ͏ Job Sum</t>
+          <t>Agentic AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Agentic AI Engineer City: Pune State/Province: Maharashtra Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10322,7 @@
       </c>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/23385-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/19657-en_US</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -10320,17 +10335,17 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>bb5a134aabb09236d773</t>
+          <t>712e3cf849669eebaeb3</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 1/16/25 Job Description: Job Description Designation: Analyst Band: B1 Job Location: Bangalore ( Work from Office Time: 6:00 PM-3:30 AM JOB DESCRIPTION: • Build customizations using extensions and scripts to meet business needs. • Actively identify opportunities to leverage Coupa functionality to improve efficiency. • Troubleshoot and debug production issues that users may have which could be data, process, Coupa configuration or integration related. • Support the Procure-to-Pay department during the month-end/quarter-end/Year-end close process. • Ensure that change control procedures are implemented and used for all production deployments. • User administration including ass</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram, Bengaluru State/Province: Haryana, Karnataka Posting Start Date: 1/8/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Des</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10387,7 @@
       </c>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/162758-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/19047-en_US</t>
         </is>
       </c>
       <c r="J146" t="b">
@@ -10380,22 +10395,22 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-03T17:08:04+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>97dfd4270978d9297118</t>
+          <t>2309aeb0bc27a46040b3</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 7/30/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 10/24/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Des</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10422,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DATA ANALYST</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10437,7 +10452,7 @@
       </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/DATA-ANALYST/197280-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/182957-en_US</t>
         </is>
       </c>
       <c r="J147" t="b">
@@ -10445,22 +10460,22 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-09-23T14:05:04+00:00</t>
+          <t>2026-09-15T13:59:48+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>d0914ba92a9b445faf35</t>
+          <t>7cb438ddc969c89c7d8c</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>DATA ANALYST Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ANALYST City: Bengaluru State/Province: Karnataka Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 9/2/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: ͏ Job Sum</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10487,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10502,7 +10517,7 @@
       </c>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Analyst/196228-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/23385-en_US</t>
         </is>
       </c>
       <c r="J148" t="b">
@@ -10510,22 +10525,22 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-08-29T01:26:31+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>f7d25f7312ae32cfbc12</t>
+          <t>bb5a134aabb09236d773</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 8/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 1/16/25 Job Description: Job Description Designation: Analyst Band: B1 Job Location: Bangalore ( Work from Office Time: 6:00 PM-3:30 AM JOB DESCRIPTION: • Build customizations using extensions and scripts to meet business needs. • Actively identify opportunities to leverage Coupa functionality to improve efficiency. • Troubleshoot and debug production issues that users may have which could be data, process, Coupa configuration or integration related. • Support the Procure-to-Pay department during the month-end/quarter-end/Year-end close process. • Ensure that change control procedures are implemented and used for all production deployments. • User administration including ass</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10552,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10567,7 +10582,7 @@
       </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Analyst/200306-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/162758-en_US</t>
         </is>
       </c>
       <c r="J149" t="b">
@@ -10575,22 +10590,22 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-09-14T01:28:49+00:00</t>
+          <t>2026-08-03T17:08:04+00:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>d884e86067c9f7f10787</t>
+          <t>97dfd4270978d9297118</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 9/14/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 7/30/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10617,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DATA ANALYST</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10632,7 +10647,7 @@
       </c>
       <c r="I150" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Engineer/192310-en_US</t>
+          <t>https://careers.wipro.com/job/DATA-ANALYST/197280-en_US</t>
         </is>
       </c>
       <c r="J150" t="b">
@@ -10640,22 +10655,22 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-08-18T21:08:33+00:00</t>
+          <t>2026-09-23T14:05:04+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>d47c28254b000471923e</t>
+          <t>d0914ba92a9b445faf35</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Fremont State/Province: California Posting Start Date: 8/12/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descriptio</t>
+          <t>DATA ANALYST Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ANALYST City: Bengaluru State/Province: Karnataka Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10682,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10697,7 +10712,7 @@
       </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Engineer-Snowflake/200874-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Analyst/196228-en_US</t>
         </is>
       </c>
       <c r="J151" t="b">
@@ -10705,22 +10720,22 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-09-17T08:03:32+00:00</t>
+          <t>2026-08-29T01:26:31+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>cffdb590701a93c539f7</t>
+          <t>f7d25f7312ae32cfbc12</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer - Snowflake City: Hyderabad State/Province: Telangana Posting Start Date: 9/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.</t>
+          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 8/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10747,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10762,7 +10777,7 @@
       </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Engineer-Snowflake/200876-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Analyst/200306-en_US</t>
         </is>
       </c>
       <c r="J152" t="b">
@@ -10770,22 +10785,22 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-09-17T08:03:32+00:00</t>
+          <t>2026-09-14T01:28:49+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>20859ae6fdf458f20e60</t>
+          <t>d884e86067c9f7f10787</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer - Snowflake City: Hyderabad State/Province: Telangana Posting Start Date: 9/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.</t>
+          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 9/14/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10812,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Data Governance</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10827,7 +10842,7 @@
       </c>
       <c r="I153" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Governance/179068-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Engineer/192310-en_US</t>
         </is>
       </c>
       <c r="J153" t="b">
@@ -10840,17 +10855,17 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>3f7c4b325f4b1f4d7d95</t>
+          <t>d47c28254b000471923e</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Data Governance Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Governance City: Hyderabad State/Province: Telangana Posting Start Date: 8/4/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descri</t>
+          <t>Data Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer City: Fremont State/Province: California Posting Start Date: 8/12/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descriptio</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10877,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Data Governance Architect</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10892,7 +10907,7 @@
       </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Governance-Architect/193372-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Engineer-Snowflake/200874-en_US</t>
         </is>
       </c>
       <c r="J154" t="b">
@@ -10900,22 +10915,22 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30:24+00:00</t>
+          <t>2026-09-17T08:03:32+00:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>edf308822f3df20c07d0</t>
+          <t>cffdb590701a93c539f7</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Data Governance Architect Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Governance Architect City: Bengaluru State/Province: Karnataka Posting Start Date: 8/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.</t>
+          <t>Data Engineer - Snowflake Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer - Snowflake City: Hyderabad State/Province: Telangana Posting Start Date: 9/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10942,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Data Operations Analyst / Senior Analyst</t>
+          <t>Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10957,7 +10972,7 @@
       </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Operations-Analyst-Senior-Analyst/192719-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Engineer-Snowflake/200876-en_US</t>
         </is>
       </c>
       <c r="J155" t="b">
@@ -10965,22 +10980,22 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-09-25T01:55:13+00:00</t>
+          <t>2026-09-17T08:03:32+00:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>0abc1c6fe1f2d9a02d7f</t>
+          <t>20859ae6fdf458f20e60</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Data Operations Analyst / Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Operations Analyst / Senior Analyst City: Curitiba State/Province: Parana Posting Start Date: 8/10/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional inf</t>
+          <t>Data Engineer - Snowflake Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Engineer - Snowflake City: Hyderabad State/Province: Telangana Posting Start Date: 9/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.</t>
         </is>
       </c>
     </row>
@@ -10992,7 +11007,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Data Governance</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -11022,7 +11037,7 @@
       </c>
       <c r="I156" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Generative-AI-Engineer/187523-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Governance/179068-en_US</t>
         </is>
       </c>
       <c r="J156" t="b">
@@ -11030,22 +11045,22 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-08-19T18:08:19+00:00</t>
+          <t>2026-08-18T21:08:33+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>6f69e0d39b8c90e69cfb</t>
+          <t>3f7c4b325f4b1f4d7d95</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Generative AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Generative AI Engineer City: Bengaluru State/Province: Karnataka Posting Start Date: 9/10/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.</t>
+          <t>Data Governance Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Governance City: Hyderabad State/Province: Telangana Posting Start Date: 8/4/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descri</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11072,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Job Description: Data Operations, Investment Data Management</t>
+          <t>Data Governance Architect</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -11087,7 +11102,7 @@
       </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Operations%2C-Investment-Data-Management/192721-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Governance-Architect/193372-en_US</t>
         </is>
       </c>
       <c r="J157" t="b">
@@ -11095,22 +11110,22 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-18T21:08:33+00:00</t>
+          <t>2026-09-22T18:30:24+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>280de90787812a9f6d98</t>
+          <t>edf308822f3df20c07d0</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Data Operations, Investment Data Management Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Operations, Investment Data Management City: Curitiba State/Province: Parana Posting Start Date: 9/22/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For addition</t>
+          <t>Data Governance Architect Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Governance Architect City: Bengaluru State/Province: Karnataka Posting Start Date: 8/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11137,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lead Analyst</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11152,7 +11167,7 @@
       </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Lead-Analyst/123472-en_US</t>
+          <t>https://careers.wipro.com/job/Generative-AI-Engineer/187523-en_US</t>
         </is>
       </c>
       <c r="J158" t="b">
@@ -11160,22 +11175,22 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-08T00:15:00+00:00</t>
+          <t>2026-08-19T18:08:19+00:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>5b23b17405108c284d71</t>
+          <t>6f69e0d39b8c90e69cfb</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Lead Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Lead Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 6/18/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description</t>
+          <t>Generative AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Generative AI Engineer City: Bengaluru State/Province: Karnataka Posting Start Date: 9/10/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11202,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PLM AI Engineer</t>
+          <t>Job Description: Data Operations, Investment Data Management</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11217,7 +11232,7 @@
       </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/PLM-AI-Engineer/185484-en_US</t>
+          <t>https://careers.wipro.com/job/Data-Operations%2C-Investment-Data-Management/192721-en_US</t>
         </is>
       </c>
       <c r="J159" t="b">
@@ -11225,22 +11240,22 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-09-17T18:40:12+00:00</t>
+          <t>2026-08-18T21:08:33+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>a164c0d142b84a13709b</t>
+          <t>280de90787812a9f6d98</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>PLM AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: PLM AI Engineer City: Sunnyvale State/Province: California Posting Start Date: 9/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Desc</t>
+          <t>Data Operations, Investment Data Management Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Operations, Investment Data Management City: Curitiba State/Province: Parana Posting Start Date: 9/22/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For addition</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11267,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PLM AI Engineer</t>
+          <t>Lead Analyst</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11282,7 +11297,7 @@
       </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/PLM-AI-Engineer/185485-en_US</t>
+          <t>https://careers.wipro.com/job/Lead-Analyst/123472-en_US</t>
         </is>
       </c>
       <c r="J160" t="b">
@@ -11290,22 +11305,22 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-09-28T19:01:50+00:00</t>
+          <t>2026-08-08T00:15:00+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>3d3c284c6f97accaf8d0</t>
+          <t>5b23b17405108c284d71</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>PLM AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: PLM AI Engineer City: Sunnyvale State/Province: California Posting Start Date: 9/28/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Desc</t>
+          <t>Lead Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Lead Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 6/18/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11332,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Senior Analyst</t>
+          <t>PLM AI Engineer</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11347,7 +11362,7 @@
       </c>
       <c r="I161" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Senior-Analyst/16386-en_US</t>
+          <t>https://careers.wipro.com/job/PLM-AI-Engineer/185484-en_US</t>
         </is>
       </c>
       <c r="J161" t="b">
@@ -11355,22 +11370,22 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-17T18:40:12+00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-29T00:48:58+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>891e384b5304d97d4cca</t>
+          <t>a164c0d142b84a13709b</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Senior Analyst City: State/Province: Posting Start Date: 4/3/25 Job Description: Job Description JOB DESCRIPTION – Legal &amp; Compliance Services LOB Financial Services PREFERRED SECTOR/INDUSTRY Legal &amp; Compliance DESIGNATION B2 – Sr. Analyst QUALIFICATION • CS. (Must) • LL. B (preferred but not mandatory) JOB LOCATION Delhi/NCR EXPERIENCE REQUIRED 3.5- 6 years JOB RESPONSIBILITIES The role of Sr. Analyst in Legal &amp; Compliance shall encompass various tasks including, but not limited to, the following: • Preparation of management committee meetings, board meetings and the GP’s of Client funds • Drafting of management committee and board meetings minutes and review of GP minutes including maintaining policies/minutes trackers/action logs in t</t>
+          <t>PLM AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: PLM AI Engineer City: Sunnyvale State/Province: California Posting Start Date: 9/17/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Desc</t>
         </is>
       </c>
     </row>
@@ -11382,65 +11397,195 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
+          <t>PLM AI Engineer</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>HTTP+Playwright</t>
+        </is>
+      </c>
+      <c r="I162" s="1" t="inlineStr">
+        <is>
+          <t>https://careers.wipro.com/job/PLM-AI-Engineer/185485-en_US</t>
+        </is>
+      </c>
+      <c r="J162" t="b">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2026-09-28T19:01:50+00:00</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:55:28+00:00</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>3d3c284c6f97accaf8d0</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>PLM AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: PLM AI Engineer City: Sunnyvale State/Province: California Posting Start Date: 9/28/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
           <t>Senior Analyst</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>See posting</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>See posting</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>See posting</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>HTTP+Playwright</t>
         </is>
       </c>
-      <c r="I162" s="1" t="inlineStr">
+      <c r="I163" s="1" t="inlineStr">
+        <is>
+          <t>https://careers.wipro.com/job/Senior-Analyst/16386-en_US</t>
+        </is>
+      </c>
+      <c r="J163" t="b">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-07-30T00:33:09+00:00</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:55:28+00:00</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>891e384b5304d97d4cca</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Senior Analyst City: State/Province: Posting Start Date: 4/3/25 Job Description: Job Description JOB DESCRIPTION – Legal &amp; Compliance Services LOB Financial Services PREFERRED SECTOR/INDUSTRY Legal &amp; Compliance DESIGNATION B2 – Sr. Analyst QUALIFICATION • CS. (Must) • LL. B (preferred but not mandatory) JOB LOCATION Delhi/NCR EXPERIENCE REQUIRED 3.5- 6 years JOB RESPONSIBILITIES The role of Sr. Analyst in Legal &amp; Compliance shall encompass various tasks including, but not limited to, the following: • Preparation of management committee meetings, board meetings and the GP’s of Client funds • Drafting of management committee and board meetings minutes and review of GP minutes including maintaining policies/minutes trackers/action logs in t</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Senior Analyst</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>See posting</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>HTTP+Playwright</t>
+        </is>
+      </c>
+      <c r="I164" s="1" t="inlineStr">
         <is>
           <t>https://careers.wipro.com/job/Senior-Analyst/14307-en_US</t>
         </is>
       </c>
-      <c r="J162" t="b">
-        <v>0</v>
-      </c>
-      <c r="K162" t="inlineStr">
+      <c r="J164" t="b">
+        <v>0</v>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>2026-07-30T19:17:06+00:00</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>2026-09-29T00:48:58+00:00</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:55:28+00:00</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t>39bd94d407e60c75b549</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr">
+      <c r="N164" t="inlineStr">
         <is>
           <t>Senior Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Senior Analyst City: Gurugram State/Province: Haryana Posting Start Date: 4/11/25 Job Description: Job Description Job title: Senior Analyst – Investment Management – Structured Finance Band: B2 - Senior Analyst Experience Range: Minimum 4 year Shift Timings-: 2:00 PM - 11:30 PM IST Responsibilities: • Deal Management: Collaborate closely with ABF Deal Analysts to assist in investment management and monitoring activities for structured finance deals. • IC Memos: Support the deal team in updating Investment Committee approval memos, ensuring a comprehensive understanding of each deal's intricacies. • Term sheets: Analyze closing documents such as credit agreements, indentures and note purchase agreements and set up processes for analyzing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N162"/>
+  <autoFilter ref="A1:N164"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
@@ -11603,6 +11748,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/data-ai-jobs.xlsx
+++ b/output/data-ai-jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$N$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N227"/>
+  <dimension ref="A1:N231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -522,7 +522,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Metals Analyst job in Frankfort, Illinois, USA | Actalent Careers</t>
+          <t>1st Shift Quality Analyst Float Role job in Oak Creek, Wisconsin, USA | Actalent Careers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006333019/Metals-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006325804/1st-Shift-Quality-Analyst-Float-Role</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -560,39 +560,39 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>800b8d8fff873ef4f971</t>
+          <t>47aa21ac9c6aa6fc5cc3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Metals Analyst job in Frankfort, Illinois, USA | Laboratory &amp; Sciences jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices af9576fb35144862b5cd58625cd3ba57</t>
+          <t>1st Shift Quality Analyst Float Role job in Oak Creek, Wisconsin, USA | Laboratory &amp; Sciences jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices f3383697147b4ec5ab41b068158e6529</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kforce</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IT App Security Analyst</t>
+          <t>Quality Analyst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Vandalia, Ohio, 45377, USA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -602,7 +602,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -617,7 +622,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://myhiring.kforce.com/careersection/ex/jobdetail.ftl?job=260569&amp;tz=GMT%2B00%3A00&amp;tzname=UTC</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006307531/Quality-Analyst</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -625,39 +630,39 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1deefb33608c95298288</t>
+          <t>83e23d9636b0a5999c9b</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Kforce Career Section Go to the main content section. | My Account Options | We're glad you're here. This service is set to disconnect automatically after {0} minutes of inactivity. Your session will end in {1} minutes. Click OK to reset the timer to {0} minutes. You have been signed out. This service is set to sign out after {0} minutes of inactivity. Job Search My Jobpage Basic Search | Advanced Search | My Submissions | My Job Cart | My Saved Searches | Beginning of the main content section. Return to the home page Printable Format Return to previous position on page - ( ) Qualifications : Refer a friend for this job Refer a friend Refer a candidate Submit a candidate's profile</t>
+          <t>Actively Interviewing for Quality Analysts in Dayton, OH! Job Description The Quality Analyst I performs quality control inspection and disposition of materials and products according to established specifications and regulatory requirements. This role conducts inspections using appropriate measuring instruments and methods, manages non-conforming materials and products within the established Quality System, and ensures adherence to applicable FDA, OSHA, and ISO regulations and standards. The position involves working under limited supervision, supporting lot release activities, and contributing to continuous improvement of quality processes in a rapidly growing, state-of-the-art facility. Responsibilities Perform reviews of batch production records and manufacturing records as part of lot release activities. Coordinate and track Corrective and Preventive Action (CAPA), Non-Conforming Report (NCR), and Deviation records, ensuring all tasks are completed on time. Coordinate and track the site environmental monitoring (EM) testing program. Assist teams in coordinating problem solving and root cause analysis for quality events. Ensure the development, review, and release of quarterly environmental monitoring trending reports and promptly escalate significant trends to management. Provide input based on knowledge and experience with batch release requirements. Provide Quality Management System (QMS) operations support to all current Good Manufacturing Practice (CGMP) departments. Perform Quality Control activities at processing or distribution sites, including incoming material inspections, in-process inspections, and finished product inspections. Inspect a range of products including medical devices, sterile processed human tissue-based products, unprocessed human tissue, component supplies, and labeling materials. Maintain accurate and complete records of Quality Control activities in accordance with Good Documentation Practices (GDP). Provide support related to gowning qualification and training. Ensure timely issuance, review, and approval of microbiology and environmental monitoring testing results. Interface with colleagues to ensure effective corrective and preventive actions are implemented for recurring product or process discrepancies. Assist in the review and approval of equipment qualifications. Assist in the review of calibration and preventive maintenance activities. Assist in hosting onsite regulatory audits and inspections. Essential Skills Bachelor’s degree in a Life Science discipline or a related field. Minimum of 1–2 years of relevant industry experience with GMP, GDP, or GxP within a medical device, pharmaceutical, or tissue commercial organization preferred. Experience working in an FDA-regulated environment, particularly medical device, human tissue, or pharmaceutical manufacturing preferred. Demonstrated experience with Quality System elements for CAPA, Non-Conforming Reports (NCRs), and Deviations. Experience with Microsoft E</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Logistics Analyst</t>
+          <t>Quality Analyst</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>Vandalia, Ohio, 45377, USA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -667,12 +672,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>["CONTRACTOR"]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -687,7 +692,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/logistics-analyst-/5880519</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006317887/Quality-Analyst</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -695,54 +700,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>55a327dd3e52a4c3c560</t>
+          <t>8759483a60f0331dc0db</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Logistics Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Logistics Analyst Reference Number: 5880519 Published Date: 10/07/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE As a Logistics Analyst, you will support the Logistics and Transportation departments by enhancing data visibility, automating reporting processes, and developing analytical tools that facilitate faster and more informed business decisions. The ideal candidate will demonstrate strong analytical skills, a proactive approach, and excellent communication abilities, aligning well with the organization’s commitment to operational excellence and continuous improvement. Job Title: Logistics Analyst Location: Valencia, CA Pay Range: $28 - $30/hr. Shift: 40 hours a week What's the Job? Support Logistics and Transportation teams by improving data visibility and developing analytical tools. Automate recurring logistics reports to streamline data collection and reduce manual effort. Analyze transportation and logistics data to identify trends, risks, and cost-saving opportunities. Create and maintain Power BI dashboards and reports supporting operational metrics. Collaborate with cross-functional teams to translate operational needs into technical solutions and automation workflows. What's Needed? Bachelor’s degree in supply chain, Business Analytics, Data Analytics, or related field. 2–5 years of experience developing reports and dashboards using Power BI. Strong proficiency in Microsoft Excel, including data analysis, PivotTables, and advanced formulas. Experience working with ERP systems such as JD Edwards (JDE), SAP, or similar platforms. Excellent analytical, problem-solving, and communication skills with the ability to work with la</t>
+          <t>We are actively hiring for Quality Analysts to support a regenerative medicine laboratory here in the north Dayton, OH area. This role will primarily involve reviewing documentation to support the lab, coordinating and tracking Corrective and Preventative Actions (CAPAs), and other desk related duties. This role will not be in the lab, and will be more of a desk based role. Ideal candidates will have a Bachelors Degree in a scientific field and at minimum 6 months-1+ year of experience working in a highly regulated environment (food manufacturing, pharmaceutical, cosmetic, etc.). INTERESTED CANDIDATES CAN SEND UPDATED RESUMES TO MAMCDONOUGH @ACTALENTSERVICES .COM OR TEXT MARISA AT 330. 397. 1302 TO SET UP AN IMMEDIATE PHONE INTERVIEW! Job Description The Quality Analyst I performs quality control inspection and disposition of materials and products according to established specifications and regulatory requirements. This role conducts inspections using appropriate measuring instruments and methods, manages non-conforming materials and products within the established Quality System, and ensures adherence to applicable FDA, OSHA, and ISO regulations and standards. The position involves working under limited supervision, supporting lot release activities, and contributing to continuous improvement of quality processes in a rapidly growing, state-of-the-art facility. Responsibilities Perform reviews of batch production records and manufacturing records as part of lot release activities. Coordinate and track Corrective and Preventive Action (CAPA), Non-Conforming Report (NCR), and Deviation records, ensuring all tasks are completed on time. Coordinate and track the site environmental monitoring (EM) testing program. Assist teams in coordinating problem solving and root cause analysis for quality events. Ensure the development, review, and release of quarterly environmental monitoring trending reports and promptly escalate significant trends to management. Provide input based on knowledge and experience with batch release requirements. Provide Quality Management System (QMS) operations support to all current Good Manufacturing Practice (CGMP) departments. Perform Quality Control activities at processing or distribution sites, including incoming material inspections, in-process inspections, and finished product inspections. Inspect a range of products including medical devices, sterile processed human tissue-based products, unprocessed human tissue, component supplies, and labeling materials. Maintain accurate and complete records of Quality Control activities in accordance with Good Documentation Practices (GDP). Provide support related to gowning qualification and training. Ensure timely issuance, review, and approval of microbiology and environmental monitoring testing results. Interface with colleagues to ensure effective corrective and preventive actions are implemented for recurring product or process discrepancies. Assist in the review and approv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MeeBoss</t>
+          <t>Actalent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Remote Data Analyst</t>
+          <t>Scientific Quality Analyst</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Dayton, Ohio, 45390, USA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>["full-time", "part-time"]</t>
+          <t>["FULL_TIME"]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -752,12 +757,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/f9de3a96b9b346f33nJ60g~~</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006308834/Scientific-Quality-Analyst</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -765,54 +770,54 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>be9c60d44dc0559d1e15</t>
+          <t>f8084ffe768e890b6ed2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Remote Data Analyst Company: Gylden Pharma Position: Data Analyst Work Arrangement: 100% Remote Compensation: $68 per hour Schedule: Flexible — Full-Time or Part-Time Position Overview Gylden Pharma is seeking a detail-oriented and analytical Data Analyst to join our remote team. The Data Analyst will collect, analyze, interpret, and present data to support informed business decisions and improve operational performance. The ideal candidate will be comfortable working with large datasets, identifying trends and patterns, preparing reports and dashboards, and communicating analytical findings to both technical and non-technical stakeholders. This position offers flexible working hours , with the option to work either full-time or part-time based on availability and project requirements. Key Responsibilities Collect, organize, validate, and analyze data from multiple sources. Identify trends, patterns, anomalies, and opportunities within datasets. Develop and maintain reports, dashboards, and data visualizations. Translate business questions into meaningful data analyses. Prepare regular and ad-hoc analytical reports for management and stakeholders. Monitor key performance indicators (KPIs) and provide actionable insights. Collaborate with project managers, business teams, and other departments to support data-driven decision-making. Perform data cleaning, validation, and quality checks. Maintain accurate documentation of data sources, methodologies, and analytical processes. Assist with forecasting, performance analysis, and operational reporting. Communicate findings clearly through presentations, reports, and visualizations. Identify opportunities to improve data quality, reporting processes, and analytical workflows. Protect confidential and sensitive company information in accordance with applicable policies. Qualifications Bachelor's degree in Data Analytics, Statistics, Mathematics, Computer Science, Business, Economics, or a related field preferred. 2+ years of experience in data analysis, business intelligence, reporting, or a related field preferred. Strong proficiency in Microsoft Excel and experience working with spreadsheets and large datasets. Experience with SQL and relational databases. Experience using data visualization tools such as Tableau, Power BI, or similar platforms . Strong analytical and problem-solving abilities. Excellent attention to detail and accuracy. Ability to communicate complex analytical findings in a clear and understandable manner. Strong written and verbal communication skills. Ability to manage multiple projects and deadlines independently in a remote environment. Preferred Qualifications Experience working in pharmaceutical, healthcare, biotechnology, life sciences, or another regulated industry. Experience with Python, R, or other data-analysis programming languages. Experience with statistical analysis and forecasting. Familiarity with healthcare, pharmaceutical, clinical, or operational datasets. Knowle</t>
+          <t>We are actively hiring for Quality Analysts to support a regenerative medicine laboratory here in the north Dayton, OH area. This role will primarily involve reviewing documentation to support the lab, coordinating and tracking Corrective and Preventative Actions (CAPAs), and other desk related duties. This role will not be in the lab, and will be more of a desk based role. Ideal candidates will have a Bachelors Degree in a scientific field and at minimum 6 months-1+ year of experience working in a highly regulated environment (food manufacturing, pharmaceutical, cosmetic, etc.). Job Description The Quality Analyst I performs quality control inspection and disposition of materials and products according to established specifications and regulatory requirements. This role conducts inspections using appropriate measuring instruments and methods, manages non-conforming materials and products within the established Quality System, and ensures adherence to applicable FDA, OSHA, and ISO regulations and standards. The position involves working under limited supervision, supporting lot release activities, and contributing to continuous improvement of quality processes in a rapidly growing, state-of-the-art facility. Responsibilities Perform reviews of batch production records and manufacturing records as part of lot release activities. Coordinate and track Corrective and Preventive Action (CAPA), Non-Conforming Report (NCR), and Deviation records, ensuring all tasks are completed on time. Coordinate and track the site environmental monitoring (EM) testing program. Assist teams in coordinating problem solving and root cause analysis for quality events. Ensure the development, review, and release of quarterly environmental monitoring trending reports and promptly escalate significant trends to management. Provide input based on knowledge and experience with batch release requirements. Provide Quality Management System (QMS) operations support to all current Good Manufacturing Practice (CGMP) departments. Perform Quality Control activities at processing or distribution sites, including incoming material inspections, in-process inspections, and finished product inspections. Inspect a range of products including medical devices, sterile processed human tissue-based products, unprocessed human tissue, component supplies, and labeling materials. Maintain accurate and complete records of Quality Control activities in accordance with Good Documentation Practices (GDP). Provide support related to gowning qualification and training. Ensure timely issuance, review, and approval of microbiology and environmental monitoring testing results. Interface with colleagues to ensure effective corrective and preventive actions are implemented for recurring product or process discrepancies. Assist in the review and approval of equipment qualifications. Assist in the review of calibration and preventive maintenance activities. Assist in hosting onsite regulatory audits and insp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motion Recruitment</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Python, AI/ML Data Pipelines)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>CHENNAI, Tamil Nadu, India</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -827,7 +832,7 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/contract/data-engineer-snowflake-python-ai-ml-data-pipelines/891815</t>
+          <t>https://careers.cognizant.com/us-en/jobs/00069423521/aws-data-engineer</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -835,54 +840,54 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15f141f7e604c151832a</t>
+          <t>8858c10cf79d8cbbc873</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>A leading global IT consulting and business services organization is seeking a Database Administrator to support long-term engagements with public sector and local government organizations throughout the San Diego area. This is a multi-year contract opportunity where you'll leverage SQL Server, Oracle, and MySQL expertise to support critical databases that power essential community and government service. This is an opportunity to join a highly visible team responsible for maintaining the stability, security, and performance of mission-critical database environments. The ideal candidate enjoys solving complex database challenges, ensuring high availability, and optimizing enterprise-scale systems. You'll work with experienced technology professionals while supporting organizations that deliver meaningful services to their communities. Contract Duration: Multi-Year Contract Required Skills &amp; Experience Database Administration experience Microsoft SQL Server Database design and architecture Database security and access management Backup and recovery strategies Desired Skills &amp; Experience · Public sector or government experience · Experience supporting enterprise-scale database environments · Database migration experience · Performance monitoring and capacity planning · Strong troubleshooting and problem-solving skills What You Will Be Doing Tech Breakdown 50% SQL Server Administration 25% Oracle &amp; MySQL Administration 15% Database Performance &amp; Optimization 10% Security, Backup &amp; Recovery Daily Responsibilities · 70% Hands-On Database Administration · 20% Performance Monitoring &amp; Troubleshooting · 10% Team Collaboration &amp; Documentation</t>
+          <t>Job Summary The Technology Specialist will design build and optimize generative artificial intelligence solutions using AWS Bedrock text and image capabilities within a hybrid work model. The role involves collaborating with cross functional teams to deliver secure and scalable platforms that enhance customer experiences while aligning with enterprise standards and regulatory expectations across all cloud based solutions. Responsibilities Design generative artificial intelligence solutions that use AWS Bedrock text and image services to address complex business problems and deliver measurable value for clients and stakeholders. Develop robust and reusable prompt engineering patterns for AWS Bedrock text models to ensure consistent performance reliability and alignment with organizational guidance for responsible artificial intelligence. Build and maintain pipelines that orchestrate AWS Bedrock image generation workflows integrating data preparation inference and post processing components in an efficient and observable manner. Implement secure access patterns for AWS Bedrock resources by configuring identity and access management logging and encryption controls that comply with enterprise security policies. Optimize performance and cost of Bedrock based solutions by tuning model configuration right sizing infrastructure and instrumenting detailed metrics to track quality and efficiency. Collaborate with application developers data engineers and product teams to integrate Bedrock based capabilities into web mobile and backend systems using cloud native patterns. Translate business requirements into detailed technical designs for generative artificial intelligence services ensuring traceability from user needs to implementation and validation. Perform rigorous testing validation and evaluation of Bedrock text and image outputs using automated checks human review processes and feedback loops to maintain high quality results. Create clear technical documentation including solution diagrams playbooks runbooks and design decisions to support ongoing maintenance and knowledge transfer within the team. Guide peers on best practices for using generative artificial intelligence in production including safety guardrails bias mitigation content filtering and observability design. Participate in code reviews architectural discussions and incident reviews to continuously improve the resilience reliability and maintainability of Bedrock based solutions. Coordinate with governance risk and compliance stakeholders to ensure generative artificial intelligence usage aligns with organizational policies data privacy expectations and regional regulations. Engage with business partners to demonstrate prototypes gather feedback and refine generative artificial intelligence experiences so that outcomes align with customer expectations and organizational purpose. Qualifications Exhibit six to ten years of experience in designing and implementing cloud based solutions with</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Motion Recruitment</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Python, AI/ML Data Pipelines)</t>
+          <t>Video Content Analyst with Dutch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>Lisbon, Lisboa, Portugal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL_TIME</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -897,7 +902,7 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/contract/data-engineer-snowflake-python-ai-ml-data-pipelines/891811</t>
+          <t>https://careers.cognizant.com/us-en/jobs/32121/video-content-analyst-with-dutch</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -905,34 +910,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ac913caadefeaa9d0a60</t>
+          <t>5063bf0d81c9af2f3a95</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>A leading wealth management technology firm is seeking a Data Engineer to join their growing AI and Data team. This fully remote contract opportunity offers the chance to build modern data solutions leveraging Snowflake, Python, dbt, Airflow, and AI/ML technologies that support enterprise-scale analytics and next-generation AI applications. Candidates who convert to full-time should be in or willing to relocate to one of the organization's hub locations in Atlanta, GA; La Vista, NE; Oakdale, MN; Scottsdale, AZ; or St. Petersburg, FL. This role sits at the center of data engineering and artificial intelligence initiatives. The team is building the infrastructure behind advanced AI solutions, including RAG applications, vector search, and machine learning systems. They're looking for an engineer who enjoys solving complex data challenges while working with cutting-edge AI technologies. You'll have the opportunity to help shape the future of data platforms within a highly respected financial services organization while gaining hands-on experience with modern AI architectures and enterprise-scale data environments. Contract Duration: 12 Months Required Skills &amp; Experience · Strong SQL development experience · Python and/or Scala for data pipeline development · Snowflake · dbt for data transformation and orchestration · Airflow or similar workflow orchestration tools Desired Skills &amp; Experience Scala experience Experience supporting production AI/ML systems Experience with cloud-native data platforms Data governance and data quality expertise Knowledge of large language models and AI infrastructure What You Will Be Doing Tech Breakdown · 40% Snowflake, SQL &amp; Data Engineering · 25% Python Development · 20% AI/ML Data Pipelines &amp; RAG · 15% dbt &amp; Airflow Orchestration Daily Responsibilities 80% Hands-On Engineering 10% Cross-Functional Collaboration 10% Architecture &amp; Planning</t>
+          <t>Job location: Lisbon/ Portugal Shift: rotative 24/7 WORK FROM THE OFFICE Are you a fan of vlogging or constantly looking to videos to help solve your challenges? Do you want to learn more about social media regulation, online free speech, internal controls or maybe even learn about EU policy making? If the answer is yes, then we have an amazing opportunity for you as a Video Content Analyst. Join our team for the world’s best loved video-sharing website! We are looking for: Proficiency of Dutch language at min. C1 level and English at B2 level, Availability to work on 24/7 shift (including weekend shifts) from the office, Excellent communication (verbal and written) and interpersonal skills, Quick learning and organizational skills - adaptability to learn new processes, concepts, Strong attention to detail and a desire to deliver accurately, efficiently, and to a high standard, Having a neutral mindset to alternative video content that needs classification, Ability to review content that may be deemed inappropriate and/or contain sensitive and explicit material, sometimes involving graphic, discriminatory or otherwise disturbing subjects on text or video formats. Benefits Opportunity to be part of a global organization focused on development, Open-minded and multinational environment, Training &amp; development opportunities including language courses, Professional development and clear career path, Full equipment and paid training provided from the first day of work, Extensive benefits package: private medical healthcare, life insurance, cafeteria benefits, Relocation allowance and assistance - Only applies to new hires relocating from outside of Portugal. The focus of the role will be to: Review and process incoming privacy requests through online tools, Analyze and identify content that is not in compliance with requirements and flag for action in a timely manner, Review the reported content within agreed turnaround times and standards of quality; Continually educate about changes to policies and protocols, Address complex privacy cases and regulatory inquiries, Effectively collaborate with team members on a range of projects to improve internal efficiency and effectiveness. Content Moderators play an important role in ensuring the safety of online communities against harmful user generated content. Safeguarding the online communication space can lead to meaningful and rewarding work for a content moderator as the mission of moderation aims to create positive, safe and inclusive environments for everyone. Rewarding outcomes are not often without challenges. As a part of the job requirement, you will be required to review and analyze explicit and extremely sensitive content sometimes involving graphic or otherwise disturbing text, videos, and images which may be disturbing due to their egregious nature. The content under review is likely to expose the reviewer to crime scenes, dangerous or derogatory content, abuse, harassment and sexually explicit</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>MeeBoss</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>281 results for Data Engineer jobs</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -947,7 +952,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["full-time", "part-time"]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -962,7 +972,7 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://www.roberthalf.com/us/en/jobs/all/data-engineer</t>
+          <t>https://meeboss.com/job/6af294dec98c2c523nF82Q~~</t>
         </is>
       </c>
       <c r="J8" t="b">
@@ -970,54 +980,49 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>421b3ba8d8ce7d6aa83d</t>
+          <t>14c3ad04e844b761a276</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>281 Results for Data Engineer Jobs Search jobs now Find the right job type for you Create a job alert Explore how we help job seekers Contract talent Full-Time talent Learn how we work with you Executive search Finance and Accounting Technology Marketing and Creative Legal Administrative and Customer Support Technology Risk, Audit and Compliance Finance and Accounting Digital, Marketing and Customer Experience Legal Operations Human Resources 2027 Salary Guide Demand for Skilled Talent Report Job Market Outlook Press Room Tech insights Labor market overview AI in recruiting Navigating the AI era Staffing for small businesses Cost of a bad hire Browse jobs Find your next hire Our locations Add your latest resume to match with open positions. 281 results for Data Engineer jobs Data Engineer Atlanta, GA onsite Permanent / Full Time 100000 - 120000 USD / Yearly Robert Half is working with a client in the metro-Atlanta area seeking a Data Engineer. Develop ETL/ELT pipelines Integrate multiple data sources Optimize performance Build data models Manage cloud environments Support analytics teams 2026-10-02T00:00:00Z Data Engineer Remote, OH remote Temporary / Contract 0 - 0 USD / Yearly We are looking for a Data Engineer to support data-focused initiatives with a strong emphasis on controls, process clarity, and technical documentation. This is a Long-term Contract position expected to begin as a 3-4 month engagement at 40 hours per week, with remote work flexibility. The ideal candidate will help strengthen data workflows, improve reliability across engineering processes, and create well-organized documentation that supports ongoing delivery and compliance. Responsibilities: • Design, build, and maintain data pipelines that support reliable movement and transformation of information across platforms. • Develop clear technical documentation, data process records, and control-related artifacts to improve transparency and audit readiness. • Use Python, Apache Spark, and ETL frameworks to prepare, cleanse, and transform large datasets for downstream consumption. • Work with Hadoop- and Kafka-based environments to support scalable data processing and streaming or batch integration needs. • Review existing data workflows to identify gaps in controls, consistency, and documentation quality, then recommend practical improvements. • Collaborate with cross-functional stakeholders to clarify data requirements, align engineering deliverables, and support operational continuity. • Monitor pipeline performance and troubleshoot data issues to maintain dependable processing and accurate outputs. 2026-09-30T00:00:00Z Data Engineer St. Paul, MN onsite Temporary / Contract 47.5 - 55 USD / Hourly We are looking for an experienced Data Engineer to jcreate and enhance dependable data platforms that support HR and enterprise analytics, partnering closely with analysts, engineering leads, and business stakeholders on site. The position focuses on building scalable pipelines, s</t>
+          <t>Description We are excited to welcome a diligent and detail-oriented Accounts Payable Clerk to our friendly and dynamic finance team. In this role, you will play a crucial part in ensuring that our company’s financial obligations are met accurately and on time. The ideal candidate thrives in a collaborative environment, has a keen eye for detail, and enjoys working with numbers and processes. As an Accounts Payable Clerk, you will be responsible for managing invoices, processing payments, and maintaining strong vendor relationships. This position offers a wonderful opportunity to grow your skills within a supportive company that values integrity, accuracy, and teamwork. If you are someone who is organized, reliable, and passionate about contributing to smooth financial operations, we would love to meet you and explore how you can become a vital part of our team! Responsibilities Process and review invoices to ensure accuracy and proper authorization. Prepare and execute payments to vendors in a timely manner. Maintain and update accounts payable records and reports. Reconcile vendor statements and resolve any discrepancies. Collaborate with other departments to verify purchase orders and invoice details. Respond to vendor inquiries professionally and promptly. Assist with month-end and year-end closing activities related to accounts payable. Requirements Proven experience as an Accounts Payable Clerk or in a similar financial role. Strong understanding of basic accounting principles and financial processes. Proficiency in accounting software and Microsoft Excel. Excellent attention to detail and organizational skills. Ability to manage multiple tasks and deadlines effectively. Good communication skills both written and verbal. High school diploma or equivalent; additional qualifications in accounting are a plus.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>Robert Half</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst - Agile, UAT &amp; Requirements</t>
+          <t>277 results for data engineer jobs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hoover, AL, 35244, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TEMP TO HIRE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1027,12 +1032,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Business-Systems-Analyst-AL-Hoover-Rose-International-Job-508770.html</t>
+          <t>https://www.roberthalf.com/us/en/jobs/all/data-engineer</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1040,22 +1045,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>f7e50ce31d5a1e29cb55</t>
+          <t>4acc4352f7b7243bebf0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Required Education:â¢ Bachelorâs degree in business, IT, Computer Science, or a related fieldRequired Experience:â¢ 8+ years of Business Analysis, Systems Analysis, or related IT experienceâ¢ Strong experience with Agile Business Analysis and requirements gatheringâ¢ Hands-on experience with Acceptance Testing/UAT, including test scenarios, validation, defect identification, and resolutionâ¢ Strong experience creating Business Requirements Documents (BRDs) and functional requirementsâ¢ Experience analyzing business processes and translating business needs into technical solutionsâ¢ Strong communication, analytical, problem-solving, and organizational skillsâ¢ Proficiency with Microsoft Office SuitePreferred Experience:â¢ Banking or financial services experience, preferably mortgage/home lendingâ¢ Experience with Advanced SQL, relational database queries, and data validationâ¢ Experience with Empower Software, mortgage applications, or point-of-sale applicationsâ¢ Application support and troubleshooting experienceâ¢ Experience with Business Intelligence toolsâ¢ Experience with Agile and/or Waterfall methodologiesâ¢ Project management, testing, and API experienceJob Duties:â¢ Analyze business processes, requirements, and system needs to support technology initiativesâ¢ Partner with business and IT teams to gather, document, and validate requirementsâ¢ Develop and maintain BRDs, functional requirements, process flows, and acceptance criteriaâ¢ Perform Acceptance Testing/UAT, including test planning, execution, defect tracking, and validationâ¢ Analyze existing systems and recommend process or technology improvementsâ¢ Support application troubleshooting, data analysis, and issue resolutionâ¢ Develop SQL queries as needed for data validation and analysisâ¢ Coordinate with development, testing, and business teams through implementation and releasesâ¢ Support change management and communicate project issues, risks, and recommendationsâ¢ Participate in knowledge-transfer sessions and provide guidance to less-experienced team membersâ¢ May participate in after-hours/weekend on-call support**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
+          <t>277 Results for Data Engineer Jobs Search jobs now Find the right job type for you Create a job alert Explore how we help job seekers Contract talent Full-Time talent Learn how we work with you Executive search Finance and Accounting Technology Marketing and Creative Legal Administrative and Customer Support Technology Risk, Audit and Compliance Finance and Accounting Digital, Marketing and Customer Experience Legal Operations Human Resources 2027 Salary Guide Demand for Skilled Talent Report Job Market Outlook Press Room Tech insights Labor market overview AI in recruiting Navigating the AI era Staffing for small businesses Cost of a bad hire Browse jobs Find your next hire Our locations Add your latest resume to match with open positions. 277 results for data engineer jobs Data Engineer Atlanta, GA onsite Permanent / Full Time 100000 - 120000 USD / Yearly Robert Half is working with a client in the metro-Atlanta area seeking a Data Engineer. Develop ETL/ELT pipelines Integrate multiple data sources Optimize performance Build data models Manage cloud environments Support analytics teams 2026-10-02T00:00:00Z Data Engineer Cincinnati, OH remote Temporary / Contract 0 - 0 USD / Yearly We are looking for a Data Engineer to support a short-term Contract engagement focused on assessing and strengthening OpenLink security role design for a recently acquired business. This position will play a key role in reviewing current configurations, identifying gaps in segregation of duties, and helping shape a more effective access model. The role is based in Cincinnati, Ohio, with flexibility for remote or hybrid work depending on experience and project needs. Responsibilities: • Evaluate the existing OpenLink security framework and determine how well current role assignments support appropriate access controls. • Recommend and help design an improved security role structure that aligns with segregation-of-duties expectations across the environment. • Configure and refine OpenLink settings to support a secure, scalable, and well-governed access model. • Partner with project stakeholders to document findings, explain risk areas, and outline practical remediation options. • Support analysis related to the acquired company’s OpenLink setup and identify where adjustments are needed for consistency and control. • Contribute technical expertise during project discussions, providing guidance on role configuration best practices and implementation considerations. • Use data engineering tools and scripting capabilities to assist with analysis, validation, and supporting technical tasks where applicable. 2026-09-30T00:00:00Z Data Engineer Remote, OH remote Temporary / Contract 0 - 0 USD / Yearly We are looking for a Data Engineer to support data-focused initiatives with a strong emphasis on controls, process clarity, and technical documentation. This is a Long-term Contract position expected to begin as a 3-4 month engagement at 40 hours per week, with remote work flexibi</t>
         </is>
       </c>
     </row>
@@ -1067,22 +1072,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indirect Auto Credit Analyst (Remote)</t>
+          <t>Data Engineer - Sr.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Location Englewood, Colorado, USA</t>
+          <t>Des Moines, Iowa, 50301, USA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1097,7 +1107,7 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>https://careers.teksystems.com/us/en/job/JP-006322049/Indirect-Auto-Credit-Analyst-Remote</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006299146/Data-Engineer-Sr</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -1105,49 +1115,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>41671d1b874bc2d2a0b1</t>
+          <t>a40a64aac61d42f711cb</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Indirect Auto Credit Analyst (Remote) in Cheyenne, Wyoming, USA | TEKsystems Careers Skip to main content Locations US English Saved jobs (0) Choose your language: X Close Language Selection Canada Français English Great Britain English United States English What We Do Careers Work With Us Inclusion &amp; Diversity Serving Veterans Who We Are FAQ Work With Us Inclusion &amp; Diversity Serving Veterans Saved jobs (0) Toggle navigation - Indirect Auto Credit Analyst (Remote) location Cheyenne, Wyoming, USA category Customer Service Contractor Job ID: JP-006322049 Posted: Oct 1st 2026 27 USD - 32 USD/hour Save This Job Apply Now Back to search results Previous job Next job JOB DESCRIPTION Indirect Auto Credit Analyst (Remote) Contract-to-Hire Opportunity | Remote in CO, WY, IL, TX, AZ, FL, WA, GA, VA, or HI Pay Range: $26-$32/hr Candidates who meet all required qualifications, including indirect auto underwriting experience and direct experience with required loan origination systems, may be eligible for consideration toward the higher end of the pay range. Join One of the Fastest-Growing Organizations in Indirect Lending TEKsystems is partnering with Origence, a national leader in credit union lending technology and indirect auto finance, to hire experienced Indirect Auto Credit Analysts. This is a fully remote, contract-to-hire opportunity supporting a rapidly growing lending operation. The ideal candidate has recent experience underwriting indirect auto loans, making independent credit decisions, and working with dealership and credit union partners. Origence offers a collaborative culture, strong training, career growth opportunities, and a proven track record of converting high-performing contractors into permanent employees. Why Consider This Opportunity? 100% remote work environment Contract-to-hire with strong long-term potential Work for a leader in the credit union lending space Equipment provided (laptop, dual monitors, headset, keyboard, mouse) Performance-based career advancement opportunities Supportive leadership and team environment Opportunity to make independent underwriting decisions and directly impact lending outcomes What You'll Be Doing As an Indirect Auto Credit Analyst, you'll review and underwrite vehicle loan applications submitted through dealership networks on behalf of credit union partners. Responsibilities include: Reviewing indirect auto loan applications and supporting documentation Analyzing credit bureau reports and borrower credit history Evaluating: Debt-to-Income (DTI) Payment-to-Income (PTI) Loan-to-Value (LTV) Income documentation Overall borrower risk Making loan approval, decline, and stipulation decisions within lending guidelines Documenting underwriting decisions and rationale within loan systems Communicating directly with dealerships and credit union partners Following up to obtain missing documentation and loan conditions Managing a high-volume queue while meeting production and turnaround goals Supporting fu</t>
+          <t>***MUST BE LOCAL TO DES MOINES, IA OR WILLING TO GO ONSITE IN DES MOINES, IOWA*** Description Data Engineer to join a product-focused engineering team responsible for delivering high-quality data solutions that drive business insights. This role will serve as a key contributor on a cross-functional Agile team and will help design, build, and maintain scalable data pipelines and data products that support enterprise analytics and decision-making. The ideal candidate is a proactive, hands-on engineer who can quickly adapt to a fast-paced environment, collaborate effectively with stakeholders, and contribute immediately to team objectives. Skills Python, Sql, Aws, snowflake, erwin, data modeling Top Skills Details Python,Sql,Aws Additional Skills &amp; Qualifications Team Environment • Join a collaborative team of approximately 4-6 engineers. • Work within a cross-functional Agile product team. • Regular interaction with multiple business and technology teams. • Strong emphasis on teamwork, communication, and problem-solving. Required Qualifications • Strong proficiency in Python development. • Experience working with AWS cloud services. • Strong SQL skills and experience with relational and analytical databases. • Experience using GitHub and modern source control practices. • Experience working within Agile development environments. • Strong communication and collaboration skills. • Ability to quickly learn new technologies and contribute with minimal ramp-up time. Preferred Qualifications • Experience extracting and integrating data through APIs. • Experience working with Snowflake. • Knowledge of data modeling concepts and tools such as Erwin. • Experience designing and implementing enterprise data solutions. • Familiarity with Informatica is helpful but not required. Experience Level Expert Level Job Type &amp; Location This is a Contract position based out of Des Moines, IA. Pay and Benefits The pay range for this position is $60.00 - $73.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully remote position. Application Deadline This position is antici</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>TEKsystems</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chemistry Analyst job in THOMPSONS STATION, Tennessee, USA | Actalent Careers</t>
+          <t>Service Desk Analyst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Ames, Iowa, 50010, USA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1162,42 +1177,42 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006329957/Chemistry-Analyst</t>
+          <t>https://careers.teksystems.com/us/en/job/JP-006298075/Service-Desk-Analyst</t>
         </is>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-06T17:36:06+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>85157a072803abdaa69d</t>
+          <t>b36addfa96a59084ec8a</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Chemistry Analyst job in THOMPSONS STATION, Tennessee, USA | Health &amp; Medical jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices af9576fb35144862b5cd58625cd3ba57</t>
+          <t>Description • Respond to and resolve customer requests and inquiries by tracking them in ticket management system • Provide information and instructions to users on various applications and equipment • Provide direct support via email, phone, remote, and in-person appointments • Identify technical needs of customers and find resolutions to address business needs • Install, maintain, and troubleshoot computer equipment and software • Performs routine backup and restores system and data files • Ensure devices are setup in a standard, secure, and consistent manner • Schedule customer installations and appointments • Ensure policies and standards are met and procedures are followed by staff • Maintain/manage ITS and CorePlus customer inventories • Triage incidents and requests, ensuring that students and FTEs are completing them in a timely manner • Attend team, departmental, and campus meetings • Provide guidance to student employees, including scheduling, training, and performance feedback • Document procedures, checklists, and other information required by the team • Provide backup support for purchasing CorePlus and Onsite requested IT equipment Skills Help desk, Technical support, Desktop, Customer service, Troubleshooting, Office 365, imaging Top Skills Details Help desk,Technical support,Desktop,Customer service,Troubleshooting Additional Skills &amp; Qualifications Supporting an enterprise level ticketing system. (Service Now) Job Type &amp; Location This is a Contract position based out of Ames, IA. Pay and Benefits The pay range for this position is $19.00 - $20.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) • Short and long-term disability • Health Spending Account (HSA) • Transportation benefits • Employee Assistance Program • Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a fully onsite position in Ames,IA. Application Deadline This position is anticipated to close on Sep 27, 2026. About TEKsystems We're partners in transformation. We help clients activate ideas and solutions to take advantage of a new world of opportunity. We are a team of 80,000 strong, working with over 6,000 clients, including 80% of the Fortune 500, across North America, Europe and Asia. As an industry leader in Full-Stack Technology Service</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Actalent</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Analyst job in Hazelwood, Missouri, USA | Actalent Careers</t>
+          <t>Senior AI Developer - Southlake, TX | Judge Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1227,30 +1242,30 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006322986/Data-Analyst</t>
+          <t>https://www.judge.com/jobs/details/1134711</t>
         </is>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-02T08:53:53+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>029db263f6c41aff4b9f</t>
+          <t>780df2da3a341d97cc3d</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Data Analyst job in Hazelwood, Missouri, USA | Systems &amp; Software jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices af9576fb35144862b5cd58625cd3ba57</t>
+          <t>Senior AI Developer - Southlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1277,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GIS Analyst</t>
+          <t>Chemistry Analyst job in THOMPSONS STATION, Tennessee, USA | Actalent Careers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, Missouri, 63101, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1277,12 +1292,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>["OTHER"]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1297,7 +1307,7 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-005238782/GIS-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006329957/Chemistry-Analyst</t>
         </is>
       </c>
       <c r="J13" t="b">
@@ -1310,17 +1320,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2bb0d66e462a56093e20</t>
+          <t>85157a072803abdaa69d</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Job Title: GIS Analyst Job Description The GIS Analyst will support Operation Services, an internal department that aids construction projects. The role involves completing engineering designs and cost estimates using GIS for various main and service works, collecting construction activity 'as-built' data with mobile CPS devices in the field, creating permanent asset records, and editing map features and correlating attribute data in GIS. The analyst will also perform final quality checks on GIS versioned data before posting, represent Engineering at project meetings, and conduct field visits to job sites to determine requirements for service and main work. Responsibilities Complete engineering designs and cost estimates using GIS for all types of main and service work. Collect construction activity 'as-built' using mobile CPS devices in the field for creating permanent asset records. Edit map features and correlating attribute data in the GIS. Perform final quality checks on GIS versioned data before it is posted to the GIS. Represent Engineering at internal and external project meetings as required. Visit job sites to determine requirements for service and main work. Perform preliminary reviews of development plans and interface with customers. Implement and train Engineering staff on new work processes for the GIS mapping system. Distribute and update maps for other departments as requested. Approve requests for the acquisition and release of easements and vacation of rights-of-way. Perform pipeline safety compliance-related GIS analysis as directed. Execute all other duties as assigned. Essential Skills Proficiency in ArcGIS and CAD. Knowledge of geography and construction drawings. Experience with as-built drawings, cost forecasting, and drafting. Additional Skills &amp; Qualifications Ability to complete engineering designs and cost estimates using GIS. Experience in collecting construction activity 'as-built' data using mobile CPS devices. Skill in editing map features and correlating attribute data in GIS. Work Environment The role is based in a professional engineering office, initially requiring attendance five days per week, reducing to three days per week after training. Work may be performed in both office and field settings, with exposure to the elements. Typical hours are 7:00 a.m. to 3:45 p.m., Monday through Friday, with potential for overtime and travel. Pay and Benefits The pay range for this position is $25.00 - $27.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependent</t>
+          <t>Chemistry Analyst job in THOMPSONS STATION, Tennessee, USA | Health &amp; Medical jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices f3383697147b4ec5ab41b068158e6529</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1342,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inventory Analyst</t>
+          <t>Data Analyst job in Hazelwood, Missouri, USA | Actalent Careers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ponca City, Oklahoma, 74601, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1347,12 +1357,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>["FULL_TIME"]</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1367,7 +1372,7 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006302292/Inventory-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006322986/Data-Analyst</t>
         </is>
       </c>
       <c r="J14" t="b">
@@ -1375,22 +1380,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-05T09:25:56+00:00</t>
+          <t>2026-10-02T08:53:53+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ec610b5ec2ceee97639e</t>
+          <t>029db263f6c41aff4b9f</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Job Title: Inventory Analyst Job Description We are seeking an experienced Inventory Analyst to support inventory control, materials management, and production operations within a manufacturing environment. This individual will play a critical role in maintaining inventory accuracy, supporting production schedules, investigating inventory discrepancies, and ensuring materials are available to meet customer and operational demands. The Inventory Analyst will partner closely with Production, Engineering, Materials Management, Supply Chain, and Warehouse teams to optimize material flow, improve inventory processes, and support overall operational efficiency. The ideal candidate will have experience with inventory management systems, cycle counting, ERP systems, and manufacturing operations. Responsibilities Perform daily cycle counts and inventory audits to maintain inventory accuracy. Investigate, analyze, and resolve inventory discrepancies. Monitor inventory levels and material availability to support production schedules. Maintain and update inventory records within ERP/MRP systems. Coordinate with production, warehouse, engineering, and supplier teams regarding material shortages and inventory concerns. Analyze inventory trends and recommend process improvements. Support receiving discrepancy investigations and non-conforming material processes. Assist with quarterly physical inventories and inventory reconciliations. Manage inventory transactions and ensure accurate item master data. Support continuous improvement initiatives related to inventory control and materials management. Essential Skills Bachelor's degree with 1+ year of related experience, Associate degree with 6+ years of experience, or equivalent combination of education and experience. Experience in inventory control, supply chain, materials management, or manufacturing operations. ERP/MRP system experience. Strong Microsoft Office skills, particularly Excel. Excellent organizational, analytical, and problem-solving skills. Strong attention to detail and data accuracy. Ability to manage multiple priorities in a fast-paced manufacturing environment. Strong communication and cross-functional collaboration skills. Additional Skills &amp; Qualifications SAP experience. Forklift certification or material handling experience. Shipping and receiving experience. Experience using RF scanners and barcode systems. APICS/CPIM certification. Knowledge of inventory optimization and continuous improvement methodologies. Experience supporting manufacturing and production environments. Work Environment This is a full-time, onsite role within a manufacturing environment. The position involves a fast-paced production setting supporting multiple departments, with frequent interaction with suppliers, production personnel, warehouse teams, and engineering groups. The work involves a combination of office-based analytical tasks and hands-on inventory audits within the production facility. Occasional overtim</t>
+          <t>Data Analyst job in Hazelwood, Missouri, USA | Systems &amp; Software jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices f3383697147b4ec5ab41b068158e6529</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1407,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>QA Analyst (1st Or 2nd Shift)</t>
+          <t>GIS Analyst</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, Minnesota, 55343, USA</t>
+          <t>St. Louis, Missouri, 63101, USA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1417,12 +1422,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
+          <t>["OTHER"]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006315478/QA-Analyst-1st-Or-2nd-Shift</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-005238782/GIS-Analyst</t>
         </is>
       </c>
       <c r="J15" t="b">
@@ -1445,22 +1450,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-05T09:25:56+00:00</t>
+          <t>2026-10-06T17:36:06+00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>43608f876bda7d0082c0</t>
+          <t>2bb0d66e462a56093e20</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Quality Assurance Specialist Long-Term Opportunity | Pharmaceuticals | Offers Benefits Job Description The QA Specialist plays a key role in ensuring product quality and regulatory compliance by auditing the facility and production lines, evaluating raw materials, bulk, and finished products, and driving continuous improvement efforts. This position is highly visible on the manufacturing floor and supports a world-class manufacturing control program through careful documentation review, training, and proactive quality oversight. Key Responsibilities Review batch records and manufacturing documentation to ensure GMP/GDP compliance. Support manufacturing operations through floor presence, audits, inspections, and quality oversight. Investigate deviations, non-conformances, and OOS events; perform root cause analysis and support CAPA activities. Train and mentor production personnel on quality systems, SOPs, and regulatory requirements. Approve production activities and product releases while ensuring specifications are met. Maintain and update SOPs, work instructions, controlled forms, and quality documentation. Identify recurring quality issues, implement corrective actions, and drive continuous improvement initiatives. Partner with production and warehouse teams to promote a strong quality culture and maintain compliance. Support lean manufacturing initiatives, including 5S and waste reduction efforts. Required Qualifications Bachelor's degree in Biology, Chemistry, or a related scientific discipline. 1+ year of experience in a GMP-regulated manufacturing environment (pharmaceutical, medical device, food, cosmetic, etc.). Experience reviewing batch records, manufacturing documentation, or production records. Working knowledge of GMP, GDP, FDA regulations, and quality systems. Experience with investigations, deviations, non-conformances, OOS events, and CAPA processes. Job Type &amp; Location This is a Contract to Hire position based out of Eden Prairie, MN. Pay and Benefits The pay range for this position is $25.00 - $30.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: Medical, dental &amp; vision Critical Illness, Accident, and Hospital 401(k) Retirement Plan Pre-tax and Roth post-tax contributions available Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) Short and long-term disability Health Spending Account (HSA) Transportation benefits Employee Assistance Program Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a f</t>
+          <t>Job Title: GIS Analyst Job Description The GIS Analyst will support Operation Services, an internal department that aids construction projects. The role involves completing engineering designs and cost estimates using GIS for various main and service works, collecting construction activity 'as-built' data with mobile CPS devices in the field, creating permanent asset records, and editing map features and correlating attribute data in GIS. The analyst will also perform final quality checks on GIS versioned data before posting, represent Engineering at project meetings, and conduct field visits to job sites to determine requirements for service and main work. Responsibilities Complete engineering designs and cost estimates using GIS for all types of main and service work. Collect construction activity 'as-built' using mobile CPS devices in the field for creating permanent asset records. Edit map features and correlating attribute data in the GIS. Perform final quality checks on GIS versioned data before it is posted to the GIS. Represent Engineering at internal and external project meetings as required. Visit job sites to determine requirements for service and main work. Perform preliminary reviews of development plans and interface with customers. Implement and train Engineering staff on new work processes for the GIS mapping system. Distribute and update maps for other departments as requested. Approve requests for the acquisition and release of easements and vacation of rights-of-way. Perform pipeline safety compliance-related GIS analysis as directed. Execute all other duties as assigned. Essential Skills Proficiency in ArcGIS and CAD. Knowledge of geography and construction drawings. Experience with as-built drawings, cost forecasting, and drafting. Additional Skills &amp; Qualifications Ability to complete engineering designs and cost estimates using GIS. Experience in collecting construction activity 'as-built' data using mobile CPS devices. Skill in editing map features and correlating attribute data in GIS. Work Environment The role is based in a professional engineering office, initially requiring attendance five days per week, reducing to three days per week after training. Work may be performed in both office and field settings, with exposure to the elements. Typical hours are 7:00 a.m. to 3:45 p.m., Monday through Friday, with potential for overtime and travel. Pay and Benefits The pay range for this position is $25.00 - $27.00/hr. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: • Medical, dental &amp; vision • Critical Illness, Accident, and Hospital • 401(k) Retirement Plan – Pre-tax and Roth post-tax contributions available • Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependent</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1477,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qc Lab Analyst job in Saint Louis, Missouri, USA | Actalent Careers</t>
+          <t>Metals Analyst job in Frankfort, Illinois, USA | Actalent Careers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1502,7 +1507,7 @@
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006320418/Qc-Lab-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006333019/Metals-Analyst</t>
         </is>
       </c>
       <c r="J16" t="b">
@@ -1510,22 +1515,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-06T17:36:06+00:00</t>
+          <t>2026-10-07T02:48:05+00:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>421c39c3a1e87f73dbee</t>
+          <t>800b8d8fff873ef4f971</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Qc Lab Analyst job in Saint Louis, Missouri, USA | Laboratory &amp; Sciences jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices af9576fb35144862b5cd58625cd3ba57</t>
+          <t>Metals Analyst job in Frankfort, Illinois, USA | Laboratory &amp; Sciences jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices f3383697147b4ec5ab41b068158e6529</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1542,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Research Contracts &amp; Budgets Analyst job in Anaheim, California, USA | Actalent Careers</t>
+          <t>QA Analyst (1st Or 2nd Shift)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Eden Prairie, Minnesota, 55343, USA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1552,7 +1557,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>["CONTRACTOR"]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1567,7 +1577,7 @@
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006322572/Research-Contracts-Budgets-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006315478/QA-Analyst-1st-Or-2nd-Shift</t>
         </is>
       </c>
       <c r="J17" t="b">
@@ -1575,22 +1585,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-05T09:25:56+00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>54d44277d6240ae1b012</t>
+          <t>43608f876bda7d0082c0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Research Contracts &amp; Budgets Analyst job in Anaheim, California, USA | Clinical jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices af9576fb35144862b5cd58625cd3ba57</t>
+          <t>Quality Assurance Specialist Long-Term Opportunity | Pharmaceuticals | Offers Benefits Job Description The QA Specialist plays a key role in ensuring product quality and regulatory compliance by auditing the facility and production lines, evaluating raw materials, bulk, and finished products, and driving continuous improvement efforts. This position is highly visible on the manufacturing floor and supports a world-class manufacturing control program through careful documentation review, training, and proactive quality oversight. Key Responsibilities Review batch records and manufacturing documentation to ensure GMP/GDP compliance. Support manufacturing operations through floor presence, audits, inspections, and quality oversight. Investigate deviations, non-conformances, and OOS events; perform root cause analysis and support CAPA activities. Train and mentor production personnel on quality systems, SOPs, and regulatory requirements. Approve production activities and product releases while ensuring specifications are met. Maintain and update SOPs, work instructions, controlled forms, and quality documentation. Identify recurring quality issues, implement corrective actions, and drive continuous improvement initiatives. Partner with production and warehouse teams to promote a strong quality culture and maintain compliance. Support lean manufacturing initiatives, including 5S and waste reduction efforts. Required Qualifications Bachelor's degree in Biology, Chemistry, or a related scientific discipline. 1+ year of experience in a GMP-regulated manufacturing environment (pharmaceutical, medical device, food, cosmetic, etc.). Experience reviewing batch records, manufacturing documentation, or production records. Working knowledge of GMP, GDP, FDA regulations, and quality systems. Experience with investigations, deviations, non-conformances, OOS events, and CAPA processes. Job Type &amp; Location This is a Contract to Hire position based out of Eden Prairie, MN. Pay and Benefits The pay range for this position is $25.00 - $30.00/hr. Individual compensation offered for this position within this range will depend on many factors, including qualifications, skills, relevant experience, job knowledge, geographic location, internal equity, and other pertinent job-related factors. Eligibility requirements apply to some benefits and may depend on your job classification and length of employment. Benefits are subject to change and may be subject to specific elections, plan, or program terms. If eligible, the benefits available for this temporary role may include the following: Medical, dental &amp; vision Critical Illness, Accident, and Hospital 401(k) Retirement Plan Pre-tax and Roth post-tax contributions available Life Insurance (Voluntary Life &amp; AD&amp;D for the employee and dependents) Short and long-term disability Health Spending Account (HSA) Transportation benefits Employee Assistance Program Time Off/Leave (PTO, Vacation or Sick Leave) Workplace Type This is a f</t>
         </is>
       </c>
     </row>
@@ -1602,27 +1612,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thermal Analyst</t>
+          <t>Qc Lab Analyst job in Saint Louis, Missouri, USA | Actalent Careers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, Texas, 73301, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>["CONTRACTOR"]</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1637,7 +1642,7 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>https://careers.actalentservices.com/us/en/job/JP-006308058/Thermal-Analyst</t>
+          <t>https://careers.actalentservices.com/us/en/job/JP-006320418/Qc-Lab-Analyst</t>
         </is>
       </c>
       <c r="J18" t="b">
@@ -1645,22 +1650,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-06T17:36:06+00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19929aa06fa395a0a6b8</t>
+          <t>421c39c3a1e87f73dbee</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Job Title: Sr Mechanical Analyst – Structural and Thermal Analysis! Job Description This role provides technical leadership in mechanical analysis for complex electronic systems across a broad portfolio of aerospace, defense, intelligence, cyber, and space programs. You will perform high-quality structural and thermal analyses, guide design optimization, and support both local and remote programs. The position offers the opportunity to work with advanced technologies, collaborate with multidisciplinary teams, and contribute directly to mission-critical systems that support national security and public safety. Responsibilities Provide technical leadership and deliver high-quality mechanical analysis support to locally based programs as well as other programs across the broader electronic systems portfolio, including remote support as needed. Plan, coordinate, and execute analysis activities in collaboration with program engineers and program leadership, ensuring alignment with technical requirements, schedules, and program objectives. Perform structural analyses using both classical hand-calculation methods and finite element methods to evaluate modal response, random vibration, shock, and static structural performance. Perform thermal analyses, including steady-state and transient heat transfer evaluations, to ensure robust thermal performance and compliance with requirements. Create detailed finite element models (FEM) at levels ranging from sub-components to full system assemblies using Siemens Simcenter 3D/NX, NASTRAN, Ansys Mechanical, and Ansys Icepak. Post-process and interpret finite element analysis results to assess structural and thermal performance, identify risks, and propose design improvements. Collaborate closely with mechanical, electrical, optical, and other engineering disciplines to optimize system designs and ensure robust, integrated solutions across the full product portfolio. Document analysis methods, assumptions, models, results, and conclusions in clear, professional reports and presentations suitable for internal and external stakeholders. Present analysis findings, design recommendations, and risk assessments to internal teams and external customers in a clear and concise manner. Mentor and coach less experienced engineers and part-time analysts, providing technical guidance, feedback, and support to help develop their skills. Review analysis work products from other team members to ensure technical accuracy, completeness, and adherence to standards and best practices. Contribute to a collaborative, inclusive team culture by communicating effectively, maintaining a positive attitude, and supporting cross-functional teamwork. Essential Skills Bachelor’s degree in Mechanical Engineering or Aerospace Engineering. At least 4 years of relevant experience in mechanical analysis or a closely related field. Proven experience performing modal analyses of structures to evaluate natural frequencies and mode shapes. Proven experie</t>
+          <t>Qc Lab Analyst job in Saint Louis, Missouri, USA | Laboratory &amp; Sciences jobs at Actalent Contact Us Locations Canada FR United Kingdom EN United States EN India EN Careers Manufacturing, Mechanical, &amp; Electrical Systems &amp; Software Architecture, Environmental, &amp; Civil Transmission, Distribution, &amp; Power Construction Management Health &amp; Medical Clinical Laboratory &amp; Sciences Contact Us Locations Language selection Canada FR United Kingdom EN United States EN India EN Toggle navigation We're sorry… the job you are trying to apply for has been filled. Maybe you would like to consider the Categories below : © 2026 Actalent, Inc. All rights reserved. Services &amp; Solutions Industries Insights About Us Locations Careers CONSULTANT LOGIN LCA Code of Conduct Terms &amp; Conditions Privacy Notices CA Notice at Collection CA Notice at Collection (For Employees and Job Applicants) Mandatory Notices Cookie Notice Cookie Settings Sitemap Accessibility Your Privacy Choices f3383697147b4ec5ab41b068158e6529</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1725,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1790,7 +1795,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1860,7 +1865,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1930,7 +1935,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2000,7 +2005,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2070,7 +2075,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2140,7 +2145,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2210,7 +2215,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2280,7 +2285,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2350,7 +2355,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2420,7 +2425,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2490,7 +2495,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2560,7 +2565,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2630,7 +2635,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2700,7 +2705,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2770,7 +2775,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2840,7 +2845,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2910,7 +2915,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2980,7 +2985,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3050,7 +3055,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3120,7 +3125,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3190,7 +3195,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3260,7 +3265,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3330,7 +3335,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3400,7 +3405,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3470,7 +3475,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3540,7 +3545,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3610,7 +3615,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3680,7 +3685,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3750,7 +3755,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3820,7 +3825,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3890,7 +3895,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3960,7 +3965,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4030,7 +4035,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4100,7 +4105,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4170,7 +4175,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4240,7 +4245,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4310,7 +4315,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4380,7 +4385,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4450,7 +4455,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4590,7 +4595,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4660,7 +4665,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4730,7 +4735,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4800,7 +4805,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4870,7 +4875,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4940,7 +4945,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5010,7 +5015,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5080,7 +5085,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5150,7 +5155,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5220,7 +5225,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5290,7 +5295,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5360,7 +5365,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5430,7 +5435,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5500,7 +5505,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5570,7 +5575,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5640,7 +5645,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5710,7 +5715,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5780,7 +5785,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5850,7 +5855,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5920,7 +5925,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5990,7 +5995,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6060,7 +6065,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6130,7 +6135,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6200,7 +6205,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6270,7 +6275,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6340,7 +6345,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6410,7 +6415,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6480,7 +6485,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6550,7 +6555,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6620,7 +6625,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6690,7 +6695,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6760,7 +6765,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6830,7 +6835,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6900,7 +6905,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6970,7 +6975,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7040,7 +7045,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7110,7 +7115,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7180,7 +7185,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7250,7 +7255,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7267,17 +7272,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ManpowerGroup</t>
+          <t>Kforce</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Call Center Quality Analyst</t>
+          <t>IT App Security Analyst</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>City or Zip Code City or Zip Code</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7287,12 +7292,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Temporary</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/call-center-quality-analyst/5895136</t>
+          <t>https://myhiring.kforce.com/careersection/ex/jobdetail.ftl?job=260569&amp;tz=GMT%2B00%3A00&amp;tzname=UTC</t>
         </is>
       </c>
       <c r="J99" t="b">
@@ -7315,22 +7315,22 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-10-03T08:28:30+00:00</t>
+          <t>2026-10-07T02:48:05+00:00</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>a806e9f54a0f5a32333c</t>
+          <t>1deefb33608c95298288</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Call Center Quality Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Call Center Quality Analyst Reference Number: 5895136 Published Date: 10/03/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the healthcare and government services sector, is seeking a dedicated and detail-oriented Call Center Quality Analyst to join their team. As a Call Center Quality Analyst, you will be an integral part of the Quality Assurance team supporting various functional areas. The ideal candidate will demonstrate strong analytical skills, excellent communication abilities, and a proactive approach to continuous improvement, aligning successfully within a dynamic and inclusive work environment. Job Title: Call Center Quality Analyst Location: East Hartford, CT Pay Range: 22.40 Shift: Monday Through Friday What's the Job? Conduct comprehensive quality reviews across multiple functional areas to ensure compliance and excellence. Identify trends or issues in quality assessments and recommend strategies for ongoing improvement. Maintain high performance standards with a quality score of 96% or higher and challenge percentages under 5% monthly. Update and manage quality monitoring data to track assessment outcomes and support process enhancements. Collaborate with team members and other departments to implement quality processes and support organizational goals. What's Needed? College degree preferred; relevant experience in government services, health, or human services is advantageous. Strong verbal and written communication skills, with the ability to produce clear documentation. Excellent organizational, analytical, and problem-solving skills. Ability to work independently,</t>
+          <t>Kforce Career Section Go to the main content section. | My Account Options | We're glad you're here. This service is set to disconnect automatically after {0} minutes of inactivity. Your session will end in {1} minutes. Click OK to reset the timer to {0} minutes. You have been signed out. This service is set to sign out after {0} minutes of inactivity. Job Search My Jobpage Basic Search | Advanced Search | My Submissions | My Job Cart | My Saved Searches | Beginning of the main content section. Return to the home page Printable Format Return to previous position on page - ( ) Qualifications : Refer a friend for this job Refer a friend Refer a candidate Submit a candidate's profile</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Credit Analyst</t>
+          <t>Call Center Quality Analyst</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/administration-and-support/credit-analyst/5891598</t>
+          <t>https://www.manpower.com/en/job/administration-and-support/call-center-quality-analyst/5895136</t>
         </is>
       </c>
       <c r="J100" t="b">
@@ -7390,17 +7390,17 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>478306b6fada52ab1df8</t>
+          <t>a806e9f54a0f5a32333c</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Credit Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Credit Analyst Reference Number: 5891598 Published Date: 10/03/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Join the Manpower Team Supporting Acushnet Company! We're hiring a Credit Analyst to support Acushnet Company, the organization behind industry-leading brands like Titleist and FootJoy. This position offers the opportunity to contribute to a globally recognized company while building your experience in credit analysis and financial risk management. If you're analytical, detail-oriented, and looking for an opportunity to grow your finance career, we'd love to hear from you. What's In It for You? Competitive pay at $32 per hour Hybrid flexibility - office is in Fairhaven, MA Full-time schedule with consistent hours Weekly pay through Manpower Opportunity to support a globally recognized organization Build valuable experience in credit analysis and finance Potential for contract extension based on business needs and performance What You'll Do As a Credit Analyst, you'll play a key role in managing credit risk and supporting the company's financial operations by: Managing a portfolio of customer accounts throughout the order-to-cash process Reviewing financial statements, credit reports, and supporting data to assess creditworthiness Establishing and maintaining appropriate credit limits Monitoring customer accounts and addressing delinquent balances Negotiating payment solutions and helping reduce financial risk Processing new customer credit applications and maintaining accurate account records Collaborating with Sales, Customer Service, and Finance teams to support efficient credit and collection activities What We're Looking</t>
+          <t>Call Center Quality Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Call Center Quality Analyst Reference Number: 5895136 Published Date: 10/03/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the healthcare and government services sector, is seeking a dedicated and detail-oriented Call Center Quality Analyst to join their team. As a Call Center Quality Analyst, you will be an integral part of the Quality Assurance team supporting various functional areas. The ideal candidate will demonstrate strong analytical skills, excellent communication abilities, and a proactive approach to continuous improvement, aligning successfully within a dynamic and inclusive work environment. Job Title: Call Center Quality Analyst Location: East Hartford, CT Pay Range: 22.40 Shift: Monday Through Friday What's the Job? Conduct comprehensive quality reviews across multiple functional areas to ensure compliance and excellence. Identify trends or issues in quality assessments and recommend strategies for ongoing improvement. Maintain high performance standards with a quality score of 96% or higher and challenge percentages under 5% monthly. Update and manage quality monitoring data to track assessment outcomes and support process enhancements. Collaborate with team members and other departments to implement quality processes and support organizational goals. What's Needed? College degree preferred; relevant experience in government services, health, or human services is advantageous. Strong verbal and written communication skills, with the ability to produce clear documentation. Excellent organizational, analytical, and problem-solving skills. Ability to work independently,</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Data Lead — Data Governance / MDG</t>
+          <t>Credit Analyst</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/data-lead-data-governance-mdg/409871</t>
+          <t>https://www.manpower.com/en/job/administration-and-support/credit-analyst/5891598</t>
         </is>
       </c>
       <c r="J101" t="b">
@@ -7455,22 +7455,22 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-10-02T21:44:50+00:00</t>
+          <t>2026-10-03T08:28:30+00:00</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>51dd1f94c7ae7d93ab36</t>
+          <t>478306b6fada52ab1df8</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Data Lead — Data Governance / MDG | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Data Lead — Data Governance / MDG Reference Number: 409871 Published Date: 10/02/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the autonomous mobility sector, is seeking a Data Lead — Data Governance / MDG to join their team. As a Data Lead — Data Governance / MDG, you will be part of the Data Management Department supporting cross-functional teams involved in manufacturing operations and enterprise data initiatives. The ideal candidate will demonstrate strong analytical skills, proactive communication, and collaborative spirit, which will align successfully in the organization. Job Title: Data Lead — Data Governance / MDG Location: Foster City, CA Pay Range: $90-$95/hour+ Benefits What's the Job? Lead current-state assessment of existing data management processes, tools, workflows, controls, and governance practices. Conduct comprehensive gap analysis between current MDM capabilities and target-state MDG solutions, focusing on workflow, approvals, stewardship, and data quality. Evaluate SAP MDG and comparable platforms to determine fit with business needs and existing SAP landscape. Partner with cross-functional teams to define and develop a scalable data governance operating model aligned with enterprise goals. Create detailed roadmaps, executive documentation, and strategic recommendations to support phased implementation and continuous improvement. What's Needed? 8 to 10 years of experience in data management, data governance, or enterprise data roles, with a focus on SAP data processes. Strong understanding of data governance concepts including ownership, stewardship,</t>
+          <t>Credit Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Credit Analyst Reference Number: 5891598 Published Date: 10/03/2026 Job Type: Temporary Industry: Administration and Support Hours: Full Time APPLY NOW SAVE SHARE Join the Manpower Team Supporting Acushnet Company! We're hiring a Credit Analyst to support Acushnet Company, the organization behind industry-leading brands like Titleist and FootJoy. This position offers the opportunity to contribute to a globally recognized company while building your experience in credit analysis and financial risk management. If you're analytical, detail-oriented, and looking for an opportunity to grow your finance career, we'd love to hear from you. What's In It for You? Competitive pay at $32 per hour Hybrid flexibility - office is in Fairhaven, MA Full-time schedule with consistent hours Weekly pay through Manpower Opportunity to support a globally recognized organization Build valuable experience in credit analysis and finance Potential for contract extension based on business needs and performance What You'll Do As a Credit Analyst, you'll play a key role in managing credit risk and supporting the company's financial operations by: Managing a portfolio of customer accounts throughout the order-to-cash process Reviewing financial statements, credit reports, and supporting data to assess creditworthiness Establishing and maintaining appropriate credit limits Monitoring customer accounts and addressing delinquent balances Negotiating payment solutions and helping reduce financial risk Processing new customer credit applications and maintaining accurate account records Collaborating with Sales, Customer Service, and Finance teams to support efficient credit and collection activities What We're Looking</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Finance Operations Analyst</t>
+          <t>Data Lead — Data Governance / MDG</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/finance-operations-analyst/411813</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/data-lead-data-governance-mdg/409871</t>
         </is>
       </c>
       <c r="J102" t="b">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-02T21:44:50+00:00</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>94f070dac724bf6ab6ff</t>
+          <t>51dd1f94c7ae7d93ab36</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Finance Operations Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Finance Operations Analyst Reference Number: 411813 Published Date: 10/02/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in the automotive and manufacturing industry, is seeking a Finance Operations Analyst to join their team. As a Finance Operations Analyst, you will be part of the Operations department supporting program financial governance, cost estimation, and budget management. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication skills, which will align successfully in the organization. Job Title: Finance Operations Analyst Location: Foster City, CA (Fully Onsite) Pay Range: $60-$65/hour + Benefits What's the Job? Build and maintain financial models supporting program budgets, cost baselines, and should-cost analysis Track actuals versus forecast across program spend; prepare variance analysis and clear narratives for leadership Support monthly and quarterly close activities related to program cost tracking, including accruals and invoice reconciliation Reconcile vendor invoices and purchase orders against budgets, flag discrepancies before program reviews Partner with cross-functional teams to validate cost estimates and assess financial impacts of design or sourcing changes What's Needed? Bachelor's degree in Finance, Accounting, Economics, or a related field 2-4 years of experience in FP&amp;A, financial analysis, or cost accounting roles Strong financial modeling skills in Excel or Sheets, including variance analysis and scenario modeling Experience working with cross-functional teams outside of finance, such as engineering and procurement</t>
+          <t>Data Lead — Data Governance / MDG | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Data Lead — Data Governance / MDG Reference Number: 409871 Published Date: 10/02/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the autonomous mobility sector, is seeking a Data Lead — Data Governance / MDG to join their team. As a Data Lead — Data Governance / MDG, you will be part of the Data Management Department supporting cross-functional teams involved in manufacturing operations and enterprise data initiatives. The ideal candidate will demonstrate strong analytical skills, proactive communication, and collaborative spirit, which will align successfully in the organization. Job Title: Data Lead — Data Governance / MDG Location: Foster City, CA Pay Range: $90-$95/hour+ Benefits What's the Job? Lead current-state assessment of existing data management processes, tools, workflows, controls, and governance practices. Conduct comprehensive gap analysis between current MDM capabilities and target-state MDG solutions, focusing on workflow, approvals, stewardship, and data quality. Evaluate SAP MDG and comparable platforms to determine fit with business needs and existing SAP landscape. Partner with cross-functional teams to define and develop a scalable data governance operating model aligned with enterprise goals. Create detailed roadmaps, executive documentation, and strategic recommendations to support phased implementation and continuous improvement. What's Needed? 8 to 10 years of experience in data management, data governance, or enterprise data roles, with a focus on SAP data processes. Strong understanding of data governance concepts including ownership, stewardship,</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst</t>
+          <t>Finance Operations Analyst</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/hybrid-financial-analyst-/5856631</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/finance-operations-analyst/411813</t>
         </is>
       </c>
       <c r="J103" t="b">
@@ -7595,22 +7595,22 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-10-06T09:24:12+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>f177712205fd7fd46f19</t>
+          <t>94f070dac724bf6ab6ff</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Hybrid Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Hybrid Financial Analyst Reference Number: 5856631 Published Date: 10/06/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the financial services industry, is seeking a Hybrid Financial Analyst to join their team. As a Hybrid Financial Analyst, you will be part of the Finance Department supporting the Corporate Restructuring team. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: Hybrid Financial Analyst Location: El Segundo, CA (Hybrid - Remote and Onsite) Pay Range: $27.00/hr to $29.00/hr Shift: 10am to 6:30pm PT What's the Job? Monitor court websites for newly filed documents related to cases Review claims filed by creditors and respond to inquiries via phone and email Assist with special projects and perform administrative quality control reviews Manage case dockets and update public access websites with filed documents Coordinate and review ballots, proofs of claim, and change of address information What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus What's in it for me? Opportunity to grow into a Case Consultant role with potential salary increases Potential for promotion to management positions within the team Supportive work environment with professional development opportunities Flexible</t>
+          <t>Finance Operations Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Finance Operations Analyst Reference Number: 411813 Published Date: 10/02/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leader in the automotive and manufacturing industry, is seeking a Finance Operations Analyst to join their team. As a Finance Operations Analyst, you will be part of the Operations department supporting program financial governance, cost estimation, and budget management. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication skills, which will align successfully in the organization. Job Title: Finance Operations Analyst Location: Foster City, CA (Fully Onsite) Pay Range: $60-$65/hour + Benefits What's the Job? Build and maintain financial models supporting program budgets, cost baselines, and should-cost analysis Track actuals versus forecast across program spend; prepare variance analysis and clear narratives for leadership Support monthly and quarterly close activities related to program cost tracking, including accruals and invoice reconciliation Reconcile vendor invoices and purchase orders against budgets, flag discrepancies before program reviews Partner with cross-functional teams to validate cost estimates and assess financial impacts of design or sourcing changes What's Needed? Bachelor's degree in Finance, Accounting, Economics, or a related field 2-4 years of experience in FP&amp;A, financial analysis, or cost accounting roles Strong financial modeling skills in Excel or Sheets, including variance analysis and scenario modeling Experience working with cross-functional teams outside of finance, such as engineering and procurement</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Marketing Intelligence Analyst</t>
+          <t>Hybrid Financial Analyst</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/business-operations/marketing-intelligence-analyst/5883169</t>
+          <t>https://www.manpower.com/en/job/computer/hybrid-financial-analyst-/5856631</t>
         </is>
       </c>
       <c r="J104" t="b">
@@ -7665,22 +7665,22 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-10-03T08:28:30+00:00</t>
+          <t>2026-10-06T09:24:12+00:00</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>f7f171cfdb72efcca1a0</t>
+          <t>f177712205fd7fd46f19</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Marketing Intelligence Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Marketing Intelligence Analyst Reference Number: 5883169 Published Date: 10/03/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the manufacturing industry, is seeking a dedicated and innovative Marketing Intelligence Analyst to join their dynamic team. As a vital member of the marketing department supporting strategic initiatives, the ideal candidate will demonstrate analytical thinking, collaboration, and a proactive mindset to thrive in a fast-paced environment. Job Title: Marketing Intelligence Analyst Location: Atlanta, GA Pay Range: $97,000- $100,000 What's the Job? Design, develop, and maintain marketing dashboards using Power BI to deliver real-time insights on campaigns, audiences, content, and communication channels. Analyze historical and current marketing data to identify trends, opportunities, and key drivers affecting campaign performance and audience engagement. Create predictive models to forecast campaign outcomes, optimize channel mix, timing, and budget allocation, supporting data-driven marketing strategies. Collaborate with marketing, IT, and data engineering teams to integrate diverse data sources, ensuring a comprehensive view of marketing performance and customer behavior. Translate complex datasets and analytics into clear, actionable recommendations for marketing leadership to inform messaging, spend, and campaign design. What's Needed? Bachelor’s degree in Business, Marketing, Data Analytics, Information Systems, or related field. At least 2 years of experience supporting marketing teams with business intelligence, analytics, or data analysis. Proficiency in Powe</t>
+          <t>Hybrid Financial Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Hybrid Financial Analyst Reference Number: 5856631 Published Date: 10/06/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the financial services industry, is seeking a Hybrid Financial Analyst to join their team. As a Hybrid Financial Analyst, you will be part of the Finance Department supporting the Corporate Restructuring team. The ideal candidate will have strong analytical skills, attention to detail, and excellent communication abilities, which will align successfully in the organization. Job Title: Hybrid Financial Analyst Location: El Segundo, CA (Hybrid - Remote and Onsite) Pay Range: $27.00/hr to $29.00/hr Shift: 10am to 6:30pm PT What's the Job? Monitor court websites for newly filed documents related to cases Review claims filed by creditors and respond to inquiries via phone and email Assist with special projects and perform administrative quality control reviews Manage case dockets and update public access websites with filed documents Coordinate and review ballots, proofs of claim, and change of address information What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus What's in it for me? Opportunity to grow into a Case Consultant role with potential salary increases Potential for promotion to management positions within the team Supportive work environment with professional development opportunities Flexible</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Process Improvement Analyst</t>
+          <t>Logistics Analyst</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/process-improvement-analyst/411665</t>
+          <t>https://www.manpower.com/en/job/business-operations/logistics-analyst-/5880519</t>
         </is>
       </c>
       <c r="J105" t="b">
@@ -7735,22 +7735,22 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-07T02:48:05+00:00</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>90e82fcf9fb38e699886</t>
+          <t>55a327dd3e52a4c3c560</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Process Improvement Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Process Improvement Analyst Reference Number: 411665 Published Date: 10/02/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the transportation and logistics industry, is seeking a Process Improvement Analyst to join their team. As a Process Improvement Analyst, you will be part of the Fleet Operations department supporting various teams involved in operational excellence and process enhancement. The ideal candidate will have strong analytical skills, proactive mindset, and excellent communication abilities, which will align successfully in the organization. Job Title: Process Improvement Analyst Location: Foster City, CA Pay Range: $50/hour + Benefits What's the Job? Collaborate cross-functionally to gather, document, and prioritize requests for process improvements and playbook updates from various sources. Support the development and documentation of operational procedures within Fleet Operations. Coordinate with teams such as BaseOps, RemoteOps, Product, and Engineering to ensure project progress and alignment. Provide bi-weekly updates to stakeholders on ongoing process improvement initiatives. Assist in creating new processes and maintaining playbook documentation for on-site and robotic operations. What's Needed? Bachelor's degree in Business Administration, Operations Management, or a related field. 3+ years of experience in program management, operational excellence, or process improvement. Experience developing operational efficiencies in remote or similar environments such as call centers or teleoperation centers. Proficiency in data analysis and metrics to support strateg</t>
+          <t>Logistics Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Logistics Analyst Reference Number: 5880519 Published Date: 10/07/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE As a Logistics Analyst, you will support the Logistics and Transportation departments by enhancing data visibility, automating reporting processes, and developing analytical tools that facilitate faster and more informed business decisions. The ideal candidate will demonstrate strong analytical skills, a proactive approach, and excellent communication abilities, aligning well with the organization’s commitment to operational excellence and continuous improvement. Job Title: Logistics Analyst Location: Valencia, CA Pay Range: $28 - $30/hr. Shift: 40 hours a week What's the Job? Support Logistics and Transportation teams by improving data visibility and developing analytical tools. Automate recurring logistics reports to streamline data collection and reduce manual effort. Analyze transportation and logistics data to identify trends, risks, and cost-saving opportunities. Create and maintain Power BI dashboards and reports supporting operational metrics. Collaborate with cross-functional teams to translate operational needs into technical solutions and automation workflows. What's Needed? Bachelor’s degree in supply chain, Business Analytics, Data Analytics, or related field. 2–5 years of experience developing reports and dashboards using Power BI. Strong proficiency in Microsoft Excel, including data analysis, PivotTables, and advanced formulas. Experience working with ERP systems such as JD Edwards (JDE), SAP, or similar platforms. Excellent analytical, problem-solving, and communication skills with the ability to work with la</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Purchasing Analyst</t>
+          <t>Marketing Intelligence Analyst</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/management/purchasing-analyst/5890232</t>
+          <t>https://www.manpower.com/en/job/business-operations/marketing-intelligence-analyst/5883169</t>
         </is>
       </c>
       <c r="J106" t="b">
@@ -7805,22 +7805,22 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-10-05T02:26:52+00:00</t>
+          <t>2026-10-03T08:28:30+00:00</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>deae9ca8108b93dce864</t>
+          <t>f7f171cfdb72efcca1a0</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Purchasing Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Purchasing Analyst Reference Number: 5890232 Published Date: 10/05/2026 Job Type: Temporary Industry: Management Hours: Full Time APPLY NOW SAVE SHARE Now Hiring: Purchasing Analyst Location: Dallas, TX Schedule: Monday-Friday | Approximately 7:00 AM - 4:00 PM Salary: $60,000 - $90,000 per year We are seeking an experienced Purchasing Analyst with experience in a manufacturing environment. The ideal candidate will have a strong background in sourcing, purchasing, and supply chain management. Key Responsibilities: Source and purchase metals, raw materials, and production supplies Analyze inventory levels and production requirements to determine purchasing needs Utilize ERP systems to manage purchasing activities and inventory data Develop and maintain vendor relationships Track purchase orders and ensure on-time delivery of materials Resolve shortages, delays, and other supply chain issues Support production operations by ensuring material availability Qualifications: Purchasing experience in a manufacturing environment required Experience sourcing metals, raw materials, and production supplies Strong ERP system experience required Ability to analyze inventory and production data to support purchasing decisions Proven vendor management and negotiation skills Strong organizational and problem-solving abilities If this is a role that interests you and you’d like to learn more, click Apply Now, and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis and Talent Solutions Manpower® is a global leader in contingent staffing and permanent resourcing, providing companies wit</t>
+          <t>Marketing Intelligence Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Marketing Intelligence Analyst Reference Number: 5883169 Published Date: 10/03/2026 Job Type: Temporary Industry: Business Operations Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the manufacturing industry, is seeking a dedicated and innovative Marketing Intelligence Analyst to join their dynamic team. As a vital member of the marketing department supporting strategic initiatives, the ideal candidate will demonstrate analytical thinking, collaboration, and a proactive mindset to thrive in a fast-paced environment. Job Title: Marketing Intelligence Analyst Location: Atlanta, GA Pay Range: $97,000- $100,000 What's the Job? Design, develop, and maintain marketing dashboards using Power BI to deliver real-time insights on campaigns, audiences, content, and communication channels. Analyze historical and current marketing data to identify trends, opportunities, and key drivers affecting campaign performance and audience engagement. Create predictive models to forecast campaign outcomes, optimize channel mix, timing, and budget allocation, supporting data-driven marketing strategies. Collaborate with marketing, IT, and data engineering teams to integrate diverse data sources, ensuring a comprehensive view of marketing performance and customer behavior. Translate complex datasets and analytics into clear, actionable recommendations for marketing leadership to inform messaging, spend, and campaign design. What's Needed? Bachelor’s degree in Business, Marketing, Data Analytics, Information Systems, or related field. At least 2 years of experience supporting marketing teams with business intelligence, analytics, or data analysis. Proficiency in Powe</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Remote Data Analyst CA only</t>
+          <t>Process Improvement Analyst</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-ca-only-/5889335</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/process-improvement-analyst/411665</t>
         </is>
       </c>
       <c r="J107" t="b">
@@ -7875,22 +7875,22 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-10-04T11:28:51+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1c85522cebc8534c6229</t>
+          <t>90e82fcf9fb38e699886</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Remote Data Analyst CA only | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst CA only Reference Number: 5889335 Published Date: 10/04/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the restructuring and legal support industry, is seeking a dedicated and detail-oriented Remote Data Analyst CA only to join their team. As a Remote Data Analyst CA only, you will be part of the Corporate Restructuring department supporting critical legal and administrative functions. The ideal candidate will demonstrate strong organizational skills, excellent communication abilities, and a proactive mindset, which will align successfully in the organization. Job Title: Remote Data Analyst CA only Location: El Segundo, CA Pay Range: $27.00 to $29.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status, claim deadlines, and disbursements Assist with preparing and reviewing legal documents, ballots, and proofs of claim Coordinate mailings, compile service lists, and prepare affidavits of service Perform administrative quality control reviews to ensure accuracy and compliance What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus but not required What's in it for me? Weekly pay, with opportunities for overtime True contract-to-hire opportun</t>
+          <t>Process Improvement Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Process Improvement Analyst Reference Number: 411665 Published Date: 10/02/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the transportation and logistics industry, is seeking a Process Improvement Analyst to join their team. As a Process Improvement Analyst, you will be part of the Fleet Operations department supporting various teams involved in operational excellence and process enhancement. The ideal candidate will have strong analytical skills, proactive mindset, and excellent communication abilities, which will align successfully in the organization. Job Title: Process Improvement Analyst Location: Foster City, CA Pay Range: $50/hour + Benefits What's the Job? Collaborate cross-functionally to gather, document, and prioritize requests for process improvements and playbook updates from various sources. Support the development and documentation of operational procedures within Fleet Operations. Coordinate with teams such as BaseOps, RemoteOps, Product, and Engineering to ensure project progress and alignment. Provide bi-weekly updates to stakeholders on ongoing process improvement initiatives. Assist in creating new processes and maintaining playbook documentation for on-site and robotic operations. What's Needed? Bachelor's degree in Business Administration, Operations Management, or a related field. 3+ years of experience in program management, operational excellence, or process improvement. Experience developing operational efficiencies in remote or similar environments such as call centers or teleoperation centers. Proficiency in data analysis and metrics to support strateg</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>US - Sr Project Analyst</t>
+          <t>Purchasing Analyst</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>https://www.manpower.com/en/job/architecture-and-engineering/us-sr-project-analyst/410080</t>
+          <t>https://www.manpower.com/en/job/management/purchasing-analyst/5890232</t>
         </is>
       </c>
       <c r="J108" t="b">
@@ -7945,39 +7945,39 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-10-03T02:21:50+00:00</t>
+          <t>2026-10-05T02:26:52+00:00</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>18c5d451b034a7172ed8</t>
+          <t>deae9ca8108b93dce864</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>US - Sr Project Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) US - Sr Project Analyst Reference Number: 410080 Published Date: 10/03/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Sr Project Analyst | Charlotte, NC Our client, a leading aerospace and defense technology organization, is seeking a Sr Project Analyst to join their team.As a Sr. Project Analyst, you will be part of the Benefits Compliance team supporting HR, Legal, Finance, and external vendor partners. The ideal candidate will have strong analytical skills, attention to detail, and the ability to manage multiple priorities, which will align successfully within the organization. Job Title: Sr Project Analyst Location: Charlotte, NC Pay Range: $56.00/hour What’s the Job? Manage the preparation, coordination, and submission of IRS Form 5500 filings and supporting schedules across multiple benefit plans. Ensure compliance with ERISA, IRS, DOL, ACA, HIPAA, COBRA, FMLA, and state disability regulations. Support SEC Form 11-K filings and maintain required benefits documentation and disclosures. Partner with auditors, third-party administrators, legal counsel, and internal stakeholders to ensure accurate and timely regulatory submissions. Analyze plan data, support audits, track compliance deadlines, and drive continuous process improvements. What’s Needed? Bachelor's degree in Accounting, Finance, Business, or a related field. Minimum 3 years of accounting and auditing experience, preferably with public company financial statements. Strong analytical, organizational, and problem-solving skills with excellent attention to detail. Ability to manage multiple priorities and regulatory deadlines while maintaining a high level of a</t>
+          <t>Purchasing Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Purchasing Analyst Reference Number: 5890232 Published Date: 10/05/2026 Job Type: Temporary Industry: Management Hours: Full Time APPLY NOW SAVE SHARE Now Hiring: Purchasing Analyst Location: Dallas, TX Schedule: Monday-Friday | Approximately 7:00 AM - 4:00 PM Salary: $60,000 - $90,000 per year We are seeking an experienced Purchasing Analyst with experience in a manufacturing environment. The ideal candidate will have a strong background in sourcing, purchasing, and supply chain management. Key Responsibilities: Source and purchase metals, raw materials, and production supplies Analyze inventory levels and production requirements to determine purchasing needs Utilize ERP systems to manage purchasing activities and inventory data Develop and maintain vendor relationships Track purchase orders and ensure on-time delivery of materials Resolve shortages, delays, and other supply chain issues Support production operations by ensuring material availability Qualifications: Purchasing experience in a manufacturing environment required Experience sourcing metals, raw materials, and production supplies Strong ERP system experience required Ability to analyze inventory and production data to support purchasing decisions Proven vendor management and negotiation skills Strong organizational and problem-solving abilities If this is a role that interests you and you’d like to learn more, click Apply Now, and a recruiter will be in touch with you to discuss this great opportunity. We look forward to speaking with you! About ManpowerGroup, Parent Company of: Manpower, Experis and Talent Solutions Manpower® is a global leader in contingent staffing and permanent resourcing, providing companies wit</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MeeBoss</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Remote Data Analyst CA only</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7987,12 +7987,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>["full-time", "part-time"]</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8002,12 +8002,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/4ef5b514d62010e03nFy3w~~</t>
+          <t>https://www.manpower.com/en/job/computer/remote-data-analyst-ca-only-/5889335</t>
         </is>
       </c>
       <c r="J109" t="b">
@@ -8015,54 +8015,54 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-10-06T17:36:06+00:00</t>
+          <t>2026-10-04T11:28:51+00:00</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>5a98eacf0fee8021dd22</t>
+          <t>1c85522cebc8534c6229</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Description We are seeking a highly motivated and detail-oriented Data Analyst to join our dynamic team. As a Data Analyst, you will play a crucial role in transforming raw data into meaningful insights that drive strategic decision-making across the organization. You will work closely with cross-functional teams to gather, analyze, and interpret large datasets, identifying trends, patterns, and opportunities for improvement. The ideal candidate is proficient in statistical analysis and data visualization, has a strong analytical mindset, and is passionate about leveraging data to solve complex business problems. This role demands excellent communication skills to effectively present findings and collaborate with stakeholders at all levels. You will be instrumental in optimizing our data processes, ensuring data accuracy and integrity while contributing to the development of data-driven strategies that enhance operational efficiency and customer satisfaction. If you thrive in a fast-paced, collaborative environment and are eager to contribute your expertise to a forward-thinking company, this position offers an exciting opportunity to advance your career in data analytics while making a tangible impact on our business objectives. Responsibilities Gather, clean, and analyze large datasets to support business decisions. Develop and maintain dashboards and reports to visualize key performance indicators. Collaborate with cross-functional teams to understand data needs and deliver actionable insights. Identify trends, patterns, and anomalies in complex data sets. Perform statistical analysis to evaluate business processes and recommend improvements. Ensure data accuracy, integrity, and security throughout the analysis process. Present findings and insights to stakeholders through clear and concise reports and presentations. Support ad-hoc data requests and perform data mining as needed. Requirements Bachelor's degree in Data Science, Statistics, Mathematics, Computer Science, or related field. Proficiency in SQL for data extraction and manipulation. Experience with data visualization tools such as Tableau, Power BI, or similar. Strong analytical skills with the ability to interpret complex data. Knowledge of statistical analysis and modeling techniques. Familiarity with programming languages like Python or R is preferred. Excellent communication and presentation skills to convey data insights effectively. Detail-oriented with strong problem-solving abilities. Ability to work independently and collaboratively in a fast-paced environment.</t>
+          <t>Remote Data Analyst CA only | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) Remote Data Analyst CA only Reference Number: 5889335 Published Date: 10/04/2026 Job Type: Temporary Industry: Computer Hours: Full Time APPLY NOW SAVE SHARE Our client, a leading organization in the restructuring and legal support industry, is seeking a dedicated and detail-oriented Remote Data Analyst CA only to join their team. As a Remote Data Analyst CA only, you will be part of the Corporate Restructuring department supporting critical legal and administrative functions. The ideal candidate will demonstrate strong organizational skills, excellent communication abilities, and a proactive mindset, which will align successfully in the organization. Job Title: Remote Data Analyst CA only Location: El Segundo, CA Pay Range: $27.00 to $29.00hr Shift: 10:00am to 7:30pm PT, Monday-Friday What's the Job? Monitor court websites for newly filed documents and update case dockets accordingly Respond to creditor inquiries via phone and email regarding case status, claim deadlines, and disbursements Assist with preparing and reviewing legal documents, ballots, and proofs of claim Coordinate mailings, compile service lists, and prepare affidavits of service Perform administrative quality control reviews to ensure accuracy and compliance What's Needed? Ability to quickly learn and navigate proprietary software and applications Strong attention to detail and organizational skills Excellent written and verbal communication skills Proficiency with Microsoft Office Suite, especially Excel and Outlook One to two years of related office experience or relevant training is a plus but not required What's in it for me? Weekly pay, with opportunities for overtime True contract-to-hire opportun</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MeeBoss</t>
+          <t>ManpowerGroup</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>US - Sr Project Analyst</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>City or Zip Code City or Zip Code</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>["full-time", "part-time"]</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/b7f9b2aeb4b7883c3nBz0g~~</t>
+          <t>https://www.manpower.com/en/job/architecture-and-engineering/us-sr-project-analyst/410080</t>
         </is>
       </c>
       <c r="J110" t="b">
@@ -8085,22 +8085,22 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-10-03T02:21:50+00:00</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>8a46d82aecd31b6ce96c</t>
+          <t>18c5d451b034a7172ed8</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>About This Role We are looking for a skilled Data Analyst to join our team remotely. In this role, you will analyze data to help drive business decisions and improve our processes. Responsibilities Utilize SQL to extract and manipulate data from databases. Create visualizations to represent data insights clearly. Perform statistical analysis to support decision-making. Clean and prepare data for analysis. Use Python for data analysis and machine learning applications. Collaborate with team members to develop data-driven strategies. What We're Looking For High school diploma or equivalent education. Proven experience in data analysis. Strong skills in Excel and data visualization tools. Familiarity with statistical methods and machine learning techniques. Ability to work independently in a remote environment. Benefits &amp; Compensation Competitive hourly rate of $35-45. Flexible work schedule. Opportunities for professional development. Health and wellness benefits. A collaborative and supportive work environment.</t>
+          <t>US - Sr Project Analyst | Manpower US Contact Us United States (English) NEWSLETTER Stay up-to-date with the latest news in your industry. For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Search Jobs Find your next career. Search and apply for jobs you are interested in. Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH SEE ALL JOBS Sign In/Up Login FIND A JOB Job Title, Industry or Skill Job Title, Industry or Skill City or Zip Code City or Zip Code SEARCH JOBS For Job Seekers Working for Manpower Getting Started with Manpower Finding a Job MyPath My Manpower App Mature Worker Program Academy of Advanced Manufacturing For Employers Our Solutions Industries We Serve Workforce Tools Workforce Programs Post a Job with Manpower About Us Working with Manpower Awards and Recognition Find a Branch Contact Us Blog Job Seeker Advice and Resources Talent Pulse Contact Us United States (English) US - Sr Project Analyst Reference Number: 410080 Published Date: 10/03/2026 Job Type: Temporary Industry: Architecture and Engineering Hours: Full Time APPLY NOW SAVE SHARE Sr Project Analyst | Charlotte, NC Our client, a leading aerospace and defense technology organization, is seeking a Sr Project Analyst to join their team.As a Sr. Project Analyst, you will be part of the Benefits Compliance team supporting HR, Legal, Finance, and external vendor partners. The ideal candidate will have strong analytical skills, attention to detail, and the ability to manage multiple priorities, which will align successfully within the organization. Job Title: Sr Project Analyst Location: Charlotte, NC Pay Range: $56.00/hour What’s the Job? Manage the preparation, coordination, and submission of IRS Form 5500 filings and supporting schedules across multiple benefit plans. Ensure compliance with ERISA, IRS, DOL, ACA, HIPAA, COBRA, FMLA, and state disability regulations. Support SEC Form 11-K filings and maintain required benefits documentation and disclosures. Partner with auditors, third-party administrators, legal counsel, and internal stakeholders to ensure accurate and timely regulatory submissions. Analyze plan data, support audits, track compliance deadlines, and drive continuous process improvements. What’s Needed? Bachelor's degree in Accounting, Finance, Business, or a related field. Minimum 3 years of accounting and auditing experience, preferably with public company financial statements. Strong analytical, organizational, and problem-solving skills with excellent attention to detail. Ability to manage multiple priorities and regulatory deadlines while maintaining a high level of a</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/34f202bf86e427103ndz0g~~</t>
+          <t>https://meeboss.com/job/b7f9b2aeb4b7883c3nBz0g~~</t>
         </is>
       </c>
       <c r="J111" t="b">
@@ -8155,22 +8155,22 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>57acc90c8e31f810f918</t>
+          <t>8a46d82aecd31b6ce96c</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Description We are seeking a highly motivated and detail-oriented Data Analyst to join our dynamic team. The ideal candidate will play a critical role in analyzing data to help drive strategic business decisions. As a Data Analyst, you will be responsible for gathering, processing, and interpreting complex datasets to uncover trends, patterns, and insights that support key initiatives across various departments. You will work closely with cross-functional teams including marketing, finance, product development, and operations to provide data-driven recommendations that improve performance and foster growth. This position requires a strong analytical mindset, excellent problem-solving skills, and proficiency in data visualization and statistical tools. The successful candidate will be adept at transforming raw data into actionable intelligence, communicating findings effectively to both technical and non-technical stakeholders, and continuously optimizing data collection and analysis processes. If you are passionate about leveraging data to influence business strategy and enjoy working in a fast-paced environment, we encourage you to apply and become a vital member of our innovative organization. Responsibilities Collect, process, and analyze large datasets to identify trends and insights. Develop and maintain dashboards and reports for ongoing performance tracking. Collaborate with cross-functional teams to understand data needs and deliver solutions. Perform data cleaning and validation to ensure accuracy and consistency. Use statistical methods to analyze data and generate useful business reports. Present analytical findings clearly and effectively to both technical and non-technical audiences. Continuously improve data collection processes and analytical tools. Support decision-making by providing actionable recommendations based on data analysis.</t>
+          <t>About This Role We are looking for a skilled Data Analyst to join our team remotely. In this role, you will analyze data to help drive business decisions and improve our processes. Responsibilities Utilize SQL to extract and manipulate data from databases. Create visualizations to represent data insights clearly. Perform statistical analysis to support decision-making. Clean and prepare data for analysis. Use Python for data analysis and machine learning applications. Collaborate with team members to develop data-driven strategies. What We're Looking For High school diploma or equivalent education. Proven experience in data analysis. Strong skills in Excel and data visualization tools. Familiarity with statistical methods and machine learning techniques. Ability to work independently in a remote environment. Benefits &amp; Compensation Competitive hourly rate of $35-45. Flexible work schedule. Opportunities for professional development. Health and wellness benefits. A collaborative and supportive work environment.</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>["full-time", "part-time", "temporary"]</t>
+          <t>["full-time", "part-time"]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>https://meeboss.com/job/dc6fa56630d71ea03nFy3A~~</t>
+          <t>https://meeboss.com/job/4ef5b514d62010e03nFy3w~~</t>
         </is>
       </c>
       <c r="J112" t="b">
@@ -8230,49 +8230,49 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>b4322d2f5cbac897ab34</t>
+          <t>5a98eacf0fee8021dd22</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Description We are seeking a highly skilled and motivated Data Engineer to join our dynamic team. In this role, you will be responsible for designing, building, and maintaining scalable data pipelines and infrastructure that support our data analytics and business intelligence initiatives. The ideal candidate is passionate about data, highly proficient in data engineering best practices, and has a strong foundation in software engineering and data architecture. You will collaborate with data scientists, analysts, and various stakeholders to ensure efficient data flow and reliable data access across the organization. This position offers the opportunity to work with cutting-edge technologies in a fast-paced environment, contributing directly to data-driven decision making and innovation. If you have a strong background in data engineering, a problem-solving mindset, and the ability to thrive in a collaborative team setting, we would love to hear from you. Responsibilities Design, develop, and maintain scalable and reliable data pipelines and ETL processes. Collaborate with data scientists, analysts, and engineers to understand data requirements and deliver solutions. Optimize data systems for performance, reliability, and scalability. Implement and manage data storage solutions including data warehouses and data lakes. Ensure data quality and integrity across all systems and workflows. Monitor and troubleshoot data pipeline issues and implement necessary fixes promptly. Stay up to date with industry trends and integrate new technologies as appropriate to improve data engineering processes. Requirements Bachelor’s degree in Computer Science, Engineering, or a related field. Proven experience as a Data Engineer or in a similar role. Strong proficiency in SQL and experience with relational and NoSQL databases. Experience with ETL tools and building data pipelines using technologies such as Apache Spark, Apache Airflow, or similar. Proficiency in programming languages such as Python, Java, or Scala. Familiarity with cloud platforms like AWS, GCP, or Azure and their data engineering services. Strong problem-solving skills with the ability to work independently and collaboratively within a team.</t>
+          <t>Description We are seeking a highly motivated and detail-oriented Data Analyst to join our dynamic team. As a Data Analyst, you will play a crucial role in transforming raw data into meaningful insights that drive strategic decision-making across the organization. You will work closely with cross-functional teams to gather, analyze, and interpret large datasets, identifying trends, patterns, and opportunities for improvement. The ideal candidate is proficient in statistical analysis and data visualization, has a strong analytical mindset, and is passionate about leveraging data to solve complex business problems. This role demands excellent communication skills to effectively present findings and collaborate with stakeholders at all levels. You will be instrumental in optimizing our data processes, ensuring data accuracy and integrity while contributing to the development of data-driven strategies that enhance operational efficiency and customer satisfaction. If you thrive in a fast-paced, collaborative environment and are eager to contribute your expertise to a forward-thinking company, this position offers an exciting opportunity to advance your career in data analytics while making a tangible impact on our business objectives. Responsibilities Gather, clean, and analyze large datasets to support business decisions. Develop and maintain dashboards and reports to visualize key performance indicators. Collaborate with cross-functional teams to understand data needs and deliver actionable insights. Identify trends, patterns, and anomalies in complex data sets. Perform statistical analysis to evaluate business processes and recommend improvements. Ensure data accuracy, integrity, and security throughout the analysis process. Present findings and insights to stakeholders through clear and concise reports and presentations. Support ad-hoc data requests and perform data mining as needed. Requirements Bachelor's degree in Data Science, Statistics, Mathematics, Computer Science, or related field. Proficiency in SQL for data extraction and manipulation. Experience with data visualization tools such as Tableau, Power BI, or similar. Strong analytical skills with the ability to interpret complex data. Knowledge of statistical analysis and modeling techniques. Familiarity with programming languages like Python or R is preferred. Excellent communication and presentation skills to convey data insights effectively. Detail-oriented with strong problem-solving abilities. Ability to work independently and collaboratively in a fast-paced environment.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Motion Recruitment</t>
+          <t>MeeBoss</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>["full-time", "part-time"]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/agentic-ai-engineer/891578</t>
+          <t>https://meeboss.com/job/34f202bf86e427103ndz0g~~</t>
         </is>
       </c>
       <c r="J113" t="b">
@@ -8295,54 +8295,54 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>04610522eb708a5f80ae</t>
+          <t>57acc90c8e31f810f918</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Seeking an Agentic AI Engineer for a full-time, onsite opportunity in Dallas, TX (5 days per week onsite). This role is with a venture-backed artificial intelligence startup focused on building autonomous AI systems for the middle market. The ideal candidate will help design and scale AI-powered engineering workflows, leveraging LLMs, agentic AI frameworks, automation platforms, and modern software engineering practices to transform how products are built and delivered. What makes this opportunity unique? You'll join an early-stage startup that has secured funding and established initial customer traction, giving you the opportunity to influence both product and technical strategy. This is a highly visible role where you'll work directly with leadership to build the infrastructure, guardrails, and evaluation systems that enable AI-assisted development at scale. It's an ideal opportunity for someone who wants significant ownership, exposure to cutting-edge AI technologies, and the ability to shape how engineering teams leverage AI in the future. Required Skills &amp; Experience Experience building solutions with modern AI and LLM technologies Strong software engineering and systems design experience Experience with AI agents, orchestration frameworks, and development automation Ability to design scalable workflows, evaluation frameworks, and engineering processes Experience implementing software quality controls, testing frameworks, and automation Desired Skills &amp; Experience Experience building agentic AI applications Deep familiarity with LLM evaluation techniques Experience developing internal developer platforms or tooling Exposure to AI-assisted software development workflows Startup experience What You Will Be Doing Tech Breakdown 40% Agentic AI Infrastructure &amp; Orchestration 25% AI Evaluation &amp; Quality Systems 20% Developer Productivity &amp; Enablement 15% Security, Governance &amp; Process Optimization Daily Responsibilities Build tooling and infrastructure that enables engineers to effectively leverage AI agents Design context management, evaluation, and verification systems for AI-generated code Establish guardrails, testing strategies, and quality controls for AI-assisted development Measure and optimize engineering productivity through automation and analytics Partner with engineering leadership to identify and implement best practices The Offer You will receive the following benefits: Eligible for Salary Bonus Medical, Dental, and Vision Insurance Vacation Time Stock Options Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Description We are seeking a highly motivated and detail-oriented Data Analyst to join our dynamic team. The ideal candidate will play a critical role in analyzing data to help drive strategic business decisions. As a Data Analyst, you will be responsible for gathering, processing, and interpreting complex datasets to uncover trends, patterns, and insights that support key initiatives across various departments. You will work closely with cross-functional teams including marketing, finance, product development, and operations to provide data-driven recommendations that improve performance and foster growth. This position requires a strong analytical mindset, excellent problem-solving skills, and proficiency in data visualization and statistical tools. The successful candidate will be adept at transforming raw data into actionable intelligence, communicating findings effectively to both technical and non-technical stakeholders, and continuously optimizing data collection and analysis processes. If you are passionate about leveraging data to influence business strategy and enjoy working in a fast-paced environment, we encourage you to apply and become a vital member of our innovative organization. Responsibilities Collect, process, and analyze large datasets to identify trends and insights. Develop and maintain dashboards and reports for ongoing performance tracking. Collaborate with cross-functional teams to understand data needs and deliver solutions. Perform data cleaning and validation to ensure accuracy and consistency. Use statistical methods to analyze data and generate useful business reports. Present analytical findings clearly and effectively to both technical and non-technical audiences. Continuously improve data collection processes and analytical tools. Support decision-making by providing actionable recommendations based on data analysis.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Motion Recruitment</t>
+          <t>MeeBoss</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - CTH</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Worth, Texas, 76155, United States</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>["full-time", "part-time", "temporary"]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/fort-worth/contract/associate-data-engineer-cth/884700</t>
+          <t>https://meeboss.com/job/dc6fa56630d71ea03nFy3A~~</t>
         </is>
       </c>
       <c r="J114" t="b">
@@ -8365,22 +8365,22 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-09-15T18:37:24+00:00</t>
+          <t>2026-10-06T17:36:06+00:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>eeba2482b3e3680a7e15</t>
+          <t>b4322d2f5cbac897ab34</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Description: Associate Data Engineer Location: Fort Worth Texas 76155 United State (Hybrid) What you'll do As noted above, this list is intended to reflect the current job but there may be additional essential functions (and certainly non-essential job functions) that are not referenced. Management will modify the job or require other tasks be performed whenever it is deemed appropriate to do so, observing, of course, any legal obligations including any collective bargaining obligations. • Work closely with source data application teams and product owners to design, implement and support analytics solutions that provide insights to make better decisions • Implement data migration and data engineering solutions using Azure products and services: (Azure Data Lake Storage, Azure Data Factory, Azure Functions, Event Hub, Azure Stream Analytics, Azure Databricks, etc.) and traditional data warehouse tools • Perform multiple aspects involved in the development lifecycle - design, cloud engineering (Infrastructure, network, security, and administration), ingestion, preparation, data modeling, testing, CICD pipelines, performance tuning, deployments, consumption, BI, alerting, prod support • Develop technical solutions and collaborate within a team environment as well as work independently • Be a part of a DevOps team that completely owns and supports their product • Follow coding standards, best practices and privacy and security guidelines • Be part of multi-functional technical and domain skills team All you'll need for success Minimum Qualifications - Education &amp; Prior Job Experience • Bachelor's degree in Computer Science, Computer Engineering, Technology, Information Systems (CIS/MIS), Engineering or related technical discipline, or equivalent experience/training • 1+ years experience building data solutions, using agile and DevOps practices. • 1+ years data analytics experience using SQL • 1+ years experience with Cloud technologies (especially Microsoft Azure) Preferred Qualifications - Education &amp; Prior Job Experience • 2+ years software solution development using agile, dev ops practices. • 2+ years data analytics experience using SQL • 2+ years using SQL, Python and Spark • 1+ years experience with Cloud Technologies (especially Microsoft Azure) Skills, Licenses, and Certifications • Expertise with a Cloud based technology stack for data management, ingestion, curation and consumption layers. • Azure Databricks 1-3 years of experience is needed for this role Top Skills: SQL, building data solutions, develops practices, Microsoft Azure(Generic), Python, Sequel Nice to Have Skills: Spark and Databricks Describe a great candidate that you are looking for and what skills and experience they will have: Knowledge of software design principles, understanding of big data, knowledge of SQL, good work ethics What is the team environment and structure like?:Very laid-back work environment, with a tech lead and 3 other senior and junior developers. Candid</t>
+          <t>Description We are seeking a highly skilled and motivated Data Engineer to join our dynamic team. In this role, you will be responsible for designing, building, and maintaining scalable data pipelines and infrastructure that support our data analytics and business intelligence initiatives. The ideal candidate is passionate about data, highly proficient in data engineering best practices, and has a strong foundation in software engineering and data architecture. You will collaborate with data scientists, analysts, and various stakeholders to ensure efficient data flow and reliable data access across the organization. This position offers the opportunity to work with cutting-edge technologies in a fast-paced environment, contributing directly to data-driven decision making and innovation. If you have a strong background in data engineering, a problem-solving mindset, and the ability to thrive in a collaborative team setting, we would love to hear from you. Responsibilities Design, develop, and maintain scalable and reliable data pipelines and ETL processes. Collaborate with data scientists, analysts, and engineers to understand data requirements and deliver solutions. Optimize data systems for performance, reliability, and scalability. Implement and manage data storage solutions including data warehouses and data lakes. Ensure data quality and integrity across all systems and workflows. Monitor and troubleshoot data pipeline issues and implement necessary fixes promptly. Stay up to date with industry trends and integrate new technologies as appropriate to improve data engineering processes. Requirements Bachelor’s degree in Computer Science, Engineering, or a related field. Proven experience as a Data Engineer or in a similar role. Strong proficiency in SQL and experience with relational and NoSQL databases. Experience with ETL tools and building data pipelines using technologies such as Apache Spark, Apache Airflow, or similar. Proficiency in programming languages such as Python, Java, or Scala. Familiarity with cloud platforms like AWS, GCP, or Azure and their data engineering services. Strong problem-solving skills with the ability to work independently and collaboratively within a team.</t>
         </is>
       </c>
     </row>
@@ -8392,27 +8392,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Business Data Analyst</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, 30009, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/business-data-analyst/887454</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/agentic-ai-engineer/891578</t>
         </is>
       </c>
       <c r="J115" t="b">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-09-14T21:22:24+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>fd8f32a1f36407c076dc</t>
+          <t>04610522eb708a5f80ae</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Job Description Business Data Analyst Location: Remote (US) Duration: 6-Month Contract (Potential Extension) Compensation: Up to $40/hr A leading business intelligence and information services organization is seeking a Business Data Analyst to support a high-visibility analytics platform used to drive strategic decision-making across multiple departments. This role is ideal for someone who enjoys working with complex datasets, uncovering meaningful insights, improving data quality, and developing solutions that help business teams make better decisions. The successful candidate will partner closely with stakeholders to understand business needs, identify opportunities for improvement, and deliver reliable reporting and analytical tools. The position combines data analysis, business problem-solving, reporting, and technical solution development in a collaborative remote environment. While a strong analytical mindset is critical, the ability to leverage technology to automate processes and improve efficiency will be equally important. Required Skills &amp; Experience 3+ years of experience in a Data Analyst, Business Data Analyst, Reporting Analyst, or Business Intelligence Analyst role Advanced experience using Python for data analysis, automation, and data processing Strong experience working with large and complex datasets Experience using Pandas and related data analysis libraries Proven ability to identify and resolve data quality issues Experience building reports, dashboards, and business insights for stakeholders Experience integrating and analyzing data from multiple sources including APIs, spreadsheets, and databases Strong analytical, critical thinking, and problem-solving skills Ability to communicate findings and recommendations to both technical and non-technical audiences Desired Skills &amp; Experience Experience with business intelligence and reporting solutions Familiarity with Streamlit, Dash, Gradio, or similar data applications SQL and database experience Experience with data validation and quality control processes Knowledge of modern data governance practices Experience creating automated reporting workflows Exposure to cloud-based analytics environments Background supporting sales, operations, financial, or strategic reporting functions What You Will Be Doing Daily Responsibilities Analyze, validate, and standardize data from multiple business sources Support and enhance a production analytics platform used across the organization Develop automated processes that improve reporting efficiency and data accuracy Build dashboards, reports, and analytical solutions for business stakeholders Investigate data discrepancies and implement quality control measures Integrate data from external and internal systems to improve visibility and decision-making Partner directly with business teams to gather requirements and deliver solutions Identify opportunities to streamline processes and improve operational reporting Create documentation for rep</t>
+          <t>Seeking an Agentic AI Engineer for a full-time, onsite opportunity in Dallas, TX (5 days per week onsite). This role is with a venture-backed artificial intelligence startup focused on building autonomous AI systems for the middle market. The ideal candidate will help design and scale AI-powered engineering workflows, leveraging LLMs, agentic AI frameworks, automation platforms, and modern software engineering practices to transform how products are built and delivered. What makes this opportunity unique? You'll join an early-stage startup that has secured funding and established initial customer traction, giving you the opportunity to influence both product and technical strategy. This is a highly visible role where you'll work directly with leadership to build the infrastructure, guardrails, and evaluation systems that enable AI-assisted development at scale. It's an ideal opportunity for someone who wants significant ownership, exposure to cutting-edge AI technologies, and the ability to shape how engineering teams leverage AI in the future. Required Skills &amp; Experience Experience building solutions with modern AI and LLM technologies Strong software engineering and systems design experience Experience with AI agents, orchestration frameworks, and development automation Ability to design scalable workflows, evaluation frameworks, and engineering processes Experience implementing software quality controls, testing frameworks, and automation Desired Skills &amp; Experience Experience building agentic AI applications Deep familiarity with LLM evaluation techniques Experience developing internal developer platforms or tooling Exposure to AI-assisted software development workflows Startup experience What You Will Be Doing Tech Breakdown 40% Agentic AI Infrastructure &amp; Orchestration 25% AI Evaluation &amp; Quality Systems 20% Developer Productivity &amp; Enablement 15% Security, Governance &amp; Process Optimization Daily Responsibilities Build tooling and infrastructure that enables engineers to effectively leverage AI agents Design context management, evaluation, and verification systems for AI-generated code Establish guardrails, testing strategies, and quality controls for AI-assisted development Measure and optimize engineering productivity through automation and analytics Partner with engineering leadership to identify and implement best practices The Offer You will receive the following benefits: Eligible for Salary Bonus Medical, Dental, and Vision Insurance Vacation Time Stock Options Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -8462,17 +8462,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer - Python/SQL/PowerBi/Security Analytics</t>
+          <t>Associate Data Engineer - CTH</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, 30009, United States</t>
+          <t>Fort Worth, Texas, 76155, United States</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-security-analytics/888444</t>
+          <t>https://motionrecruitment.com/tech-jobs/fort-worth/contract/associate-data-engineer-cth/884700</t>
         </is>
       </c>
       <c r="J116" t="b">
@@ -8505,22 +8505,22 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-09-25T19:01:26+00:00</t>
+          <t>2026-09-15T18:37:24+00:00</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>ad181cacc5375145c150</t>
+          <t>eeba2482b3e3680a7e15</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Job Description A leading organization within a highly regulated cloud environment is seeking a Cybersecurity Data Engineer to support security analytics, continuous monitoring, and automation initiatives across enterprise and cloud platforms. This role is ideal for someone who enjoys working at the intersection of cybersecurity, data engineering, and analytics. You'll leverage security telemetry, vulnerability data, and operational metrics to create meaningful insights, automate reporting processes, and improve overall security visibility. While the environment operates under regulatory requirements, the primary focus is on security data analysis, dashboard development, monitoring, and automation. You will collaborate with security, engineering, and infrastructure teams to build scalable reporting solutions, develop security metrics, and enhance the organization's ability to identify trends, risks, and opportunities for improvement. Location: Alpharetta, GA (Hybrid, 1 day onsite per week) Contract: 6 Months with potential extension and conversion opportunity Compensation: $40-$60/hour Required Skills &amp; Experience 3+ years of experience in cybersecurity, security analytics, security operations, or a related field Strong Python development and automation experience Advanced SQL skills with experience querying and analyzing large datasets Experience building dashboards and reports using Power BI or similar BI platforms Experience working with security logs, alerts, telemetry, vulnerability data, and incident response information Experience with Microsoft Defender or similar security monitoring solutions Familiarity with Microsoft Azure and cloud security concepts Understanding of security operations, threat monitoring, vulnerability management, and incident response Experience with ETL processes, reporting workflows, and data analytics Strong analytical, troubleshooting, and communication skills Desired Skills &amp; Experience Experience working in a Blue Team or Security Operations Center (SOC) environment Experience developing security analytics and reporting solutions Familiarity with FedRAMP, NIST, or similar regulatory frameworks Experience automating security monitoring or reporting processes using Python or PowerShell Relevant cybersecurity certifications What You Will Be Doing Daily Responsibilities: 100% Hands On Analyze security data from logs, vulnerability scans, monitoring platforms, and incident response activities Design, develop, and maintain Power BI dashboards and reporting solutions Build automation tools and reporting processes using Python Write and optimize SQL queries to support investigations, metrics, and reporting needs Monitor security events and telemetry to identify trends, anomalies, and potential threats Support security operations through incident analysis and continuous monitoring activities Develop and track security KPIs and operational metrics Partner with security, engineering, and infrastructure teams to improve se</t>
+          <t>Description: Associate Data Engineer Location: Fort Worth Texas 76155 United State (Hybrid) What you'll do As noted above, this list is intended to reflect the current job but there may be additional essential functions (and certainly non-essential job functions) that are not referenced. Management will modify the job or require other tasks be performed whenever it is deemed appropriate to do so, observing, of course, any legal obligations including any collective bargaining obligations. • Work closely with source data application teams and product owners to design, implement and support analytics solutions that provide insights to make better decisions • Implement data migration and data engineering solutions using Azure products and services: (Azure Data Lake Storage, Azure Data Factory, Azure Functions, Event Hub, Azure Stream Analytics, Azure Databricks, etc.) and traditional data warehouse tools • Perform multiple aspects involved in the development lifecycle - design, cloud engineering (Infrastructure, network, security, and administration), ingestion, preparation, data modeling, testing, CICD pipelines, performance tuning, deployments, consumption, BI, alerting, prod support • Develop technical solutions and collaborate within a team environment as well as work independently • Be a part of a DevOps team that completely owns and supports their product • Follow coding standards, best practices and privacy and security guidelines • Be part of multi-functional technical and domain skills team All you'll need for success Minimum Qualifications - Education &amp; Prior Job Experience • Bachelor's degree in Computer Science, Computer Engineering, Technology, Information Systems (CIS/MIS), Engineering or related technical discipline, or equivalent experience/training • 1+ years experience building data solutions, using agile and DevOps practices. • 1+ years data analytics experience using SQL • 1+ years experience with Cloud technologies (especially Microsoft Azure) Preferred Qualifications - Education &amp; Prior Job Experience • 2+ years software solution development using agile, dev ops practices. • 2+ years data analytics experience using SQL • 2+ years using SQL, Python and Spark • 1+ years experience with Cloud Technologies (especially Microsoft Azure) Skills, Licenses, and Certifications • Expertise with a Cloud based technology stack for data management, ingestion, curation and consumption layers. • Azure Databricks 1-3 years of experience is needed for this role Top Skills: SQL, building data solutions, develops practices, Microsoft Azure(Generic), Python, Sequel Nice to Have Skills: Spark and Databricks Describe a great candidate that you are looking for and what skills and experience they will have: Knowledge of software design principles, understanding of big data, knowledge of SQL, good work ethics What is the team environment and structure like?:Very laid-back work environment, with a tech lead and 3 other senior and junior developers. Candid</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer, Python/SQL/PowerBi - Georgia</t>
+          <t>Business Data Analyst</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-georgia/887207</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/business-data-analyst/887454</t>
         </is>
       </c>
       <c r="J117" t="b">
@@ -8575,22 +8575,22 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-09-10T18:09:10+00:00</t>
+          <t>2026-09-14T21:22:24+00:00</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>ee4d1750d211c7261738</t>
+          <t>fd8f32a1f36407c076dc</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Job Description An industry-leading organization is hiring a Cybersecurity Data Engineer to help transform security and vulnerability data into actionable insights for security and engineering teams. This is a highly data-focused security position centered around collecting, processing, analyzing, and reporting on data generated from vulnerability scans and security tools. In this role, you will use Python and SQL to work with security data, build and maintain data pipelines, and transform raw scan data into clean, usable datasets. You will also develop reporting and dashboards using Power BI, Microsoft Fabric, or similar data visualization tools . The ideal candidate has a strong background in data engineering, cybersecurity, or a combination of both. Candidates with experience as a Data Engineer working with security data, Cybersecurity Engineer with strong Python and SQL skills, or Security Analyst who has moved into data and automation are encouraged to apply. Required Skills &amp; Experience Strong proficiency in Python Strong proficiency in SQL Experience working with data pipelines, ETL, databases, or data warehousing Experience working with Power BI, Microsoft Fabric, or similar business intelligence/data visualization platforms Experience working with security, vulnerability, compliance, or cybersecurity-related data Experience analyzing data from vulnerability scans, security tools, assessments, or similar sources Strong data analysis and problem-solving skills Experience working with large datasets Experience with JSON, XML, and Excel Bachelor's degree 3–5+ years of relevant professional experience Desired Skills &amp; Experience Experience working in a cybersecurity, information security, or security engineering environment Experience with vulnerability management or security scanning tools Experience automating security or data processes with Python Experience building security dashboards and reporting in Power BI Experience with Microsoft Azure or cloud security Experience with Microsoft Defender or similar security platforms Experience working with security logs, alerts, vulnerability data, or other security telemetry Familiarity with FedRAMP, NIST, or other security/compliance frameworks Experience with PowerShell Experience supporting security metrics, continuous monitoring, or security posture reporting What You Will Be Doing Daily Responsibilities Collect, process, and analyze data from vulnerability scans, security tools, assessments, and other security sources Build and maintain data pipelines and ETL processes for security-related data Use Python to automate data processing, analysis, reporting, and security workflows Use SQL to query databases, manipulate data, and develop reporting datasets Transform raw scan and security data into clean, usable datasets Build and maintain Power BI and Microsoft Fabric dashboards and reports Develop KPIs and metrics to help security teams measure and track their security posture Analyze large secu</t>
+          <t>Job Description Business Data Analyst Location: Remote (US) Duration: 6-Month Contract (Potential Extension) Compensation: Up to $40/hr A leading business intelligence and information services organization is seeking a Business Data Analyst to support a high-visibility analytics platform used to drive strategic decision-making across multiple departments. This role is ideal for someone who enjoys working with complex datasets, uncovering meaningful insights, improving data quality, and developing solutions that help business teams make better decisions. The successful candidate will partner closely with stakeholders to understand business needs, identify opportunities for improvement, and deliver reliable reporting and analytical tools. The position combines data analysis, business problem-solving, reporting, and technical solution development in a collaborative remote environment. While a strong analytical mindset is critical, the ability to leverage technology to automate processes and improve efficiency will be equally important. Required Skills &amp; Experience 3+ years of experience in a Data Analyst, Business Data Analyst, Reporting Analyst, or Business Intelligence Analyst role Advanced experience using Python for data analysis, automation, and data processing Strong experience working with large and complex datasets Experience using Pandas and related data analysis libraries Proven ability to identify and resolve data quality issues Experience building reports, dashboards, and business insights for stakeholders Experience integrating and analyzing data from multiple sources including APIs, spreadsheets, and databases Strong analytical, critical thinking, and problem-solving skills Ability to communicate findings and recommendations to both technical and non-technical audiences Desired Skills &amp; Experience Experience with business intelligence and reporting solutions Familiarity with Streamlit, Dash, Gradio, or similar data applications SQL and database experience Experience with data validation and quality control processes Knowledge of modern data governance practices Experience creating automated reporting workflows Exposure to cloud-based analytics environments Background supporting sales, operations, financial, or strategic reporting functions What You Will Be Doing Daily Responsibilities Analyze, validate, and standardize data from multiple business sources Support and enhance a production analytics platform used across the organization Develop automated processes that improve reporting efficiency and data accuracy Build dashboards, reports, and analytical solutions for business stakeholders Investigate data discrepancies and implement quality control measures Integrate data from external and internal systems to improve visibility and decision-making Partner directly with business teams to gather requirements and deliver solutions Identify opportunities to streamline processes and improve operational reporting Create documentation for rep</t>
         </is>
       </c>
     </row>
@@ -8602,12 +8602,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Data Architect | Richardson | AWS</t>
+          <t>Cybersecurity Data Engineer - Python/SQL/PowerBi/Security Analytics</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Richardson, Texas, 75080, United States</t>
+          <t>Alpharetta, Georgia, 30009, United States</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/richardson/direct-hire/data-architect-richardson-aws/884037</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-security-analytics/888444</t>
         </is>
       </c>
       <c r="J118" t="b">
@@ -8645,22 +8645,22 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-08-20T15:21:06+00:00</t>
+          <t>2026-09-25T19:01:26+00:00</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>a3f3fd8a2c38f7e08d8d</t>
+          <t>ad181cacc5375145c150</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>We are seeking a Senior Data Architect to help drive the next generation of enterprise data capabilities within a rapidly growing, newly centralized data organization. This role will play a key part in designing and implementing modern data architectures, data products, and strategic roadmaps that support enterprise-wide analytics, reporting, and AI initiatives. In this highly visible position, you will partner directly with business leaders, engineering teams, and data stakeholders to define data strategy, architect scalable solutions, and establish best practices across a modern AWS and Snowflake ecosystem. This is an opportunity to influence the future-state data platform from the ground up within a highly collaborative and strategic environment. Required Skills &amp; Experience Strong experience designing enterprise Data Architectures, Data Warehouses, and scalable cloud-based data platforms Deep expertise with AWS and Snowflake, including warehouse sizing, clustering, partitioning, and performance optimization Experience developing data roadmaps, architecture standards, and long-term data strategies Strong understanding of data ingestion patterns, data integration frameworks, and modern data engineering practices Desired Skills &amp; Experience Experience with AI-enabled data architectures and emerging AI technologies Knowledge of RAG (Retrieval-Augmented Generation), Vector Databases, MCP, and Large Language Models (LLMs) Experience building data products and supporting advanced analytics initiatives Financial services, banking, or regulated industry experience What You Will Be Doing Design and implement enterprise data architectures leveraging AWS and Snowflake Define data platform strategy, roadmaps, and best practices in partnership with business and technology leaders Architect scalable data ingestion, storage, governance, and analytics solutions Evaluate and incorporate emerging AI technologies and data products into the organization's long-term vision Applicants must be currently authorized to work in the US on a full-time basis now and in the future</t>
+          <t>Job Description A leading organization within a highly regulated cloud environment is seeking a Cybersecurity Data Engineer to support security analytics, continuous monitoring, and automation initiatives across enterprise and cloud platforms. This role is ideal for someone who enjoys working at the intersection of cybersecurity, data engineering, and analytics. You'll leverage security telemetry, vulnerability data, and operational metrics to create meaningful insights, automate reporting processes, and improve overall security visibility. While the environment operates under regulatory requirements, the primary focus is on security data analysis, dashboard development, monitoring, and automation. You will collaborate with security, engineering, and infrastructure teams to build scalable reporting solutions, develop security metrics, and enhance the organization's ability to identify trends, risks, and opportunities for improvement. Location: Alpharetta, GA (Hybrid, 1 day onsite per week) Contract: 6 Months with potential extension and conversion opportunity Compensation: $40-$60/hour Required Skills &amp; Experience 3+ years of experience in cybersecurity, security analytics, security operations, or a related field Strong Python development and automation experience Advanced SQL skills with experience querying and analyzing large datasets Experience building dashboards and reports using Power BI or similar BI platforms Experience working with security logs, alerts, telemetry, vulnerability data, and incident response information Experience with Microsoft Defender or similar security monitoring solutions Familiarity with Microsoft Azure and cloud security concepts Understanding of security operations, threat monitoring, vulnerability management, and incident response Experience with ETL processes, reporting workflows, and data analytics Strong analytical, troubleshooting, and communication skills Desired Skills &amp; Experience Experience working in a Blue Team or Security Operations Center (SOC) environment Experience developing security analytics and reporting solutions Familiarity with FedRAMP, NIST, or similar regulatory frameworks Experience automating security monitoring or reporting processes using Python or PowerShell Relevant cybersecurity certifications What You Will Be Doing Daily Responsibilities: 100% Hands On Analyze security data from logs, vulnerability scans, monitoring platforms, and incident response activities Design, develop, and maintain Power BI dashboards and reporting solutions Build automation tools and reporting processes using Python Write and optimize SQL queries to support investigations, metrics, and reporting needs Monitor security events and telemetry to identify trends, anomalies, and potential threats Support security operations through incident analysis and continuous monitoring activities Develop and track security KPIs and operational metrics Partner with security, engineering, and infrastructure teams to improve se</t>
         </is>
       </c>
     </row>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks)</t>
+          <t>Cybersecurity Data Engineer, Python/SQL/PowerBi - Georgia</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>Alpharetta, Georgia, 30009, United States</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/data-engineer-databricks/891575</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/cybersecurity-data-engineer-python-sql-powerbi-georgia/887207</t>
         </is>
       </c>
       <c r="J119" t="b">
@@ -8715,22 +8715,22 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-09-10T18:09:10+00:00</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>8e507a40a646b69b913b</t>
+          <t>ee4d1750d211c7261738</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Seeking a Data Engineer for a full-time opportunity supporting a leading research, analytics, and technology organization within the utility and energy industry. This role will focus on designing, building, and optimizing modern data solutions leveraging Databricks, Spark, Python, AWS, SQL, and PostgreSQL to support both client-facing and SaaS-based data products. The position offers the opportunity to work on large-scale data platforms that help utilities improve customer engagement, grid operations, and business performance. You'll join a highly collaborative Machine Learning Engineering team where you'll work alongside data scientists, machine learning engineers, analysts, and software engineers to build impactful data solutions. This role is ideal for someone who enjoys solving complex data challenges, mentoring other engineers, and expanding their expertise in cloud data platforms, analytics, and machine learning technologies while contributing to meaningful work within the evolving energy sector. This is a fully remote oppurtunitiy. Required Skills &amp; Experience · 5+ years of experience in Data Engineering or a related field · Expert-level proficiency in Python, SQL, Databricks, and Spark · Experience building cloud-based data pipelines in AWS · Strong understanding of data engineering best practices and scalable architectures · Knowledge of data governance, security, privacy, and retention practices Desired Skills &amp; Experience Experience optimizing ETL workflows within Databricks Knowledge of data lineage and data quality frameworks Experience supporting machine learning and data science initiatives Prior experience within the utility or energy industry Master's degree in a related STEM field What You Will Be Doing Tech Breakdown 40% Databricks &amp; Spark Development 30% Data Pipeline Engineering 20% AWS Data Platform &amp; Infrastructure 10% Collaboration, Mentorship &amp; Innovation Daily Responsibilities Design, develop, and maintain scalable data pipelines and infrastructure Build and support data lakes, analytics platforms, and data products Collaborate with cross-functional teams to deliver business-driven solutions Monitor, troubleshoot, and improve data quality, reliability, and availability The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Eligible for salary bonus PTO &amp; Paid Holidays 401(k) with Company Match Remote Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description An industry-leading organization is hiring a Cybersecurity Data Engineer to help transform security and vulnerability data into actionable insights for security and engineering teams. This is a highly data-focused security position centered around collecting, processing, analyzing, and reporting on data generated from vulnerability scans and security tools. In this role, you will use Python and SQL to work with security data, build and maintain data pipelines, and transform raw scan data into clean, usable datasets. You will also develop reporting and dashboards using Power BI, Microsoft Fabric, or similar data visualization tools . The ideal candidate has a strong background in data engineering, cybersecurity, or a combination of both. Candidates with experience as a Data Engineer working with security data, Cybersecurity Engineer with strong Python and SQL skills, or Security Analyst who has moved into data and automation are encouraged to apply. Required Skills &amp; Experience Strong proficiency in Python Strong proficiency in SQL Experience working with data pipelines, ETL, databases, or data warehousing Experience working with Power BI, Microsoft Fabric, or similar business intelligence/data visualization platforms Experience working with security, vulnerability, compliance, or cybersecurity-related data Experience analyzing data from vulnerability scans, security tools, assessments, or similar sources Strong data analysis and problem-solving skills Experience working with large datasets Experience with JSON, XML, and Excel Bachelor's degree 3–5+ years of relevant professional experience Desired Skills &amp; Experience Experience working in a cybersecurity, information security, or security engineering environment Experience with vulnerability management or security scanning tools Experience automating security or data processes with Python Experience building security dashboards and reporting in Power BI Experience with Microsoft Azure or cloud security Experience with Microsoft Defender or similar security platforms Experience working with security logs, alerts, vulnerability data, or other security telemetry Familiarity with FedRAMP, NIST, or other security/compliance frameworks Experience with PowerShell Experience supporting security metrics, continuous monitoring, or security posture reporting What You Will Be Doing Daily Responsibilities Collect, process, and analyze data from vulnerability scans, security tools, assessments, and other security sources Build and maintain data pipelines and ETL processes for security-related data Use Python to automate data processing, analysis, reporting, and security workflows Use SQL to query databases, manipulate data, and develop reporting datasets Transform raw scan and security data into clean, usable datasets Build and maintain Power BI and Microsoft Fabric dashboards and reports Develop KPIs and metrics to help security teams measure and track their security posture Analyze large secu</t>
         </is>
       </c>
     </row>
@@ -8742,17 +8742,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake / dbt / Fivetran)</t>
+          <t>Data Architect | Richardson | AWS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Addison, Texas, 75001, United States</t>
+          <t>Richardson, Texas, 75080, United States</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/addison/direct-hire/data-engineer-snowflake-dbt-fivetran/891565</t>
+          <t>https://motionrecruitment.com/tech-jobs/richardson/direct-hire/data-architect-richardson-aws/884037</t>
         </is>
       </c>
       <c r="J120" t="b">
@@ -8785,22 +8785,22 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-08-20T15:21:06+00:00</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>9a28e93eb4abf69a9f14</t>
+          <t>a3f3fd8a2c38f7e08d8d</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Seeking a Senior Data Engineer for a full-time, hybrid role in Addison, TX (3 days onsite). This position will play a key role in building and ultimately owning a modern data platform for a growing home services organization, leveraging Snowflake, dbt, Fivetran, Azure, and AI technologies. The ideal candidate will help drive enterprise reporting, data warehousing, and future AI initiatives across a multi-site business operating nationwide. What makes this opportunity unique? You'll join during company-wide data transformation, helping build and own a brand-new Snowflake environment from the ground up. This is a high-impact role offering significant ownership, direct exposure to executive leadership, hands-on work with AI technologies, and a clear path to becoming the organization's long-term data engineering leader. Required Skills &amp; Experience · 7+ years of Data Engineering experience · Strong hands-on experience with Snowflake , including administration, optimization, and performance tuning · Advanced dbt experience with ownership of production projects (models, tests, snapshots, macros, CI/CD, and environment management) · Experience with Fivetran , Airbyte, Stitch, or similar ELT/integration platforms · Strong understanding of data warehousing concepts and dimensional data modeling Desired Skills &amp; Experience Snowflake Cortex Experience AI/LLM integrations and prompt engineering experience Experience with Great Expectations, Monte Carlo, Elementary, Soda, or similar data quality tools. SnowPro Certification Experience in multi-site or rapidly growing organizations through M&amp;A activities. What You Will Be Doing Tech Breakdown · 40 % Snowflake Administration &amp; Optimization · 30 % dbt Development &amp; Data Modeling · 20 % Data Pipeline Development &amp; ELT Management · 10 % AI &amp; Advanced Analytics Initiatives Daily Responsibilities · Own and optimize the Snowflake platform and data warehouse · Develop and maintain dbt models, data pipelines, and data marts · Manage data ingestion and integrations through Fivetran and related tools · Ensure data quality, monitoring, and pipeline reliability · Partner with business stakeholders and consulting teams to deliver scalable analytics solutions · Evaluate and implement AI-driven capabilities, including Snowflake Cortex and LLM integrations · Drive data engineering best practices, governance, and platform growth throughout the organization The Offer You will receive the following benefits: Eligible for salary bonus Medical, Dental &amp; Vision Insurance PTO &amp; Paid Holidays 401(k) with Company Match Hybrid Schedule (3 Days Onsite) Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>We are seeking a Senior Data Architect to help drive the next generation of enterprise data capabilities within a rapidly growing, newly centralized data organization. This role will play a key part in designing and implementing modern data architectures, data products, and strategic roadmaps that support enterprise-wide analytics, reporting, and AI initiatives. In this highly visible position, you will partner directly with business leaders, engineering teams, and data stakeholders to define data strategy, architect scalable solutions, and establish best practices across a modern AWS and Snowflake ecosystem. This is an opportunity to influence the future-state data platform from the ground up within a highly collaborative and strategic environment. Required Skills &amp; Experience Strong experience designing enterprise Data Architectures, Data Warehouses, and scalable cloud-based data platforms Deep expertise with AWS and Snowflake, including warehouse sizing, clustering, partitioning, and performance optimization Experience developing data roadmaps, architecture standards, and long-term data strategies Strong understanding of data ingestion patterns, data integration frameworks, and modern data engineering practices Desired Skills &amp; Experience Experience with AI-enabled data architectures and emerging AI technologies Knowledge of RAG (Retrieval-Augmented Generation), Vector Databases, MCP, and Large Language Models (LLMs) Experience building data products and supporting advanced analytics initiatives Financial services, banking, or regulated industry experience What You Will Be Doing Design and implement enterprise data architectures leveraging AWS and Snowflake Define data platform strategy, roadmaps, and best practices in partnership with business and technology leaders Architect scalable data ingestion, storage, governance, and analytics solutions Evaluate and incorporate emerging AI technologies and data products into the organization's long-term vision Applicants must be currently authorized to work in the US on a full-time basis now and in the future</t>
         </is>
       </c>
     </row>
@@ -8812,27 +8812,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Data Engineer / Charlotte / Hybrid</t>
+          <t>Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Charlotte, NC, 28202, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/data-engineer-charlotte-hybrid/861817</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/data-engineer-databricks/891575</t>
         </is>
       </c>
       <c r="J121" t="b">
@@ -8855,22 +8855,22 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-08-04T16:52:57+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>c4ff54db51fe9b4cb6c0</t>
+          <t>8e507a40a646b69b913b</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Outstanding long-term contract opportunity! A well-known Financial Services Company is looking for a Data Engineer in Charlotte, NC (Hybrid). Work with the brightest minds at one of the largest financial institutions in the world. This is long-term contract opportunity that includes a competitive benefit package! Our client has been around for over 150 years and is continuously innovating in today's digital age. If you want to work for a company that is not only a household name, but also truly cares about satisfying customers' financial needs and helping people succeed financially, apply today. Contract Duration: 12 Months Required Skills &amp; Experience 7+ years of Data engineering experience 7+ years of MS SQL server experience 7+ years of Teradata experience 7+ years of SDLC (System Development Life Cycle) experience 5+ years of experience in Teradata database technology and products such as TASM, Unity, Data mover and Query Grid 5+ years of ETL (Extract, Transform, Load) development experience using Ab Initio 5+ years of Autosys experience 5+ years of scripting and automation experience 4+ years of experience with Enterprise Risk Data What You Will Be Doing Provide technology design, develop and support Risk and Regulatory platform capabilities, functions and processes. Understand business requirements with respects to data and reporting needs. Analyze source data and perform data gap analysis, source to target mappings, and data integration design. Design and implement highly distributed, scalable processes - Data Enrichments using Ab Initio, SQL, Strong data enrichment &amp; delivery techniques using various technology stack: Jenkins, Artifactory, Git, Autosys, DTS, NDM, and PCF. Evaluate solutions, review system architecture, design and tools to achieve project objectives including usability, performance, reliability, and monitoring, control, and security requirements. Assist all technology partners/developers to use the agreed technology/tools and interfaces to ensure smooth integration, security &amp; reliability across DEV, SIT, UAT and Production. Performance tuning and designing of high-performance applications involving huge data processing.</t>
+          <t>Seeking a Data Engineer for a full-time opportunity supporting a leading research, analytics, and technology organization within the utility and energy industry. This role will focus on designing, building, and optimizing modern data solutions leveraging Databricks, Spark, Python, AWS, SQL, and PostgreSQL to support both client-facing and SaaS-based data products. The position offers the opportunity to work on large-scale data platforms that help utilities improve customer engagement, grid operations, and business performance. You'll join a highly collaborative Machine Learning Engineering team where you'll work alongside data scientists, machine learning engineers, analysts, and software engineers to build impactful data solutions. This role is ideal for someone who enjoys solving complex data challenges, mentoring other engineers, and expanding their expertise in cloud data platforms, analytics, and machine learning technologies while contributing to meaningful work within the evolving energy sector. This is a fully remote oppurtunitiy. Required Skills &amp; Experience · 5+ years of experience in Data Engineering or a related field · Expert-level proficiency in Python, SQL, Databricks, and Spark · Experience building cloud-based data pipelines in AWS · Strong understanding of data engineering best practices and scalable architectures · Knowledge of data governance, security, privacy, and retention practices Desired Skills &amp; Experience Experience optimizing ETL workflows within Databricks Knowledge of data lineage and data quality frameworks Experience supporting machine learning and data science initiatives Prior experience within the utility or energy industry Master's degree in a related STEM field What You Will Be Doing Tech Breakdown 40% Databricks &amp; Spark Development 30% Data Pipeline Engineering 20% AWS Data Platform &amp; Infrastructure 10% Collaboration, Mentorship &amp; Innovation Daily Responsibilities Design, develop, and maintain scalable data pipelines and infrastructure Build and support data lakes, analytics platforms, and data products Collaborate with cross-functional teams to deliver business-driven solutions Monitor, troubleshoot, and improve data quality, reliability, and availability The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Eligible for salary bonus PTO &amp; Paid Holidays 401(k) with Company Match Remote Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -8882,12 +8882,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Data Quality Tester / ETL / SQL / Chicago</t>
+          <t>Data Engineer (Snowflake / dbt / Fivetran)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, 60603, United States</t>
+          <t>Addison, Texas, 75001, United States</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chicago/contract/data-quality-tester-etl-sql-chicago/888265</t>
+          <t>https://motionrecruitment.com/tech-jobs/addison/direct-hire/data-engineer-snowflake-dbt-fivetran/891565</t>
         </is>
       </c>
       <c r="J122" t="b">
@@ -8925,22 +8925,22 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-09-23T18:46:37+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>947d7f87986456a2fec1</t>
+          <t>9a28e93eb4abf69a9f14</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>A leading organization is seeking a Data Quality Assurance Engineer to join its growing Data &amp; Analytics team in a hybrid work environment. This full-time opportunity offers the chance to work with modern data warehousing technologies, cloud data platforms, ETL processes, Master Data Management solutions, and business intelligence tools that support critical enterprise initiatives. This role is ideal for someone who enjoys solving complex data challenges and ensuring information accuracy across large-scale systems. The successful candidate will play a key role in establishing and expanding enterprise data quality standards while partnering closely with analytics, architecture, engineering, and business teams. This is an opportunity to make a measurable impact, gain visibility across multiple departments, and influence the future direction of data quality practices. Required Skills &amp; Experience • Strong hands-on experience with ETL testing and data validation • Advanced SQL skills for data analysis, reconciliation, and verification • Experience working with dimensional data models and data warehouses • Ability to execute data migration and data integrity testing initiatives • Experience creating test plans, test cases, and regression testing strategies • Strong root cause analysis and troubleshooting skills • Experience working within Agile delivery environments • Excellent communication and stakeholder management skills Desired Skills &amp; Experience • Experience with Amazon Redshift or other cloud-based data warehouses • Exposure to Master Data Management (MDM) platforms • Experience validating BI dashboards and enterprise reporting solutions • Knowledge of Tableau, Power BI, Hex, or similar analytics platforms • Experience with Python, PowerShell, JavaScript, C#, or similar scripting languages • Experience with SSIS packages or related ETL technologies • Background in data quality frameworks and automation initiatives What You Will Be Doing • Validate data movement between source and target systems • Execute ETL, regression, migration, and performance testing activities • Perform data reconciliation and integrity checks across enterprise platforms • Develop and maintain testing documentation and test strategies • Partner with engineering teams to identify and resolve data issues • Support analytics teams through report and dashboard validation • Help establish best practices for data quality and testing governance Tech Breakdown • 40% SQL &amp; Data Validation • 25% ETL Testing &amp; Data Integration • 20% Data Warehousing &amp; Cloud Platforms • 15% Analytics &amp; Reporting Tools Daily Responsibilities • 70% Hands On Testing &amp; Validation • 10% Test Planning &amp; Documentation • 20% Team Collaboration &amp; Stakeholder Engagement The Offer • Bonus eligible You will receive the following benefits: • Medical, Dental, and Vision Insurance • Vacation Time • 401(k) Program • Paid Holidays • Professional Development Opportunities • Stock Options (where applicable) Applicants</t>
+          <t>Seeking a Senior Data Engineer for a full-time, hybrid role in Addison, TX (3 days onsite). This position will play a key role in building and ultimately owning a modern data platform for a growing home services organization, leveraging Snowflake, dbt, Fivetran, Azure, and AI technologies. The ideal candidate will help drive enterprise reporting, data warehousing, and future AI initiatives across a multi-site business operating nationwide. What makes this opportunity unique? You'll join during company-wide data transformation, helping build and own a brand-new Snowflake environment from the ground up. This is a high-impact role offering significant ownership, direct exposure to executive leadership, hands-on work with AI technologies, and a clear path to becoming the organization's long-term data engineering leader. Required Skills &amp; Experience · 7+ years of Data Engineering experience · Strong hands-on experience with Snowflake , including administration, optimization, and performance tuning · Advanced dbt experience with ownership of production projects (models, tests, snapshots, macros, CI/CD, and environment management) · Experience with Fivetran , Airbyte, Stitch, or similar ELT/integration platforms · Strong understanding of data warehousing concepts and dimensional data modeling Desired Skills &amp; Experience Snowflake Cortex Experience AI/LLM integrations and prompt engineering experience Experience with Great Expectations, Monte Carlo, Elementary, Soda, or similar data quality tools. SnowPro Certification Experience in multi-site or rapidly growing organizations through M&amp;A activities. What You Will Be Doing Tech Breakdown · 40 % Snowflake Administration &amp; Optimization · 30 % dbt Development &amp; Data Modeling · 20 % Data Pipeline Development &amp; ELT Management · 10 % AI &amp; Advanced Analytics Initiatives Daily Responsibilities · Own and optimize the Snowflake platform and data warehouse · Develop and maintain dbt models, data pipelines, and data marts · Manage data ingestion and integrations through Fivetran and related tools · Ensure data quality, monitoring, and pipeline reliability · Partner with business stakeholders and consulting teams to deliver scalable analytics solutions · Evaluate and implement AI-driven capabilities, including Snowflake Cortex and LLM integrations · Drive data engineering best practices, governance, and platform growth throughout the organization The Offer You will receive the following benefits: Eligible for salary bonus Medical, Dental &amp; Vision Insurance PTO &amp; Paid Holidays 401(k) with Company Match Hybrid Schedule (3 Days Onsite) Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -8952,17 +8952,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Data Scientist / Fully Remote / Work Life Balance</t>
+          <t>Data Engineer (Snowflake, Python, AI/ML Data Pipelines)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Detroit, Michigan, 48226, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/detroit/contract/data-scientist-fully-remote-work-life-balance/887341</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/contract/data-engineer-snowflake-python-ai-ml-data-pipelines/891815</t>
         </is>
       </c>
       <c r="J123" t="b">
@@ -8995,22 +8995,22 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-09-11T18:11:05+00:00</t>
+          <t>2026-10-07T02:48:05+00:00</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>af0f816b04e17bba2a23</t>
+          <t>15f141f7e604c151832a</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>A rapidly growing analytics and technology consulting organization is seeking a Data Scientist to join its team. This full-time opportunity offers the chance to work with modern analytics technologies including Python, SQL, Databricks, Tableau, Power BI, and machine learning platforms while helping enterprise clients solve complex business challenges through data. Candidates can expect a highly collaborative environment where analytics, engineering, and business strategy intersect. What makes this opportunity especially exciting is the variety of projects and industries you'll support. Rather than being limited to a single product or business unit, you'll tackle forecasting, customer analytics, optimization, experimentation, and predictive modeling initiatives for organizations making critical decisions around customers, products, and market strategy. This role is ideal for someone who enjoys both deep technical problem solving and partnering with stakeholders to drive measurable business outcomes. Required Skills &amp; Experience 2+ years of professional Data Science or Advanced Analytics experience Strong Python development skills Advanced SQL experience Experience building predictive models and machine learning solutions Experience with forecasting, regression, classification, or segmentation Databricks experience Tableau and/or Power BI experience Git or GitLab experience Strong communication and stakeholder management skills Bachelor's degree in a quantitative discipline or equivalent experience Desired Skills &amp; Experience Optimization modeling experience A/B testing and experimentation design MLflow or MLOps exposure SAS or R experience Data governance and data quality expertise Experience within consulting environments What You Will Be Doing Tech Breakdown 40% Python &amp; Machine Learning 30% SQL &amp; Data Engineering Collaboration 20% Visualization &amp; Reporting 10% MLOps &amp; Model Deployment Daily Responsibilities 80% Hands On 5% Management Duties 15% Team Collaboration The Offer Competitive hourly rate You will receive the following benefits: Medical, Dental, and Vision Insurance Career Development Opportunities Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
+          <t>A leading global IT consulting and business services organization is seeking a Database Administrator to support long-term engagements with public sector and local government organizations throughout the San Diego area. This is a multi-year contract opportunity where you'll leverage SQL Server, Oracle, and MySQL expertise to support critical databases that power essential community and government service. This is an opportunity to join a highly visible team responsible for maintaining the stability, security, and performance of mission-critical database environments. The ideal candidate enjoys solving complex database challenges, ensuring high availability, and optimizing enterprise-scale systems. You'll work with experienced technology professionals while supporting organizations that deliver meaningful services to their communities. Contract Duration: Multi-Year Contract Required Skills &amp; Experience Database Administration experience Microsoft SQL Server Database design and architecture Database security and access management Backup and recovery strategies Desired Skills &amp; Experience · Public sector or government experience · Experience supporting enterprise-scale database environments · Database migration experience · Performance monitoring and capacity planning · Strong troubleshooting and problem-solving skills What You Will Be Doing Tech Breakdown 50% SQL Server Administration 25% Oracle &amp; MySQL Administration 15% Database Performance &amp; Optimization 10% Security, Backup &amp; Recovery Daily Responsibilities · 70% Hands-On Database Administration · 20% Performance Monitoring &amp; Troubleshooting · 10% Team Collaboration &amp; Documentation</t>
         </is>
       </c>
     </row>
@@ -9022,17 +9022,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lead Senior Technology and Data Engineer - Raleigh, Nc</t>
+          <t>Data Engineer (Snowflake, Python, AI/ML Data Pipelines)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raleigh, North Carolina, 27639, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/raleigh/contract/lead-senior-technology-and-data-engineer-raleigh-nc/885751</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/contract/data-engineer-snowflake-python-ai-ml-data-pipelines/891811</t>
         </is>
       </c>
       <c r="J124" t="b">
@@ -9065,22 +9065,22 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-10-07T02:48:05+00:00</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>a468a6ee8abaf78d93d2</t>
+          <t>ac913caadefeaa9d0a60</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Job Description An enterprise technology company is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Raleigh, North Carolina . This role is centered on strengthening Infrastructure as Code security across cloud environments and supporting secure software delivery practices at scale. The team is focused on building preventative controls, improving policy management, and increasing visibility into security issues before code and infrastructure reach production. The ideal candidate will enjoy working across security, DevOps, and engineering functions to develop practical solutions that improve risk management while supporting the speed and efficiency of modern development teams. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and training activities. Manage policy</t>
+          <t>A leading wealth management technology firm is seeking a Data Engineer to join their growing AI and Data team. This fully remote contract opportunity offers the chance to build modern data solutions leveraging Snowflake, Python, dbt, Airflow, and AI/ML technologies that support enterprise-scale analytics and next-generation AI applications. Candidates who convert to full-time should be in or willing to relocate to one of the organization's hub locations in Atlanta, GA; La Vista, NE; Oakdale, MN; Scottsdale, AZ; or St. Petersburg, FL. This role sits at the center of data engineering and artificial intelligence initiatives. The team is building the infrastructure behind advanced AI solutions, including RAG applications, vector search, and machine learning systems. They're looking for an engineer who enjoys solving complex data challenges while working with cutting-edge AI technologies. You'll have the opportunity to help shape the future of data platforms within a highly respected financial services organization while gaining hands-on experience with modern AI architectures and enterprise-scale data environments. Contract Duration: 12 Months Required Skills &amp; Experience · Strong SQL development experience · Python and/or Scala for data pipeline development · Snowflake · dbt for data transformation and orchestration · Airflow or similar workflow orchestration tools Desired Skills &amp; Experience Scala experience Experience supporting production AI/ML systems Experience with cloud-native data platforms Data governance and data quality expertise Knowledge of large language models and AI infrastructure What You Will Be Doing Tech Breakdown · 40% Snowflake, SQL &amp; Data Engineering · 25% Python Development · 20% AI/ML Data Pipelines &amp; RAG · 15% dbt &amp; Airflow Orchestration Daily Responsibilities 80% Hands-On Engineering 10% Cross-Functional Collaboration 10% Architecture &amp; Planning</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lead Technology and Data Engineer - Chandler, Az</t>
+          <t>Data Engineer / Charlotte / Hybrid</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chandler, Arizona, 85244, United States</t>
+          <t>Charlotte, NC, 28202, United States</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chandler/contract/lead-technology-and-data-engineer-chandler-az/885745</t>
+          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/data-engineer-charlotte-hybrid/861817</t>
         </is>
       </c>
       <c r="J125" t="b">
@@ -9135,22 +9135,22 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-08-04T16:52:57+00:00</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>ff09e0a1045d952ba482</t>
+          <t>c4ff54db51fe9b4cb6c0</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Job Description A forward-thinking enterprise organization is looking to add a Technology and Data Engineer 5 to its hybrid team in Chandler, Arizona . This opportunity is ideal for an engineer who enjoys working at the intersection of cloud security, automation, and infrastructure governance. The team is focused on improving how security is integrated into cloud deployments by leveraging Infrastructure as Code controls, automated policy validation, and secure development practices. In this role, you will contribute to initiatives designed to strengthen cloud environments, improve security coverage across deployment pipelines, and provide engineers with practical tools and processes that support secure infrastructure delivery. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and tra</t>
+          <t>Outstanding long-term contract opportunity! A well-known Financial Services Company is looking for a Data Engineer in Charlotte, NC (Hybrid). Work with the brightest minds at one of the largest financial institutions in the world. This is long-term contract opportunity that includes a competitive benefit package! Our client has been around for over 150 years and is continuously innovating in today's digital age. If you want to work for a company that is not only a household name, but also truly cares about satisfying customers' financial needs and helping people succeed financially, apply today. Contract Duration: 12 Months Required Skills &amp; Experience 7+ years of Data engineering experience 7+ years of MS SQL server experience 7+ years of Teradata experience 7+ years of SDLC (System Development Life Cycle) experience 5+ years of experience in Teradata database technology and products such as TASM, Unity, Data mover and Query Grid 5+ years of ETL (Extract, Transform, Load) development experience using Ab Initio 5+ years of Autosys experience 5+ years of scripting and automation experience 4+ years of experience with Enterprise Risk Data What You Will Be Doing Provide technology design, develop and support Risk and Regulatory platform capabilities, functions and processes. Understand business requirements with respects to data and reporting needs. Analyze source data and perform data gap analysis, source to target mappings, and data integration design. Design and implement highly distributed, scalable processes - Data Enrichments using Ab Initio, SQL, Strong data enrichment &amp; delivery techniques using various technology stack: Jenkins, Artifactory, Git, Autosys, DTS, NDM, and PCF. Evaluate solutions, review system architecture, design and tools to achieve project objectives including usability, performance, reliability, and monitoring, control, and security requirements. Assist all technology partners/developers to use the agreed technology/tools and interfaces to ensure smooth integration, security &amp; reliability across DEV, SIT, UAT and Production. Performance tuning and designing of high-performance applications involving huge data processing.</t>
         </is>
       </c>
     </row>
@@ -9162,27 +9162,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake</t>
+          <t>Data Quality Tester / ETL / SQL / Chicago</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>City of Industry, California, 91732, United States</t>
+          <t>Chicago, Illinois, 60603, United States</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/city-of-industry/direct-hire/mid-senior-data-engineer-sql-python-dbt-and-snowflake/885666</t>
+          <t>https://motionrecruitment.com/tech-jobs/chicago/contract/data-quality-tester-etl-sql-chicago/888265</t>
         </is>
       </c>
       <c r="J126" t="b">
@@ -9205,22 +9205,22 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-08-20T21:14:14+00:00</t>
+          <t>2026-09-23T18:46:37+00:00</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>4b469a327ab71e782f37</t>
+          <t>947d7f87986456a2fec1</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake City of Industry, CA | Full-Time Our client is a growing organization seeking a Data Engineer to join its expanding technology team. This is a hands-on role focused on building and maintaining production data solutions, supporting critical data operations, and improving the reliability and scalability of the overall data environment. The ideal candidate is a strong hands-on engineer who enjoys working with production systems, troubleshooting unfamiliar problems, and taking ownership of data pipelines and operational processes. What You’ll Be Doing Design, build, and maintain production-grade data pipelines and transformations Develop and maintain reliable data models supporting reporting, analytics, and business applications Work extensively with SQL, Python, dbt, and cloud-based data technologies Own day-to-day production data operations, including orchestration, scheduled refreshes, monitoring, and alerting Troubleshoot pipeline failures, data quality issues, and other production incidents Support database administration activities, including user access, roles, permissions, performance, and maintenance Manage data deployments and contribute to CI/CD and infrastructure automation Investigate unfamiliar or poorly documented data sources and determine how systems, schemas, and integrations function Build data solutions supporting reporting, billing, customer, and operational use cases Integrate and work with data from internal, third-party, and legacy systems Partner with engineering, product, operations, and business teams to translate requirements into technical solutions Participate in code reviews and contribute to engineering standards and best practices Improve documentation, knowledge sharing, and overall platform reliability Required Qualifications Strong SQL skills, including complex joins, window functions, aggregations, NULL handling, and understanding of data grain Hands-on Python development experience, including maintaining code running in production Professional experience building or supporting production data pipelines Experience with a modern data transformation framework; dbt strongly preferred Strong understanding of dimensional data modeling, including: Fact and dimension tables Data grain Conformed dimensions Slowly changing dimensions Experience supporting production environments, including deployments, monitoring, environment management, troubleshooting, and incident response Strong experience with Git, pull requests, code reviews, and CI/CD Ability to independently investigate and debug unfamiliar technical problems Strong communication skills and ability to work across technical and business teams Comfortable contributing within an established architecture and engineering environment Preferred Qualifications Experience with Snowflake Experience with Microsoft Azure Familiarity with Azure Data Factory (ADF), ADLS Gen2, and/or Key Vault Terraform or other Infrastructu</t>
+          <t>A leading organization is seeking a Data Quality Assurance Engineer to join its growing Data &amp; Analytics team in a hybrid work environment. This full-time opportunity offers the chance to work with modern data warehousing technologies, cloud data platforms, ETL processes, Master Data Management solutions, and business intelligence tools that support critical enterprise initiatives. This role is ideal for someone who enjoys solving complex data challenges and ensuring information accuracy across large-scale systems. The successful candidate will play a key role in establishing and expanding enterprise data quality standards while partnering closely with analytics, architecture, engineering, and business teams. This is an opportunity to make a measurable impact, gain visibility across multiple departments, and influence the future direction of data quality practices. Required Skills &amp; Experience • Strong hands-on experience with ETL testing and data validation • Advanced SQL skills for data analysis, reconciliation, and verification • Experience working with dimensional data models and data warehouses • Ability to execute data migration and data integrity testing initiatives • Experience creating test plans, test cases, and regression testing strategies • Strong root cause analysis and troubleshooting skills • Experience working within Agile delivery environments • Excellent communication and stakeholder management skills Desired Skills &amp; Experience • Experience with Amazon Redshift or other cloud-based data warehouses • Exposure to Master Data Management (MDM) platforms • Experience validating BI dashboards and enterprise reporting solutions • Knowledge of Tableau, Power BI, Hex, or similar analytics platforms • Experience with Python, PowerShell, JavaScript, C#, or similar scripting languages • Experience with SSIS packages or related ETL technologies • Background in data quality frameworks and automation initiatives What You Will Be Doing • Validate data movement between source and target systems • Execute ETL, regression, migration, and performance testing activities • Perform data reconciliation and integrity checks across enterprise platforms • Develop and maintain testing documentation and test strategies • Partner with engineering teams to identify and resolve data issues • Support analytics teams through report and dashboard validation • Help establish best practices for data quality and testing governance Tech Breakdown • 40% SQL &amp; Data Validation • 25% ETL Testing &amp; Data Integration • 20% Data Warehousing &amp; Cloud Platforms • 15% Analytics &amp; Reporting Tools Daily Responsibilities • 70% Hands On Testing &amp; Validation • 10% Test Planning &amp; Documentation • 20% Team Collaboration &amp; Stakeholder Engagement The Offer • Bonus eligible You will receive the following benefits: • Medical, Dental, and Vision Insurance • Vacation Time • 401(k) Program • Paid Holidays • Professional Development Opportunities • Stock Options (where applicable) Applicants</t>
         </is>
       </c>
     </row>
@@ -9232,27 +9232,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SAP Master Data Architect - Needham, Ma</t>
+          <t>Data Scientist / Fully Remote / Work Life Balance</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Needham, MA, 02492, United States</t>
+          <t>Detroit, Michigan, 48226, United States</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/needham/direct-hire/sap-master-data-architect-needham-ma/888810</t>
+          <t>https://motionrecruitment.com/tech-jobs/detroit/contract/data-scientist-fully-remote-work-life-balance/887341</t>
         </is>
       </c>
       <c r="J127" t="b">
@@ -9275,22 +9275,22 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-09-30T21:56:04+00:00</t>
+          <t>2026-09-11T18:11:05+00:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>32d5d84ff07e48b35fdd</t>
+          <t>af0f816b04e17bba2a23</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Job Description A global organization undergoing large-scale digital transformation is seeking a SAP Master Data Architect to help modernize and strengthen enterprise data capabilities. This role is a unique opportunity to influence how critical business data is structured, governed, and leveraged across the organization while remaining deeply involved in execution and solution delivery. This position is ideal for someone who enjoys solving complex data challenges, improving enterprise processes, and partnering with stakeholders across Finance, Supply Chain, Operations, Sales, and Technology. The successful candidate will play a key role in shaping master data strategy while spending the majority of their time driving hands-on implementation and optimization efforts. Location: Needham, MA Schedule: Hybrid Employment Type: Full-Time Required Skills &amp; Experience 10+ years of experience working with enterprise applications, data management, or business systems 5+ years of experience supporting SAP Master Data Management initiatives Deep knowledge of SAP ECC and/or S/4HANA environments Expertise across Material, Customer, Vendor, and Financial Master Data domains Strong understanding of enterprise data architecture and cross-system integration Experience with master data governance, quality programs, and data lifecycle management Demonstrated success leading SAP MDM, MDG, migration, or transformation initiatives Experience partnering with business and technical stakeholders to define scalable solutions Strong communication and problem-solving skills Desired Skills &amp; Experience SAP MDG implementation experience Manufacturing, supply chain, or order-to-cash process knowledge Experience working with Salesforce, Snowflake, or other enterprise platforms Exposure to ERP modernization or enterprise transformation programs Experience improving enterprise data quality and governance frameworks Bachelor's degree in Information Technology, Business, Computer Science, or a related field What You Will Be Doing Daily Responsibilities 70% Hands On Design and implement SAP master data solutions across multiple business domains Lead master data initiatives from discovery and design through deployment and optimization Drive data migration, cleansing, validation, and quality improvement efforts Define data standards, hierarchies, ownership models, and governance processes Analyze complex data issues and develop long-term solutions that improve accuracy and consistency Build and enhance frameworks that improve enterprise-wide data management practices Partner with business users to translate requirements into scalable technical solutions Support integrations between SAP and connected enterprise applications Serve as a subject matter expert for master data strategy, architecture, and execution 30% Strategic Influence Help define long-term enterprise data management objectives Partner with stakeholders to prioritize initiatives based on business impact Enhance governance</t>
+          <t>A rapidly growing analytics and technology consulting organization is seeking a Data Scientist to join its team. This full-time opportunity offers the chance to work with modern analytics technologies including Python, SQL, Databricks, Tableau, Power BI, and machine learning platforms while helping enterprise clients solve complex business challenges through data. Candidates can expect a highly collaborative environment where analytics, engineering, and business strategy intersect. What makes this opportunity especially exciting is the variety of projects and industries you'll support. Rather than being limited to a single product or business unit, you'll tackle forecasting, customer analytics, optimization, experimentation, and predictive modeling initiatives for organizations making critical decisions around customers, products, and market strategy. This role is ideal for someone who enjoys both deep technical problem solving and partnering with stakeholders to drive measurable business outcomes. Required Skills &amp; Experience 2+ years of professional Data Science or Advanced Analytics experience Strong Python development skills Advanced SQL experience Experience building predictive models and machine learning solutions Experience with forecasting, regression, classification, or segmentation Databricks experience Tableau and/or Power BI experience Git or GitLab experience Strong communication and stakeholder management skills Bachelor's degree in a quantitative discipline or equivalent experience Desired Skills &amp; Experience Optimization modeling experience A/B testing and experimentation design MLflow or MLOps exposure SAS or R experience Data governance and data quality expertise Experience within consulting environments What You Will Be Doing Tech Breakdown 40% Python &amp; Machine Learning 30% SQL &amp; Data Engineering Collaboration 20% Visualization &amp; Reporting 10% MLOps &amp; Model Deployment Daily Responsibilities 80% Hands On 5% Management Duties 15% Team Collaboration The Offer Competitive hourly rate You will receive the following benefits: Medical, Dental, and Vision Insurance Career Development Opportunities Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
         </is>
       </c>
     </row>
@@ -9302,12 +9302,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SAP Snowflake Analytics Engineer / Hybrid / Scottsdale, AZ</t>
+          <t>Lead Senior Technology and Data Engineer - Raleigh, Nc</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, 85251, United States</t>
+          <t>Raleigh, North Carolina, 27639, United States</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/scottsdale/contract/sap-snowflake-analytics-engineer-hybrid-scottsdale-az/886105</t>
+          <t>https://motionrecruitment.com/tech-jobs/raleigh/contract/lead-senior-technology-and-data-engineer-raleigh-nc/885751</t>
         </is>
       </c>
       <c r="J128" t="b">
@@ -9345,22 +9345,22 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-09-16T23:20:04+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>ad6fe94f94bd642a688c</t>
+          <t>a468a6ee8abaf78d93d2</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Our client, a clean energy developer and operator across the US, is actively hiring an Analytics Engineer to join their team in Scottsdale, AZ! This will be a hybrid role and will require 3 days a week onsite. In this role, you will be responsible for building and owning the semantic layer and data mart strategy that connects the raw operational and financial data to the business teams who depend on it. A significant portion of your work will focus on modeling data replicated from SAP, our financial and other operational platforms into Snowflake building clean, tested, and well-documented dbt models that serve Hex dashboards and Snowflake semantic models queryable by LLMs. Contract Duration: 12 Months Required Skills &amp; Experience Bachelor's degree in Computer Science, Engineering, Mathematics, or related field 3+ years in an Analytics Engineering, Data Engineering, or BI Engineering role Working knowledge of Snowflake SQL and Python proficiency What You Will Be Doing Design and maintain the staging and intermediate dbt model layers for financial, operational, and asset-management data replicated from SAP (ERP) into Snowflake Build and maintain Snowflake semantic models (definitions that allow LLMs and BI tools to query business metrics without ad-hoc SQL Create documentation, data dictionaries, and training materials that enable analysts to use data marts and Hex workbooks independently</t>
+          <t>Job Description An enterprise technology company is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Raleigh, North Carolina . This role is centered on strengthening Infrastructure as Code security across cloud environments and supporting secure software delivery practices at scale. The team is focused on building preventative controls, improving policy management, and increasing visibility into security issues before code and infrastructure reach production. The ideal candidate will enjoy working across security, DevOps, and engineering functions to develop practical solutions that improve risk management while supporting the speed and efficiency of modern development teams. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and training activities. Manage policy</t>
         </is>
       </c>
     </row>
@@ -9372,27 +9372,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Senior AI Engineer II</t>
+          <t>Lead Technology and Data Engineer - Chandler, Az</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>Chandler, Arizona, 85244, United States</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-ai-engineer-ii/891580</t>
+          <t>https://motionrecruitment.com/tech-jobs/chandler/contract/lead-technology-and-data-engineer-chandler-az/885745</t>
         </is>
       </c>
       <c r="J129" t="b">
@@ -9415,22 +9415,22 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>daa3e2d26d4032e1ed04</t>
+          <t>ff09e0a1045d952ba482</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Seeking a Senior AI Engineer II for a full-time opportunity in Phoenix, AZ with a leading digital payments and financial technology organization. This role will focus on building production-grade AI applications utilizing Python, Agentic AI, Large Language Models (LLMs), RAG architecture, agent orchestration frameworks, cloud technologies (AWS/GCP), and backend APIs. The ideal candidate will help deliver both internal and customer-facing AI solutions on an enterprise scale. What makes this opportunity unique? This team is focused on building real AI products, not research projects or proof-of-concepts. You'll work directly on multiple enterprise AI initiatives centered around Agentic AI, helping deliver intelligent solutions that impact both internal operations and customer experiences. This is an excellent opportunity for an engineer who enjoys building production AI systems and wants to work on cutting-edge AI initiatives within a technology-driven environment. Required Skills &amp; Experience · Strong Python development experience · Experience building Agentic AI applications · Experience working with Large Language Models (LLMs) · Experience implementing RAG (Retrieval-Augmented Generation) solutions · Experience with agent orchestration frameworks Desired Skills &amp; Experience · Customer-facing product experience · React and/or TypeScript · Mobile development experience (iOS, Android, Swift, Kotlin) · Fintech or regulated industry experience · AI evaluation, monitoring, or observability experience What You Will Be Doing Tech Breakdown 40% Agentic AI Development 30% LLM &amp; RAG Solutions 20% API &amp; Backend Development 10% Cloud Infrastructure &amp; AI Operations Daily Responsibilities · Build and deploy production AI applications · Design and implement Agentic AI workflows and orchestration solutions · Develop LLM and RAG-based applications · Build APIs and backend services supporting AI products · Collaborate with product and engineering teams to deliver AI capabilities The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Eligible for salary bonus PTO &amp; Paid Holidays 401(k) with Company Match Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description A forward-thinking enterprise organization is looking to add a Technology and Data Engineer 5 to its hybrid team in Chandler, Arizona . This opportunity is ideal for an engineer who enjoys working at the intersection of cloud security, automation, and infrastructure governance. The team is focused on improving how security is integrated into cloud deployments by leveraging Infrastructure as Code controls, automated policy validation, and secure development practices. In this role, you will contribute to initiatives designed to strengthen cloud environments, improve security coverage across deployment pipelines, and provide engineers with practical tools and processes that support secure infrastructure delivery. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions, and tra</t>
         </is>
       </c>
     </row>
@@ -9442,12 +9442,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chicago, VA, 60606, United States</t>
+          <t>City of Industry, California, 91732, United States</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer/885522</t>
+          <t>https://motionrecruitment.com/tech-jobs/city-of-industry/direct-hire/mid-senior-data-engineer-sql-python-dbt-and-snowflake/885666</t>
         </is>
       </c>
       <c r="J130" t="b">
@@ -9485,22 +9485,22 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-08-19T18:08:19+00:00</t>
+          <t>2026-08-20T21:14:14+00:00</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>968938ae19236c36071b</t>
+          <t>4b469a327ab71e782f37</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Join a growing, data-driven organization that is investing heavily in its modern cloud data platform and analytics capabilities. We are seeking a Senior Databricks Data Engineer to design, build, and optimize enterprise-scale data solutions using Databricks, Azure, PySpark, Delta Lake, SQL, and modern cloud technologies. This is a full-time opportunity for an engineer who is passionate about building scalable data products and shaping the future of data architecture. You'll have the opportunity to drive architecture decisions, influence engineering standards, and help build a best-in-class Lakehouse platform from the ground up. We're looking for someone who thrives in complex environments, enjoys solving large-scale data challenges, and wants to work alongside talented engineers who value innovation and continuous learning. If you're seeking a role that offers technical ownership, career growth, exposure to cutting-edge technologies, and strong work-life balance, this is an opportunity worth exploring. Required Skills &amp; Experience 7+ years of experience in Data Engineering, Data Warehousing, or Data Platform development 3+ years of hands-on Databricks experience in a production environment Strong expertise with PySpark and Apache Spark Advanced SQL development and query optimization skills Experience building ETL/ELT pipelines at enterprise scale Experience working within Azure, AWS, or GCP cloud environments Excellent communication skills and ability to partner with technical and business stakeholders Desired Skills &amp; Experience Azure Data Factory, Azure Synapse, or Microsoft Fabric experience Experience with Kafka or event-driven architectures Databricks Workflows, Airflow, or similar orchestration tools Infrastructure as Code using Terraform or ARM templates Experience supporting AI, Machine Learning, or advanced analytics initiatives Prior experience mentoring engineers or leading technical initiatives What You Will Be Doing Tech Breakdown 50% Databricks / PySpark / Spark 25% Azure Data Platform Services 25% SQL &amp; Data Modeling Daily Responsibilities 70% Hands On 30% Team Collaboration The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Mid-Senior Data Engineer – SQL, Python, dbt &amp; Snowflake City of Industry, CA | Full-Time Our client is a growing organization seeking a Data Engineer to join its expanding technology team. This is a hands-on role focused on building and maintaining production data solutions, supporting critical data operations, and improving the reliability and scalability of the overall data environment. The ideal candidate is a strong hands-on engineer who enjoys working with production systems, troubleshooting unfamiliar problems, and taking ownership of data pipelines and operational processes. What You’ll Be Doing Design, build, and maintain production-grade data pipelines and transformations Develop and maintain reliable data models supporting reporting, analytics, and business applications Work extensively with SQL, Python, dbt, and cloud-based data technologies Own day-to-day production data operations, including orchestration, scheduled refreshes, monitoring, and alerting Troubleshoot pipeline failures, data quality issues, and other production incidents Support database administration activities, including user access, roles, permissions, performance, and maintenance Manage data deployments and contribute to CI/CD and infrastructure automation Investigate unfamiliar or poorly documented data sources and determine how systems, schemas, and integrations function Build data solutions supporting reporting, billing, customer, and operational use cases Integrate and work with data from internal, third-party, and legacy systems Partner with engineering, product, operations, and business teams to translate requirements into technical solutions Participate in code reviews and contribute to engineering standards and best practices Improve documentation, knowledge sharing, and overall platform reliability Required Qualifications Strong SQL skills, including complex joins, window functions, aggregations, NULL handling, and understanding of data grain Hands-on Python development experience, including maintaining code running in production Professional experience building or supporting production data pipelines Experience with a modern data transformation framework; dbt strongly preferred Strong understanding of dimensional data modeling, including: Fact and dimension tables Data grain Conformed dimensions Slowly changing dimensions Experience supporting production environments, including deployments, monitoring, environment management, troubleshooting, and incident response Strong experience with Git, pull requests, code reviews, and CI/CD Ability to independently investigate and debug unfamiliar technical problems Strong communication skills and ability to work across technical and business teams Comfortable contributing within an established architecture and engineering environment Preferred Qualifications Experience with Snowflake Experience with Microsoft Azure Familiarity with Azure Data Factory (ADF), ADLS Gen2, and/or Key Vault Terraform or other Infrastructu</t>
         </is>
       </c>
     </row>
@@ -9512,17 +9512,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (dbt, Snowflake, Modern Analytics Stack)</t>
+          <t>SAP Master Data Architect - Needham, Ma</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>Needham, MA, 02492, United States</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-snowflake-modern-analytics-stack/891598</t>
+          <t>https://motionrecruitment.com/tech-jobs/needham/direct-hire/sap-master-data-architect-needham-ma/888810</t>
         </is>
       </c>
       <c r="J131" t="b">
@@ -9555,22 +9555,22 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-09-30T21:56:04+00:00</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>4013757fbda640752fe6</t>
+          <t>32d5d84ff07e48b35fdd</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Join a rapidly growing logistics and supply chain technology organization that is expanding its data capabilities to support large-scale operations across North America. This is a full-time, remote opportunity with a preference for candidates located in the Pacific or Mountain time zones . Working in a fully remote environment, you'll leverage modern technologies including Azure, Snowflake, dbt, Python, and Terraform to help build and scale a robust cloud data platform. This remote role is ideal for a data professional who enjoys owning the operational side of data engineering. The organization already has strong foundations in architecture, ingestion, and data modeling, and is seeking someone who can deepen the platform through data transformations, pipeline development, DBA-focused work, and production operations. You'll join a collaborative, low-ego remote team that values autonomy, engineering excellence, and meaningful ownership, with the opportunity to make a significant impact without the churn-and-burn pace often associated with startup environments. Required Skills &amp; Experience · 2+ years of professional Data Engineering experience · Strong experience with Azure Data Factory (ADF) and Azure Data Lake · Advanced SQL and data transformation expertise · Experience building and maintaining production data pipelines · Strong understanding of data operations, platform support, and troubleshooting Desired Skills &amp; Experience · dbt · Snowflake · CI/CD pipelines · Terraform · Python What You Will Be Doing Tech Breakdown · 35% Data Pipeline Development · 25% Data Transformations &amp; Modeling · 20% Database Operations &amp; Administration · 10% Cloud Infrastructure &amp; Automation · 10% Cross-Functional Collaboration Daily Responsibilities Build and maintain scalable data pipelines and transformation workflows Support database administration and operational data platform needs Develop and optimize data models, reporting datasets, and business-critical transformations Monitor pipeline health, troubleshoot production issues, and improve reliability Collaborate closely with engineering leadership and business stakeholders The Offer You will receive the following benefits: · Medical, Dental, and Vision Insurance · PTO and Paid Holidays · Bonus Eligible · 401(k) · Career Growth Opportunities · Fully Remote Work Environment Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Job Description A global organization undergoing large-scale digital transformation is seeking a SAP Master Data Architect to help modernize and strengthen enterprise data capabilities. This role is a unique opportunity to influence how critical business data is structured, governed, and leveraged across the organization while remaining deeply involved in execution and solution delivery. This position is ideal for someone who enjoys solving complex data challenges, improving enterprise processes, and partnering with stakeholders across Finance, Supply Chain, Operations, Sales, and Technology. The successful candidate will play a key role in shaping master data strategy while spending the majority of their time driving hands-on implementation and optimization efforts. Location: Needham, MA Schedule: Hybrid Employment Type: Full-Time Required Skills &amp; Experience 10+ years of experience working with enterprise applications, data management, or business systems 5+ years of experience supporting SAP Master Data Management initiatives Deep knowledge of SAP ECC and/or S/4HANA environments Expertise across Material, Customer, Vendor, and Financial Master Data domains Strong understanding of enterprise data architecture and cross-system integration Experience with master data governance, quality programs, and data lifecycle management Demonstrated success leading SAP MDM, MDG, migration, or transformation initiatives Experience partnering with business and technical stakeholders to define scalable solutions Strong communication and problem-solving skills Desired Skills &amp; Experience SAP MDG implementation experience Manufacturing, supply chain, or order-to-cash process knowledge Experience working with Salesforce, Snowflake, or other enterprise platforms Exposure to ERP modernization or enterprise transformation programs Experience improving enterprise data quality and governance frameworks Bachelor's degree in Information Technology, Business, Computer Science, or a related field What You Will Be Doing Daily Responsibilities 70% Hands On Design and implement SAP master data solutions across multiple business domains Lead master data initiatives from discovery and design through deployment and optimization Drive data migration, cleansing, validation, and quality improvement efforts Define data standards, hierarchies, ownership models, and governance processes Analyze complex data issues and develop long-term solutions that improve accuracy and consistency Build and enhance frameworks that improve enterprise-wide data management practices Partner with business users to translate requirements into scalable technical solutions Support integrations between SAP and connected enterprise applications Serve as a subject matter expert for master data strategy, architecture, and execution 30% Strategic Influence Help define long-term enterprise data management objectives Partner with stakeholders to prioritize initiatives based on business impact Enhance governance</t>
         </is>
       </c>
     </row>
@@ -9582,17 +9582,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Databricks / AI / Chicagoland Area</t>
+          <t>SAP Snowflake Analytics Engineer / Hybrid / Scottsdale, AZ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Oak Brook, Illinois, 60523, United States</t>
+          <t>Scottsdale, AZ, 85251, United States</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/oak-brook/contract/senior-data-engineer-databricks-ai-chicagoland-area/885362</t>
+          <t>https://motionrecruitment.com/tech-jobs/scottsdale/contract/sap-snowflake-analytics-engineer-hybrid-scottsdale-az/886105</t>
         </is>
       </c>
       <c r="J132" t="b">
@@ -9625,22 +9625,22 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-08-18T18:12:31+00:00</t>
+          <t>2026-09-16T23:20:04+00:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>0fd058a73f75ae299c7d</t>
+          <t>ad6fe94f94bd642a688c</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>A rapidly growing enterprise organization in the automotive technology and distribution space is seeking a Data Engineer to join its team in Oak Brook, Illinois. This full-time role offers the opportunity to build scalable cloud-based data solutions that support analytics, operational reporting, machine learning, and AI initiatives. The ideal candidate will have experience with Python, SQL, modern data platforms, and enterprise-scale ETL development. What makes this opportunity stand out is the chance to help modernize a complex data ecosystem that spans cloud platforms, APIs, operational applications, and legacy databases. The organization is making substantial investments in data-driven decision making and artificial intelligence, creating an environment where engineers can influence architecture, work with cutting-edge technologies, and make a measurable business impact. This is an ideal role for professionals who enjoy solving large-scale data challenges while collaborating with cross-functional stakeholders. Required Skills &amp; Experience 4+ years of Data Engineering experience Strong SQL development expertise Python or Scala programming experience Experience building ETL/ELT pipelines Hands-on experience with Snowflake, Databricks, Redshift, or BigQuery Knowledge of data warehousing concepts and dimensional modeling Experience with orchestration platforms such as Airflow, Prefect, or Dagster Understanding of CI/CD practices and version control Experience integrating data from APIs and enterprise applications Desired Skills &amp; Experience AWS cloud experience Experience with Kafka or Kinesis Streaming data architecture AI/ML data pipeline exposure Supply chain, ERP, or CRM integration experience Data observability and monitoring tools Enterprise-scale data modernization projects Master's degree in Computer Science, Engineering, or related field What You Will Be Doing Tech Breakdown 40% Python Development 30% SQL &amp; Data Engineering 20% Cloud Data Platforms (Snowflake/Databricks/AWS) 10% Data Orchestration &amp; Automation Daily Responsibilities 75% Hands On Engineering 15% Team Collaboration 10% Strategic Architecture &amp; Design The Offer Competitive Salary You will receive the following benefits: Medical, Dental, and Vision Insurance Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
+          <t>Our client, a clean energy developer and operator across the US, is actively hiring an Analytics Engineer to join their team in Scottsdale, AZ! This will be a hybrid role and will require 3 days a week onsite. In this role, you will be responsible for building and owning the semantic layer and data mart strategy that connects the raw operational and financial data to the business teams who depend on it. A significant portion of your work will focus on modeling data replicated from SAP, our financial and other operational platforms into Snowflake building clean, tested, and well-documented dbt models that serve Hex dashboards and Snowflake semantic models queryable by LLMs. Contract Duration: 12 Months Required Skills &amp; Experience Bachelor's degree in Computer Science, Engineering, Mathematics, or related field 3+ years in an Analytics Engineering, Data Engineering, or BI Engineering role Working knowledge of Snowflake SQL and Python proficiency What You Will Be Doing Design and maintain the staging and intermediate dbt model layers for financial, operational, and asset-management data replicated from SAP (ERP) into Snowflake Build and maintain Snowflake semantic models (definitions that allow LLMs and BI tools to query business metrics without ad-hoc SQL Create documentation, data dictionaries, and training materials that enable analysts to use data marts and Hex workbooks independently</t>
         </is>
       </c>
     </row>
@@ -9652,12 +9652,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Databricks / End-to-End Ownerhp</t>
+          <t>Senior AI Engineer II</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, 60603, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer-databricks-end-to-end-ownerhp/876474</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-ai-engineer-ii/891580</t>
         </is>
       </c>
       <c r="J133" t="b">
@@ -9695,22 +9695,22 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-09-01T18:18:15+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>804829dfb347ca52e5ac</t>
+          <t>daa3e2d26d4032e1ed04</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>A well-established, global professional services organization is expanding its Data &amp; AI engineering team and hiring a Data Engineer to support a large-scale cloud data platform initiative. This role is based in Chicago and focuses on building modern data pipelines using Azure Databricks, Python, SQL, and Spark in a production environment. This is a hands-on engineering opportunity for someone who enjoys owning data pipelines end-to-end and wants exposure to enterprise-scale data challenges. You’ll work alongside experienced engineers and business partners to turn raw data into trusted, analytics-ready datasets that power reporting, insights, and AI use cases. This team is early in its Databricks journey, which means your work will matter immediately. You’ll help shape how pipelines are built, how data is governed, and how the platform evolves over time. It’s ideal for a strong mid-level engineer who wants to deepen their Databricks expertise while working on a highly visible, long-term transformation initiative. Required Skills &amp; Experience 6+ years of hands-on data engineering experience Strong experience building pipelines using Databricks Proficiency in Python and SQL for production data processing Working knowledge of Apache Spark and Delta Lake Experience with cloud data storage (ADLS, object storage) Experience with data modeling and schema design Familiarity with Git, CI/CD concepts, and basic testing/monitoring Desired Skills &amp; Experience Azure Databricks in an enterprise environment Experience with Unity Catalog and Databricks Jobs/Workflows Exposure to streaming or CDC pipelines Experience supporting BI or AI use cases Familiarity with Infrastructure as Code What You Will Be Doing Tech Breakdown 70% Azure Databricks / Spark / Delta Lake 20% Python &amp; SQL development 10% CI/CD, testing, and optimization Daily Responsibilities 80% Hands-On Engineering 10% Collaboration with BI, AI, and product teams 10% Documentation, reviews, and platform improvements The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Seeking a Senior AI Engineer II for a full-time opportunity in Phoenix, AZ with a leading digital payments and financial technology organization. This role will focus on building production-grade AI applications utilizing Python, Agentic AI, Large Language Models (LLMs), RAG architecture, agent orchestration frameworks, cloud technologies (AWS/GCP), and backend APIs. The ideal candidate will help deliver both internal and customer-facing AI solutions on an enterprise scale. What makes this opportunity unique? This team is focused on building real AI products, not research projects or proof-of-concepts. You'll work directly on multiple enterprise AI initiatives centered around Agentic AI, helping deliver intelligent solutions that impact both internal operations and customer experiences. This is an excellent opportunity for an engineer who enjoys building production AI systems and wants to work on cutting-edge AI initiatives within a technology-driven environment. Required Skills &amp; Experience · Strong Python development experience · Experience building Agentic AI applications · Experience working with Large Language Models (LLMs) · Experience implementing RAG (Retrieval-Augmented Generation) solutions · Experience with agent orchestration frameworks Desired Skills &amp; Experience · Customer-facing product experience · React and/or TypeScript · Mobile development experience (iOS, Android, Swift, Kotlin) · Fintech or regulated industry experience · AI evaluation, monitoring, or observability experience What You Will Be Doing Tech Breakdown 40% Agentic AI Development 30% LLM &amp; RAG Solutions 20% API &amp; Backend Development 10% Cloud Infrastructure &amp; AI Operations Daily Responsibilities · Build and deploy production AI applications · Design and implement Agentic AI workflows and orchestration solutions · Develop LLM and RAG-based applications · Build APIs and backend services supporting AI products · Collaborate with product and engineering teams to deliver AI capabilities The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Eligible for salary bonus PTO &amp; Paid Holidays 401(k) with Company Match Strong Growth &amp; Leadership Opportunity Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -9722,17 +9722,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | DBT Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>Chicago, VA, 60606, United States</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-specialist/886415</t>
+          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer/885522</t>
         </is>
       </c>
       <c r="J134" t="b">
@@ -9765,22 +9765,22 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-08-30T23:11:06+00:00</t>
+          <t>2026-08-19T18:08:19+00:00</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>0104668f9fd195e113f5</t>
+          <t>968938ae19236c36071b</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Job Description We are searching for a seasoned Data Engineer with a specialty in the workings of DBT. In this position you will be joining a small team (3-4 people) and helping across a variety of data projects (storage, ingestion, data cleaning, transformation) specifically focused on the building, rebuilding and owning of internal DBT project (models, tests, macros, docs, exposures). This person will be setting the standard for data testing &amp; modelling. Experience in a cloud-based environment (Snowflake Ideally) is also required. This is an opportunity to join a smaller team and own projects from start to finish without huge oversight or micromanagement. This is a fully remote position within the US with a team across three separate time zones. Required Skills &amp; Experience 7+ Years of Data Engineering 3+ years with DBT Cloud platforms Snowflake Databricks Python Desired Skills &amp; Experience BI/Data visualization PowerBI, Fabric, tableau What You Will Be Doing Daily Responsibilities 80% 20% Team Collaboration The Offer You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>Join a growing, data-driven organization that is investing heavily in its modern cloud data platform and analytics capabilities. We are seeking a Senior Databricks Data Engineer to design, build, and optimize enterprise-scale data solutions using Databricks, Azure, PySpark, Delta Lake, SQL, and modern cloud technologies. This is a full-time opportunity for an engineer who is passionate about building scalable data products and shaping the future of data architecture. You'll have the opportunity to drive architecture decisions, influence engineering standards, and help build a best-in-class Lakehouse platform from the ground up. We're looking for someone who thrives in complex environments, enjoys solving large-scale data challenges, and wants to work alongside talented engineers who value innovation and continuous learning. If you're seeking a role that offers technical ownership, career growth, exposure to cutting-edge technologies, and strong work-life balance, this is an opportunity worth exploring. Required Skills &amp; Experience 7+ years of experience in Data Engineering, Data Warehousing, or Data Platform development 3+ years of hands-on Databricks experience in a production environment Strong expertise with PySpark and Apache Spark Advanced SQL development and query optimization skills Experience building ETL/ELT pipelines at enterprise scale Experience working within Azure, AWS, or GCP cloud environments Excellent communication skills and ability to partner with technical and business stakeholders Desired Skills &amp; Experience Azure Data Factory, Azure Synapse, or Microsoft Fabric experience Experience with Kafka or event-driven architectures Databricks Workflows, Airflow, or similar orchestration tools Infrastructure as Code using Terraform or ARM templates Experience supporting AI, Machine Learning, or advanced analytics initiatives Prior experience mentoring engineers or leading technical initiatives What You Will Be Doing Tech Breakdown 50% Databricks / PySpark / Spark 25% Azure Data Platform Services 25% SQL &amp; Data Modeling Daily Responsibilities 70% Hands On 30% Team Collaboration The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -9792,17 +9792,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Snowflake | DBT | FiveTran | Addison, TX</t>
+          <t>Senior Data Engineer (dbt, Snowflake, Modern Analytics Stack)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Addison, Texas, 75001, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/addison/direct-hire/senior-data-engineer-snowflake-dbt-fivetran-addison-tx/884977</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-snowflake-modern-analytics-stack/891598</t>
         </is>
       </c>
       <c r="J135" t="b">
@@ -9835,22 +9835,22 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-08-30T23:11:06+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>4e0366afed1d5979acd2</t>
+          <t>4013757fbda640752fe6</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>We are hiring for a Senior Data Engineer to join a manufacturing &amp; services organization to help build &amp; own a new data warehouse. This person will be working with a consulting org &amp; internal leadership to establish a data warehouse, build ingestions from data sources, and surface clean data for internal reporting &amp; future AI use. This is a senior level position Ideal for someone who has independently designed, built &amp; maintained data pipelines and is comfortable working relatively independently. To be considered applicants must have experience with the core tech stack of Snowflake, DBT, and Fivetran This is a hybrid position (3x/week) in Addison, TX Applicants must be currently authorized to work in the US on a full-time basis now and in the future. Required Skills &amp; Experience 7+ years of experience in data engineering Snowflake DBT Fivetran Python SQL Desired Skills &amp; Experience Bachelor’s degree in computer science, data analytics, or similar What You Will Be Doing Daily Responsibilities 80% Hands On 20% Team Collaboration The Offer Eligible for Annual Salary Bonus You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) &amp; Match</t>
+          <t>Join a rapidly growing logistics and supply chain technology organization that is expanding its data capabilities to support large-scale operations across North America. This is a full-time, remote opportunity with a preference for candidates located in the Pacific or Mountain time zones . Working in a fully remote environment, you'll leverage modern technologies including Azure, Snowflake, dbt, Python, and Terraform to help build and scale a robust cloud data platform. This remote role is ideal for a data professional who enjoys owning the operational side of data engineering. The organization already has strong foundations in architecture, ingestion, and data modeling, and is seeking someone who can deepen the platform through data transformations, pipeline development, DBA-focused work, and production operations. You'll join a collaborative, low-ego remote team that values autonomy, engineering excellence, and meaningful ownership, with the opportunity to make a significant impact without the churn-and-burn pace often associated with startup environments. Required Skills &amp; Experience · 2+ years of professional Data Engineering experience · Strong experience with Azure Data Factory (ADF) and Azure Data Lake · Advanced SQL and data transformation expertise · Experience building and maintaining production data pipelines · Strong understanding of data operations, platform support, and troubleshooting Desired Skills &amp; Experience · dbt · Snowflake · CI/CD pipelines · Terraform · Python What You Will Be Doing Tech Breakdown · 35% Data Pipeline Development · 25% Data Transformations &amp; Modeling · 20% Database Operations &amp; Administration · 10% Cloud Infrastructure &amp; Automation · 10% Cross-Functional Collaboration Daily Responsibilities Build and maintain scalable data pipelines and transformation workflows Support database administration and operational data platform needs Develop and optimize data models, reporting datasets, and business-critical transformations Monitor pipeline health, troubleshoot production issues, and improve reliability Collaborate closely with engineering leadership and business stakeholders The Offer You will receive the following benefits: · Medical, Dental, and Vision Insurance · PTO and Paid Holidays · Bonus Eligible · 401(k) · Career Growth Opportunities · Fully Remote Work Environment Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -9862,27 +9862,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | dbt, Snowflake &amp; Data Transformation</t>
+          <t>Senior Data Engineer / Databricks / AI / Chicagoland Area</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, Texas, 75201, United States</t>
+          <t>Oak Brook, Illinois, 60523, United States</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FULL TIME</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-snowflake-and-data-transformation/891600</t>
+          <t>https://motionrecruitment.com/tech-jobs/oak-brook/contract/senior-data-engineer-databricks-ai-chicagoland-area/885362</t>
         </is>
       </c>
       <c r="J136" t="b">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-08-18T18:12:31+00:00</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>01a0bdefd40d307d2fff</t>
+          <t>0fd058a73f75ae299c7d</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Join a leading healthcare workforce technology organization that develops the software powering critical healthcare recruiting and workforce management operations nationwide. This is a full-time, 100% remote opportunity, with team members distributed across the Eastern, Central, and Mountain time zones. You'll work with a modern data stack built around dbt, Snowflake, SQL, Python, and cloud-native technologies to support enterprise analytics, reporting, and business intelligence initiatives. This fully remote role is ideal for a seasoned data engineer who wants to make a significant impact within a growing and highly collaborative organization. The team is seeking a strong dbt practitioner with experience building transformation frameworks from the ground up and a deep understanding of modern analytics engineering practices. Beyond core data engineering responsibilities, you'll have opportunities to influence reporting strategy, build integrations with business-facing platforms, help evaluate future analytics tools, and contribute to the evolution of the company's data ecosystem. Required Skills &amp; Experience · 6+ years of Data Engineering, Analytics Engineering, or related experience · 3+ years of hands-on dbt experience ( required ) · Strong experience building and maintaining dbt projects from the ground up · Expert-level SQL skills · Hands-on experience with Snowflake Desired Skills &amp; Experience · Python · Fivetran · Power BI or other enterprise reporting platforms · Cloud-native data platforms and tooling · CI/CD practices for analytics engineering What You Will Be Doing Tech Breakdown · 40% dbt · 30% Snowflake · 15% SQL Development · 10% Data Integration &amp; ETL/ELT · 5% Reporting &amp; Analytics Tooling Daily Responsibilities · 60% Hands-On Data Engineering &amp; Analytics Engineering · 15% Data Modeling &amp; Transformation Design · 15% Stakeholder Collaboration &amp; Reporting Support · 10% Technical Planning &amp; Process Improvement The Offer You will receive the following benefits: · Medical, Dental, and Vision Insurance · 401(k) · PTO and Paid Holidays · Career Growth Opportunities · Fully Remote Work Environment Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>A rapidly growing enterprise organization in the automotive technology and distribution space is seeking a Data Engineer to join its team in Oak Brook, Illinois. This full-time role offers the opportunity to build scalable cloud-based data solutions that support analytics, operational reporting, machine learning, and AI initiatives. The ideal candidate will have experience with Python, SQL, modern data platforms, and enterprise-scale ETL development. What makes this opportunity stand out is the chance to help modernize a complex data ecosystem that spans cloud platforms, APIs, operational applications, and legacy databases. The organization is making substantial investments in data-driven decision making and artificial intelligence, creating an environment where engineers can influence architecture, work with cutting-edge technologies, and make a measurable business impact. This is an ideal role for professionals who enjoy solving large-scale data challenges while collaborating with cross-functional stakeholders. Required Skills &amp; Experience 4+ years of Data Engineering experience Strong SQL development expertise Python or Scala programming experience Experience building ETL/ELT pipelines Hands-on experience with Snowflake, Databricks, Redshift, or BigQuery Knowledge of data warehousing concepts and dimensional modeling Experience with orchestration platforms such as Airflow, Prefect, or Dagster Understanding of CI/CD practices and version control Experience integrating data from APIs and enterprise applications Desired Skills &amp; Experience AWS cloud experience Experience with Kafka or Kinesis Streaming data architecture AI/ML data pipeline exposure Supply chain, ERP, or CRM integration experience Data observability and monitoring tools Enterprise-scale data modernization projects Master's degree in Computer Science, Engineering, or related field What You Will Be Doing Tech Breakdown 40% Python Development 30% SQL &amp; Data Engineering 20% Cloud Data Platforms (Snowflake/Databricks/AWS) 10% Data Orchestration &amp; Automation Daily Responsibilities 75% Hands On Engineering 15% Team Collaboration 10% Strategic Architecture &amp; Design The Offer Competitive Salary You will receive the following benefits: Medical, Dental, and Vision Insurance Applicants must be currently authorized to work in the US on a full-time basis now and in the future. #LI-CD1</t>
         </is>
       </c>
     </row>
@@ -9932,17 +9932,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Senior Python Data Engineer / Architecture / ETL Pipelines / Hybrid in Smyrna</t>
+          <t>Senior Data Engineer / Databricks / End-to-End Ownerhp</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Marietta, Georgia, 30067, United States</t>
+          <t>Chicago, Illinois, 60603, United States</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/marietta/direct-hire/senior-python-data-engineer-architecture-etl-pipelines-hybrid-in-smyrna/878315</t>
+          <t>https://motionrecruitment.com/tech-jobs/chicago/direct-hire/senior-data-engineer-databricks-end-to-end-ownerhp/876474</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9975,22 +9975,22 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-08-04T13:37:21+00:00</t>
+          <t>2026-09-01T18:18:15+00:00</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>e4f94c56e691df2a6089</t>
+          <t>804829dfb347ca52e5ac</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>A client is looking to bring on a Staff Python Data Engineer to join their team. This team is based in Marietta, GA and in the 2 days week. For the first 3 months, you’ll be heavily on-site partnering with the CTO as this is his key product and they are still hands on. You’ll be joining a growing team working on a variety of different applications internally and externally for shipping out collectible products. You’ll be architecting new features, leading the development, joining a team of software developers and some in the infrastructure. You’ll be the sole owner of this analytics product that is used by real estate agents to view modeled data of transactions. You’d be working mostly in an individual capacity with support from others on the data teams. You’d be joining a high-level team to make a massive impact on the products and team that is scaling rapidly! This client is looking for someone who is extremely independent and seeks other confident individuals to make a significant impact on their services, new initiatives, and culture. They’re looking for someone with strong critical thinking and decision making skills who can hit the ground running. Required Skills &amp; Experience 8+ years of experience with Python 5+ years of experience with Postgres 5+ years of experience with Kafka, Kubernetes 5+ years of experience with data warehousing 4-year degree Desired Skills &amp; Experience Experience with real estate products What You Will Be Doing Tech Breakdown 10% Leadership 90% Development Daily Responsibilities 90% Hands-on development 10% Leadership The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance 401k matching Bonus Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>A well-established, global professional services organization is expanding its Data &amp; AI engineering team and hiring a Data Engineer to support a large-scale cloud data platform initiative. This role is based in Chicago and focuses on building modern data pipelines using Azure Databricks, Python, SQL, and Spark in a production environment. This is a hands-on engineering opportunity for someone who enjoys owning data pipelines end-to-end and wants exposure to enterprise-scale data challenges. You’ll work alongside experienced engineers and business partners to turn raw data into trusted, analytics-ready datasets that power reporting, insights, and AI use cases. This team is early in its Databricks journey, which means your work will matter immediately. You’ll help shape how pipelines are built, how data is governed, and how the platform evolves over time. It’s ideal for a strong mid-level engineer who wants to deepen their Databricks expertise while working on a highly visible, long-term transformation initiative. Required Skills &amp; Experience 6+ years of hands-on data engineering experience Strong experience building pipelines using Databricks Proficiency in Python and SQL for production data processing Working knowledge of Apache Spark and Delta Lake Experience with cloud data storage (ADLS, object storage) Experience with data modeling and schema design Familiarity with Git, CI/CD concepts, and basic testing/monitoring Desired Skills &amp; Experience Azure Databricks in an enterprise environment Experience with Unity Catalog and Databricks Jobs/Workflows Exposure to streaming or CDC pipelines Experience supporting BI or AI use cases Familiarity with Infrastructure as Code What You Will Be Doing Tech Breakdown 70% Azure Databricks / Spark / Delta Lake 20% Python &amp; SQL development 10% CI/CD, testing, and optimization Daily Responsibilities 80% Hands-On Engineering 10% Collaboration with BI, AI, and product teams 10% Documentation, reviews, and platform improvements The Offer Bonus eligible You will receive the following benefits: Medical, Dental, and Vision Insurance Vacation Time Stock Options Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -10002,27 +10002,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Senior Technology and Data Engineer - AWS/Python/Wiz - Charlotte, Nc</t>
+          <t>Senior Data Engineer | DBT Specialist</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Charlotte, North Carolina, 28270, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/senior-technology-and-data-engineer-aws-python-wiz-charlotte-nc/885741</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-specialist/886415</t>
         </is>
       </c>
       <c r="J138" t="b">
@@ -10045,22 +10045,22 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-08-30T23:11:06+00:00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>fd3fc8487a48b83c5587</t>
+          <t>0104668f9fd195e113f5</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Job Description A large enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Charlotte, North Carolina . This role supports enterprise cloud security initiatives focused on Infrastructure as Code (IaC), CI/CD security integration, policy enforcement, and developer enablement. The selected professional will work closely with engineering, security, and platform teams to strengthen deployment security across cloud-native environments. This position offers the opportunity to influence security controls at scale while helping teams build, test, and deploy infrastructure in a secure and efficient manner. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Monitor pipeline health and troubleshoot failed scans. Validate severity, de-duplicate findings, suppress false positives, and route issues to appropriate teams. Tune IaC policies and manage staged policy enforcement. Integrate Wiz CLI into CI/CD pipelines and implement gating thresholds. Publish artifacts for traceability and optimize scan performance. Deploy and maintain Wiz DevOps extensions and Wiz Scanner integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins environments. Enable local scanning, pull request scanning, and IDE workflows. Partner with platform teams to embed security controls into standard deployment processes. Provide support sessions, remediation guidance, and developer enablement resources. Manage upgrades, policy refreshes, and tool reliability initiatives. Coordinate with vendor support teams and product resources. Maintain exception management processes and governance controls. Integrate workflows with ServiceNow for tracking and reporting. Create dashboards covering coverage, MTTR, block rates, exception aging, and audit evidence. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medica</t>
+          <t>Job Description We are searching for a seasoned Data Engineer with a specialty in the workings of DBT. In this position you will be joining a small team (3-4 people) and helping across a variety of data projects (storage, ingestion, data cleaning, transformation) specifically focused on the building, rebuilding and owning of internal DBT project (models, tests, macros, docs, exposures). This person will be setting the standard for data testing &amp; modelling. Experience in a cloud-based environment (Snowflake Ideally) is also required. This is an opportunity to join a smaller team and own projects from start to finish without huge oversight or micromanagement. This is a fully remote position within the US with a team across three separate time zones. Required Skills &amp; Experience 7+ Years of Data Engineering 3+ years with DBT Cloud platforms Snowflake Databricks Python Desired Skills &amp; Experience BI/Data visualization PowerBI, Fabric, tableau What You Will Be Doing Daily Responsibilities 80% 20% Team Collaboration The Offer You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10072,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Senior Technology and Data Engineer - Irving, Tx</t>
+          <t>Senior Data Engineer | Snowflake | DBT | FiveTran | Addison, TX</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Irving, Texas, 75059, United States</t>
+          <t>Addison, Texas, 75001, United States</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/irving/contract/senior-technology-and-data-engineer-irving-tx/885743</t>
+          <t>https://motionrecruitment.com/tech-jobs/addison/direct-hire/senior-data-engineer-snowflake-dbt-fivetran-addison-tx/884977</t>
         </is>
       </c>
       <c r="J139" t="b">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-08-30T23:11:06+00:00</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>e1a6ec1ce6f095d8053c</t>
+          <t>4e0366afed1d5979acd2</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Job Description A growing enterprise technology team is seeking a Technology and Data Engineer 5 for a hybrid position in Irving, TX . This role is focused on securing Infrastructure as Code deployments and helping engineering teams identify cloud security risks before they reach production. The ideal candidate will bring experience building policy-driven security controls, supporting CI/CD environments, and improving security visibility across modern cloud platforms. You will work with development, platform, and security teams to enhance automated scanning, strengthen governance processes, and support scalable cloud security practices across the organization. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, consulting experience, training, military experience, or education. 8+ years of AppSec, Cloud Security, or DevSecOps experience. Hands-on Terraform and Kubernetes security experience. Experience using Wiz or similar IaC security tools. Policy as Code experience using OPA/Rego or equivalent technologies. Strong understanding of CI/CD tools and Git-based workflows. Excellent communication and troubleshooting skills. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect management experience. VS Code or developer IDE enablement experience. AWS, Azure, or GCP certifications. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA. Build automated regression tests for security policies. Monitor pipeline health and investigate scan failures. Validate findings, remove duplicates, and reduce false positives. Manage policy updates and staged enforcement processes. Integrate Wiz CLI into CI/CD workflows. Deploy and maintain Wiz scanning solutions and extensions. Support GitHub, GitLab, Azure DevOps, and Jenkins integrations. Enable local, pull request, and IDE-based scanning workflows. Partner with engineering teams to improve adoption of security controls. Provide remediation guidance and developer support. Maintain platform upgrades, testing, and tool reliability. Coordinate with vendor support and product teams. Track exceptions and governance requirements. Integrate findings workflows with ServiceNow. Prepare dashboards, metrics, audit evidence, and reporting. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
+          <t>We are hiring for a Senior Data Engineer to join a manufacturing &amp; services organization to help build &amp; own a new data warehouse. This person will be working with a consulting org &amp; internal leadership to establish a data warehouse, build ingestions from data sources, and surface clean data for internal reporting &amp; future AI use. This is a senior level position Ideal for someone who has independently designed, built &amp; maintained data pipelines and is comfortable working relatively independently. To be considered applicants must have experience with the core tech stack of Snowflake, DBT, and Fivetran This is a hybrid position (3x/week) in Addison, TX Applicants must be currently authorized to work in the US on a full-time basis now and in the future. Required Skills &amp; Experience 7+ years of experience in data engineering Snowflake DBT Fivetran Python SQL Desired Skills &amp; Experience Bachelor’s degree in computer science, data analytics, or similar What You Will Be Doing Daily Responsibilities 80% Hands On 20% Team Collaboration The Offer Eligible for Annual Salary Bonus You will receive the following benefits: Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) &amp; Match</t>
         </is>
       </c>
     </row>
@@ -10142,27 +10142,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Senior Technology and Data Engineer - San Antonio, Tx</t>
+          <t>Senior Data Engineer | dbt, Snowflake &amp; Data Transformation</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Antonio, MA, 28248, United States</t>
+          <t>Dallas, Texas, 75201, United States</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/san-antonio/contract/senior-technology-and-data-engineer-san-antonio-tx/885752</t>
+          <t>https://motionrecruitment.com/tech-jobs/dallas/direct-hire/senior-data-engineer-dbt-snowflake-and-data-transformation/891600</t>
         </is>
       </c>
       <c r="J140" t="b">
@@ -10185,22 +10185,22 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-08-21T18:13:57+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>f2be99140aa593342f82</t>
+          <t>01a0bdefd40d307d2fff</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Job Description A dynamic enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in San Antonio, Texas . This position is geared toward professionals who are passionate about cloud security and Infrastructure as Code governance. The team is focused on building security directly into cloud deployment processes, helping engineering organizations identify misconfigurations early, strengthen policy compliance, and improve overall security posture. You'll have the opportunity to work alongside cloud, platform, and security teams to enhance automated controls, streamline security operations, and promote secure development practices across complex enterprise environments. This role is ideal for someone who enjoys solving technical challenges, driving automation, and helping organizations scale cloud security capabilities. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deploym</t>
+          <t>Join a leading healthcare workforce technology organization that develops the software powering critical healthcare recruiting and workforce management operations nationwide. This is a full-time, 100% remote opportunity, with team members distributed across the Eastern, Central, and Mountain time zones. You'll work with a modern data stack built around dbt, Snowflake, SQL, Python, and cloud-native technologies to support enterprise analytics, reporting, and business intelligence initiatives. This fully remote role is ideal for a seasoned data engineer who wants to make a significant impact within a growing and highly collaborative organization. The team is seeking a strong dbt practitioner with experience building transformation frameworks from the ground up and a deep understanding of modern analytics engineering practices. Beyond core data engineering responsibilities, you'll have opportunities to influence reporting strategy, build integrations with business-facing platforms, help evaluate future analytics tools, and contribute to the evolution of the company's data ecosystem. Required Skills &amp; Experience · 6+ years of Data Engineering, Analytics Engineering, or related experience · 3+ years of hands-on dbt experience ( required ) · Strong experience building and maintaining dbt projects from the ground up · Expert-level SQL skills · Hands-on experience with Snowflake Desired Skills &amp; Experience · Python · Fivetran · Power BI or other enterprise reporting platforms · Cloud-native data platforms and tooling · CI/CD practices for analytics engineering What You Will Be Doing Tech Breakdown · 40% dbt · 30% Snowflake · 15% SQL Development · 10% Data Integration &amp; ETL/ELT · 5% Reporting &amp; Analytics Tooling Daily Responsibilities · 60% Hands-On Data Engineering &amp; Analytics Engineering · 15% Data Modeling &amp; Transformation Design · 15% Stakeholder Collaboration &amp; Reporting Support · 10% Technical Planning &amp; Process Improvement The Offer You will receive the following benefits: · Medical, Dental, and Vision Insurance · 401(k) · PTO and Paid Holidays · Career Growth Opportunities · Fully Remote Work Environment Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -10212,12 +10212,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Technolgy and Data Engineer 5 - Des Moines, Ia</t>
+          <t>Senior Python Data Engineer / Architecture / ETL Pipelines / Hybrid in Smyrna</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Des Moines, Iowa, 50308, United States</t>
+          <t>Marietta, Georgia, 30067, United States</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FULL TIME</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/des-moines/contract/technolgy-and-data-engineer-5-des-moines-ia/885746</t>
+          <t>https://motionrecruitment.com/tech-jobs/marietta/direct-hire/senior-python-data-engineer-architecture-etl-pipelines-hybrid-in-smyrna/878315</t>
         </is>
       </c>
       <c r="J141" t="b">
@@ -10255,22 +10255,22 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-09-18T13:23:55+00:00</t>
+          <t>2026-08-04T13:37:21+00:00</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>6bf0c522dd76b4f094da</t>
+          <t>e4f94c56e691df2a6089</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Job Description A growing enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Des Moines, Iowa . This position will focus on improving cloud infrastructure security by embedding automated controls into development and deployment workflows. The team is looking for someone who can help enhance Infrastructure as Code security practices, support policy governance initiatives, and strengthen security oversight throughout the software delivery process. You will collaborate with engineers, security professionals, and platform teams to create scalable solutions that help identify risk early, improve compliance alignment, and enable secure cloud deployments across enterprise environments. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions,</t>
+          <t>A client is looking to bring on a Staff Python Data Engineer to join their team. This team is based in Marietta, GA and in the 2 days week. For the first 3 months, you’ll be heavily on-site partnering with the CTO as this is his key product and they are still hands on. You’ll be joining a growing team working on a variety of different applications internally and externally for shipping out collectible products. You’ll be architecting new features, leading the development, joining a team of software developers and some in the infrastructure. You’ll be the sole owner of this analytics product that is used by real estate agents to view modeled data of transactions. You’d be working mostly in an individual capacity with support from others on the data teams. You’d be joining a high-level team to make a massive impact on the products and team that is scaling rapidly! This client is looking for someone who is extremely independent and seeks other confident individuals to make a significant impact on their services, new initiatives, and culture. They’re looking for someone with strong critical thinking and decision making skills who can hit the ground running. Required Skills &amp; Experience 8+ years of experience with Python 5+ years of experience with Postgres 5+ years of experience with Kafka, Kubernetes 5+ years of experience with data warehousing 4-year degree Desired Skills &amp; Experience Experience with real estate products What You Will Be Doing Tech Breakdown 10% Leadership 90% Development Daily Responsibilities 90% Hands-on development 10% Leadership The Offer You will receive the following benefits: Medical, Dental, and Vision Insurance 401k matching Bonus Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -10282,12 +10282,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Technology and Data Engineer - Washington, Dc</t>
+          <t>Senior Technology and Data Engineer - AWS/Python/Wiz - Charlotte, Nc</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Washington, District Of Columbia, 20420, United States</t>
+          <t>Charlotte, North Carolina, 28270, United States</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/washington/contract/technology-and-data-engineer-washington-dc/885753</t>
+          <t>https://motionrecruitment.com/tech-jobs/charlotte/contract/senior-technology-and-data-engineer-aws-python-wiz-charlotte-nc/885741</t>
         </is>
       </c>
       <c r="J142" t="b">
@@ -10325,22 +10325,22 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-09-18T13:23:55+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>ba8b64ba649bef28e6a0</t>
+          <t>fd3fc8487a48b83c5587</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Job Description A large enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Washington, DC . This position supports key cloud security initiatives designed to improve how infrastructure is built, secured, and deployed across the organization. The team is focused on implementing preventative controls within Infrastructure as Code workflows, strengthening governance processes, and helping engineering teams address security concerns earlier in the development lifecycle. The selected candidate will work across security, cloud, and engineering functions to support scalable security practices that improve visibility, streamline risk management, and enhance the reliability of cloud deployment processes. This is an excellent opportunity for someone who enjoys combining technical security expertise with automation and collaboration. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize</t>
+          <t>Job Description A large enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Charlotte, North Carolina . This role supports enterprise cloud security initiatives focused on Infrastructure as Code (IaC), CI/CD security integration, policy enforcement, and developer enablement. The selected professional will work closely with engineering, security, and platform teams to strengthen deployment security across cloud-native environments. This position offers the opportunity to influence security controls at scale while helping teams build, test, and deploy infrastructure in a secure and efficient manner. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Monitor pipeline health and troubleshoot failed scans. Validate severity, de-duplicate findings, suppress false positives, and route issues to appropriate teams. Tune IaC policies and manage staged policy enforcement. Integrate Wiz CLI into CI/CD pipelines and implement gating thresholds. Publish artifacts for traceability and optimize scan performance. Deploy and maintain Wiz DevOps extensions and Wiz Scanner integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins environments. Enable local scanning, pull request scanning, and IDE workflows. Partner with platform teams to embed security controls into standard deployment processes. Provide support sessions, remediation guidance, and developer enablement resources. Manage upgrades, policy refreshes, and tool reliability initiatives. Coordinate with vendor support teams and product resources. Maintain exception management processes and governance controls. Integrate workflows with ServiceNow for tracking and reporting. Create dashboards covering coverage, MTTR, block rates, exception aging, and audit evidence. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medica</t>
         </is>
       </c>
     </row>
@@ -10352,12 +10352,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Technology and Data Engineer 5 - Minneapolic, Mn</t>
+          <t>Senior Technology and Data Engineer - Irving, Tx</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Minneapolis, Minnesota, 55408, United States</t>
+          <t>Irving, Texas, 75059, United States</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/minneapolis/contract/technology-and-data-engineer-5-minneapolic-mn/885744</t>
+          <t>https://motionrecruitment.com/tech-jobs/irving/contract/senior-technology-and-data-engineer-irving-tx/885743</t>
         </is>
       </c>
       <c r="J143" t="b">
@@ -10400,17 +10400,17 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>e9d3b3cd2bc35cb85d4a</t>
+          <t>e1a6ec1ce6f095d8053c</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Job Description A respected enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Minneapolis, Minnesota . In this role, you will help advance security practices across cloud infrastructure and software delivery environments by integrating security controls directly into the deployment process. The team is focused on improving Infrastructure as Code security, strengthening governance standards, and providing engineering teams with actionable feedback that supports secure deployments. This position offers the opportunity to work on complex cloud security initiatives while partnering with development, platform, and DevOps teams to improve risk visibility, automate security validation, and enhance overall operational effectiveness. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct off</t>
+          <t>Job Description A growing enterprise technology team is seeking a Technology and Data Engineer 5 for a hybrid position in Irving, TX . This role is focused on securing Infrastructure as Code deployments and helping engineering teams identify cloud security risks before they reach production. The ideal candidate will bring experience building policy-driven security controls, supporting CI/CD environments, and improving security visibility across modern cloud platforms. You will work with development, platform, and security teams to enhance automated scanning, strengthen governance processes, and support scalable cloud security practices across the organization. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work experience, consulting experience, training, military experience, or education. 8+ years of AppSec, Cloud Security, or DevSecOps experience. Hands-on Terraform and Kubernetes security experience. Experience using Wiz or similar IaC security tools. Policy as Code experience using OPA/Rego or equivalent technologies. Strong understanding of CI/CD tools and Git-based workflows. Excellent communication and troubleshooting skills. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect management experience. VS Code or developer IDE enablement experience. AWS, Azure, or GCP certifications. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA. Build automated regression tests for security policies. Monitor pipeline health and investigate scan failures. Validate findings, remove duplicates, and reduce false positives. Manage policy updates and staged enforcement processes. Integrate Wiz CLI into CI/CD workflows. Deploy and maintain Wiz scanning solutions and extensions. Support GitHub, GitLab, Azure DevOps, and Jenkins integrations. Enable local, pull request, and IDE-based scanning workflows. Partner with engineering teams to improve adoption of security controls. Provide remediation guidance and developer support. Maintain platform upgrades, testing, and tool reliability. Coordinate with vendor support and product teams. Track exceptions and governance requirements. Integrate findings workflows with ServiceNow. Prepare dashboards, metrics, audit evidence, and reporting. The Offer Hybrid Schedule 6-Month Contract W2 Only You will receive the following benefits Medical Insurance Dental Benefits Vision Benefits Paid Time Off (PTO) 401(k) Applicants must be currently authorized to work in the US on a full-time basis now and in the future.</t>
         </is>
       </c>
     </row>
@@ -10422,17 +10422,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Threat Detection &amp; Security Analytics Engineer - Georgia</t>
+          <t>Senior Technology and Data Engineer - San Antonio, Tx</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, 30009, United States</t>
+          <t>San Antonio, MA, 28248, United States</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/threat-detection-and-security-analytics-engineer-georgia/888545</t>
+          <t>https://motionrecruitment.com/tech-jobs/san-antonio/contract/senior-technology-and-data-engineer-san-antonio-tx/885752</t>
         </is>
       </c>
       <c r="J144" t="b">
@@ -10465,49 +10465,54 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-09-28T19:01:50+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>a5c7a5407f8dbed28b03</t>
+          <t>f2be99140aa593342f82</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Job Description A leading enterprise technology organization is seeking a Threat Detection &amp; Security Analytics Engineer to join its cybersecurity team. This role is designed for a security-first professional who can strengthen threat detection, monitoring, incident analysis, and vulnerability management efforts while leveraging data and automation to improve security visibility and operational effectiveness. The ideal candidate will bring hands-on experience in security operations, threat monitoring, and incident response, along with the analytical skills needed to transform security telemetry into actionable insights. This position works closely with security, engineering, and infrastructure teams to identify risks, improve detection capabilities, and enhance overall security posture across enterprise and cloud environments. While Python, SQL, and reporting tools are important components of the role, the primary focus is cybersecurity operations, threat detection, and security analytics. Required Skills &amp; Experience 5+ years of experience in cybersecurity, security operations, threat detection, or a related security discipline Strong experience with threat monitoring, incident response, and vulnerability management Experience investigating security events, alerts, logs, and telemetry Hands-on experience with Microsoft Defender or similar security platforms Experience working within Microsoft Azure environments Strong Python scripting and automation skills Strong SQL skills with experience querying and analyzing security data Understanding of security operations, threat detection methodologies, and incident response processes Ability to communicate technical findings and security risks to various stakeholders Strong analytical, troubleshooting, and problem-solving abilities Desired Skills &amp; Experience Experience in a SOC, Security Operations, or Blue Team environment Experience developing security analytics and detection use cases Familiarity with regulated environments and continuous monitoring programs Experience automating security workflows with Python or PowerShell Experience building dashboards and operational reporting solutions using Power BI or similar tools Knowledge of threat hunting techniques and security investigation methodologies Security certifications are a plus What You Will Be Doing Daily Responsibilities Monitor, investigate, and respond to security alerts and suspicious activity across enterprise and cloud environments Analyze security telemetry to identify trends, anomalies, threats, and operational risks Support incident response, containment, and remediation efforts Evaluate vulnerability data and partner with technical teams to prioritize remediation activities Develop and enhance security detections, monitoring capabilities, and operational processes Build automation solutions using Python to improve security operations efficiency Utilize SQL to support investigations, reporting, and security analytics initiatives Crea</t>
+          <t>Job Description A dynamic enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in San Antonio, Texas . This position is geared toward professionals who are passionate about cloud security and Infrastructure as Code governance. The team is focused on building security directly into cloud deployment processes, helping engineering organizations identify misconfigurations early, strengthen policy compliance, and improve overall security posture. You'll have the opportunity to work alongside cloud, platform, and security teams to enhance automated controls, streamline security operations, and promote secure development practices across complex enterprise environments. This role is ideal for someone who enjoys solving technical challenges, driving automation, and helping organizations scale cloud security capabilities. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deploym</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Pyramid Consulting</t>
+          <t>Motion Recruitment</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Temporary Finance Analyst, Store Planning</t>
+          <t>Technolgy and Data Engineer 5 - Des Moines, Ia</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Des Moines, Iowa, 50308, United States</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10517,12 +10522,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>https://www.pyramidcg.com/job-details/temporary-finance-analyst-store-planning-in-operations-jobs-1669426</t>
+          <t>https://motionrecruitment.com/tech-jobs/des-moines/contract/technolgy-and-data-engineer-5-des-moines-ia/885746</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -10530,54 +10535,54 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-10-02T21:44:50+00:00</t>
+          <t>2026-09-18T13:23:55+00:00</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>0d4acc12e5d1bf3a0a35</t>
+          <t>6bf0c522dd76b4f094da</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>{"css":"*#dm *.dmBody nav.u_1049841281{\ncolor:black !important}\n.u_1948361810{\n}\n.u_1828143305{\n}\n.u_1134588705{\n}\n*#dm *.dmBody div.u_1948361810{\nbackground-color:rgba(0,0,0,0) !important}\n*#dm *.dmBody div.u_1915430311 .similarJobsTitle{\nfont-weight:normal !important;\nfont-family:Dosis !important}\n*#dm *.dmBody div.u_1337134807 .linkApplyBtnText{\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1662312594 .linkApplyBtnText{\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-printJob .printJob{\ncolor:rgba(0,0,0,1) !important;\nfont-family:franklingothicurw !important}\n*#dm *.dmBody *.u_1955642683 div.shmJobAlert-Button{\ntext-align:LEFT !important}\n*#dm *.dmBody div.u_1045457657{\nbackground-color:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1662312594 .shLinkApplyBtn{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-title{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-saveJob div{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-printJob span{\nfont-family:Karla-VariableFont_wght !important;\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-emailJob a{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1955642683 input.shmJobAlert-Input{\ncolor:rgba(31,56,73,1) !important;\nbackground-color:rgba(0,0,0,0) !important;\nborder-style:solid !important;\nborder-width:1px !important;\nborder-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button span.text{\nfont-weight:bold !important;\ncolor:rgba(255,255,255,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button:hover span.text{\ncolor:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button.hover span.text{\ncolor:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1915430311 .similarJobsTitle h3{\nfont-family:Karla-VariableFont_wght !important;\ncolor:rgba(31,56,73,1) !important;\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1915430311 .sjJobName{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1915430311 .sjplaceTxt{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1915430311 .sjWorkTypeText{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1337134807 .shLinkApplyBtn{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody section.u_1897767439{\nbackground-image:url(https://irp.cdn-website.com/adb40814/dms3rep/multi/opt/Watercolor-Background-4-01-2880w.png) !important;\nbackground-color:rgb(238,238,238) !important;\nbackground-repeat:no-repeat !important;\nbackground-size:cover !important}\n*#dm *.dmBody div.u_1523290715 .wrapper{\ncolor:rgba(31,56,73,1) !i</t>
+          <t>Job Description A growing enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Des Moines, Iowa . This position will focus on improving cloud infrastructure security by embedding automated controls into development and deployment workflows. The team is looking for someone who can help enhance Infrastructure as Code security practices, support policy governance initiatives, and strengthen security oversight throughout the software delivery process. You will collaborate with engineers, security professionals, and platform teams to create scalable solutions that help identify risk early, improve compliance alignment, and enable secure cloud deployments across enterprise environments. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct office hours, troubleshooting sessions,</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>Motion Recruitment</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Compliance Analyst</t>
+          <t>Technology and Data Engineer - Washington, Dc</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cupertino, CA, 95014, USA</t>
+          <t>Washington, District Of Columbia, 20420, United States</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
+          <t>CONTRACT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10587,12 +10592,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Data-Analyst-CA-Cupertino-Rose-International-Job-508612.html</t>
+          <t>https://motionrecruitment.com/tech-jobs/washington/contract/technology-and-data-engineer-washington-dc/885753</t>
         </is>
       </c>
       <c r="J146" t="b">
@@ -10600,49 +10605,54 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-10-02T21:44:50+00:00</t>
+          <t>2026-09-18T13:23:55+00:00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>32a8063ea2aab7937a22</t>
+          <t>ba8b64ba649bef28e6a0</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Education/Experience: â¢ 3-5 years of related experience with a bachelor's degree in a related field. Duties: â¢ This position will be part of the Business Conduct and Compliance team. Specifically, the position will work on global regulatory compliance initiatives, primarily focused on third-party due diligence. The candidate has a proven track record of:â¢ Background in reviewing third-party due diligence screening reports and identifying potential issues based on risk criteria and regulations.â¢ Working on anti-corruption regulatory compliance program initiatives.â¢ Experience in research, including on regulatory matters.â¢ Familiarity with compliance systems and documentation is a plus.â¢ Above average Excel and Tableau skills.â¢ Working independently on multiple initiatives or standalone projects.â¢ Simultaneously working with multiple teams, balancing various priorities, problem-solving in high-demand situations, defining and establishing attainable measures of success, and regularly achieving positive outcomes as part of a global team.â¢ Exceptional communication and analytical skills.â¢ High level of attention to detail.â¢ Strong teamwork and relationship-building skills.â¢ Ability to work alone or part of a team based on project needs.â¢ Ability to manage several projects simultaneously.â¢ Experience conducting due diligence research, a plus.**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
+          <t>Job Description A large enterprise technology organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Washington, DC . This position supports key cloud security initiatives designed to improve how infrastructure is built, secured, and deployed across the organization. The team is focused on implementing preventative controls within Infrastructure as Code workflows, strengthening governance processes, and helping engineering teams address security concerns earlier in the development lifecycle. The selected candidate will work across security, cloud, and engineering functions to support scalable security practices that improve visibility, streamline risk management, and enhance the reliability of cloud deployment processes. This is an excellent opportunity for someone who enjoys combining technical security expertise with automation and collaboration. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>Motion Recruitment</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING EMPLOYEE RELATIONS ANALYST HR IN REMOTE, USA!</t>
+          <t>Technology and Data Engineer 5 - Minneapolic, Mn</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Minneapolis, Minnesota, 55408, United States</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -10652,12 +10662,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Analyst-Remote-Rose-International-Job-508767.html</t>
+          <t>https://motionrecruitment.com/tech-jobs/minneapolis/contract/technology-and-data-engineer-5-minneapolic-mn/885744</t>
         </is>
       </c>
       <c r="J147" t="b">
@@ -10665,49 +10675,54 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-08-21T18:13:57+00:00</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>15de6a36dc4d5539ab23</t>
+          <t>e9d3b3cd2bc35cb85d4a</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Employee Relations Analyst HR - Remote, USA | Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING EMPLOYEE RELATIONS ANALYST HR IN REMOTE, USA! Date Posted: 10/06/2026 Hiring Organization: Rose International Position Number: 508767 Industry: Pharmaceutical/Healthcare Job Title: Employee Relations Analyst HR Job Location: Remote, USA Work Model: Remote Shift: Monday-Friday 8:30a-5:00p EST or Monday-Friday 10:30a-7p EST Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 2 Min Hourly Rate($): 20.00 Max Hourly Rate($): 21.00 Must Have Skills/Attributes: Case Management, Document Review, PHR, Problem Management Experience Desired: Experience and understanding in Employee Relations, Labor Relations, or as an HR Generalist (2+ yrs), Knowledge of current state and federal employment/labor laws and regulations (2+ yrs), Leadership experience (2+ yrs) Required Minimum Education: High School Diploma or equivalent Preferred Education: Bachelorâs Degree Preferred Certifications/Licenses: HR/SPHR and/or CP/SCP (SHRM) **C2C is not available** Job Description Required Education â¢ High school diploma Preferred Education â¢ Bachelorâs Degree Preferred License/Certification â¢ PHR/SPHR and/or CP/SCP (SHRM) Required Experience â¢ 2+ years of practical experience and understanding in Employee Relations, Labor Relations, or as an HR Generalist â¢ Leadership experience can substitute for 2+ years of practical experience and understanding in Employee Relations, Labor Relations, or as an HR Generalist â¢ Knowledge of current state and federal employment/labor laws and regulations â¢ Strong real-time problem-solving and decision-making skills Preferred Experience â¢ Prior mentoring, leadership, mediation, or consulting experience Analyst I â Colleague Relations Overview â¢ Serve as a primary point of contact for colleagues, providing guidance on a broad range of workplace issues and concerns, including reasonable accommodation, workforce reduction, colleague performance, attendance, and policy interpretation â¢ Respond to a significant volume of colleague inquiries and provide timely, effective solutions during initial contact â¢ Support a positive, healthy working environment by demonstrating respect, care, and empathy while applying a fair and balanced approach to resolving policy-related concerns â¢ Provide cross-functional support to other departments as required â¢ Demonstrate sound judgment, mitigate risk, collaborate effectively, and build trust with colleagues at all levels of the organization Job Duties â¢ Obtain, review, and manage accommodation-related documentation, ensuring timely, confidential, and accurate recordkeeping throughout the accommodation process â¢ Conduct case-related research and gather relevant information, records, and supporting documentation to assist internal stakeholders and legal counsel with employment-related matters â¢ Perform administrative activit</t>
+          <t>Job Description A respected enterprise organization is seeking a Technology and Data Engineer 5 for a hybrid opportunity in Minneapolis, Minnesota . In this role, you will help advance security practices across cloud infrastructure and software delivery environments by integrating security controls directly into the deployment process. The team is focused on improving Infrastructure as Code security, strengthening governance standards, and providing engineering teams with actionable feedback that supports secure deployments. This position offers the opportunity to work on complex cloud security initiatives while partnering with development, platform, and DevOps teams to improve risk visibility, automate security validation, and enhance overall operational effectiveness. Required Skills &amp; Experience 7+ years of Engineering experience, or equivalent demonstrated through one or a combination of the following: work or consulting experience, training, military experience, education. 8+ years in AppSec, Cloud Security, or DevSecOps with hands-on Terraform and Kubernetes security experience. Practical experience operating Wiz (or similar) for IaC in CI/CD environments. Policy as Code skills using OPA/Rego or equivalent rule tuning experience. Strong CI/CD knowledge and Git workflow experience. Excellent communication skills with the ability to support development teams and drive remediation efforts. Desired Skills &amp; Experience ServiceNow AVR/CVR/ITSM integration experience. JIRA or defect-routing experience. VS Code and IDE enablement experience. Cloud certifications including AWS, Azure, or GCP. Terraform Associate, CKA, or CKAD certifications. Python, Bash, or PowerShell scripting experience. What You Will Be Doing Daily Responsibilities Design, implement, and tune custom IaC rules in Rego/OPA to extend security coverage beyond built-in capabilities. Build automated regression tests using Terraform plans, Kubernetes manifests, and sample repositories. Perform pipeline health checks and investigate failed security scans. Monitor platform availability and scanning effectiveness to minimize engineering disruption. Validate finding severity and remove duplicate or inaccurate results. Route security issues to the appropriate service and application owners. Tune policy-as-code controls in alignment with enterprise standards and governance requirements. Implement staged enforcement models using report, warning, and blocking controls. Integrate Wiz CLI into CI/CD workflows and configure security gates. Publish security artifacts for traceability and compliance reporting. Deploy and maintain Wiz DevOps extensions and scanning integrations. Support GitHub, GitLab, Azure DevOps, and Jenkins security workflows. Enable pull-request, merge-request, local workstation, and IDE-based scanning capabilities. Partner with platform engineering teams to standardize secure deployment templates. Deliver remediation guidance and support developer adoption efforts. Conduct off</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>Motion Recruitment</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING SENIOR BUSINESS INTELLIGENCE / TABLEAU ADMINISTRATOR IN Hartford, CT, USA!</t>
+          <t>Threat Detection &amp; Security Analytics Engineer - Georgia</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Alpharetta, Georgia, 30009, United States</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -10717,12 +10732,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Tableau-Developer-CT-Hartford-Rose-International-Job-508717.html</t>
+          <t>https://motionrecruitment.com/tech-jobs/alpharetta/contract/threat-detection-and-security-analytics-engineer-georgia/888545</t>
         </is>
       </c>
       <c r="J148" t="b">
@@ -10730,34 +10745,34 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-10-06T01:45:24+00:00</t>
+          <t>2026-09-28T19:01:50+00:00</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>81728d3cd37ccb12f606</t>
+          <t>a5c7a5407f8dbed28b03</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence / Tableau Administrator - Hartford, CT | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR BUSINESS INTELLIGENCE / TABLEAU ADMINISTRATOR IN Hartford, CT, USA! Date Posted: 10/05/2026 Hiring Organization: Rose International Position Number: 508717 Industry: Government/Staffing Job Title: Senior Business Intelligence / Tableau Administrator Job Location: Hartford, CT, USA, 06106 Work Model: Hybrid Work Model Details: Hybrid Schedule : 8o% remote and 20 % in person Shift: M-F 8am to 5pm Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 3 Min Hourly Rate($): 55.00 Max Hourly Rate($): 62.00 Must Have Skills/Attributes: Azure, SalesForce, SQL, Tableau Experience Desired: Experience with Tableau Cloud administration and support (5 yrs), Experience with dashboards and supporting enterprise reporting and analytics platforms (5 yrs), Strong SQL skills and experience working with Azure SQL Database or similar relational databases (5 yrs), Microsoft SQL Server (7-9 yrs), Experience with Transact-SQL (4-6 yrs), SQL Server Reporting Services (SSRS) (4-6 yrs), Comfortable engaging and escalating issues to Salesforce (1 yrs) **C2C is not available** Job Description ***Only qualified Business Intelligence / Tableau Administrator candidates located near the Hartford, CT area will be considered due to the role requiring an onsite presence *** Required Skills: â¢ Experience with Tableau Cloud administration and support â¢ Experience with Salesforce objects, fields, relationships, and the impact of different design decisions. Ability to apply best practices â¢ Experience with dashboards and supporting enterprise reporting and analytics platforms â¢ Strong SQL skills and experience working with Azure SQL Database or similar relational databases â¢ Experience with user management including new user setup, user deactivation, roles, profiles, permission sets, sharing rules and other routine tasks â¢ Critical thinking and problem solving around issues such as user access, declarative logic, business requests, Environment management, and backup solutions â¢ Comfortable engaging and escalating issues to Salesforce â¢ Microsoft SQL Server â¢ Transact-SQL â¢ SQL Server Reporting Services (SSRS) â¢ Work on all phases of SDLC and create/maintain required technical documentation â¢ Work with the Salesforce Architect to establish best practices â¢ Work with management to supply input for key design and architecture decisions, as well as work estimation and resource planning â¢ Provide guidance and training to team members Preferred Skills: â¢ Experience with Azure Data Factory (ADF). â¢ Experience with MuleSoft Runtime Fabric (RTF) or MuleSoft integrations. â¢ Experience working with Salesforce data and reporting environments. â¢ Microsoft Azure experience. About the role: The agency needs the service of a mid to Senior level BI/Tableau Admin. The candi</t>
+          <t>Job Description A leading enterprise technology organization is seeking a Threat Detection &amp; Security Analytics Engineer to join its cybersecurity team. This role is designed for a security-first professional who can strengthen threat detection, monitoring, incident analysis, and vulnerability management efforts while leveraging data and automation to improve security visibility and operational effectiveness. The ideal candidate will bring hands-on experience in security operations, threat monitoring, and incident response, along with the analytical skills needed to transform security telemetry into actionable insights. This position works closely with security, engineering, and infrastructure teams to identify risks, improve detection capabilities, and enhance overall security posture across enterprise and cloud environments. While Python, SQL, and reporting tools are important components of the role, the primary focus is cybersecurity operations, threat detection, and security analytics. Required Skills &amp; Experience 5+ years of experience in cybersecurity, security operations, threat detection, or a related security discipline Strong experience with threat monitoring, incident response, and vulnerability management Experience investigating security events, alerts, logs, and telemetry Hands-on experience with Microsoft Defender or similar security platforms Experience working within Microsoft Azure environments Strong Python scripting and automation skills Strong SQL skills with experience querying and analyzing security data Understanding of security operations, threat detection methodologies, and incident response processes Ability to communicate technical findings and security risks to various stakeholders Strong analytical, troubleshooting, and problem-solving abilities Desired Skills &amp; Experience Experience in a SOC, Security Operations, or Blue Team environment Experience developing security analytics and detection use cases Familiarity with regulated environments and continuous monitoring programs Experience automating security workflows with Python or PowerShell Experience building dashboards and operational reporting solutions using Power BI or similar tools Knowledge of threat hunting techniques and security investigation methodologies Security certifications are a plus What You Will Be Doing Daily Responsibilities Monitor, investigate, and respond to security alerts and suspicious activity across enterprise and cloud environments Analyze security telemetry to identify trends, anomalies, threats, and operational risks Support incident response, containment, and remediation efforts Evaluate vulnerability data and partner with technical teams to prioritize remediation activities Develop and enhance security detections, monitoring capabilities, and operational processes Build automation solutions using Python to improve security operations efficiency Utilize SQL to support investigations, reporting, and security analytics initiatives Crea</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Rose International</t>
+          <t>Pyramid Consulting</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING SENIOR DATA ANALYST (POWER BI AZURE CLOUD COST) IN Mechanicsville, VA, USA!</t>
+          <t>Temporary Finance Analyst, Store Planning</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10767,12 +10782,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -10787,7 +10802,7 @@
       </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Data-Analyst-VA-Mechanicsville-Rose-International-Job-508649.html</t>
+          <t>https://www.pyramidcg.com/job-details/temporary-finance-analyst-store-planning-in-operations-jobs-1669426</t>
         </is>
       </c>
       <c r="J149" t="b">
@@ -10795,22 +10810,22 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-10-02T21:44:50+00:00</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>4a20de8cc6f2a2b64806</t>
+          <t>0d4acc12e5d1bf3a0a35</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Senior Data Analyst (Power BI Azure Cloud Cost) - Mechanicsville, VA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR DATA ANALYST (POWER BI AZURE CLOUD COST) IN Mechanicsville, VA, USA! Date Posted: 10/05/2026 Hiring Organization: Rose International Position Number: 508649 Industry: Government/Staffing Job Title: Senior Data Analyst (Power BI Azure Cloud Cost) Job Location: Mechanicsville, VA, USA, 23116 Work Model: Hybrid Work Model Details: Hybrid- 2-3 days onsite per week Shift: M-F 8am to 5pm Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 45.00 Max Hourly Rate($): 48.00 Must Have Skills/Attributes: Azure, Data Analysis, PowerBI Experience Desired: Advanced level of proficiency in Power BI, including Power Query and DAX, Excel (advanced), and data (6 yrs), Some data modeling and data manipulation skills to maintain data sets from multiple, heterogenous (5 yrs), High familiarity with Azure cost management, Apptio, and cloud billing structures (5 yrs), Understanding of server migration strategies and workload cost modeling (5 yrs), Ability to translate technical data into insights for technical teams and managers (5 yrs), Proficiency in Power BI, including independently updating data, performing queries, and managing (6 yrs), Experience with Azure Reserved Instances and Just-In-Time (JIT) capacity planning (1 yrs) Required Minimum Education: Bachelorâs Degree Preferred Certifications/Licenses: FinOps certification or training **C2C is not available** Job Description ***Only qualified Data Analyst candidates located near the Mechanicsville, VA area will be considered due to the role requiring an onsite presence *** Required Skills: â¢ Bachelorâs degree in Finance, Data Analytics, Information Systems, or related field. Preferred Certifications: â¢ FinOps certification or training Required Skills: â¢ Advanced level of proficiency in Power BI, including Power Query and DAX, Excel (advanced), and data visualization best practices (6 Years) â¢ Some data modeling and data manipulation skills to maintain data sets from multiple, heterogenous sources (5 Years) â¢ High familiarity with Azure cost management, Apptio, and cloud billing structures (5 Years) â¢ Understanding of server migration strategies and workload cost modelling (5 Years) â¢ Ability to translate technical data into insights for technical teams and managers (5 Years) â¢ Ability to work independently and apply critical thinking to analyze complex financial data and develop actionable recommendations (4 Years) â¢ Proficiency in Power BI, including independently updating data, performing queries, and managing and analyzing datasets with little to no assistance (6 Years) â¢ Ability to translate complex data into clear, accurate, and actionable information for leadership and decision-making (4 Years) Preferred Skills: â¢ Experience with Azure Reserved Instances and Just</t>
+          <t>{"css":"*#dm *.dmBody nav.u_1049841281{\ncolor:black !important}\n.u_1948361810{\n}\n.u_1828143305{\n}\n.u_1134588705{\n}\n*#dm *.dmBody div.u_1948361810{\nbackground-color:rgba(0,0,0,0) !important}\n*#dm *.dmBody div.u_1915430311 .similarJobsTitle{\nfont-weight:normal !important;\nfont-family:Dosis !important}\n*#dm *.dmBody div.u_1337134807 .linkApplyBtnText{\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1662312594 .linkApplyBtnText{\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-printJob .printJob{\ncolor:rgba(0,0,0,1) !important;\nfont-family:franklingothicurw !important}\n*#dm *.dmBody *.u_1955642683 div.shmJobAlert-Button{\ntext-align:LEFT !important}\n*#dm *.dmBody div.u_1045457657{\nbackground-color:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1662312594 .shLinkApplyBtn{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-title{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-saveJob div{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-printJob span{\nfont-family:Karla-VariableFont_wght !important;\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1170511016 .jobBtn-emailJob a{\ncolor:rgba(31,56,73,1) !important;\nfont-family:Karla-VariableFont_wght !important}\n*#dm *.dmBody div.u_1955642683 input.shmJobAlert-Input{\ncolor:rgba(31,56,73,1) !important;\nbackground-color:rgba(0,0,0,0) !important;\nborder-style:solid !important;\nborder-width:1px !important;\nborder-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button span.text{\nfont-weight:bold !important;\ncolor:rgba(255,255,255,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button:hover span.text{\ncolor:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button.hover span.text{\ncolor:rgba(244,221,198,1) !important}\n*#dm *.dmBody div.u_1955642683 div.shmJobAlert-Button{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody div.u_1915430311 .similarJobsTitle h3{\nfont-family:Karla-VariableFont_wght !important;\ncolor:rgba(31,56,73,1) !important;\nfont-weight:bold !important}\n*#dm *.dmBody div.u_1915430311 .sjJobName{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1915430311 .sjplaceTxt{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1915430311 .sjWorkTypeText{\ncolor:rgba(31,56,73,1) !important}\n*#dm *.dmBody div.u_1337134807 .shLinkApplyBtn{\nbackground-color:rgba(156,174,188,1) !important}\n*#dm *.dmBody section.u_1897767439{\nbackground-image:url(https://irp.cdn-website.com/adb40814/dms3rep/multi/opt/Watercolor-Background-4-01-2880w.png) !important;\nbackground-color:rgb(238,238,238) !important;\nbackground-repeat:no-repeat !important;\nbackground-size:cover !important}\n*#dm *.dmBody div.u_1523290715 .wrapper{\ncolor:rgba(31,56,73,1) !i</t>
         </is>
       </c>
     </row>
@@ -10822,22 +10837,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING SENIOR IT BUSINESS ANALYST PROCESS MAPPING &amp; DOCUMENTATION IN Spartanburg, SC, USA!</t>
+          <t>Compliance Analyst</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Cupertino, CA, 95014, USA</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Temporary</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -10852,7 +10872,7 @@
       </c>
       <c r="I150" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Business-Analyst-SC-Spartanburg-Rose-International-Job-508662.html</t>
+          <t>https://www.roseint.com/Jobs/Data-Analyst-CA-Cupertino-Rose-International-Job-508612.html</t>
         </is>
       </c>
       <c r="J150" t="b">
@@ -10860,22 +10880,22 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-10-02T21:44:50+00:00</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>c09dd50ebdab359cb1ed</t>
+          <t>32a8063ea2aab7937a22</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Senior IT Business Analyst Process Mapping &amp; Documentation - Spartanburg, SC | Onsite, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR IT BUSINESS ANALYST PROCESS MAPPING &amp; DOCUMENTATION IN Spartanburg, SC, USA! Date Posted: 10/05/2026 Hiring Organization: Rose International Position Number: 508662 Industry: Government/Staffing Job Title: Senior IT Business Analyst Process Mapping &amp; Documentation Job Location: Spartanburg, SC, USA, 29303 Work Model: Onsite Shift: Mon-Fri, 8:00 AM - 5:00 PM Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 55.00 Max Hourly Rate($): 57.00 Must Have Skills/Attributes: Business Analysis, Documentation, MS Excel, Process Mapping Experience Desired: Demonstrated business analysis experience in complex IT or technology environments (10+ yrs), Strong requirements elicitation interviewing facilitation and stakeholder-management skills (5+ yrs), Advanced proficiency with Microsoft 365 including Word Excel PowerPoint Teams SharePoint and related (5+ yrs), Strong proficiency with Microsoft Visio for process mapping workflow documentation (5+ yrs), Working with technical SMEs across infrastructure applications service delivery cybersecurity (5+ yrs) Preferred Education: Bachelorâs Degree Preferred Certifications/Licenses: CBAP CCBA PMI-PBA PMP ITIL **C2C is not available** Job Description PREFERRED EDUCATION: â¢ Bachelor's degree in information technology information systems business or a related field OR equivalent relevant professional experience Demonstrated experience and quality of prior work are more important than a specific certification PREFERRED CERTIFICATION: â¢ CBAP CCBA PMI-PBA PMP ITIL Foundation or comparable professional certification Certifications are preferred but will not substitute for demonstrated experience and strong work products REQUIRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ 10+ years of demonstrated business analysis experience in complex IT or technology environments â¢ Strong requirements elicitation interviewing facilitation and stakeholder-management skills â¢ Advanced proficiency with Microsoft 365 including Word Excel PowerPoint Teams SharePoint and related collaboration tools â¢ Strong proficiency with Microsoft Visio for process mapping workflow documentation and technical/business diagrams â¢ Experience working with technical SMEs across infrastructure applications service delivery cybersecurity or similar IT disciplines â¢ Ability to analyze undocumented or inconsistently documented processes and convert institutional knowledge into structured artifacts â¢ Excellent written verbal organizational and analytical skills â¢ Ability to manage multiple workstreams priorities dependencies and deliverables with limited supervision PREFERRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ Experience with documentation recovery IT operational maturity knowledge-management or process</t>
+          <t>Education/Experience: â¢ 3-5 years of related experience with a bachelor's degree in a related field. Duties: â¢ This position will be part of the Business Conduct and Compliance team. Specifically, the position will work on global regulatory compliance initiatives, primarily focused on third-party due diligence. The candidate has a proven track record of:â¢ Background in reviewing third-party due diligence screening reports and identifying potential issues based on risk criteria and regulations.â¢ Working on anti-corruption regulatory compliance program initiatives.â¢ Experience in research, including on regulatory matters.â¢ Familiarity with compliance systems and documentation is a plus.â¢ Above average Excel and Tableau skills.â¢ Working independently on multiple initiatives or standalone projects.â¢ Simultaneously working with multiple teams, balancing various priorities, problem-solving in high-demand situations, defining and establishing attainable measures of success, and regularly achieving positive outcomes as part of a global team.â¢ Exceptional communication and analytical skills.â¢ High level of attention to detail.â¢ Strong teamwork and relationship-building skills.â¢ Ability to work alone or part of a team based on project needs.â¢ Ability to manage several projects simultaneously.â¢ Experience conducting due diligence research, a plus.**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10907,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NEW JOB OPENING VULNERABILITY MANAGEMENT ANALYST, SECURITY SCANNING, RISK &amp; AUTOMATION IN RICHMOND, VA, USA!</t>
+          <t>NEW JOB OPENING EMPLOYEE RELATIONS ANALYST HR IN REMOTE, USA!</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10897,7 +10917,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -10917,7 +10937,7 @@
       </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/IT-Security-Analyst-VA-Richmond-Rose-International-Job-508744.html</t>
+          <t>https://www.roseint.com/Jobs/Analyst-Remote-Rose-International-Job-508767.html</t>
         </is>
       </c>
       <c r="J151" t="b">
@@ -10925,22 +10945,22 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-10-06T17:36:06+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>9c60da1902c9fb9e2a6e</t>
+          <t>15de6a36dc4d5539ab23</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Vulnerability Management Analyst, Security Scanning, Risk &amp; Automation - Richmond, VA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING VULNERABILITY MANAGEMENT ANALYST, SECURITY SCANNING, RISK &amp; AUTOMATION IN RICHMOND, VA, USA! Date Posted: 10/06/2026 Hiring Organization: Rose International Position Number: 508744 Industry: Government/Staffing Job Title: Vulnerability Management Analyst, Security Scanning, Risk &amp; Automation Job Location: Richmond, VA, USA, 23219 Work Model: Hybrid Work Model Details: ON SITE: 2-3 days/week Shift: M-F 8am to 5pm Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 60.00 Max Hourly Rate($): 70.00 Must Have Skills/Attributes: Information Security, MS Office, SharePoint, Vulnerability, Written Communication Experience Desired: Experience and proficiency with Microsoft, SharePoint and Power BI (5 yrs), Information Security-related experience (5 yrs), Proven analytical and problem-solving abilities (5 yrs), Excellent verbal and written communication skills (5 yrs), Ability to work independently with minimal direction and as a team (5 yrs), Experience troubleshooting vulnerability scan tools and scan configurations (3 yrs), Software Vulnerability Management related experience (3 yrs) **C2C is not available** Job Description ***Only qualified Vulnerability Management Analyst candidates located near the Richmond, VA area will be considered due to the role requiring an onsite presence *** Required Skills: â¢ Information Security-related experience (5 Years) â¢ Software Vulnerability Management related experience (3 Years) â¢ Experience troubleshooting vulnerability scan tools and scan configurations (3 Years) â¢ Experience with automation supporting vulnerability assessment operations (3 Years) â¢ Experience supporting Information System Vulnerability Management (ISVM) scans and compliance activities (3 Years) â¢ Experience with API discovery and security scanning (3 Years) â¢ Experience and proficiency with Microsoft, SharePoint and Power BI (5 Years) â¢ Proven analytical and problem-solving abilities (5 Years) â¢ Excellent verbal and written communication skills (5 Years) â¢ Ability to work independently with minimal direction and as a team (5 Years) â¢ Highly motivated and self-directed (5 Years) About the role: The client is seeking a Risk and Vulnerability Analyst to support vulnerability assessment and risk analysis activities at the client. This role is responsible for conducting vulnerability scanning and analysis, supporting remediation efforts, supporting scanning operations, and helping improve enterprise visibility into security weaknesses and cyber risks. Responsibilities: â¢ Perform vulnerability assessments and assist security scanning across operating systems, databases, web applications, and enterprise infrastructure â¢ Analyze vulnerabilities and support development of remediation recommendations</t>
+          <t>Employee Relations Analyst HR - Remote, USA | Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING EMPLOYEE RELATIONS ANALYST HR IN REMOTE, USA! Date Posted: 10/06/2026 Hiring Organization: Rose International Position Number: 508767 Industry: Pharmaceutical/Healthcare Job Title: Employee Relations Analyst HR Job Location: Remote, USA Work Model: Remote Shift: Monday-Friday 8:30a-5:00p EST or Monday-Friday 10:30a-7p EST Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 2 Min Hourly Rate($): 20.00 Max Hourly Rate($): 21.00 Must Have Skills/Attributes: Case Management, Document Review, PHR, Problem Management Experience Desired: Experience and understanding in Employee Relations, Labor Relations, or as an HR Generalist (2+ yrs), Knowledge of current state and federal employment/labor laws and regulations (2+ yrs), Leadership experience (2+ yrs) Required Minimum Education: High School Diploma or equivalent Preferred Education: Bachelorâs Degree Preferred Certifications/Licenses: HR/SPHR and/or CP/SCP (SHRM) **C2C is not available** Job Description Required Education â¢ High school diploma Preferred Education â¢ Bachelorâs Degree Preferred License/Certification â¢ PHR/SPHR and/or CP/SCP (SHRM) Required Experience â¢ 2+ years of practical experience and understanding in Employee Relations, Labor Relations, or as an HR Generalist â¢ Leadership experience can substitute for 2+ years of practical experience and understanding in Employee Relations, Labor Relations, or as an HR Generalist â¢ Knowledge of current state and federal employment/labor laws and regulations â¢ Strong real-time problem-solving and decision-making skills Preferred Experience â¢ Prior mentoring, leadership, mediation, or consulting experience Analyst I â Colleague Relations Overview â¢ Serve as a primary point of contact for colleagues, providing guidance on a broad range of workplace issues and concerns, including reasonable accommodation, workforce reduction, colleague performance, attendance, and policy interpretation â¢ Respond to a significant volume of colleague inquiries and provide timely, effective solutions during initial contact â¢ Support a positive, healthy working environment by demonstrating respect, care, and empathy while applying a fair and balanced approach to resolving policy-related concerns â¢ Provide cross-functional support to other departments as required â¢ Demonstrate sound judgment, mitigate risk, collaborate effectively, and build trust with colleagues at all levels of the organization Job Duties â¢ Obtain, review, and manage accommodation-related documentation, ensuring timely, confidential, and accurate recordkeeping throughout the accommodation process â¢ Conduct case-related research and gather relevant information, records, and supporting documentation to assist internal stakeholders and legal counsel with employment-related matters â¢ Perform administrative activit</t>
         </is>
       </c>
     </row>
@@ -10952,27 +10972,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Senior IT Financial Analyst Technology Strategic Spend</t>
+          <t>NEW JOB OPENING SENIOR BUSINESS INTELLIGENCE / TABLEAU ADMINISTRATOR IN Hartford, CT, USA!</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chicago, IL, 60604, USA</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>TEMPORARY</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10987,7 +11002,7 @@
       </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
-          <t>https://www.roseint.com/Jobs/Business-Analyst-IL-Chicago-Rose-International-Job-508698.html</t>
+          <t>https://www.roseint.com/Jobs/Tableau-Developer-CT-Hartford-Rose-International-Job-508717.html</t>
         </is>
       </c>
       <c r="J152" t="b">
@@ -10995,34 +11010,34 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-10-06T01:45:24+00:00</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>432cf3df22781ff2c600</t>
+          <t>81728d3cd37ccb12f606</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Education Requirements:- High School diploma or equivalentPreferred Education:- Bachelor's degreeRequired Skills for the Business Consultant:- 7 to 10 years of related experience with emphasis on project analysis and management reporting, planning, and analysis- Analytical and problem-solving skills required to evaluate financial results and projections across all financial statements- Effective written and verbal communication skills are necessary to present relevant information to senior management and business unit officers- Strong personal computer skills and analytics tools usage (Power BI, SQL, Excel, Word and PowerPoint) are required to perform analyses and communicate financial information- Strong accounting (GAAP), reporting and financial analysis usually acquired through an advanced degree program or related work experience is requiredBusiness Consultant Overview:The Business Consultant will join the Technology Strategic Spend Team to drive the delivery of information for decision making and various analysis for the Company's Technology Organization. This role is responsible for Technology-specific analysis (focused on strategy, labor, hardware, software, etc.), but will work closely to coordinate efforts among Technology, Finance and Procurement to drive the analyses into actionable efforts. Planning and analysis will need to be prepared and presented to many roles across the Company including Technology Leadership, engineers, project managers, finance managers, and procurement specialists, using Power Point, Excel, and/or Power BI / other analytical tools.Responsibilities:- Drive analysis and presentation material for IT Capital Expenditures in the Technology Portfolio, including consideration for strategic prioritization, developing budgets, forecasting, and variance analysis- Create Leadership-level analyses that inform on Technology usage and demand, financial impacts, contractual analysis, while considering potential- Build financial business cases for technology decisions (e.g. considerations for switching vendors, adding new products or capabilities, etc.)- Leverage data analytics tools (Power BI, SQL, Excel, etc.) to reach data-driven suggestions that drive strategic discussions and planning efforts with senior leadership- Work with finance and procurement to analyze and report on efforts for productivity and automation- Conduct and lead special projects and ad hoc requests to support the Technology function**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
+          <t>Senior Business Intelligence / Tableau Administrator - Hartford, CT | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR BUSINESS INTELLIGENCE / TABLEAU ADMINISTRATOR IN Hartford, CT, USA! Date Posted: 10/05/2026 Hiring Organization: Rose International Position Number: 508717 Industry: Government/Staffing Job Title: Senior Business Intelligence / Tableau Administrator Job Location: Hartford, CT, USA, 06106 Work Model: Hybrid Work Model Details: Hybrid Schedule : 8o% remote and 20 % in person Shift: M-F 8am to 5pm Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 3 Min Hourly Rate($): 55.00 Max Hourly Rate($): 62.00 Must Have Skills/Attributes: Azure, SalesForce, SQL, Tableau Experience Desired: Experience with Tableau Cloud administration and support (5 yrs), Experience with dashboards and supporting enterprise reporting and analytics platforms (5 yrs), Strong SQL skills and experience working with Azure SQL Database or similar relational databases (5 yrs), Microsoft SQL Server (7-9 yrs), Experience with Transact-SQL (4-6 yrs), SQL Server Reporting Services (SSRS) (4-6 yrs), Comfortable engaging and escalating issues to Salesforce (1 yrs) **C2C is not available** Job Description ***Only qualified Business Intelligence / Tableau Administrator candidates located near the Hartford, CT area will be considered due to the role requiring an onsite presence *** Required Skills: â¢ Experience with Tableau Cloud administration and support â¢ Experience with Salesforce objects, fields, relationships, and the impact of different design decisions. Ability to apply best practices â¢ Experience with dashboards and supporting enterprise reporting and analytics platforms â¢ Strong SQL skills and experience working with Azure SQL Database or similar relational databases â¢ Experience with user management including new user setup, user deactivation, roles, profiles, permission sets, sharing rules and other routine tasks â¢ Critical thinking and problem solving around issues such as user access, declarative logic, business requests, Environment management, and backup solutions â¢ Comfortable engaging and escalating issues to Salesforce â¢ Microsoft SQL Server â¢ Transact-SQL â¢ SQL Server Reporting Services (SSRS) â¢ Work on all phases of SDLC and create/maintain required technical documentation â¢ Work with the Salesforce Architect to establish best practices â¢ Work with management to supply input for key design and architecture decisions, as well as work estimation and resource planning â¢ Provide guidance and training to team members Preferred Skills: â¢ Experience with Azure Data Factory (ADF). â¢ Experience with MuleSoft Runtime Fabric (RTF) or MuleSoft integrations. â¢ Experience working with Salesforce data and reporting environments. â¢ Microsoft Azure experience. About the role: The agency needs the service of a mid to Senior level BI/Tableau Admin. The candi</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - REMOTE | Judge Group</t>
+          <t>NEW JOB OPENING SENIOR DATA ANALYST (POWER BI AZURE CLOUD COST) IN Mechanicsville, VA, USA!</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -11032,12 +11047,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11052,7 +11067,7 @@
       </c>
       <c r="I153" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155561</t>
+          <t>https://www.roseint.com/Jobs/Data-Analyst-VA-Mechanicsville-Rose-International-Job-508649.html</t>
         </is>
       </c>
       <c r="J153" t="b">
@@ -11065,29 +11080,29 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>500619a71ed4996ff9fc</t>
+          <t>4a20de8cc6f2a2b64806</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior Data Analyst (Power BI Azure Cloud Cost) - Mechanicsville, VA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR DATA ANALYST (POWER BI AZURE CLOUD COST) IN Mechanicsville, VA, USA! Date Posted: 10/05/2026 Hiring Organization: Rose International Position Number: 508649 Industry: Government/Staffing Job Title: Senior Data Analyst (Power BI Azure Cloud Cost) Job Location: Mechanicsville, VA, USA, 23116 Work Model: Hybrid Work Model Details: Hybrid- 2-3 days onsite per week Shift: M-F 8am to 5pm Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 45.00 Max Hourly Rate($): 48.00 Must Have Skills/Attributes: Azure, Data Analysis, PowerBI Experience Desired: Advanced level of proficiency in Power BI, including Power Query and DAX, Excel (advanced), and data (6 yrs), Some data modeling and data manipulation skills to maintain data sets from multiple, heterogenous (5 yrs), High familiarity with Azure cost management, Apptio, and cloud billing structures (5 yrs), Understanding of server migration strategies and workload cost modeling (5 yrs), Ability to translate technical data into insights for technical teams and managers (5 yrs), Proficiency in Power BI, including independently updating data, performing queries, and managing (6 yrs), Experience with Azure Reserved Instances and Just-In-Time (JIT) capacity planning (1 yrs) Required Minimum Education: Bachelorâs Degree Preferred Certifications/Licenses: FinOps certification or training **C2C is not available** Job Description ***Only qualified Data Analyst candidates located near the Mechanicsville, VA area will be considered due to the role requiring an onsite presence *** Required Skills: â¢ Bachelorâs degree in Finance, Data Analytics, Information Systems, or related field. Preferred Certifications: â¢ FinOps certification or training Required Skills: â¢ Advanced level of proficiency in Power BI, including Power Query and DAX, Excel (advanced), and data visualization best practices (6 Years) â¢ Some data modeling and data manipulation skills to maintain data sets from multiple, heterogenous sources (5 Years) â¢ High familiarity with Azure cost management, Apptio, and cloud billing structures (5 Years) â¢ Understanding of server migration strategies and workload cost modelling (5 Years) â¢ Ability to translate technical data into insights for technical teams and managers (5 Years) â¢ Ability to work independently and apply critical thinking to analyze complex financial data and develop actionable recommendations (4 Years) â¢ Proficiency in Power BI, including independently updating data, performing queries, and managing and analyzing datasets with little to no assistance (6 Years) â¢ Ability to translate complex data into clear, accurate, and actionable information for leadership and decision-making (4 Years) Preferred Skills: â¢ Experience with Azure Reserved Instances and Just</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BUSINESS ANALYST - Boston, MA | Judge Group</t>
+          <t>NEW JOB OPENING SENIOR IT BUSINESS ANALYST PROCESS MAPPING &amp; DOCUMENTATION IN Spartanburg, SC, USA!</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11097,12 +11112,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11117,7 +11132,7 @@
       </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1150574</t>
+          <t>https://www.roseint.com/Jobs/Business-Analyst-SC-Spartanburg-Rose-International-Job-508662.html</t>
         </is>
       </c>
       <c r="J154" t="b">
@@ -11125,34 +11140,34 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-10-04T16:16:11+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>9c4f002bb00026fbc1f5</t>
+          <t>c09dd50ebdab359cb1ed</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>BUSINESS ANALYST - Boston, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior IT Business Analyst Process Mapping &amp; Documentation - Spartanburg, SC | Onsite, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING SENIOR IT BUSINESS ANALYST PROCESS MAPPING &amp; DOCUMENTATION IN Spartanburg, SC, USA! Date Posted: 10/05/2026 Hiring Organization: Rose International Position Number: 508662 Industry: Government/Staffing Job Title: Senior IT Business Analyst Process Mapping &amp; Documentation Job Location: Spartanburg, SC, USA, 29303 Work Model: Onsite Shift: Mon-Fri, 8:00 AM - 5:00 PM Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 55.00 Max Hourly Rate($): 57.00 Must Have Skills/Attributes: Business Analysis, Documentation, MS Excel, Process Mapping Experience Desired: Demonstrated business analysis experience in complex IT or technology environments (10+ yrs), Strong requirements elicitation interviewing facilitation and stakeholder-management skills (5+ yrs), Advanced proficiency with Microsoft 365 including Word Excel PowerPoint Teams SharePoint and related (5+ yrs), Strong proficiency with Microsoft Visio for process mapping workflow documentation (5+ yrs), Working with technical SMEs across infrastructure applications service delivery cybersecurity (5+ yrs) Preferred Education: Bachelorâs Degree Preferred Certifications/Licenses: CBAP CCBA PMI-PBA PMP ITIL **C2C is not available** Job Description PREFERRED EDUCATION: â¢ Bachelor's degree in information technology information systems business or a related field OR equivalent relevant professional experience Demonstrated experience and quality of prior work are more important than a specific certification PREFERRED CERTIFICATION: â¢ CBAP CCBA PMI-PBA PMP ITIL Foundation or comparable professional certification Certifications are preferred but will not substitute for demonstrated experience and strong work products REQUIRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ 10+ years of demonstrated business analysis experience in complex IT or technology environments â¢ Strong requirements elicitation interviewing facilitation and stakeholder-management skills â¢ Advanced proficiency with Microsoft 365 including Word Excel PowerPoint Teams SharePoint and related collaboration tools â¢ Strong proficiency with Microsoft Visio for process mapping workflow documentation and technical/business diagrams â¢ Experience working with technical SMEs across infrastructure applications service delivery cybersecurity or similar IT disciplines â¢ Ability to analyze undocumented or inconsistently documented processes and convert institutional knowledge into structured artifacts â¢ Excellent written verbal organizational and analytical skills â¢ Ability to manage multiple workstreams priorities dependencies and deliverables with limited supervision PREFERRED EXPERIENCE KNOWLEDGE ABILITIES AND SKILLS: â¢ Experience with documentation recovery IT operational maturity knowledge-management or process</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Business Analyst - Denver, CO | Judge Group</t>
+          <t>NEW JOB OPENING VULNERABILITY MANAGEMENT ANALYST, SECURITY SCANNING, RISK &amp; AUTOMATION IN RICHMOND, VA, USA!</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11162,12 +11177,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Temporary</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11182,7 +11197,7 @@
       </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152312</t>
+          <t>https://www.roseint.com/Jobs/IT-Security-Analyst-VA-Richmond-Rose-International-Job-508744.html</t>
         </is>
       </c>
       <c r="J155" t="b">
@@ -11190,39 +11205,39 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-09-15T18:37:24+00:00</t>
+          <t>2026-10-06T17:36:06+00:00</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>f941cb0c25b86249f148</t>
+          <t>9c60da1902c9fb9e2a6e</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Business Analyst - Denver, CO | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Vulnerability Management Analyst, Security Scanning, Risk &amp; Automation - Richmond, VA | Hybrid, Temporary, Full-Time | Rose International Rose Home Rose News Contact Rose NEW JOB OPENING VULNERABILITY MANAGEMENT ANALYST, SECURITY SCANNING, RISK &amp; AUTOMATION IN RICHMOND, VA, USA! Date Posted: 10/06/2026 Hiring Organization: Rose International Position Number: 508744 Industry: Government/Staffing Job Title: Vulnerability Management Analyst, Security Scanning, Risk &amp; Automation Job Location: Richmond, VA, USA, 23219 Work Model: Hybrid Work Model Details: ON SITE: 2-3 days/week Shift: M-F 8am to 5pm Employment Type: Temporary FT/PT: Full-Time Estimated Duration (In months): 13 Min Hourly Rate($): 60.00 Max Hourly Rate($): 70.00 Must Have Skills/Attributes: Information Security, MS Office, SharePoint, Vulnerability, Written Communication Experience Desired: Experience and proficiency with Microsoft, SharePoint and Power BI (5 yrs), Information Security-related experience (5 yrs), Proven analytical and problem-solving abilities (5 yrs), Excellent verbal and written communication skills (5 yrs), Ability to work independently with minimal direction and as a team (5 yrs), Experience troubleshooting vulnerability scan tools and scan configurations (3 yrs), Software Vulnerability Management related experience (3 yrs) **C2C is not available** Job Description ***Only qualified Vulnerability Management Analyst candidates located near the Richmond, VA area will be considered due to the role requiring an onsite presence *** Required Skills: â¢ Information Security-related experience (5 Years) â¢ Software Vulnerability Management related experience (3 Years) â¢ Experience troubleshooting vulnerability scan tools and scan configurations (3 Years) â¢ Experience with automation supporting vulnerability assessment operations (3 Years) â¢ Experience supporting Information System Vulnerability Management (ISVM) scans and compliance activities (3 Years) â¢ Experience with API discovery and security scanning (3 Years) â¢ Experience and proficiency with Microsoft, SharePoint and Power BI (5 Years) â¢ Proven analytical and problem-solving abilities (5 Years) â¢ Excellent verbal and written communication skills (5 Years) â¢ Ability to work independently with minimal direction and as a team (5 Years) â¢ Highly motivated and self-directed (5 Years) About the role: The client is seeking a Risk and Vulnerability Analyst to support vulnerability assessment and risk analysis activities at the client. This role is responsible for conducting vulnerability scanning and analysis, supporting remediation efforts, supporting scanning operations, and helping improve enterprise visibility into security weaknesses and cyber risks. Responsibilities: â¢ Perform vulnerability assessments and assist security scanning across operating systems, databases, web applications, and enterprise infrastructure â¢ Analyze vulnerabilities and support development of remediation recommendations</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Business Analyst - Fort Washington, PA | Judge Group</t>
+          <t>Senior Business Systems Analyst - Agile, UAT &amp; Requirements</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Hoover, AL, 35244, USA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11232,7 +11247,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>TEMP TO HIRE</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11247,7 +11267,7 @@
       </c>
       <c r="I156" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148290</t>
+          <t>https://www.roseint.com/Jobs/Business-Systems-Analyst-AL-Hoover-Rose-International-Job-508770.html</t>
         </is>
       </c>
       <c r="J156" t="b">
@@ -11255,39 +11275,39 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-09-15T08:09:04+00:00</t>
+          <t>2026-10-07T02:48:05+00:00</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>8a6f124e5d536c8ef414</t>
+          <t>f7e50ce31d5a1e29cb55</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Required Education:â¢ Bachelorâs degree in business, IT, Computer Science, or a related fieldRequired Experience:â¢ 8+ years of Business Analysis, Systems Analysis, or related IT experienceâ¢ Strong experience with Agile Business Analysis and requirements gatheringâ¢ Hands-on experience with Acceptance Testing/UAT, including test scenarios, validation, defect identification, and resolutionâ¢ Strong experience creating Business Requirements Documents (BRDs) and functional requirementsâ¢ Experience analyzing business processes and translating business needs into technical solutionsâ¢ Strong communication, analytical, problem-solving, and organizational skillsâ¢ Proficiency with Microsoft Office SuitePreferred Experience:â¢ Banking or financial services experience, preferably mortgage/home lendingâ¢ Experience with Advanced SQL, relational database queries, and data validationâ¢ Experience with Empower Software, mortgage applications, or point-of-sale applicationsâ¢ Application support and troubleshooting experienceâ¢ Experience with Business Intelligence toolsâ¢ Experience with Agile and/or Waterfall methodologiesâ¢ Project management, testing, and API experienceJob Duties:â¢ Analyze business processes, requirements, and system needs to support technology initiativesâ¢ Partner with business and IT teams to gather, document, and validate requirementsâ¢ Develop and maintain BRDs, functional requirements, process flows, and acceptance criteriaâ¢ Perform Acceptance Testing/UAT, including test planning, execution, defect tracking, and validationâ¢ Analyze existing systems and recommend process or technology improvementsâ¢ Support application troubleshooting, data analysis, and issue resolutionâ¢ Develop SQL queries as needed for data validation and analysisâ¢ Coordinate with development, testing, and business teams through implementation and releasesâ¢ Support change management and communicate project issues, risks, and recommendationsâ¢ Participate in knowledge-transfer sessions and provide guidance to less-experienced team membersâ¢ May participate in after-hours/weekend on-call support**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>The Judge Group</t>
+          <t>Rose International</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Business Systems Analyst - Ann Arbor, MI | Judge Group</t>
+          <t>Senior IT Financial Analyst Technology Strategic Spend</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Chicago, IL, 60604, USA</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11297,7 +11317,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>TEMPORARY</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11312,7 +11337,7 @@
       </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155278</t>
+          <t>https://www.roseint.com/Jobs/Business-Analyst-IL-Chicago-Rose-International-Job-508698.html</t>
         </is>
       </c>
       <c r="J157" t="b">
@@ -11320,22 +11345,22 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>6e9d797ff52c7f07861b</t>
+          <t>432cf3df22781ff2c600</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Business Systems Analyst - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Education Requirements:- High School diploma or equivalentPreferred Education:- Bachelor's degreeRequired Skills for the Business Consultant:- 7 to 10 years of related experience with emphasis on project analysis and management reporting, planning, and analysis- Analytical and problem-solving skills required to evaluate financial results and projections across all financial statements- Effective written and verbal communication skills are necessary to present relevant information to senior management and business unit officers- Strong personal computer skills and analytics tools usage (Power BI, SQL, Excel, Word and PowerPoint) are required to perform analyses and communicate financial information- Strong accounting (GAAP), reporting and financial analysis usually acquired through an advanced degree program or related work experience is requiredBusiness Consultant Overview:The Business Consultant will join the Technology Strategic Spend Team to drive the delivery of information for decision making and various analysis for the Company's Technology Organization. This role is responsible for Technology-specific analysis (focused on strategy, labor, hardware, software, etc.), but will work closely to coordinate efforts among Technology, Finance and Procurement to drive the analyses into actionable efforts. Planning and analysis will need to be prepared and presented to many roles across the Company including Technology Leadership, engineers, project managers, finance managers, and procurement specialists, using Power Point, Excel, and/or Power BI / other analytical tools.Responsibilities:- Drive analysis and presentation material for IT Capital Expenditures in the Technology Portfolio, including consideration for strategic prioritization, developing budgets, forecasting, and variance analysis- Create Leadership-level analyses that inform on Technology usage and demand, financial impacts, contractual analysis, while considering potential- Build financial business cases for technology decisions (e.g. considerations for switching vendors, adding new products or capabilities, etc.)- Leverage data analytics tools (Power BI, SQL, Excel, etc.) to reach data-driven suggestions that drive strategic discussions and planning efforts with senior leadership- Work with finance and procurement to analyze and report on efforts for productivity and automation- Conduct and lead special projects and ad hoc requests to support the Technology function**Only those lawfully authorized to work in the designated country associated with the position will be considered.** **Please note that all Position start dates and duration are estimates and may be reduced or lengthened based upon a clientâs business needs and requirements.**</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11372,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Clinical Data Analyst - Mendota, MN | Judge Group</t>
+          <t>AI/ML Engineer - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11357,7 +11382,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -11377,7 +11402,7 @@
       </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152038</t>
+          <t>https://www.judge.com/jobs/details/1155561</t>
         </is>
       </c>
       <c r="J158" t="b">
@@ -11385,22 +11410,22 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-09-20T17:52:22+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>bfe14f70ddd5ffa00fc7</t>
+          <t>500619a71ed4996ff9fc</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Clinical Data Analyst - Mendota, MN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>AI/ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11437,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group</t>
+          <t>BUSINESS ANALYST - Boston, MA | Judge Group</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11442,7 +11467,7 @@
       </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151557</t>
+          <t>https://www.judge.com/jobs/details/1150574</t>
         </is>
       </c>
       <c r="J159" t="b">
@@ -11450,22 +11475,22 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-09-22T23:20:34+00:00</t>
+          <t>2026-10-04T16:16:11+00:00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>dbbd50ecf8c65363c2cf</t>
+          <t>9c4f002bb00026fbc1f5</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>BUSINESS ANALYST - Boston, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11502,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Data Analyst - Bridgeport, PA | Judge Group</t>
+          <t>Business Analyst - Denver, CO | Judge Group</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11507,7 +11532,7 @@
       </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1136576</t>
+          <t>https://www.judge.com/jobs/details/1152312</t>
         </is>
       </c>
       <c r="J160" t="b">
@@ -11515,22 +11540,22 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-15T18:37:24+00:00</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>c0ccf3207abc77a8082c</t>
+          <t>f941cb0c25b86249f148</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Data Analyst - Bridgeport, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Business Analyst - Denver, CO | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11567,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Data Analyst - Quincy, MA | Judge Group</t>
+          <t>Business Analyst - Fort Washington, PA | Judge Group</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11572,7 +11597,7 @@
       </c>
       <c r="I161" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1154548</t>
+          <t>https://www.judge.com/jobs/details/1148290</t>
         </is>
       </c>
       <c r="J161" t="b">
@@ -11580,22 +11605,22 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-10-05T02:26:52+00:00</t>
+          <t>2026-09-15T08:09:04+00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>a1a20ebd60e4b3f275ed</t>
+          <t>8a6f124e5d536c8ef414</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Data Analyst - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Business Analyst - Fort Washington, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11607,7 +11632,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Data Analyst - REMOTE | Judge Group</t>
+          <t>Business Systems Analyst - Ann Arbor, MI | Judge Group</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11617,7 +11642,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -11637,7 +11662,7 @@
       </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152271</t>
+          <t>https://www.judge.com/jobs/details/1155278</t>
         </is>
       </c>
       <c r="J162" t="b">
@@ -11645,22 +11670,22 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-09-15T18:37:24+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>b4f1d6b499090da09acc</t>
+          <t>6e9d797ff52c7f07861b</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Data Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Business Systems Analyst - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11697,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group</t>
+          <t>Clinical Data Analyst - Mendota, MN | Judge Group</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11702,7 +11727,7 @@
       </c>
       <c r="I163" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1153276</t>
+          <t>https://www.judge.com/jobs/details/1152038</t>
         </is>
       </c>
       <c r="J163" t="b">
@@ -11710,22 +11735,22 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-09-21T21:30:32+00:00</t>
+          <t>2026-09-20T17:52:22+00:00</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>4f3de9bf942013deebd3</t>
+          <t>bfe14f70ddd5ffa00fc7</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Clinical Data Analyst - Mendota, MN | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11762,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group</t>
+          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11747,7 +11772,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -11767,7 +11792,7 @@
       </c>
       <c r="I164" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1154009</t>
+          <t>https://www.judge.com/jobs/details/1151557</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -11775,22 +11800,22 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-09-22T23:20:34+00:00</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>9e672045d3da1c9cd4fa</t>
+          <t>dbbd50ecf8c65363c2cf</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Cloud Data Architect (multiple openings) - Huntington Park, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11827,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Data Engineer (I) - Portland, OR | Judge Group</t>
+          <t>Data Analyst - Bridgeport, PA | Judge Group</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11832,7 +11857,7 @@
       </c>
       <c r="I165" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155357</t>
+          <t>https://www.judge.com/jobs/details/1136576</t>
         </is>
       </c>
       <c r="J165" t="b">
@@ -11840,22 +11865,22 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>05652867cf4dfd4c52ee</t>
+          <t>c0ccf3207abc77a8082c</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Data Engineer (I) - Portland, OR | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst - Bridgeport, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11892,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Data Engineer III - Newport Beach, CA | Judge Group</t>
+          <t>Data Analyst - Quincy, MA | Judge Group</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11897,7 +11922,7 @@
       </c>
       <c r="I166" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1144820</t>
+          <t>https://www.judge.com/jobs/details/1154548</t>
         </is>
       </c>
       <c r="J166" t="b">
@@ -11905,22 +11930,22 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-09-21T08:22:47+00:00</t>
+          <t>2026-10-05T02:26:52+00:00</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>31d0b821f28109290adb</t>
+          <t>a1a20ebd60e4b3f275ed</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Data Engineer III - Newport Beach, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11957,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Charlotte, NC | Judge Group</t>
+          <t>Data Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11942,7 +11967,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -11962,7 +11987,7 @@
       </c>
       <c r="I167" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151679</t>
+          <t>https://www.judge.com/jobs/details/1152271</t>
         </is>
       </c>
       <c r="J167" t="b">
@@ -11970,22 +11995,22 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-10-06T01:45:24+00:00</t>
+          <t>2026-09-15T18:37:24+00:00</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>eedfda40feaf829fbd7b</t>
+          <t>b4f1d6b499090da09acc</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -11997,7 +12022,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Irving, TX | Judge Group</t>
+          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12027,7 +12052,7 @@
       </c>
       <c r="I168" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152840</t>
+          <t>https://www.judge.com/jobs/details/1153276</t>
         </is>
       </c>
       <c r="J168" t="b">
@@ -12035,22 +12060,22 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-09-23T23:20:48+00:00</t>
+          <t>2026-09-21T21:30:32+00:00</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>4dd97acc24963fd8d2f5</t>
+          <t>4f3de9bf942013deebd3</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Data Management Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Analyst / Business Systems Analyst - Westlake, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12087,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Data Product Manager - Sacramento, CA | Judge Group</t>
+          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -12072,7 +12097,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -12092,7 +12117,7 @@
       </c>
       <c r="I169" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1135310</t>
+          <t>https://www.judge.com/jobs/details/1154009</t>
         </is>
       </c>
       <c r="J169" t="b">
@@ -12100,22 +12125,22 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>a89c4407724b716bd195</t>
+          <t>9e672045d3da1c9cd4fa</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Data Product Manager - Sacramento, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Architect w/ Snowflake experience - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12152,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Data Scientist IV - Bridgewater, NJ | Judge Group</t>
+          <t>Data Engineer (I) - Portland, OR | Judge Group</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -12157,7 +12182,7 @@
       </c>
       <c r="I170" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1073820</t>
+          <t>https://www.judge.com/jobs/details/1155357</t>
         </is>
       </c>
       <c r="J170" t="b">
@@ -12170,17 +12195,17 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>c71947cbb7c82f6e5c8f</t>
+          <t>05652867cf4dfd4c52ee</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>Data Scientist IV - Bridgewater, NJ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Engineer (I) - Portland, OR | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12217,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Helpdesk Analyst - Malvern, PA | Judge Group</t>
+          <t>Data Engineer III - Newport Beach, CA | Judge Group</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -12222,7 +12247,7 @@
       </c>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151341</t>
+          <t>https://www.judge.com/jobs/details/1144820</t>
         </is>
       </c>
       <c r="J171" t="b">
@@ -12230,22 +12255,22 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-09-23T14:05:04+00:00</t>
+          <t>2026-09-21T08:22:47+00:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>ce53ed4f7e18a63c41f4</t>
+          <t>31d0b821f28109290adb</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Helpdesk Analyst - Malvern, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Engineer III - Newport Beach, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12257,7 +12282,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Intelligence Analyst - REMOTE | Judge Group</t>
+          <t>Data Management Analyst - Charlotte, NC | Judge Group</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -12267,7 +12292,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -12287,7 +12312,7 @@
       </c>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1156125</t>
+          <t>https://www.judge.com/jobs/details/1151679</t>
         </is>
       </c>
       <c r="J172" t="b">
@@ -12295,22 +12320,22 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-06T01:45:24+00:00</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>98e906dacebe4064f706</t>
+          <t>eedfda40feaf829fbd7b</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>Intelligence Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Management Analyst - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12347,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Java/AI Developer - Charlotte, NC | Judge Group</t>
+          <t>Data Management Analyst - Irving, TX | Judge Group</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -12352,7 +12377,7 @@
       </c>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155102</t>
+          <t>https://www.judge.com/jobs/details/1152840</t>
         </is>
       </c>
       <c r="J173" t="b">
@@ -12360,22 +12385,22 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-09-30T21:56:04+00:00</t>
+          <t>2026-09-23T23:20:48+00:00</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>7d7703068cb4d997eb79</t>
+          <t>4dd97acc24963fd8d2f5</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>Java/AI Developer - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Management Analyst - Irving, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12412,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Lead Conversational AI Engineer - REMOTE | Judge Group</t>
+          <t>Data Product Manager - Sacramento, CA | Judge Group</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -12397,7 +12422,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -12417,7 +12442,7 @@
       </c>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155963</t>
+          <t>https://www.judge.com/jobs/details/1135310</t>
         </is>
       </c>
       <c r="J174" t="b">
@@ -12425,22 +12450,22 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>b18cdff9142c9775c58b</t>
+          <t>a89c4407724b716bd195</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Lead Conversational AI Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Product Manager - Sacramento, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12477,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group</t>
+          <t>Data Scientist IV - Bridgewater, NJ | Judge Group</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -12482,7 +12507,7 @@
       </c>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1140197</t>
+          <t>https://www.judge.com/jobs/details/1073820</t>
         </is>
       </c>
       <c r="J175" t="b">
@@ -12490,22 +12515,22 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>94849065fcdb6cf16558</t>
+          <t>c71947cbb7c82f6e5c8f</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Data Scientist IV - Bridgewater, NJ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12517,7 +12542,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Operations Analyst - Malvern, PA | Judge Group</t>
+          <t>Helpdesk Analyst - Malvern, PA | Judge Group</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -12547,7 +12572,7 @@
       </c>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1108434</t>
+          <t>https://www.judge.com/jobs/details/1151341</t>
         </is>
       </c>
       <c r="J176" t="b">
@@ -12555,22 +12580,22 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-10-02T21:44:50+00:00</t>
+          <t>2026-09-23T14:05:04+00:00</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>702ba6c9be606809ccb2</t>
+          <t>ce53ed4f7e18a63c41f4</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>Operations Analyst - Malvern, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Helpdesk Analyst - Malvern, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12607,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Principal AI Engineer - Detroit, MI | Judge Group</t>
+          <t>Intelligence Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -12592,7 +12617,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -12612,7 +12637,7 @@
       </c>
       <c r="I177" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155074</t>
+          <t>https://www.judge.com/jobs/details/1156125</t>
         </is>
       </c>
       <c r="J177" t="b">
@@ -12620,22 +12645,22 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-09-30T17:14:31+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2355d30c8efa7830bced</t>
+          <t>98e906dacebe4064f706</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>Principal AI Engineer - Detroit, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Intelligence Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12672,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Scrum Master - Data Platform &amp; Data Ingestion - Phoenix, AZ | Judge Group</t>
+          <t>Java/AI Developer - Charlotte, NC | Judge Group</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -12677,7 +12702,7 @@
       </c>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155146</t>
+          <t>https://www.judge.com/jobs/details/1155102</t>
         </is>
       </c>
       <c r="J178" t="b">
@@ -12690,17 +12715,17 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>c68d23afbc67162c6ccc</t>
+          <t>7d7703068cb4d997eb79</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>Scrum Master - Data Platform &amp; Data Ingestion - Phoenix, AZ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Java/AI Developer - Charlotte, NC | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12737,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Senior .Net AI Developer - Austin, TX | Judge Group</t>
+          <t>Lead Conversational AI Engineer - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12722,7 +12747,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -12742,7 +12767,7 @@
       </c>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1151815</t>
+          <t>https://www.judge.com/jobs/details/1155963</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -12750,22 +12775,22 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-09-14T15:26:51+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>149cf6b5d7418a85b10e</t>
+          <t>b18cdff9142c9775c58b</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>Senior .Net AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Lead Conversational AI Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12802,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group</t>
+          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -12807,7 +12832,7 @@
       </c>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1136598</t>
+          <t>https://www.judge.com/jobs/details/1140197</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -12815,22 +12840,22 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-10-06T01:45:24+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>7d81f6ff26fd959356ed</t>
+          <t>94849065fcdb6cf16558</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>Senior AI Product Manager - Conshohocken, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Midlevel AI Developer - Ann Arbor, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12867,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Senior Business Analyst - Boston, MA | Judge Group</t>
+          <t>Operations Analyst - Malvern, PA | Judge Group</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12872,7 +12897,7 @@
       </c>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1154546</t>
+          <t>https://www.judge.com/jobs/details/1108434</t>
         </is>
       </c>
       <c r="J181" t="b">
@@ -12880,22 +12905,22 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-10-06T22:02:56+00:00</t>
+          <t>2026-10-02T21:44:50+00:00</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>454f5478c6a0c50b41e4</t>
+          <t>702ba6c9be606809ccb2</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>Senior Business Analyst - Boston, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Operations Analyst - Malvern, PA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12932,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group</t>
+          <t>Principal AI Engineer - Detroit, MI | Judge Group</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12937,7 +12962,7 @@
       </c>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1148934</t>
+          <t>https://www.judge.com/jobs/details/1155074</t>
         </is>
       </c>
       <c r="J182" t="b">
@@ -12945,22 +12970,22 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-09-18T22:59:13+00:00</t>
+          <t>2026-09-30T17:14:31+00:00</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>07bfae59552b3c821572</t>
+          <t>2355d30c8efa7830bced</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Principal AI Engineer - Detroit, MI | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12997,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Senior GEN AI Engineer - Plano, TX | Judge Group</t>
+          <t>Scrum Master - Data Platform &amp; Data Ingestion - Phoenix, AZ | Judge Group</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -13002,7 +13027,7 @@
       </c>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1154729</t>
+          <t>https://www.judge.com/jobs/details/1155146</t>
         </is>
       </c>
       <c r="J183" t="b">
@@ -13015,17 +13040,17 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>6bf83cf7a5d0f827095f</t>
+          <t>c68d23afbc67162c6ccc</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>Senior GEN AI Engineer - Plano, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Scrum Master - Data Platform &amp; Data Ingestion - Phoenix, AZ | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13062,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group</t>
+          <t>Senior .Net AI Developer - Austin, TX | Judge Group</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -13067,7 +13092,7 @@
       </c>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1152660</t>
+          <t>https://www.judge.com/jobs/details/1151815</t>
         </is>
       </c>
       <c r="J184" t="b">
@@ -13075,22 +13100,22 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-09-16T23:20:04+00:00</t>
+          <t>2026-09-14T15:26:51+00:00</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2cc2da9382ae114b4977</t>
+          <t>149cf6b5d7418a85b10e</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior .Net AI Developer - Austin, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -13102,7 +13127,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Sr. AI / ML Engineer - REMOTE | Judge Group</t>
+          <t>Senior Business Analyst - Boston, MA | Judge Group</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -13112,7 +13137,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -13132,7 +13157,7 @@
       </c>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1146485</t>
+          <t>https://www.judge.com/jobs/details/1154546</t>
         </is>
       </c>
       <c r="J185" t="b">
@@ -13140,22 +13165,22 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-10-06T22:02:56+00:00</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>c8fc83cf9a9fbd548fd2</t>
+          <t>454f5478c6a0c50b41e4</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>Sr. AI / ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior Business Analyst - Boston, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -13167,7 +13192,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group</t>
+          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -13197,7 +13222,7 @@
       </c>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1147907</t>
+          <t>https://www.judge.com/jobs/details/1148934</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -13205,22 +13230,22 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-09-05T22:30:10+00:00</t>
+          <t>2026-09-18T22:59:13+00:00</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>94c82ba3d6ab78504fcf</t>
+          <t>07bfae59552b3c821572</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior Cloud Data Engineer - Quincy, MA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13257,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Tapestry Configuration Analyst - REMOTE | Judge Group</t>
+          <t>Senior GEN AI Engineer - Plano, TX | Judge Group</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -13242,7 +13267,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -13262,7 +13287,7 @@
       </c>
       <c r="I187" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1099718</t>
+          <t>https://www.judge.com/jobs/details/1154729</t>
         </is>
       </c>
       <c r="J187" t="b">
@@ -13270,22 +13295,22 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-10-05T02:26:52+00:00</t>
+          <t>2026-09-30T21:56:04+00:00</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>867e313f74ad45486e73</t>
+          <t>6bf83cf7a5d0f827095f</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>Tapestry Configuration Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Senior GEN AI Engineer - Plano, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13322,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Tax Analyst - Lake Mary, FL | Judge Group</t>
+          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -13327,7 +13352,7 @@
       </c>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>https://www.judge.com/jobs/details/1155540</t>
+          <t>https://www.judge.com/jobs/details/1152660</t>
         </is>
       </c>
       <c r="J188" t="b">
@@ -13335,34 +13360,34 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-09-16T23:20:04+00:00</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>c1f19da46a8f861b7cfe</t>
+          <t>2cc2da9382ae114b4977</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>Tax Analyst - Lake Mary, FL | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
+          <t>Sr Applied AI Engineer - Dallas, TX | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Administrative Assistant/Entry Level Business Analyst</t>
+          <t>Sr. AI / ML Engineer - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -13372,17 +13397,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2015-10-20</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -13392,12 +13412,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86114043-administrative-assistant-entry-level-business-analyst?oga=true</t>
+          <t>https://www.judge.com/jobs/details/1146485</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -13405,34 +13425,34 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>0824e44805cde39b3822</t>
+          <t>c8fc83cf9a9fbd548fd2</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Under the direction of supervisors, will be responsible for providing administrative support, as well as general clerical/secretarial support to the team. Ability to act as a team player, strong interpersonal skills, and willingness to multi-task and prioritize are critical requirements. Skills/Knowledge Required: MUST have - advanced skills: MS Outlook, Visio, Excel, Word, PowerPoint MUST have - experience with SOW contracts MUST have - IProcurement (Oracle) experience (2-4 years) Ability to work independently, while acting as a team player, as certain responsibilities will be shared. Willingness to work in a fast paced environment where individual initiative and accountability to the team are required. Strong interpersonal skills Ability to multi-task and prioritize. Excellent written and oral communication skills. "}, "qualifications": {"title": "Qualifications", "text": " Responsibilities will include, but are not limited to, the following: Providing administrative support to supervisors, including: Managing schedules, meetings, travel arrangements, and expense reports. Offering general secretarial/clerical support to supervisors. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. Implementing/organizing/maintaining files, records, and databases. Updating invoice tracking for supervisors. Telephone coverage, as assigned. Providing shared support to department Managers. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, kushal kumar Contact: +1 (201)932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>Sr. AI / ML Engineer - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -13447,12 +13467,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2016-01-13</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -13462,12 +13477,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I190" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/88443359-application-support-analyst?oga=true</t>
+          <t>https://www.judge.com/jobs/details/1147907</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -13475,34 +13490,34 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-09-05T22:30:10+00:00</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>4299b8fc9cc8be3bfc33</t>
+          <t>94c82ba3d6ab78504fcf</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Key Responsibilities : • Flexible to work between 12pm to 9pm, Sunday to Friday (5 days a week) • Fully responsible for delivery of key feeds within the agreed SLA • Monitoring, Trouble shooting and Supporting the day to day activities • Use business and application knowledge to investigate issues raised and assist in the production of Incident reports, which form part of the shift handover • This role is to be the interface between users and IT project • Adherence to documented procedural standards • Escalate issues which cannot be resolved by the Analyst, in a timely manner • Have a strong Customer Focus in order to provide a professional support service to both internal and external cliental • To assist with the streamlining of the support area i.e. suggesting where procedures can be improved without the introduction of risk • Maintain Knowledge base and share experience with support team members • Should take ownership of any tasks/issue handled by the team (even when other teams involved) "}, "qualifications": {"title": "Qualifications", "text": " Qualifications / Technical knowledge &amp; Experience required : Qualifications: • Graduate in Computer Science discipline Technical Skills: • SQL knowledge (be able to read/write complex queries with joint between table, knowledge on optimizing SQL statements) • Unix (be comfortable working on a Unix environment) "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal kumar 201-932-1539 "}}</t>
+          <t>Sr. Solutions Analyst (Agentic AI Architecture) - Elk Grove, CA | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Applications System Analyst</t>
+          <t>Tapestry Configuration Analyst - REMOTE | Judge Group</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -13512,17 +13527,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2017-02-01</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -13532,12 +13542,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107273359-applications-system-analyst?oga=true</t>
+          <t>https://www.judge.com/jobs/details/1099718</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -13545,34 +13555,34 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-10-05T02:26:52+00:00</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>e8f6fd68f0c8963a7a1b</t>
+          <t>867e313f74ad45486e73</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " • Reviews, analyzes, and modifies programming systems including encoding, testing, debugging and installing to support an organization's application systems. • Consults with users to identify current operating procedures and to clarify program objectives. • May be expected to write documentation to describe program development, logic, coding, and corrections. • Writes manual for users to describe installation and operating procedures. • May require a bachelor's degree in a related area and 2-5 years of experience in the field or in a related area. • Familiar with relational databases and client-server concepts. • Relies on limited experience and judgment to plan and accomplish goals. • Performs a variety of tasks. Works under general supervision; typically reports to a project leader or manager. • A certain degree of creativity and latitude is required. "}, "qualifications": {"title": "Qualifications", "text": " NOTE: Need Google Analytics "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
+          <t>Tapestry Configuration Analyst - REMOTE | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>US Tech Solutions</t>
+          <t>The Judge Group</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Business Analyst/Qlikeview Developer</t>
+          <t>Tax Analyst - Lake Mary, FL | Judge Group</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13587,12 +13597,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -13602,12 +13607,12 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>SmartRecruiters API</t>
+          <t>HTTP+Playwright</t>
         </is>
       </c>
       <c r="I192" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86505098-business-analyst-qlikeview-developer?oga=true</t>
+          <t>https://www.judge.com/jobs/details/1155540</t>
         </is>
       </c>
       <c r="J192" t="b">
@@ -13615,22 +13620,22 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-07-30T00:33:09+00:00</t>
+          <t>2026-10-05T20:07:45+00:00</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>9247a1e706741e8b0544</t>
+          <t>c1f19da46a8f861b7cfe</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " SPECIFIC SKILLS REQUIRED Superior knowledge of standard database tools, especially SQL Query writing, including relational and multidimensional database skills using SQL, Oracle, Sybase, MS Access. Must have at least 5-7 years’ experience in building and managing databases. 3-5 years’ experience with implementing and managing BI tools like Cognos, Business Objects, Microstrategy etc. Experience in developing and designing interactive dash boards and query, reporting, and analysis software, including data visualization programs like QlikTech, Tableau, Microsoft etc. QlikView Designer and Developer, User Interface Design, VBScript, Agile Development. 2-3 yrs experience designing &amp; developing query &amp; reports using in-memory data visualization programs Qlikview or Tableau is required. Experience in gathering requirement, server installation, migration, security management. Experience in developing QlikView and QVD files. Experience in setting up and management of QlikView server providing permission to users The Qlikview developer will be responsible for developing and documenting the Qlikview solution according to specified business requirements. The Qlik Developer will be responsible to build the data model and perform appropriate extract-transformation load (ETL) in support of the business requirements. "}, "qualifications": {"title": "Qualifications", "text": " EXPERIENCE REQUIRED Master’s degree in Computer Science, Information Technology or Information Sciences or Technical Discipline or equivalent 5-7 years of experience in business analytics; close work with sales analysis or providing tools to sales teams Database and SQL experience required. Excellent Analytical Skills are required. Experience in building dashboards and implementing businesses solutions. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>Tax Analyst - Lake Mary, FL | Judge Group Skip to content Judge Group Menu Open navigation About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Resources Find a Job Contact Us Search Search Search Judge.com Submit search query Search Close search field Close Close navigation Close By providing your phone number, you consent to: (1) receive automated text messages and calls from the Judge Group, Inc. and its affiliates (collectively “Judge”) to such phone number regarding job opportunities, your job application, and for other related purposes. Message &amp; data rates apply and message frequency may vary. Consistent with Judge's Privacy Policy , information obtained from your consent will not be shared with third parties for marketing/promotional purposes. Reply STOP to opt out of receiving telephone calls and text messages from Judge and HELP for help. Apply now First Name Last Name Email Phone Number Country We do not accept applications from the EU at this time. Please select United States Canada Street Address City State/Region Zip / Postal Code Upload your resume * Accepted file types: pdf, doc, docx, rtf, odt, or txt. Max size 10 MB Choose file No file chosen Related Postings Judge Group About Judge IT Consulting Talent, Staffing, &amp; Executive Search Learning Solutions Industries We Serve Find a Job Resources Timesheets TIC Privacy &amp; Cookies Policy Sitemap Contact Us Facebook X TikTok LinkedIn Instagram Email About Judge Leadership Internal Judge Careers Awards Locations Environmental, Social, and Governance Technology Partners Job Seekers IT Consulting Judge Copilot Adoption Studio Adobe Experience Manager Services Cloud Migration Infrastructure &amp; Wireless Strategic Roadmaps &amp; Delivery IT &amp; Business Transformation View more Talent, Staffing, &amp; Executive Search IT Staffing Healthcare Staffing Direct Hire Engineering Staffing PMaaS TalentOps Executive Search Judge Creative Studios View more Learning Solutions AI Corporate Training &amp; Workforce Upskilling Organizational Change Management Custom Learning Solutions Learning &amp; Development Staffing Facilitated Learning Events &amp; Bootcamps View more Industries We Serve Aerospace &amp; Defense Banking, Financial Services &amp; Insurance Government Healthcare Life Sciences Manufacturing &amp; Supply Chain Technology, Communications, and Media View more Privacy &amp; Cookie Policy Timesheets TIC EEO CCPA Accessibility Sitemap Copyright © 2026 The Judge Group Inc. All Rights Reserved. Do Not Sell or Share My Personal Information</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13647,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Business analyst</t>
+          <t>Administrative Assistant/Entry Level Business Analyst</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -13662,7 +13667,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2015-10-23</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -13677,7 +13682,7 @@
       </c>
       <c r="I193" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86239602-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86114043-administrative-assistant-entry-level-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -13690,17 +13695,17 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>62f9684d4a4312d88e6f</t>
+          <t>0824e44805cde39b3822</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Under the direction of supervisors, will be responsible for providing administrative support, as well as general clerical/secretarial support to the team. Ability to act as a team player, strong interpersonal skills, and willingness to multi-task and prioritize are critical requirements. Skills/Knowledge Required: MUST have - advanced skills: MS Outlook, Visio, Excel, Word, PowerPoint MUST have - experience with SOW contracts MUST have - IProcurement (Oracle) experience (2-4 years) Ability to work independently, while acting as a team player, as certain responsibilities will be shared. Willingness to work in a fast paced environment where individual initiative and accountability to the team are required. Strong interpersonal skills Ability to multi-task and prioritize. Excellent written and oral communication skills. "}, "qualifications": {"title": "Qualifications", "text": " Responsibilities will include, but are not limited to, the following: Providing administrative support to supervisors, including: Managing schedules, meetings, travel arrangements, and expense reports. Offering general secretarial/clerical support to supervisors. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. Implementing/organizing/maintaining files, records, and databases. Updating invoice tracking for supervisors. Telephone coverage, as assigned. Providing shared support to department Managers. Including: opening and sorting mail, faxing documents, making copies and maintaining supplies. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, kushal kumar Contact: +1 (201)932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -13712,7 +13717,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Business analyst</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -13727,12 +13732,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
+          <t>2016-01-13</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -13747,7 +13752,7 @@
       </c>
       <c r="I194" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85863294-business-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/88443359-application-support-analyst?oga=true</t>
         </is>
       </c>
       <c r="J194" t="b">
@@ -13760,17 +13765,17 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>cc841923fe467641e8cf</t>
+          <t>4299b8fc9cc8be3bfc33</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Key Responsibilities : • Flexible to work between 12pm to 9pm, Sunday to Friday (5 days a week) • Fully responsible for delivery of key feeds within the agreed SLA • Monitoring, Trouble shooting and Supporting the day to day activities • Use business and application knowledge to investigate issues raised and assist in the production of Incident reports, which form part of the shift handover • This role is to be the interface between users and IT project • Adherence to documented procedural standards • Escalate issues which cannot be resolved by the Analyst, in a timely manner • Have a strong Customer Focus in order to provide a professional support service to both internal and external cliental • To assist with the streamlining of the support area i.e. suggesting where procedures can be improved without the introduction of risk • Maintain Knowledge base and share experience with support team members • Should take ownership of any tasks/issue handled by the team (even when other teams involved) "}, "qualifications": {"title": "Qualifications", "text": " Qualifications / Technical knowledge &amp; Experience required : Qualifications: • Graduate in Computer Science discipline Technical Skills: • SQL knowledge (be able to read/write complex queries with joint between table, knowledge on optimizing SQL statements) • Unix (be comfortable working on a Unix environment) "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13787,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Computer Vision Algorithm Engineer</t>
+          <t>Applications System Analyst</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -13802,7 +13807,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2016-10-19</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -13817,7 +13822,7 @@
       </c>
       <c r="I195" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100672079-computer-vision-algorithm-engineer?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107273359-applications-system-analyst?oga=true</t>
         </is>
       </c>
       <c r="J195" t="b">
@@ -13830,17 +13835,17 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>17b90594009fe99d1583</t>
+          <t>e8f6fd68f0c8963a7a1b</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Description and Requirements: Responsibilities/Descriptions: The candidate is expected to play an active role in computer vision technology development and implementation. Under the supervision of a senior scientist/researcher or project leader to conduct R&amp;D work in the areas of advanced computer vision/media processing technology. Qualifications / Requirements: Ph.D or Master degree in relevant discipline/field, such as EE or CS. * Strong programming skills in C / C++ for both Windows and Linux is a must * Ample hands-on experience with OpenCV is a strong plus * High proficiency and good experience with Android programming is a big plus. * Good programming skills in Java and Python is also a plus * 3+ years algorithm R&amp;D experiences in the areas of computer vision, information retrieval, machine learning, media processing, and related fields with proven track record. * Good communication skills, both verbal and written "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Saikat Ghosh Senior Technical Recruiter Desk: (201) 524 9600 Ext. 7452 Direct: (201) 613 5178 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " • Reviews, analyzes, and modifies programming systems including encoding, testing, debugging and installing to support an organization's application systems. • Consults with users to identify current operating procedures and to clarify program objectives. • May be expected to write documentation to describe program development, logic, coding, and corrections. • Writes manual for users to describe installation and operating procedures. • May require a bachelor's degree in a related area and 2-5 years of experience in the field or in a related area. • Familiar with relational databases and client-server concepts. • Relies on limited experience and judgment to plan and accomplish goals. • Performs a variety of tasks. Works under general supervision; typically reports to a project leader or manager. • A certain degree of creativity and latitude is required. "}, "qualifications": {"title": "Qualifications", "text": " NOTE: Need Google Analytics "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13857,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Business Analyst/Qlikeview Developer</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13867,12 +13872,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>{"id": "permanent", "label": "Full-time"}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2017-02-07</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -13887,7 +13892,7 @@
       </c>
       <c r="I196" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107710098-data-architect?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86505098-business-analyst-qlikeview-developer?oga=true</t>
         </is>
       </c>
       <c r="J196" t="b">
@@ -13900,17 +13905,17 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>02e4361c9124b313e587</t>
+          <t>9247a1e706741e8b0544</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " RESPONSIBILITIES: • Translating customers business &amp; technical requirements into a data solution architecture in alignment with ADP's overall architectural directions and strategies. • A Technical leader who drives the customers’ transformation to modern Data Architecture &amp; store technologies such as NoSQL. • Develops a deep understanding of the current/future technical challenges of customers, and based on that understanding, formulates an aspirational application architecture and transformation roadmap. • Translates complex Data store centric requirements and use cases to technical artifacts such as application specifications, data models and architectural blueprints. • Identify and implement Performance improvements and track performance metrics. • Establish and drive standards (performance, security) across products. • Develop strategies for data acquisition; achieve recovery, and implementation of database. • Should work with Database Administrators and Data Analysts to ensure they can easily use and access data. • Maintain database integrity and plan for natural disaster and cyber-attacks. • Making use of code and data the architect should turn it into logical patterns that can be used for analysis purpose. • Deliver convincing and persuasive presentations to both technical and business teams. • As the custodian of Common Data Model will provide the requisite standards and governance around the canonical model. "}, "qualifications": {"title": "Qualifications", "text": " QUALIFICATIONS REQUIRED: • Excellent knowledge of Computation Theory, Data Structures, Algorithms, Design Patterns and Data Modelling techniques. • Excellent communication, articulation and presentation skills. • Experience building large scale distributed data processing systems/applications. • Strong foundational knowledge and experience with distributed systems and computing systems in general. • Deep understanding of various ETL/ELT tools is required. • Skilled at logical and physical data modeling, data policies, warehousing, strategy and query languages. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " SPECIFIC SKILLS REQUIRED Superior knowledge of standard database tools, especially SQL Query writing, including relational and multidimensional database skills using SQL, Oracle, Sybase, MS Access. Must have at least 5-7 years’ experience in building and managing databases. 3-5 years’ experience with implementing and managing BI tools like Cognos, Business Objects, Microstrategy etc. Experience in developing and designing interactive dash boards and query, reporting, and analysis software, including data visualization programs like QlikTech, Tableau, Microsoft etc. QlikView Designer and Developer, User Interface Design, VBScript, Agile Development. 2-3 yrs experience designing &amp; developing query &amp; reports using in-memory data visualization programs Qlikview or Tableau is required. Experience in gathering requirement, server installation, migration, security management. Experience in developing QlikView and QVD files. Experience in setting up and management of QlikView server providing permission to users The Qlikview developer will be responsible for developing and documenting the Qlikview solution according to specified business requirements. The Qlik Developer will be responsible to build the data model and perform appropriate extract-transformation load (ETL) in support of the business requirements. "}, "qualifications": {"title": "Qualifications", "text": " EXPERIENCE REQUIRED Master’s degree in Computer Science, Information Technology or Information Sciences or Technical Discipline or equivalent 5-7 years of experience in business analytics; close work with sales analysis or providing tools to sales teams Database and SQL experience required. Excellent Analytical Skills are required. Experience in building dashboards and implementing businesses solutions. "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13927,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Data Migration Analyst</t>
+          <t>Business analyst</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -13942,7 +13947,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2016-10-25</t>
+          <t>2015-10-23</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -13957,7 +13962,7 @@
       </c>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100992416-data-migration-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86239602-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J197" t="b">
@@ -13970,17 +13975,17 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2b87177fd8a91d1b3c10</t>
+          <t>62f9684d4a4312d88e6f</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": ""}, "qualifications": {"title": "Qualifications", "text": " Required qualifications: • At least 5 years of IT related experience • 3-5 years working with databases with demonstrated expertise in SQL, PL/SQL, Oracle 11, ETL tools, Data conversion, Data De-duplication, Data Cleansing methodologies • Be able to build SQL data queries • Demonstrated experience in analyzing data sets and Effective at understanding a problem and developing one or many approaches to solving the problem. • Assist in designing, planning and managing the data migration process. • Work with subject matter experts and project team to identify, define, collate, document and communicate the data migration requirements. • Experience in Data Migration methodologies • Highly effective working in a team, as well as working independently. • Perform source system data analysis in order to manage source to target data mapping. • Perform migration and testing of static data and transaction data from one core system to another. • Perform data migration audit, reconciliation and exception reporting. • Assist with the identification of trends or patterns in complex data sets • Filter and “clean” data, and review reports, printouts, and performance indicators Create Test Plans and Test Cases for all scenario types and execute. (i.e. positive, negative testing, boundary) Verify requirement traceability from System Requirements through test cases and defects Ensure that testing activities will allow applications to meet business requirements and systems goals, fulfil end-user requirements, and identify and resolve systems issues Work with the developers to understand the technical requirement/design being built in a project Validate Test Preparation of environments and verify all teams are aligned with what needs to occur to build/prepare the test environments Coordinate, track and report regularly on execution of system testing Verify defects are effectively recorded, communicated and understood Analyze and ensure test results and changes/defect are reflected in the test case and test cases are updated appropriately based on resolution Identify and recommend process improvements as necessary Excellent written and oral communication skills Excellent listening and interpersonal skills (includes</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -13992,7 +13997,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Data Security analyst</t>
+          <t>Business analyst</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -14012,7 +14017,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2016-10-20</t>
+          <t>2015-10-09</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14027,7 +14032,7 @@
       </c>
       <c r="I198" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100745719-data-security-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85863294-business-analyst?oga=true</t>
         </is>
       </c>
       <c r="J198" t="b">
@@ -14040,17 +14045,17 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>bce9bd6942bda16e1d08</t>
+          <t>cc841923fe467641e8cf</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Scope/Responsibilities/Duties: • 0-2 years general experience, bachelor’ s degree or equivalent combo of education/experience; • Some experience in desired tech area; position functions with high level of supervision; • Assesses security and/or compliance of university systems; responsible for assessing, monitoring and analyzing data, identifying security, risk or compliance issues and/or events • Leveraging job aids for common issues or incidents • Demonstrated ability to work in a team, attention to detail, solid written communications and some technology experience • To perform system based risk assessments. • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "qualifications": {"title": "Qualifications", "text": " • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards, Kushal Kumar Talent Acquisition Specialist Tel: 201-932-1539 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Experience: 3-5 years professional experience. Identify, communicate, and manage risks associated with projects. Identify business or customer requirements and information technology alternatives. Create project plans for information technology development and testing. Translate requirements into new information technology project specifications "}, "qualifications": {"title": "Qualifications", "text": " Education: Bachelor's Degree or equivalent unless otherwise specified "}, "additionalInformation": {"title": "Additional Information", "text": " Regards Kushal kumar Contact: +1 201-932-1539 +1 201-524-9600 ext: 7941 "}}</t>
         </is>
       </c>
     </row>
@@ -14062,7 +14067,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EDI Programmer Analyst &amp; Manager</t>
+          <t>Computer Vision Algorithm Engineer</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -14077,12 +14082,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2016-06-29</t>
+          <t>2016-10-19</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14097,7 +14102,7 @@
       </c>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93892950-edi-programmer-analyst-manager?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100672079-computer-vision-algorithm-engineer?oga=true</t>
         </is>
       </c>
       <c r="J199" t="b">
@@ -14110,17 +14115,17 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>36926768d7d1374bbba5</t>
+          <t>17b90594009fe99d1583</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: EDI Programmer Analyst &amp; Manager Duration: Permanent/Full Time Location: San Francisco, CA Interview: Phone &amp; F2F(But can do Skype) Locals are highly preferred "}, "qualifications": {"title": "Qualifications", "text": " Proficient in: · BizTalk · EDI application mapping techniques · HIPAA ASC X12 transaction sets for healthcare (834, 837, 277, 835, 997/9, 270/1, 276/7, Proprietary Auths) · HIPAA 5010 · HIPAA security policies and procedures. · .NET &amp; SQL · Systems implementation "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Chandra Kumar Tel: 201-549-2655 Desk: (201) 524 9600 Ext: 7794 chandra at ustechsolutionsinc dot com "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Description and Requirements: Responsibilities/Descriptions: The candidate is expected to play an active role in computer vision technology development and implementation. Under the supervision of a senior scientist/researcher or project leader to conduct R&amp;D work in the areas of advanced computer vision/media processing technology. Qualifications / Requirements: Ph.D or Master degree in relevant discipline/field, such as EE or CS. * Strong programming skills in C / C++ for both Windows and Linux is a must * Ample hands-on experience with OpenCV is a strong plus * High proficiency and good experience with Android programming is a big plus. * Good programming skills in Java and Python is also a plus * 3+ years algorithm R&amp;D experiences in the areas of computer vision, information retrieval, machine learning, media processing, and related fields with proven track record. * Good communication skills, both verbal and written "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Saikat Ghosh Senior Technical Recruiter Desk: (201) 524 9600 Ext. 7452 Direct: (201) 613 5178 "}}</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14137,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EFT Processing Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -14147,12 +14152,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "permanent", "label": "Full-time"}</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2015-12-09</t>
+          <t>2017-02-07</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14167,7 +14172,7 @@
       </c>
       <c r="I200" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87772674-eft-processing-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/107710098-data-architect?oga=true</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -14180,17 +14185,17 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>ff66976e897c4a7cacad</t>
+          <t>02e4361c9124b313e587</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Title: EFT Processing Analyst Duration: Approx. 3 months Location: Austin, TX Responsibilities: Perform ACH operational functions within required deadlines and NACHA compliance. Process received ACH exception-items and disputes, including DNE s and WSUD s. Originate R10 s, NOC s and other manual return items. Gather verifications for deposit-exceptions for cardholder account management. Reply to garnishments, liens, and levies in a timely, accurate, and compliant manner. Take phone calls and respond to inquiries from customers, banks, government entities, and internal departments. Provide consistent, high-quality customer service that meets or exceeds established standards. Maintain spreadsheets related to credit-adjustment activity, and create regular summaries and reports on departmental activities using Access, Excel, and Word. Recommend improvements that result in more efficient procedures. Understand and adhere to strict compliance and regulatory requirements. Comfortably work within a defined attendance and punctuality policy that is designed to help our customers. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Sam Contact : 201-613-5164 "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " RESPONSIBILITIES: • Translating customers business &amp; technical requirements into a data solution architecture in alignment with ADP's overall architectural directions and strategies. • A Technical leader who drives the customers’ transformation to modern Data Architecture &amp; store technologies such as NoSQL. • Develops a deep understanding of the current/future technical challenges of customers, and based on that understanding, formulates an aspirational application architecture and transformation roadmap. • Translates complex Data store centric requirements and use cases to technical artifacts such as application specifications, data models and architectural blueprints. • Identify and implement Performance improvements and track performance metrics. • Establish and drive standards (performance, security) across products. • Develop strategies for data acquisition; achieve recovery, and implementation of database. • Should work with Database Administrators and Data Analysts to ensure they can easily use and access data. • Maintain database integrity and plan for natural disaster and cyber-attacks. • Making use of code and data the architect should turn it into logical patterns that can be used for analysis purpose. • Deliver convincing and persuasive presentations to both technical and business teams. • As the custodian of Common Data Model will provide the requisite standards and governance around the canonical model. "}, "qualifications": {"title": "Qualifications", "text": " QUALIFICATIONS REQUIRED: • Excellent knowledge of Computation Theory, Data Structures, Algorithms, Design Patterns and Data Modelling techniques. • Excellent communication, articulation and presentation skills. • Experience building large scale distributed data processing systems/applications. • Strong foundational knowledge and experience with distributed systems and computing systems in general. • Deep understanding of various ETL/ELT tools is required. • Skilled at logical and physical data modeling, data policies, warehousing, strategy and query languages. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Kushal Kumar 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14207,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MDM Data Analyst I</t>
+          <t>Data Migration Analyst</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -14222,7 +14227,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2016-12-06</t>
+          <t>2016-10-25</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -14237,7 +14242,7 @@
       </c>
       <c r="I201" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/103472117-mdm-data-analyst-i?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100992416-data-migration-analyst?oga=true</t>
         </is>
       </c>
       <c r="J201" t="b">
@@ -14250,17 +14255,17 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>3a12d7e1695e93f24087</t>
+          <t>2b87177fd8a91d1b3c10</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Title: MDM Data Analyst I Location: Lexington, MA, 02421 Duration: 12-+ Months Description: The MDM Data Analyst reports to the MDM/Data Governance Manager and is responsible for the end-to-end master data customer and product maintenance processes within U.S. Commercial Operations. This person is responsible for MDM data quality, processes and business rules. He/she will be responsible for working with the various business area leads to ensure cross-team processes are efficient and master data is consistent, accurate and compliant across applications. % of Time Job Function and Description 35% Data Steward Team Management • Responsible for daily MDM data steward activities • Perform ad hoc customer and product master data requests • Participate in MDM UAT testing 45% Operational Excellence • Responsible for defining MDM Standard Operating Procedures (SOPs) and Work Instructions (WIs) • Responsible for ensuring the accuracy and completeness of customer and product master data • Responsible for understanding the end-to-end processes for maintaining customer master and product data across business areas • Responsible for customer and product data harmonization across multiple sources 20% Cross-Functional Collaboration • Work closely with Commercial Ops Governance team and adhere to implemented principles and process standards • Work with IT to coordinate and define business user impacts of MDM application changes including resolving issues and planning for enhancements and upgrades • Assist in the definition of master data sourcing and services strategies including the evaluation of third party data providers and services under the direction of the MDM/Data Governance Manager Education and Experience Requirements • Bachelor's degree in the field of computer science, information technology, engineering or business administration, Management Information Systems, Finance, Sciences or related area or equivalent experience • Advanced Degree preferred • 1-3 years of work experience, Pharma related preferred • Informatica MDM/IDD experience preferred • One full cycle of an MDM implementation preferred • Has basic knowledge of Pharmaceutical Commercial business environment/operations Key Skills, Abilities, and Competencies • Establishes good working relat</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": ""}, "qualifications": {"title": "Qualifications", "text": " Required qualifications: • At least 5 years of IT related experience • 3-5 years working with databases with demonstrated expertise in SQL, PL/SQL, Oracle 11, ETL tools, Data conversion, Data De-duplication, Data Cleansing methodologies • Be able to build SQL data queries • Demonstrated experience in analyzing data sets and Effective at understanding a problem and developing one or many approaches to solving the problem. • Assist in designing, planning and managing the data migration process. • Work with subject matter experts and project team to identify, define, collate, document and communicate the data migration requirements. • Experience in Data Migration methodologies • Highly effective working in a team, as well as working independently. • Perform source system data analysis in order to manage source to target data mapping. • Perform migration and testing of static data and transaction data from one core system to another. • Perform data migration audit, reconciliation and exception reporting. • Assist with the identification of trends or patterns in complex data sets • Filter and “clean” data, and review reports, printouts, and performance indicators Create Test Plans and Test Cases for all scenario types and execute. (i.e. positive, negative testing, boundary) Verify requirement traceability from System Requirements through test cases and defects Ensure that testing activities will allow applications to meet business requirements and systems goals, fulfil end-user requirements, and identify and resolve systems issues Work with the developers to understand the technical requirement/design being built in a project Validate Test Preparation of environments and verify all teams are aligned with what needs to occur to build/prepare the test environments Coordinate, track and report regularly on execution of system testing Verify defects are effectively recorded, communicated and understood Analyze and ensure test results and changes/defect are reflected in the test case and test cases are updated appropriately based on resolution Identify and recommend process improvements as necessary Excellent written and oral communication skills Excellent listening and interpersonal skills (includes</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14277,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Mobile Automation Test Analyst</t>
+          <t>Data Security analyst</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -14287,12 +14292,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2016-06-08</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -14307,7 +14312,7 @@
       </c>
       <c r="I202" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93157465-mobile-automation-test-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/100745719-data-security-analyst?oga=true</t>
         </is>
       </c>
       <c r="J202" t="b">
@@ -14320,17 +14325,17 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>80c10598e102ec2e4da0</t>
+          <t>bce9bd6942bda16e1d08</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: Mobile Automation Test Analyst Duration: 6 – 12 + Months Location: Anoka, MN Interview: Phone &amp; F2F Mandate "}, "qualifications": {"title": "Qualifications", "text": " • 8+ years of experience in software automation testing, with 3-4+ years of experience in UFT/selenium automation experience • Expert in UFT 12.5 with Perfecto Mobil combination • Object Oriented programming – class structure, code re-use, abstract thinking/Page object model • Strong sense of self-motivation, organizing, strong analytical skills and attention to details • Hands-on experience in VB/Java scripting/ Junit/TestNG/programing experience • Experience in reporting metrics and status to management • Experience writing complex SQL queries • Experience in Mobile Testing(Perfecto/Appium) • Experience working with multiple software development methodologies and QA Tools • Manual QA concepts like laying out a scenario into design steps (linear thinking) • Experience in an Agile environment/Behavior driven Development testing(Cucumber/Specflow) "}, "additionalInformation": {"title": "Additional Information", "text": " Chandra Kumar 201-549-2655 Chandra at ustechsolutionsinc com "}}</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Scope/Responsibilities/Duties: • 0-2 years general experience, bachelor’ s degree or equivalent combo of education/experience; • Some experience in desired tech area; position functions with high level of supervision; • Assesses security and/or compliance of university systems; responsible for assessing, monitoring and analyzing data, identifying security, risk or compliance issues and/or events • Leveraging job aids for common issues or incidents • Demonstrated ability to work in a team, attention to detail, solid written communications and some technology experience • To perform system based risk assessments. • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "qualifications": {"title": "Qualifications", "text": " • Review risk assessment questionnaires, perform information security control reviews and complete documentation for submission to risk management governance committees for approval or denial. "}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards, Kushal Kumar Talent Acquisition Specialist Tel: 201-932-1539 "}}</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14347,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Shipboard Business Systems Analyst</t>
+          <t>EDI Programmer Analyst &amp; Manager</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -14357,12 +14362,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2015-12-11</t>
+          <t>2016-06-29</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -14377,7 +14382,7 @@
       </c>
       <c r="I203" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87837860-shipboard-business-systems-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93892950-edi-programmer-analyst-manager?oga=true</t>
         </is>
       </c>
       <c r="J203" t="b">
@@ -14390,17 +14395,17 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>c6ecd4c346de62f82786</t>
+          <t>36926768d7d1374bbba5</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Essential Day to Day Responsibilities: • Analyzes business and user needs, documentation of requirements per RCCL standards, and translation into proper system requirement specifications. • Participate in solution option evaluations with IT teams and business partners. • Responsible for initial planning and estimation of low to moderate complexity projects and requests. • Interfaces with PMO on developing a comprehensive project plan and leading business partners in their areas such as training, testing, operational changes/plans, user acceptance testing and deployment to the field (global locations). • Remains engaged throughout the project at critical milestones, also working with business partners on their portions of the project. • Assists in providing product training to internal IT teams. Required skills/competencies: The ideal candidate will have experience working in a large hotel/resort environment along with knowledge of and experience supporting enterprise back office systems. The successful candidate will be expected to gain knowledge of current cruise, hotel/resort, entertainment and technology trends and be able to participate in discussion of their application in the cruise industry and at RCCL. "}, "qualifications": {"title": "Qualifications", "text": " CANDIDATE QUALIFICATIONS • Excellent interpersonal skills, including oral and written communication skills • Relevant experience as a Business Analyst, some directly with business teams • Hospitality Experience, including Front Office, Back Office, and Guest Entertainment Systems support required • Experience with Mobile Hospitality solutions (iOS/Android) • Excellent organizational skills • Ability to adapt and excel in a fast paced, dynamic work environment • Ability to manage changing priorities • Ability to make sound business decisions, putting the good of the team, the project and of RCCL first. • Ability to own and drive issues to resolution, sense of urgency with strong follow-up skills • Experience developing and executing testing strategies &amp; test scripts • Ability to work with and maintain confidential and proprietary information. Candidate may be required to agree to and sign project related Non-disclosure agreements. Preferred Skills: Experience of Fidelio Cruise Property</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: EDI Programmer Analyst &amp; Manager Duration: Permanent/Full Time Location: San Francisco, CA Interview: Phone &amp; F2F(But can do Skype) Locals are highly preferred "}, "qualifications": {"title": "Qualifications", "text": " Proficient in: · BizTalk · EDI application mapping techniques · HIPAA ASC X12 transaction sets for healthcare (834, 837, 277, 835, 997/9, 270/1, 276/7, Proprietary Auths) · HIPAA 5010 · HIPAA security policies and procedures. · .NET &amp; SQL · Systems implementation "}, "additionalInformation": {"title": "Additional Information", "text": " Regards, Chandra Kumar Tel: 201-549-2655 Desk: (201) 524 9600 Ext: 7794 chandra at ustechsolutionsinc dot com "}}</t>
         </is>
       </c>
     </row>
@@ -14412,7 +14417,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst/BIE</t>
+          <t>EFT Processing Analyst</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -14432,7 +14437,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2015-12-09</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -14447,7 +14452,7 @@
       </c>
       <c r="I204" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85837517-sr-data-analyst-bie?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87772674-eft-processing-analyst?oga=true</t>
         </is>
       </c>
       <c r="J204" t="b">
@@ -14460,17 +14465,17 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>598b89494bc90bc7bd81</t>
+          <t>ff66976e897c4a7cacad</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Key Responsibilities: · Track and report on the metrics and trends we rely upon to run our business. · Answer ad hoc questions that help inform our product design decisions. · Use data to identify opportunities and then use spoken and written words to influence stakeholders and tech teams to respond to them · Architect the right data ecosystem to efficiently supply the answers we need · Define product requirements, success metrics, and A/B testing schemes that accelerate our pace of innovation · Audit launched products and recommend iterative steps based on measurable results · Uphold the highest standards of data collection, reporting, and analysis across our team through all phases of software development "}, "qualifications": {"title": "Qualifications", "text": " The successful candidate will demonstrate: · A track record delivering impactful results in a consumer oriented industry · High attention to detail and precision in all forms of communication · Proven ability to influence everyone from executives to teammates · A composed, poised and professional demeanor. · A history of teamwork and willingness to roll up one’s sleeves to get the job done · Strong analytical and quantitative skills (including the ability to effectively use tools such as Excel and SQL on large data sets) and an ability to use hard data and metrics to back up assumptions and develop project business cases. Basic Qualifications · BS or MS or PHD in Applied Mathematics, Statistics, Economics, Computer Science or other quantitative disciplines · Experience working with large data sets · Excellent SQL query skills · Strong problem solving skills, and an ability to apply them in the context of a fast-paced business environment · Good written and oral communication skills to translate complex models and analysis results into layman terms · Capable and motivated to collaboratively work with a diverse and innovative team of engineers, analysts, operations personnel and business management to deliver results. · Familiarity with statistical methodologies Preferred Qualifications · Previous product or program management experience · Thrives in agile environments · Comfortable working in a Unix/Linux environment · Experience with web analytics · Experience in experimental design · Pre</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Title: EFT Processing Analyst Duration: Approx. 3 months Location: Austin, TX Responsibilities: Perform ACH operational functions within required deadlines and NACHA compliance. Process received ACH exception-items and disputes, including DNE s and WSUD s. Originate R10 s, NOC s and other manual return items. Gather verifications for deposit-exceptions for cardholder account management. Reply to garnishments, liens, and levies in a timely, accurate, and compliant manner. Take phone calls and respond to inquiries from customers, banks, government entities, and internal departments. Provide consistent, high-quality customer service that meets or exceeds established standards. Maintain spreadsheets related to credit-adjustment activity, and create regular summaries and reports on departmental activities using Access, Excel, and Word. Recommend improvements that result in more efficient procedures. Understand and adhere to strict compliance and regulatory requirements. Comfortably work within a defined attendance and punctuality policy that is designed to help our customers. "}, "qualifications": {"title": "Qualifications", "text": ""}, "additionalInformation": {"title": "Additional Information", "text": " Thanks &amp; Regards Sam Contact : 201-613-5164 "}}</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14487,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Sr. IT Communication Analyst</t>
+          <t>MDM Data Analyst I</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -14492,7 +14497,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>See posting</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -14502,7 +14507,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2016-12-06</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -14517,7 +14522,7 @@
       </c>
       <c r="I205" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86563413-sr-it-communication-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/103472117-mdm-data-analyst-i?oga=true</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -14530,17 +14535,17 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>618dae4b9e249bc47945</t>
+          <t>3a12d7e1695e93f24087</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Prerequisites: · 10-15 year experience in corporate or internal communications required IT marketing experience preferred Experience providing communications planning and implementation for a matrixed, global IT organization · Experience sourcing images, developing artwork and developing logos · Pharmaceutical industry experience a plus Ability to deal effectively with all levels of an organization, from senior executives to entry-level team members · Ability to build effective personal networks to get things done with a minimum of resources · Excellent written and verbal communication skills are required · Ability to synthesize complex IT concepts and information for a non-IT audience Strong presentation and facilitation skills · Experience planning global, remote communication events such as town halls and managing related equipment · Experience with web design and content management · Experience with SharePoint Advanced proficiency with Word, PowerPoint, Outlook and Excel · Experience in Internet imaging sourcing and concept design · Strong knowledge of communications best practices "}, "qualifications": {"title": "Qualifications", "text": " Summary: This position serves as the internal strategic and tactical communications lead for the Global Information Technology organization. Responsibilities will include, but are not limited to, the following: · Establish, maintain and evolve the communication framework within global IT organization Develop overall strategic communication plan in alignment with global IT strategies, goals and objectives · Manage and produce quarterly, global IT town hall meetings for Chief Information Officer, including logistics, agenda, content, on-site staffing and post-event measurement Manage and produce quarterly, functional town hall meetings for IT Senior Leadership Team (ITSLT) members, including logistics, agenda, content, on-site staffing and post-event measurement via surveys · Draft and review executive presentations for internal Client audiences and external industry audiences · Schedule and communicate executive meet and greet sessions (e.g., Breakfast with the CIO) · Review, edit and communicate annual Global IT goals and objectives in consultation with the Chief Information Officer Ensure strategic alignment</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Job Title: MDM Data Analyst I Location: Lexington, MA, 02421 Duration: 12-+ Months Description: The MDM Data Analyst reports to the MDM/Data Governance Manager and is responsible for the end-to-end master data customer and product maintenance processes within U.S. Commercial Operations. This person is responsible for MDM data quality, processes and business rules. He/she will be responsible for working with the various business area leads to ensure cross-team processes are efficient and master data is consistent, accurate and compliant across applications. % of Time Job Function and Description 35% Data Steward Team Management • Responsible for daily MDM data steward activities • Perform ad hoc customer and product master data requests • Participate in MDM UAT testing 45% Operational Excellence • Responsible for defining MDM Standard Operating Procedures (SOPs) and Work Instructions (WIs) • Responsible for ensuring the accuracy and completeness of customer and product master data • Responsible for understanding the end-to-end processes for maintaining customer master and product data across business areas • Responsible for customer and product data harmonization across multiple sources 20% Cross-Functional Collaboration • Work closely with Commercial Ops Governance team and adhere to implemented principles and process standards • Work with IT to coordinate and define business user impacts of MDM application changes including resolving issues and planning for enhancements and upgrades • Assist in the definition of master data sourcing and services strategies including the evaluation of third party data providers and services under the direction of the MDM/Data Governance Manager Education and Experience Requirements • Bachelor's degree in the field of computer science, information technology, engineering or business administration, Management Information Systems, Finance, Sciences or related area or equivalent experience • Advanced Degree preferred • 1-3 years of work experience, Pharma related preferred • Informatica MDM/IDD experience preferred • One full cycle of an MDM implementation preferred • Has basic knowledge of Pharmaceutical Commercial business environment/operations Key Skills, Abilities, and Competencies • Establishes good working relat</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14557,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Support Analyst</t>
+          <t>Mobile Automation Test Analyst</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -14567,12 +14572,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>{"id": "contract", "label": "Contract"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2016-06-08</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -14587,7 +14592,7 @@
       </c>
       <c r="I206" s="1" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/USTechSolutions2/109625889-support-analyst?oga=true</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/93157465-mobile-automation-test-analyst?oga=true</t>
         </is>
       </c>
       <c r="J206" t="b">
@@ -14600,29 +14605,29 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2a655a025e9258d5b76f</t>
+          <t>80c10598e102ec2e4da0</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi , My name is Raghava from Keshav Consulting Solutions. I have job opening with one of our direct clients. Below is the job description for your reference. Title: Support Analyst Duration: 12 Months Location: 4101 Capital Blvd. Raleigh NC 27604 Job Description: Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. The support consists of documenting and coordinating activities with respect to the installation and configuration of Genetec Security Center and IP cameras, SV32 devices, door aggregators and all system components deployed for FACS project. •Support to the Enterprise Application team, in respect to the installation and configuration of Genetec Security Center and IP cameras SV32 devices, door aggregators and all system components deployed for FACS project.•Assisting the deployment team with troubleshooting installation/configuration issues for the Genetec Security Center and Samsung IP cameras.•Receiving, logging and fully documenting requests for support from help desk, other service delivery staff and/or users; investigate problems and other requests for support from the deployment/project team and determine appropriate actions to be taken.•Monitoring progress of requests for support through resolution and ensure users and other interested parties are kept informed.•Escalate 3rd party software and hardware issues to Application Owner; insuring proper attention is given to the issue depending on severity and impact to project schedule.• Communicating technical information to a variety of internal and external stakeholders both verbally and in writing. Technical writing services and support for the developing software documentation at the enterprise level. Provide services documenting technical configurations for a complex multi-site deployment of a Genetec System for Access Control and Video Management at NCDOT.•Assist in the creation of document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Maintain and update as needed the document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Must have the ability to capture incidents and issues identified by the project with the ability to document resolution(s) for the team leader providing weekly status reports to Management.•Proven experience with supporting</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Position: Mobile Automation Test Analyst Duration: 6 – 12 + Months Location: Anoka, MN Interview: Phone &amp; F2F Mandate "}, "qualifications": {"title": "Qualifications", "text": " • 8+ years of experience in software automation testing, with 3-4+ years of experience in UFT/selenium automation experience • Expert in UFT 12.5 with Perfecto Mobil combination • Object Oriented programming – class structure, code re-use, abstract thinking/Page object model • Strong sense of self-motivation, organizing, strong analytical skills and attention to details • Hands-on experience in VB/Java scripting/ Junit/TestNG/programing experience • Experience in reporting metrics and status to management • Experience writing complex SQL queries • Experience in Mobile Testing(Perfecto/Appium) • Experience working with multiple software development methodologies and QA Tools • Manual QA concepts like laying out a scenario into design steps (linear thinking) • Experience in an Agile environment/Behavior driven Development testing(Cucumber/Specflow) "}, "additionalInformation": {"title": "Additional Information", "text": " Chandra Kumar 201-549-2655 Chandra at ustechsolutionsinc com "}}</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ANALYST L2</t>
+          <t>Shipboard Business Systems Analyst</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -14637,7 +14642,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2015-12-11</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -14647,12 +14657,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I207" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/ANALYST-L2/193243-en_US</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/87837860-shipboard-business-systems-analyst?oga=true</t>
         </is>
       </c>
       <c r="J207" t="b">
@@ -14660,34 +14670,34 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-10-05T09:25:56+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>226c03a4ad5d97c18697</t>
+          <t>c6ecd4c346de62f82786</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>ANALYST L2 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L2 City: Chennai State/Province: Tamil Nadu Posting Start Date: 10/5/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Ext</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Essential Day to Day Responsibilities: • Analyzes business and user needs, documentation of requirements per RCCL standards, and translation into proper system requirement specifications. • Participate in solution option evaluations with IT teams and business partners. • Responsible for initial planning and estimation of low to moderate complexity projects and requests. • Interfaces with PMO on developing a comprehensive project plan and leading business partners in their areas such as training, testing, operational changes/plans, user acceptance testing and deployment to the field (global locations). • Remains engaged throughout the project at critical milestones, also working with business partners on their portions of the project. • Assists in providing product training to internal IT teams. Required skills/competencies: The ideal candidate will have experience working in a large hotel/resort environment along with knowledge of and experience supporting enterprise back office systems. The successful candidate will be expected to gain knowledge of current cruise, hotel/resort, entertainment and technology trends and be able to participate in discussion of their application in the cruise industry and at RCCL. "}, "qualifications": {"title": "Qualifications", "text": " CANDIDATE QUALIFICATIONS • Excellent interpersonal skills, including oral and written communication skills • Relevant experience as a Business Analyst, some directly with business teams • Hospitality Experience, including Front Office, Back Office, and Guest Entertainment Systems support required • Experience with Mobile Hospitality solutions (iOS/Android) • Excellent organizational skills • Ability to adapt and excel in a fast paced, dynamic work environment • Ability to manage changing priorities • Ability to make sound business decisions, putting the good of the team, the project and of RCCL first. • Ability to own and drive issues to resolution, sense of urgency with strong follow-up skills • Experience developing and executing testing strategies &amp; test scripts • Ability to work with and maintain confidential and proprietary information. Candidate may be required to agree to and sign project related Non-disclosure agreements. Preferred Skills: Experience of Fidelio Cruise Property</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Sr. Data Analyst/BIE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -14702,7 +14712,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -14712,12 +14727,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I208" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Agentic-AI-Engineer/199620-en_US</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/85837517-sr-data-analyst-bie?oga=true</t>
         </is>
       </c>
       <c r="J208" t="b">
@@ -14725,34 +14740,34 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-09-23T08:08:19+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>69a88595cd09fa24a854</t>
+          <t>598b89494bc90bc7bd81</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Agentic AI Engineer City: Pune State/Province: Maharashtra Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": "Key Responsibilities: · Track and report on the metrics and trends we rely upon to run our business. · Answer ad hoc questions that help inform our product design decisions. · Use data to identify opportunities and then use spoken and written words to influence stakeholders and tech teams to respond to them · Architect the right data ecosystem to efficiently supply the answers we need · Define product requirements, success metrics, and A/B testing schemes that accelerate our pace of innovation · Audit launched products and recommend iterative steps based on measurable results · Uphold the highest standards of data collection, reporting, and analysis across our team through all phases of software development "}, "qualifications": {"title": "Qualifications", "text": " The successful candidate will demonstrate: · A track record delivering impactful results in a consumer oriented industry · High attention to detail and precision in all forms of communication · Proven ability to influence everyone from executives to teammates · A composed, poised and professional demeanor. · A history of teamwork and willingness to roll up one’s sleeves to get the job done · Strong analytical and quantitative skills (including the ability to effectively use tools such as Excel and SQL on large data sets) and an ability to use hard data and metrics to back up assumptions and develop project business cases. Basic Qualifications · BS or MS or PHD in Applied Mathematics, Statistics, Economics, Computer Science or other quantitative disciplines · Experience working with large data sets · Excellent SQL query skills · Strong problem solving skills, and an ability to apply them in the context of a fast-paced business environment · Good written and oral communication skills to translate complex models and analysis results into layman terms · Capable and motivated to collaboratively work with a diverse and innovative team of engineers, analysts, operations personnel and business management to deliver results. · Familiarity with statistical methodologies Preferred Qualifications · Previous product or program management experience · Thrives in agile environments · Comfortable working in a Unix/Linux environment · Experience with web analytics · Experience in experimental design · Pre</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Sr. IT Communication Analyst</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -14762,12 +14777,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -14777,12 +14797,12 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I209" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/19657-en_US</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/86563413-sr-it-communication-analyst?oga=true</t>
         </is>
       </c>
       <c r="J209" t="b">
@@ -14795,29 +14815,29 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>712e3cf849669eebaeb3</t>
+          <t>618dae4b9e249bc47945</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram, Bengaluru State/Province: Haryana, Karnataka Posting Start Date: 1/8/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Des</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": " US Tech Solutions is a global staff augmentation firm providing a wide-range of talent on-demand and total workforce solutions. To know more about US Tech Solutions, please visit our website www.ustechsolutions.com. We are constantly on the lookout for professionals to fulfill the staffing needs of our clients, sets the correct expectation and thus becomes an accelerator in the mutual growth of the individual and the organization as well. Keeping the same intent in mind, we would like you to consider the job opening with US Tech Solutions that fits your expertise and skillset. "}, "jobDescription": {"title": "Job Description", "text": " Prerequisites: · 10-15 year experience in corporate or internal communications required IT marketing experience preferred Experience providing communications planning and implementation for a matrixed, global IT organization · Experience sourcing images, developing artwork and developing logos · Pharmaceutical industry experience a plus Ability to deal effectively with all levels of an organization, from senior executives to entry-level team members · Ability to build effective personal networks to get things done with a minimum of resources · Excellent written and verbal communication skills are required · Ability to synthesize complex IT concepts and information for a non-IT audience Strong presentation and facilitation skills · Experience planning global, remote communication events such as town halls and managing related equipment · Experience with web design and content management · Experience with SharePoint Advanced proficiency with Word, PowerPoint, Outlook and Excel · Experience in Internet imaging sourcing and concept design · Strong knowledge of communications best practices "}, "qualifications": {"title": "Qualifications", "text": " Summary: This position serves as the internal strategic and tactical communications lead for the Global Information Technology organization. Responsibilities will include, but are not limited to, the following: · Establish, maintain and evolve the communication framework within global IT organization Develop overall strategic communication plan in alignment with global IT strategies, goals and objectives · Manage and produce quarterly, global IT town hall meetings for Chief Information Officer, including logistics, agenda, content, on-site staffing and post-event measurement Manage and produce quarterly, functional town hall meetings for IT Senior Leadership Team (ITSLT) members, including logistics, agenda, content, on-site staffing and post-event measurement via surveys · Draft and review executive presentations for internal Client audiences and external industry audiences · Schedule and communicate executive meet and greet sessions (e.g., Breakfast with the CIO) · Review, edit and communicate annual Global IT goals and objectives in consultation with the Chief Information Officer Ensure strategic alignment</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>US Tech Solutions</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Support Analyst</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -14832,7 +14852,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>See posting</t>
+          <t>{"id": "contract", "label": "Contract"}</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -14842,12 +14867,12 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>HTTP+Playwright</t>
+          <t>SmartRecruiters API</t>
         </is>
       </c>
       <c r="I210" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/19047-en_US</t>
+          <t>https://jobs.smartrecruiters.com/USTechSolutions2/109625889-support-analyst?oga=true</t>
         </is>
       </c>
       <c r="J210" t="b">
@@ -14860,17 +14885,17 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2309aeb0bc27a46040b3</t>
+          <t>2a655a025e9258d5b76f</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 10/24/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Des</t>
+          <t>{"companyDescription": {"title": "Company Description", "text": ""}, "jobDescription": {"title": "Job Description", "text": " Hi , My name is Raghava from Keshav Consulting Solutions. I have job opening with one of our direct clients. Below is the job description for your reference. Title: Support Analyst Duration: 12 Months Location: 4101 Capital Blvd. Raleigh NC 27604 Job Description: Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. Our Client is seeking an Expert Level Specialist Support Analyst for a 12 month engagement to provide second level support with the DOT IT Enterprise Applications Team. The support consists of documenting and coordinating activities with respect to the installation and configuration of Genetec Security Center and IP cameras, SV32 devices, door aggregators and all system components deployed for FACS project. •Support to the Enterprise Application team, in respect to the installation and configuration of Genetec Security Center and IP cameras SV32 devices, door aggregators and all system components deployed for FACS project.•Assisting the deployment team with troubleshooting installation/configuration issues for the Genetec Security Center and Samsung IP cameras.•Receiving, logging and fully documenting requests for support from help desk, other service delivery staff and/or users; investigate problems and other requests for support from the deployment/project team and determine appropriate actions to be taken.•Monitoring progress of requests for support through resolution and ensure users and other interested parties are kept informed.•Escalate 3rd party software and hardware issues to Application Owner; insuring proper attention is given to the issue depending on severity and impact to project schedule.• Communicating technical information to a variety of internal and external stakeholders both verbally and in writing. Technical writing services and support for the developing software documentation at the enterprise level. Provide services documenting technical configurations for a complex multi-site deployment of a Genetec System for Access Control and Video Management at NCDOT.•Assist in the creation of document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Maintain and update as needed the document(s) which details the information architecture, the network ids, the building locations, installation documents, configuration documents and all other project documents required for the Enterprise Applications team.•Must have the ability to capture incidents and issues identified by the project with the ability to document resolution(s) for the team leader providing weekly status reports to Management.•Proven experience with supporting</t>
         </is>
       </c>
     </row>
@@ -14882,7 +14907,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>ANALYST L2</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -14912,7 +14937,7 @@
       </c>
       <c r="I211" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/195409-en_US</t>
+          <t>https://careers.wipro.com/job/ANALYST-L2/193243-en_US</t>
         </is>
       </c>
       <c r="J211" t="b">
@@ -14920,22 +14945,22 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-09-29T08:55:28+00:00</t>
+          <t>2026-10-05T09:25:56+00:00</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2864063fe92279d4c7e0</t>
+          <t>226c03a4ad5d97c18697</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 9/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: ͏ Shift:</t>
+          <t>ANALYST L2 Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: ANALYST L2 City: Chennai State/Province: Tamil Nadu Posting Start Date: 10/5/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Ext</t>
         </is>
       </c>
     </row>
@@ -14947,7 +14972,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14977,7 +15002,7 @@
       </c>
       <c r="I212" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/175124-en_US</t>
+          <t>https://careers.wipro.com/job/Agentic-AI-Engineer/199620-en_US</t>
         </is>
       </c>
       <c r="J212" t="b">
@@ -14985,22 +15010,22 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-09-29T17:19:47+00:00</t>
+          <t>2026-09-23T08:08:19+00:00</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>0acf0fdae972a16bd140</t>
+          <t>69a88595cd09fa24a854</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram State/Province: Haryana Posting Start Date: 9/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Descrip</t>
+          <t>Agentic AI Engineer Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Agentic AI Engineer City: Pune State/Province: Maharashtra Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15067,7 @@
       </c>
       <c r="I213" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/23385-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/19657-en_US</t>
         </is>
       </c>
       <c r="J213" t="b">
@@ -15055,17 +15080,17 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>bb5a134aabb09236d773</t>
+          <t>712e3cf849669eebaeb3</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 1/16/25 Job Description: Job Description Designation: Analyst Band: B1 Job Location: Bangalore ( Work from Office Time: 6:00 PM-3:30 AM JOB DESCRIPTION: • Build customizations using extensions and scripts to meet business needs. • Actively identify opportunities to leverage Coupa functionality to improve efficiency. • Troubleshoot and debug production issues that users may have which could be data, process, Coupa configuration or integration related. • Support the Procure-to-Pay department during the month-end/quarter-end/Year-end close process. • Ensure that change control procedures are implemented and used for all production deployments. • User administration including ass</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram, Bengaluru State/Province: Haryana, Karnataka Posting Start Date: 1/8/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Des</t>
         </is>
       </c>
     </row>
@@ -15107,7 +15132,7 @@
       </c>
       <c r="I214" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Analyst/162758-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/19047-en_US</t>
         </is>
       </c>
       <c r="J214" t="b">
@@ -15115,22 +15140,22 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026-08-03T17:08:04+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>97dfd4270978d9297118</t>
+          <t>2309aeb0bc27a46040b3</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 7/30/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Desc</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 10/24/25 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Des</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15167,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DATA ANALYST</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -15172,7 +15197,7 @@
       </c>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/DATA-ANALYST/197280-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/195409-en_US</t>
         </is>
       </c>
       <c r="J215" t="b">
@@ -15180,22 +15205,22 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026-09-23T14:05:04+00:00</t>
+          <t>2026-09-29T08:55:28+00:00</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>d0914ba92a9b445faf35</t>
+          <t>2864063fe92279d4c7e0</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>DATA ANALYST Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: DATA ANALYST City: Bengaluru State/Province: Karnataka Posting Start Date: 9/23/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 9/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: ͏ Shift:</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15232,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -15237,7 +15262,7 @@
       </c>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Analyst/207025-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/175124-en_US</t>
         </is>
       </c>
       <c r="J216" t="b">
@@ -15245,22 +15270,22 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026-10-05T20:07:45+00:00</t>
+          <t>2026-09-29T17:19:47+00:00</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>1d47307f356167e7d1ee</t>
+          <t>0acf0fdae972a16bd140</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Sunnyvale State/Province: California Posting Start Date: 10/5/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Descriptio</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Gurugram State/Province: Haryana Posting Start Date: 9/29/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: Job Descrip</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15297,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -15302,7 +15327,7 @@
       </c>
       <c r="I217" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Analyst/196228-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/23385-en_US</t>
         </is>
       </c>
       <c r="J217" t="b">
@@ -15310,22 +15335,22 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026-08-29T01:26:31+00:00</t>
+          <t>2026-07-30T00:33:09+00:00</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>f7d25f7312ae32cfbc12</t>
+          <t>bb5a134aabb09236d773</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 10/6/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 1/16/25 Job Description: Job Description Designation: Analyst Band: B1 Job Location: Bangalore ( Work from Office Time: 6:00 PM-3:30 AM JOB DESCRIPTION: • Build customizations using extensions and scripts to meet business needs. • Actively identify opportunities to leverage Coupa functionality to improve efficiency. • Troubleshoot and debug production issues that users may have which could be data, process, Coupa configuration or integration related. • Support the Procure-to-Pay department during the month-end/quarter-end/Year-end close process. • Ensure that change control procedures are implemented and used for all production deployments. • User administration including ass</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15362,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -15367,7 +15392,7 @@
       </c>
       <c r="I218" s="1" t="inlineStr">
         <is>
-          <t>https://careers.wipro.com/job/Data-Analyst/200306-en_US</t>
+          <t>https://careers.wipro.com/job/Analyst/162758-en_US</t>
         </is>
       </c>
       <c r="J218" t="b">
@@ -15375,22 +15400,22 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026-09-14T01:28:49+00:00</t>
+          <t>2026-08-03T17:08:04+00:00</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-10-07T02:48:05+00:00</t>
+          <t>2026-10-07T12:12:02+00:00</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>d884e86067c9f7f10787</t>
+          <t>97dfd4270978d9297118</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>Data Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Data Analyst City: Gurugram State/Province: Haryana Posting Start Date: 9/14/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic portfolio of capabilities in consulting, design, engineering, and operations, we help clients realize their boldest ambitions and build future-ready, sustainable businesses. With over 230,000 employees and business partners across 65 countries, we deliver on the promise of helping our customers, colleagues, and communities thrive in an ever-changing world. For additional information, visit us at www.wipro.com. Job Description: J</t>
+          <t>Analyst Job Details | Wipro Limited We use cookies to offer you the best possible website experience. Your cookie preferences will be stored in your browser’s local storage. This includes cookies necessary for the website's operation. Additionally, you can freely decide and change any time whether you accept cookies or choose to opt out of cookies to improve website's performance, as well as cookies used to display content tailored to your interests. Your experience of the site and the services we are able to offer may be impacted if you do not accept all cookies. Modify Cookie Preferences Accept All Cookies Skip to main content Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Home Life at Wipro Careers Early Careers Experienced Professionals Locations Benelux Brazil Germany and Austria Korea Mexico Nordics Philippines Poland Portugal Romania Southern Europe Switzerland UK and Ireland Join Our Talent Network Language العَرَبِيَّة (السعودية) Deutsch (Deutschland) English (United States) Español (España) Español (México) Français (Canada) Français (France) Italiano (Italia) 日本語 (日本) Polski Português (Brasil) Português (Portugal) Limba Română (România) 简体中文 (中国大陆) Login Search Jobs Job Description Apply now Apply Now Start applying with LinkedIn Start Please wait... Job Title: Analyst City: Bengaluru State/Province: Karnataka Posting Start Date: 7/30/26 Wipro Limited (NYSE: WIT, BSE: 507685, NSE: WIPRO) is a leading technology services and consulting company focused on building innovative solutions that address clients’ most complex digital transformation needs. Leveraging our holistic